--- a/forms/app/pregnancy.xlsx
+++ b/forms/app/pregnancy.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2348" uniqueCount="1355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2355" uniqueCount="1361">
   <si>
     <t>type</t>
   </si>
@@ -2141,7 +2141,7 @@
     <t>anemia_tablets</t>
   </si>
   <si>
-    <t>Were you given tablets to prevent anaemia at the health facility?</t>
+    <t>Were you given tablets to prevent anemia at the health facility?</t>
   </si>
   <si>
     <t xml:space="preserve">Je, ulipata vidonge vinavyozidisha waingi wa damu mwilini ulipokwenda katika kituo cha afya? </t>
@@ -4181,6 +4181,24 @@
   </si>
   <si>
     <t xml:space="preserve">Sijui </t>
+  </si>
+  <si>
+    <t>out_of_stock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Out of stock </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vidonge vilikwisha </t>
+  </si>
+  <si>
+    <t>not_prescribed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Was not prescribed to me </t>
+  </si>
+  <si>
+    <t>Sijaadikiwa vidonge hivyo</t>
   </si>
   <si>
     <t>cottage_hospital</t>
@@ -4584,11 +4602,11 @@
     <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -10695,9 +10713,7 @@
       <c r="I167" s="13" t="s">
         <v>288</v>
       </c>
-      <c r="J167" s="7" t="s">
-        <v>289</v>
-      </c>
+      <c r="J167" s="58"/>
       <c r="K167" s="7" t="s">
         <v>290</v>
       </c>
@@ -10765,7 +10781,7 @@
         <v>477</v>
       </c>
       <c r="E169" s="7"/>
-      <c r="F169" s="58" t="s">
+      <c r="F169" s="59" t="s">
         <v>478</v>
       </c>
       <c r="G169" s="7"/>
@@ -10984,23 +11000,23 @@
       <c r="B175" s="7" t="s">
         <v>490</v>
       </c>
-      <c r="C175" s="59"/>
-      <c r="D175" s="59"/>
-      <c r="E175" s="59"/>
-      <c r="F175" s="59"/>
-      <c r="G175" s="59"/>
-      <c r="H175" s="59"/>
-      <c r="I175" s="59"/>
-      <c r="J175" s="59"/>
-      <c r="K175" s="59"/>
+      <c r="C175" s="58"/>
+      <c r="D175" s="58"/>
+      <c r="E175" s="58"/>
+      <c r="F175" s="58"/>
+      <c r="G175" s="58"/>
+      <c r="H175" s="58"/>
+      <c r="I175" s="58"/>
+      <c r="J175" s="58"/>
+      <c r="K175" s="58"/>
       <c r="L175" s="55" t="s">
         <v>491</v>
       </c>
-      <c r="M175" s="59"/>
-      <c r="N175" s="59"/>
-      <c r="O175" s="59"/>
-      <c r="P175" s="58"/>
-      <c r="Q175" s="59"/>
+      <c r="M175" s="58"/>
+      <c r="N175" s="58"/>
+      <c r="O175" s="58"/>
+      <c r="P175" s="59"/>
+      <c r="Q175" s="58"/>
       <c r="R175" s="9"/>
       <c r="S175" s="9"/>
       <c r="T175" s="9"/>
@@ -11018,27 +11034,27 @@
       <c r="B176" s="7" t="s">
         <v>492</v>
       </c>
-      <c r="C176" s="58" t="s">
+      <c r="C176" s="59" t="s">
         <v>476</v>
       </c>
-      <c r="D176" s="58" t="s">
+      <c r="D176" s="59" t="s">
         <v>477</v>
       </c>
-      <c r="E176" s="58"/>
-      <c r="F176" s="58" t="s">
+      <c r="E176" s="59"/>
+      <c r="F176" s="59" t="s">
         <v>493</v>
       </c>
-      <c r="G176" s="59"/>
-      <c r="H176" s="59"/>
-      <c r="I176" s="59"/>
-      <c r="J176" s="59"/>
-      <c r="K176" s="59"/>
-      <c r="L176" s="59"/>
-      <c r="M176" s="59"/>
-      <c r="N176" s="59"/>
-      <c r="O176" s="59"/>
-      <c r="P176" s="59"/>
-      <c r="Q176" s="59"/>
+      <c r="G176" s="58"/>
+      <c r="H176" s="58"/>
+      <c r="I176" s="58"/>
+      <c r="J176" s="58"/>
+      <c r="K176" s="58"/>
+      <c r="L176" s="58"/>
+      <c r="M176" s="58"/>
+      <c r="N176" s="58"/>
+      <c r="O176" s="58"/>
+      <c r="P176" s="58"/>
+      <c r="Q176" s="58"/>
       <c r="R176" s="9"/>
       <c r="S176" s="9"/>
       <c r="T176" s="9"/>
@@ -11050,33 +11066,33 @@
       <c r="Z176" s="9"/>
     </row>
     <row r="177">
-      <c r="A177" s="58" t="s">
+      <c r="A177" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B177" s="58" t="s">
+      <c r="B177" s="59" t="s">
         <v>494</v>
       </c>
-      <c r="C177" s="58" t="s">
+      <c r="C177" s="59" t="s">
         <v>495</v>
       </c>
-      <c r="D177" s="58" t="s">
+      <c r="D177" s="59" t="s">
         <v>496</v>
       </c>
-      <c r="E177" s="59"/>
-      <c r="F177" s="58" t="s">
+      <c r="E177" s="58"/>
+      <c r="F177" s="59" t="s">
         <v>497</v>
       </c>
-      <c r="G177" s="59"/>
-      <c r="H177" s="59"/>
-      <c r="I177" s="59"/>
-      <c r="J177" s="59"/>
-      <c r="K177" s="59"/>
-      <c r="L177" s="59"/>
-      <c r="M177" s="59"/>
-      <c r="N177" s="59"/>
-      <c r="O177" s="59"/>
-      <c r="P177" s="59"/>
-      <c r="Q177" s="59"/>
+      <c r="G177" s="58"/>
+      <c r="H177" s="58"/>
+      <c r="I177" s="58"/>
+      <c r="J177" s="58"/>
+      <c r="K177" s="58"/>
+      <c r="L177" s="58"/>
+      <c r="M177" s="58"/>
+      <c r="N177" s="58"/>
+      <c r="O177" s="58"/>
+      <c r="P177" s="58"/>
+      <c r="Q177" s="58"/>
       <c r="R177" s="9"/>
       <c r="S177" s="9"/>
       <c r="T177" s="9"/>
@@ -11088,27 +11104,27 @@
       <c r="Z177" s="9"/>
     </row>
     <row r="178">
-      <c r="A178" s="58" t="s">
+      <c r="A178" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="B178" s="58" t="s">
+      <c r="B178" s="59" t="s">
         <v>479</v>
       </c>
-      <c r="C178" s="58"/>
-      <c r="D178" s="59"/>
-      <c r="E178" s="59"/>
-      <c r="F178" s="58"/>
-      <c r="G178" s="59"/>
-      <c r="H178" s="59"/>
-      <c r="I178" s="59"/>
-      <c r="J178" s="59"/>
-      <c r="K178" s="59"/>
-      <c r="L178" s="59"/>
-      <c r="M178" s="59"/>
-      <c r="N178" s="59"/>
-      <c r="O178" s="59"/>
-      <c r="P178" s="59"/>
-      <c r="Q178" s="59"/>
+      <c r="C178" s="59"/>
+      <c r="D178" s="58"/>
+      <c r="E178" s="58"/>
+      <c r="F178" s="59"/>
+      <c r="G178" s="58"/>
+      <c r="H178" s="58"/>
+      <c r="I178" s="58"/>
+      <c r="J178" s="58"/>
+      <c r="K178" s="58"/>
+      <c r="L178" s="58"/>
+      <c r="M178" s="58"/>
+      <c r="N178" s="58"/>
+      <c r="O178" s="58"/>
+      <c r="P178" s="58"/>
+      <c r="Q178" s="58"/>
       <c r="R178" s="9"/>
       <c r="S178" s="9"/>
       <c r="T178" s="9"/>
@@ -11120,27 +11136,27 @@
       <c r="Z178" s="9"/>
     </row>
     <row r="179">
-      <c r="A179" s="58" t="s">
+      <c r="A179" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="B179" s="58" t="s">
+      <c r="B179" s="59" t="s">
         <v>463</v>
       </c>
-      <c r="C179" s="59"/>
-      <c r="D179" s="59"/>
-      <c r="E179" s="59"/>
-      <c r="F179" s="59"/>
-      <c r="G179" s="59"/>
-      <c r="H179" s="59"/>
-      <c r="I179" s="59"/>
-      <c r="J179" s="59"/>
-      <c r="K179" s="59"/>
-      <c r="L179" s="59"/>
-      <c r="M179" s="59"/>
-      <c r="N179" s="59"/>
-      <c r="O179" s="59"/>
-      <c r="P179" s="59"/>
-      <c r="Q179" s="59"/>
+      <c r="C179" s="58"/>
+      <c r="D179" s="58"/>
+      <c r="E179" s="58"/>
+      <c r="F179" s="58"/>
+      <c r="G179" s="58"/>
+      <c r="H179" s="58"/>
+      <c r="I179" s="58"/>
+      <c r="J179" s="58"/>
+      <c r="K179" s="58"/>
+      <c r="L179" s="58"/>
+      <c r="M179" s="58"/>
+      <c r="N179" s="58"/>
+      <c r="O179" s="58"/>
+      <c r="P179" s="58"/>
+      <c r="Q179" s="58"/>
       <c r="R179" s="9"/>
       <c r="S179" s="9"/>
       <c r="T179" s="9"/>
@@ -11152,35 +11168,35 @@
       <c r="Z179" s="9"/>
     </row>
     <row r="180">
-      <c r="A180" s="58" t="s">
+      <c r="A180" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="B180" s="58" t="s">
+      <c r="B180" s="59" t="s">
         <v>498</v>
       </c>
-      <c r="C180" s="58" t="s">
+      <c r="C180" s="59" t="s">
         <v>499</v>
       </c>
-      <c r="D180" s="58" t="s">
+      <c r="D180" s="59" t="s">
         <v>500</v>
       </c>
-      <c r="E180" s="59"/>
-      <c r="F180" s="58" t="s">
+      <c r="E180" s="58"/>
+      <c r="F180" s="59" t="s">
         <v>501</v>
       </c>
-      <c r="G180" s="58" t="s">
+      <c r="G180" s="59" t="s">
         <v>164</v>
       </c>
-      <c r="H180" s="59"/>
-      <c r="I180" s="59"/>
-      <c r="J180" s="59"/>
-      <c r="K180" s="59"/>
-      <c r="L180" s="59"/>
-      <c r="M180" s="59"/>
-      <c r="N180" s="59"/>
-      <c r="O180" s="59"/>
-      <c r="P180" s="59"/>
-      <c r="Q180" s="59"/>
+      <c r="H180" s="58"/>
+      <c r="I180" s="58"/>
+      <c r="J180" s="58"/>
+      <c r="K180" s="58"/>
+      <c r="L180" s="58"/>
+      <c r="M180" s="58"/>
+      <c r="N180" s="58"/>
+      <c r="O180" s="58"/>
+      <c r="P180" s="58"/>
+      <c r="Q180" s="58"/>
       <c r="R180" s="9"/>
       <c r="S180" s="9"/>
       <c r="T180" s="9"/>
@@ -11192,32 +11208,32 @@
       <c r="Z180" s="9"/>
     </row>
     <row r="181">
-      <c r="A181" s="58" t="s">
+      <c r="A181" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B181" s="58" t="s">
+      <c r="B181" s="59" t="s">
         <v>502</v>
       </c>
-      <c r="C181" s="58" t="s">
+      <c r="C181" s="59" t="s">
         <v>503</v>
       </c>
-      <c r="D181" s="58" t="s">
+      <c r="D181" s="59" t="s">
         <v>504</v>
       </c>
-      <c r="E181" s="59"/>
-      <c r="G181" s="59"/>
-      <c r="H181" s="59"/>
-      <c r="I181" s="59"/>
-      <c r="J181" s="59"/>
-      <c r="K181" s="59"/>
-      <c r="L181" s="59"/>
-      <c r="M181" s="59"/>
-      <c r="N181" s="59"/>
-      <c r="O181" s="59"/>
-      <c r="P181" s="59"/>
-      <c r="Q181" s="59"/>
-      <c r="R181" s="58"/>
-      <c r="S181" s="58"/>
+      <c r="E181" s="58"/>
+      <c r="G181" s="58"/>
+      <c r="H181" s="58"/>
+      <c r="I181" s="58"/>
+      <c r="J181" s="58"/>
+      <c r="K181" s="58"/>
+      <c r="L181" s="58"/>
+      <c r="M181" s="58"/>
+      <c r="N181" s="58"/>
+      <c r="O181" s="58"/>
+      <c r="P181" s="58"/>
+      <c r="Q181" s="58"/>
+      <c r="R181" s="59"/>
+      <c r="S181" s="59"/>
       <c r="T181" s="9"/>
       <c r="U181" s="9"/>
       <c r="V181" s="9"/>
@@ -11227,31 +11243,31 @@
       <c r="Z181" s="9"/>
     </row>
     <row r="182">
-      <c r="A182" s="58" t="s">
+      <c r="A182" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B182" s="58" t="s">
+      <c r="B182" s="59" t="s">
         <v>505</v>
       </c>
-      <c r="C182" s="59"/>
-      <c r="D182" s="59"/>
-      <c r="E182" s="59"/>
-      <c r="F182" s="59"/>
-      <c r="G182" s="59"/>
-      <c r="H182" s="59"/>
-      <c r="I182" s="59"/>
-      <c r="J182" s="59"/>
-      <c r="K182" s="59"/>
-      <c r="L182" s="59"/>
-      <c r="M182" s="59"/>
-      <c r="N182" s="59"/>
-      <c r="O182" s="59"/>
-      <c r="P182" s="59"/>
-      <c r="Q182" s="59"/>
-      <c r="R182" s="58" t="s">
+      <c r="C182" s="58"/>
+      <c r="D182" s="58"/>
+      <c r="E182" s="58"/>
+      <c r="F182" s="58"/>
+      <c r="G182" s="58"/>
+      <c r="H182" s="58"/>
+      <c r="I182" s="58"/>
+      <c r="J182" s="58"/>
+      <c r="K182" s="58"/>
+      <c r="L182" s="58"/>
+      <c r="M182" s="58"/>
+      <c r="N182" s="58"/>
+      <c r="O182" s="58"/>
+      <c r="P182" s="58"/>
+      <c r="Q182" s="58"/>
+      <c r="R182" s="59" t="s">
         <v>506</v>
       </c>
-      <c r="S182" s="58" t="s">
+      <c r="S182" s="59" t="s">
         <v>506</v>
       </c>
       <c r="T182" s="9"/>
@@ -11263,31 +11279,30 @@
       <c r="Z182" s="9"/>
     </row>
     <row r="183">
-      <c r="A183" s="58" t="s">
+      <c r="A183" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B183" s="58" t="s">
+      <c r="B183" s="59" t="s">
         <v>507</v>
       </c>
-      <c r="C183" s="59"/>
-      <c r="D183" s="59"/>
-      <c r="E183" s="59"/>
-      <c r="F183" s="59"/>
-      <c r="G183" s="59"/>
-      <c r="H183" s="59"/>
-      <c r="I183" s="59"/>
-      <c r="J183" s="59"/>
-      <c r="K183" s="59"/>
-      <c r="L183" s="59"/>
-      <c r="M183" s="59"/>
-      <c r="N183" s="59"/>
-      <c r="O183" s="59"/>
-      <c r="P183" s="59"/>
-      <c r="Q183" s="59"/>
-      <c r="R183" s="58" t="s">
+      <c r="D183" s="58"/>
+      <c r="E183" s="58"/>
+      <c r="F183" s="58"/>
+      <c r="G183" s="58"/>
+      <c r="H183" s="58"/>
+      <c r="I183" s="58"/>
+      <c r="J183" s="58"/>
+      <c r="K183" s="58"/>
+      <c r="L183" s="58"/>
+      <c r="M183" s="58"/>
+      <c r="N183" s="58"/>
+      <c r="O183" s="58"/>
+      <c r="P183" s="58"/>
+      <c r="Q183" s="58"/>
+      <c r="R183" s="59" t="s">
         <v>508</v>
       </c>
-      <c r="S183" s="58" t="s">
+      <c r="S183" s="59" t="s">
         <v>508</v>
       </c>
       <c r="T183" s="9"/>
@@ -11299,31 +11314,31 @@
       <c r="Z183" s="9"/>
     </row>
     <row r="184">
-      <c r="A184" s="58" t="s">
+      <c r="A184" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B184" s="58" t="s">
+      <c r="B184" s="59" t="s">
         <v>509</v>
       </c>
-      <c r="C184" s="59"/>
-      <c r="D184" s="59"/>
-      <c r="E184" s="59"/>
-      <c r="F184" s="59"/>
-      <c r="G184" s="59"/>
-      <c r="H184" s="59"/>
-      <c r="I184" s="59"/>
-      <c r="J184" s="59"/>
-      <c r="K184" s="59"/>
-      <c r="L184" s="59"/>
-      <c r="M184" s="59"/>
-      <c r="N184" s="59"/>
-      <c r="O184" s="59"/>
-      <c r="P184" s="59"/>
-      <c r="Q184" s="59"/>
-      <c r="R184" s="58" t="s">
+      <c r="C184" s="58"/>
+      <c r="D184" s="58"/>
+      <c r="E184" s="58"/>
+      <c r="F184" s="58"/>
+      <c r="G184" s="58"/>
+      <c r="H184" s="58"/>
+      <c r="I184" s="58"/>
+      <c r="J184" s="58"/>
+      <c r="K184" s="58"/>
+      <c r="L184" s="58"/>
+      <c r="M184" s="58"/>
+      <c r="N184" s="58"/>
+      <c r="O184" s="58"/>
+      <c r="P184" s="58"/>
+      <c r="Q184" s="58"/>
+      <c r="R184" s="59" t="s">
         <v>510</v>
       </c>
-      <c r="S184" s="58" t="s">
+      <c r="S184" s="59" t="s">
         <v>510</v>
       </c>
       <c r="T184" s="9"/>
@@ -11335,31 +11350,31 @@
       <c r="Z184" s="9"/>
     </row>
     <row r="185">
-      <c r="A185" s="58" t="s">
+      <c r="A185" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B185" s="58" t="s">
+      <c r="B185" s="59" t="s">
         <v>511</v>
       </c>
-      <c r="C185" s="59"/>
-      <c r="D185" s="59"/>
-      <c r="E185" s="59"/>
-      <c r="F185" s="59"/>
-      <c r="G185" s="59"/>
-      <c r="H185" s="59"/>
-      <c r="I185" s="59"/>
-      <c r="J185" s="59"/>
-      <c r="K185" s="59"/>
-      <c r="L185" s="59"/>
-      <c r="M185" s="59"/>
-      <c r="N185" s="59"/>
-      <c r="O185" s="59"/>
-      <c r="P185" s="59"/>
-      <c r="Q185" s="59"/>
-      <c r="R185" s="58" t="s">
+      <c r="C185" s="58"/>
+      <c r="D185" s="58"/>
+      <c r="E185" s="58"/>
+      <c r="F185" s="58"/>
+      <c r="G185" s="58"/>
+      <c r="H185" s="58"/>
+      <c r="I185" s="58"/>
+      <c r="J185" s="58"/>
+      <c r="K185" s="58"/>
+      <c r="L185" s="58"/>
+      <c r="M185" s="58"/>
+      <c r="N185" s="58"/>
+      <c r="O185" s="58"/>
+      <c r="P185" s="58"/>
+      <c r="Q185" s="58"/>
+      <c r="R185" s="59" t="s">
         <v>512</v>
       </c>
-      <c r="S185" s="58" t="s">
+      <c r="S185" s="59" t="s">
         <v>512</v>
       </c>
       <c r="T185" s="9"/>
@@ -11371,31 +11386,31 @@
       <c r="Z185" s="9"/>
     </row>
     <row r="186">
-      <c r="A186" s="58" t="s">
+      <c r="A186" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B186" s="58" t="s">
+      <c r="B186" s="59" t="s">
         <v>513</v>
       </c>
-      <c r="C186" s="59"/>
-      <c r="D186" s="59"/>
-      <c r="E186" s="59"/>
-      <c r="F186" s="59"/>
-      <c r="G186" s="59"/>
-      <c r="H186" s="59"/>
-      <c r="I186" s="59"/>
-      <c r="J186" s="59"/>
-      <c r="K186" s="59"/>
-      <c r="L186" s="59"/>
-      <c r="M186" s="59"/>
-      <c r="N186" s="59"/>
-      <c r="O186" s="59"/>
-      <c r="P186" s="59"/>
-      <c r="Q186" s="59"/>
-      <c r="R186" s="58" t="s">
+      <c r="C186" s="58"/>
+      <c r="D186" s="58"/>
+      <c r="E186" s="58"/>
+      <c r="F186" s="58"/>
+      <c r="G186" s="58"/>
+      <c r="H186" s="58"/>
+      <c r="I186" s="58"/>
+      <c r="J186" s="58"/>
+      <c r="K186" s="58"/>
+      <c r="L186" s="58"/>
+      <c r="M186" s="58"/>
+      <c r="N186" s="58"/>
+      <c r="O186" s="58"/>
+      <c r="P186" s="58"/>
+      <c r="Q186" s="58"/>
+      <c r="R186" s="59" t="s">
         <v>514</v>
       </c>
-      <c r="S186" s="58" t="s">
+      <c r="S186" s="59" t="s">
         <v>514</v>
       </c>
       <c r="T186" s="9"/>
@@ -11407,31 +11422,31 @@
       <c r="Z186" s="9"/>
     </row>
     <row r="187">
-      <c r="A187" s="58" t="s">
+      <c r="A187" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B187" s="58" t="s">
+      <c r="B187" s="59" t="s">
         <v>515</v>
       </c>
-      <c r="C187" s="59"/>
-      <c r="D187" s="59"/>
-      <c r="E187" s="59"/>
-      <c r="F187" s="59"/>
-      <c r="G187" s="59"/>
-      <c r="H187" s="59"/>
-      <c r="I187" s="59"/>
-      <c r="J187" s="59"/>
-      <c r="K187" s="59"/>
-      <c r="L187" s="59"/>
-      <c r="M187" s="59"/>
-      <c r="N187" s="59"/>
-      <c r="O187" s="59"/>
-      <c r="P187" s="59"/>
-      <c r="Q187" s="59"/>
-      <c r="R187" s="58" t="s">
+      <c r="C187" s="58"/>
+      <c r="D187" s="58"/>
+      <c r="E187" s="58"/>
+      <c r="F187" s="58"/>
+      <c r="G187" s="58"/>
+      <c r="H187" s="58"/>
+      <c r="I187" s="58"/>
+      <c r="J187" s="58"/>
+      <c r="K187" s="58"/>
+      <c r="L187" s="58"/>
+      <c r="M187" s="58"/>
+      <c r="N187" s="58"/>
+      <c r="O187" s="58"/>
+      <c r="P187" s="58"/>
+      <c r="Q187" s="58"/>
+      <c r="R187" s="59" t="s">
         <v>516</v>
       </c>
-      <c r="S187" s="58" t="s">
+      <c r="S187" s="59" t="s">
         <v>516</v>
       </c>
       <c r="T187" s="9"/>
@@ -11443,27 +11458,27 @@
       <c r="Z187" s="9"/>
     </row>
     <row r="188">
-      <c r="A188" s="58" t="s">
+      <c r="A188" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="B188" s="58" t="s">
+      <c r="B188" s="59" t="s">
         <v>498</v>
       </c>
-      <c r="C188" s="59"/>
-      <c r="D188" s="59"/>
-      <c r="E188" s="59"/>
-      <c r="F188" s="59"/>
-      <c r="G188" s="59"/>
-      <c r="H188" s="59"/>
-      <c r="I188" s="59"/>
-      <c r="J188" s="59"/>
-      <c r="K188" s="59"/>
-      <c r="L188" s="59"/>
-      <c r="M188" s="59"/>
-      <c r="N188" s="59"/>
-      <c r="O188" s="59"/>
-      <c r="P188" s="59"/>
-      <c r="Q188" s="59"/>
+      <c r="C188" s="58"/>
+      <c r="D188" s="58"/>
+      <c r="E188" s="58"/>
+      <c r="F188" s="58"/>
+      <c r="G188" s="58"/>
+      <c r="H188" s="58"/>
+      <c r="I188" s="58"/>
+      <c r="J188" s="58"/>
+      <c r="K188" s="58"/>
+      <c r="L188" s="58"/>
+      <c r="M188" s="58"/>
+      <c r="N188" s="58"/>
+      <c r="O188" s="58"/>
+      <c r="P188" s="58"/>
+      <c r="Q188" s="58"/>
       <c r="R188" s="9"/>
       <c r="S188" s="9"/>
       <c r="T188" s="9"/>
@@ -11475,35 +11490,35 @@
       <c r="Z188" s="9"/>
     </row>
     <row r="189">
-      <c r="A189" s="58" t="s">
+      <c r="A189" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="B189" s="58" t="s">
+      <c r="B189" s="59" t="s">
         <v>517</v>
       </c>
-      <c r="C189" s="58" t="s">
+      <c r="C189" s="59" t="s">
         <v>518</v>
       </c>
-      <c r="D189" s="58" t="s">
+      <c r="D189" s="59" t="s">
         <v>519</v>
       </c>
-      <c r="E189" s="58"/>
+      <c r="E189" s="59"/>
       <c r="F189" s="35" t="s">
         <v>520</v>
       </c>
-      <c r="G189" s="58" t="s">
+      <c r="G189" s="59" t="s">
         <v>117</v>
       </c>
-      <c r="H189" s="59"/>
-      <c r="I189" s="59"/>
-      <c r="J189" s="59"/>
-      <c r="K189" s="59"/>
-      <c r="L189" s="59"/>
-      <c r="M189" s="59"/>
-      <c r="N189" s="59"/>
-      <c r="O189" s="59"/>
-      <c r="P189" s="59"/>
-      <c r="Q189" s="59"/>
+      <c r="H189" s="58"/>
+      <c r="I189" s="58"/>
+      <c r="J189" s="58"/>
+      <c r="K189" s="58"/>
+      <c r="L189" s="58"/>
+      <c r="M189" s="58"/>
+      <c r="N189" s="58"/>
+      <c r="O189" s="58"/>
+      <c r="P189" s="58"/>
+      <c r="Q189" s="58"/>
       <c r="R189" s="9"/>
       <c r="S189" s="9"/>
       <c r="T189" s="9"/>
@@ -11515,33 +11530,33 @@
       <c r="Z189" s="9"/>
     </row>
     <row r="190">
-      <c r="A190" s="58" t="s">
+      <c r="A190" s="59" t="s">
         <v>135</v>
       </c>
-      <c r="B190" s="58" t="s">
+      <c r="B190" s="59" t="s">
         <v>521</v>
       </c>
-      <c r="C190" s="58" t="s">
+      <c r="C190" s="59" t="s">
         <v>522</v>
       </c>
-      <c r="D190" s="58" t="s">
+      <c r="D190" s="59" t="s">
         <v>523</v>
       </c>
-      <c r="E190" s="58" t="s">
+      <c r="E190" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="F190" s="59"/>
-      <c r="G190" s="59"/>
-      <c r="H190" s="59"/>
-      <c r="I190" s="59"/>
-      <c r="J190" s="59"/>
-      <c r="K190" s="59"/>
-      <c r="L190" s="59"/>
-      <c r="M190" s="59"/>
-      <c r="N190" s="59"/>
-      <c r="O190" s="59"/>
-      <c r="P190" s="59"/>
-      <c r="Q190" s="59"/>
+      <c r="F190" s="58"/>
+      <c r="G190" s="58"/>
+      <c r="H190" s="58"/>
+      <c r="I190" s="58"/>
+      <c r="J190" s="58"/>
+      <c r="K190" s="58"/>
+      <c r="L190" s="58"/>
+      <c r="M190" s="58"/>
+      <c r="N190" s="58"/>
+      <c r="O190" s="58"/>
+      <c r="P190" s="58"/>
+      <c r="Q190" s="58"/>
       <c r="R190" s="9"/>
       <c r="S190" s="9"/>
       <c r="T190" s="9"/>
@@ -11553,10 +11568,10 @@
       <c r="Z190" s="9"/>
     </row>
     <row r="191">
-      <c r="A191" s="58" t="s">
+      <c r="A191" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B191" s="58" t="s">
+      <c r="B191" s="59" t="s">
         <v>524</v>
       </c>
       <c r="C191" s="52" t="s">
@@ -11566,20 +11581,20 @@
         <v>526</v>
       </c>
       <c r="E191" s="52"/>
-      <c r="F191" s="58" t="s">
+      <c r="F191" s="59" t="s">
         <v>527</v>
       </c>
-      <c r="G191" s="59"/>
-      <c r="H191" s="59"/>
-      <c r="I191" s="59"/>
-      <c r="J191" s="59"/>
-      <c r="K191" s="59"/>
-      <c r="L191" s="59"/>
-      <c r="M191" s="59"/>
-      <c r="N191" s="59"/>
-      <c r="O191" s="59"/>
-      <c r="P191" s="59"/>
-      <c r="Q191" s="59"/>
+      <c r="G191" s="58"/>
+      <c r="H191" s="58"/>
+      <c r="I191" s="58"/>
+      <c r="J191" s="58"/>
+      <c r="K191" s="58"/>
+      <c r="L191" s="58"/>
+      <c r="M191" s="58"/>
+      <c r="N191" s="58"/>
+      <c r="O191" s="58"/>
+      <c r="P191" s="58"/>
+      <c r="Q191" s="58"/>
       <c r="R191" s="9"/>
       <c r="S191" s="9"/>
       <c r="T191" s="9"/>
@@ -11591,35 +11606,35 @@
       <c r="Z191" s="9"/>
     </row>
     <row r="192">
-      <c r="A192" s="58" t="s">
+      <c r="A192" s="59" t="s">
         <v>135</v>
       </c>
-      <c r="B192" s="58" t="s">
+      <c r="B192" s="59" t="s">
         <v>528</v>
       </c>
-      <c r="C192" s="58" t="s">
+      <c r="C192" s="59" t="s">
         <v>529</v>
       </c>
-      <c r="D192" s="58" t="s">
+      <c r="D192" s="59" t="s">
         <v>530</v>
       </c>
-      <c r="E192" s="58" t="s">
+      <c r="E192" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="F192" s="58" t="s">
+      <c r="F192" s="59" t="s">
         <v>531</v>
       </c>
-      <c r="G192" s="59"/>
-      <c r="H192" s="59"/>
-      <c r="I192" s="59"/>
-      <c r="J192" s="59"/>
-      <c r="K192" s="59"/>
-      <c r="L192" s="59"/>
-      <c r="M192" s="59"/>
-      <c r="N192" s="59"/>
-      <c r="O192" s="59"/>
-      <c r="P192" s="59"/>
-      <c r="Q192" s="59"/>
+      <c r="G192" s="58"/>
+      <c r="H192" s="58"/>
+      <c r="I192" s="58"/>
+      <c r="J192" s="58"/>
+      <c r="K192" s="58"/>
+      <c r="L192" s="58"/>
+      <c r="M192" s="58"/>
+      <c r="N192" s="58"/>
+      <c r="O192" s="58"/>
+      <c r="P192" s="58"/>
+      <c r="Q192" s="58"/>
       <c r="R192" s="9"/>
       <c r="S192" s="9"/>
       <c r="T192" s="9"/>
@@ -11631,35 +11646,35 @@
       <c r="Z192" s="9"/>
     </row>
     <row r="193">
-      <c r="A193" s="58" t="s">
+      <c r="A193" s="59" t="s">
         <v>532</v>
       </c>
-      <c r="B193" s="58" t="s">
+      <c r="B193" s="59" t="s">
         <v>533</v>
       </c>
-      <c r="C193" s="58" t="s">
+      <c r="C193" s="59" t="s">
         <v>534</v>
       </c>
-      <c r="D193" s="58" t="s">
+      <c r="D193" s="59" t="s">
         <v>535</v>
       </c>
-      <c r="E193" s="58" t="s">
+      <c r="E193" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="F193" s="58" t="s">
+      <c r="F193" s="59" t="s">
         <v>536</v>
       </c>
-      <c r="G193" s="59"/>
-      <c r="H193" s="59"/>
-      <c r="I193" s="59"/>
-      <c r="J193" s="59"/>
-      <c r="K193" s="59"/>
-      <c r="L193" s="59"/>
-      <c r="M193" s="59"/>
-      <c r="N193" s="59"/>
-      <c r="O193" s="59"/>
-      <c r="P193" s="59"/>
-      <c r="Q193" s="59"/>
+      <c r="G193" s="58"/>
+      <c r="H193" s="58"/>
+      <c r="I193" s="58"/>
+      <c r="J193" s="58"/>
+      <c r="K193" s="58"/>
+      <c r="L193" s="58"/>
+      <c r="M193" s="58"/>
+      <c r="N193" s="58"/>
+      <c r="O193" s="58"/>
+      <c r="P193" s="58"/>
+      <c r="Q193" s="58"/>
       <c r="R193" s="9"/>
       <c r="S193" s="9"/>
       <c r="T193" s="9"/>
@@ -11671,10 +11686,10 @@
       <c r="Z193" s="9"/>
     </row>
     <row r="194">
-      <c r="A194" s="58" t="s">
+      <c r="A194" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B194" s="58" t="s">
+      <c r="B194" s="59" t="s">
         <v>537</v>
       </c>
       <c r="C194" s="7" t="s">
@@ -11684,20 +11699,20 @@
         <v>539</v>
       </c>
       <c r="E194" s="7"/>
-      <c r="F194" s="58" t="s">
+      <c r="F194" s="59" t="s">
         <v>540</v>
       </c>
-      <c r="G194" s="59"/>
-      <c r="H194" s="59"/>
-      <c r="I194" s="59"/>
-      <c r="J194" s="59"/>
-      <c r="K194" s="59"/>
-      <c r="L194" s="59"/>
-      <c r="M194" s="59"/>
-      <c r="N194" s="59"/>
-      <c r="O194" s="59"/>
-      <c r="P194" s="59"/>
-      <c r="Q194" s="59"/>
+      <c r="G194" s="58"/>
+      <c r="H194" s="58"/>
+      <c r="I194" s="58"/>
+      <c r="J194" s="58"/>
+      <c r="K194" s="58"/>
+      <c r="L194" s="58"/>
+      <c r="M194" s="58"/>
+      <c r="N194" s="58"/>
+      <c r="O194" s="58"/>
+      <c r="P194" s="58"/>
+      <c r="Q194" s="58"/>
       <c r="R194" s="9"/>
       <c r="S194" s="9"/>
       <c r="T194" s="9"/>
@@ -11709,35 +11724,35 @@
       <c r="Z194" s="9"/>
     </row>
     <row r="195">
-      <c r="A195" s="58" t="s">
+      <c r="A195" s="59" t="s">
         <v>135</v>
       </c>
-      <c r="B195" s="58" t="s">
+      <c r="B195" s="59" t="s">
         <v>541</v>
       </c>
-      <c r="C195" s="58" t="s">
+      <c r="C195" s="59" t="s">
         <v>542</v>
       </c>
-      <c r="D195" s="58" t="s">
+      <c r="D195" s="59" t="s">
         <v>543</v>
       </c>
-      <c r="E195" s="58" t="s">
+      <c r="E195" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="F195" s="58" t="s">
+      <c r="F195" s="59" t="s">
         <v>544</v>
       </c>
-      <c r="G195" s="59"/>
-      <c r="H195" s="59"/>
-      <c r="I195" s="59"/>
-      <c r="J195" s="59"/>
-      <c r="K195" s="59"/>
-      <c r="L195" s="59"/>
-      <c r="M195" s="59"/>
-      <c r="N195" s="59"/>
-      <c r="O195" s="59"/>
-      <c r="P195" s="59"/>
-      <c r="Q195" s="59"/>
+      <c r="G195" s="58"/>
+      <c r="H195" s="58"/>
+      <c r="I195" s="58"/>
+      <c r="J195" s="58"/>
+      <c r="K195" s="58"/>
+      <c r="L195" s="58"/>
+      <c r="M195" s="58"/>
+      <c r="N195" s="58"/>
+      <c r="O195" s="58"/>
+      <c r="P195" s="58"/>
+      <c r="Q195" s="58"/>
       <c r="R195" s="9"/>
       <c r="S195" s="9"/>
       <c r="T195" s="9"/>
@@ -11749,10 +11764,10 @@
       <c r="Z195" s="9"/>
     </row>
     <row r="196">
-      <c r="A196" s="58" t="s">
+      <c r="A196" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B196" s="58" t="s">
+      <c r="B196" s="59" t="s">
         <v>545</v>
       </c>
       <c r="C196" s="52" t="s">
@@ -11762,20 +11777,20 @@
         <v>547</v>
       </c>
       <c r="E196" s="52"/>
-      <c r="F196" s="58" t="s">
+      <c r="F196" s="59" t="s">
         <v>548</v>
       </c>
-      <c r="G196" s="59"/>
-      <c r="H196" s="59"/>
-      <c r="I196" s="59"/>
-      <c r="J196" s="59"/>
-      <c r="K196" s="59"/>
-      <c r="L196" s="59"/>
-      <c r="M196" s="59"/>
-      <c r="N196" s="59"/>
-      <c r="O196" s="59"/>
-      <c r="P196" s="59"/>
-      <c r="Q196" s="59"/>
+      <c r="G196" s="58"/>
+      <c r="H196" s="58"/>
+      <c r="I196" s="58"/>
+      <c r="J196" s="58"/>
+      <c r="K196" s="58"/>
+      <c r="L196" s="58"/>
+      <c r="M196" s="58"/>
+      <c r="N196" s="58"/>
+      <c r="O196" s="58"/>
+      <c r="P196" s="58"/>
+      <c r="Q196" s="58"/>
       <c r="R196" s="9"/>
       <c r="S196" s="9"/>
       <c r="T196" s="9"/>
@@ -11787,10 +11802,10 @@
       <c r="Z196" s="9"/>
     </row>
     <row r="197">
-      <c r="A197" s="58" t="s">
+      <c r="A197" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B197" s="58" t="s">
+      <c r="B197" s="59" t="s">
         <v>549</v>
       </c>
       <c r="C197" s="52" t="s">
@@ -11800,20 +11815,20 @@
         <v>551</v>
       </c>
       <c r="E197" s="52"/>
-      <c r="F197" s="58" t="s">
+      <c r="F197" s="59" t="s">
         <v>552</v>
       </c>
-      <c r="G197" s="59"/>
-      <c r="H197" s="59"/>
-      <c r="I197" s="59"/>
-      <c r="J197" s="59"/>
-      <c r="K197" s="59"/>
-      <c r="L197" s="59"/>
-      <c r="M197" s="59"/>
-      <c r="N197" s="59"/>
-      <c r="O197" s="59"/>
-      <c r="P197" s="59"/>
-      <c r="Q197" s="59"/>
+      <c r="G197" s="58"/>
+      <c r="H197" s="58"/>
+      <c r="I197" s="58"/>
+      <c r="J197" s="58"/>
+      <c r="K197" s="58"/>
+      <c r="L197" s="58"/>
+      <c r="M197" s="58"/>
+      <c r="N197" s="58"/>
+      <c r="O197" s="58"/>
+      <c r="P197" s="58"/>
+      <c r="Q197" s="58"/>
       <c r="R197" s="9"/>
       <c r="S197" s="9"/>
       <c r="T197" s="9"/>
@@ -11825,10 +11840,10 @@
       <c r="Z197" s="9"/>
     </row>
     <row r="198">
-      <c r="A198" s="58" t="s">
+      <c r="A198" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B198" s="58" t="s">
+      <c r="B198" s="59" t="s">
         <v>553</v>
       </c>
       <c r="C198" s="7" t="s">
@@ -11838,20 +11853,20 @@
         <v>555</v>
       </c>
       <c r="E198" s="7"/>
-      <c r="F198" s="58" t="s">
+      <c r="F198" s="59" t="s">
         <v>544</v>
       </c>
-      <c r="G198" s="59"/>
-      <c r="H198" s="59"/>
-      <c r="I198" s="59"/>
-      <c r="J198" s="59"/>
-      <c r="K198" s="59"/>
-      <c r="L198" s="59"/>
-      <c r="M198" s="59"/>
-      <c r="N198" s="59"/>
-      <c r="O198" s="59"/>
-      <c r="P198" s="59"/>
-      <c r="Q198" s="59"/>
+      <c r="G198" s="58"/>
+      <c r="H198" s="58"/>
+      <c r="I198" s="58"/>
+      <c r="J198" s="58"/>
+      <c r="K198" s="58"/>
+      <c r="L198" s="58"/>
+      <c r="M198" s="58"/>
+      <c r="N198" s="58"/>
+      <c r="O198" s="58"/>
+      <c r="P198" s="58"/>
+      <c r="Q198" s="58"/>
       <c r="R198" s="9"/>
       <c r="S198" s="9"/>
       <c r="T198" s="9"/>
@@ -11863,10 +11878,10 @@
       <c r="Z198" s="9"/>
     </row>
     <row r="199">
-      <c r="A199" s="58" t="s">
+      <c r="A199" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B199" s="58" t="s">
+      <c r="B199" s="59" t="s">
         <v>556</v>
       </c>
       <c r="C199" s="7" t="s">
@@ -11876,20 +11891,20 @@
         <v>558</v>
       </c>
       <c r="E199" s="7"/>
-      <c r="F199" s="58" t="s">
+      <c r="F199" s="59" t="s">
         <v>559</v>
       </c>
-      <c r="G199" s="59"/>
-      <c r="H199" s="59"/>
-      <c r="I199" s="59"/>
-      <c r="J199" s="59"/>
-      <c r="K199" s="59"/>
-      <c r="L199" s="59"/>
-      <c r="M199" s="59"/>
-      <c r="N199" s="59"/>
-      <c r="O199" s="59"/>
-      <c r="P199" s="59"/>
-      <c r="Q199" s="59"/>
+      <c r="G199" s="58"/>
+      <c r="H199" s="58"/>
+      <c r="I199" s="58"/>
+      <c r="J199" s="58"/>
+      <c r="K199" s="58"/>
+      <c r="L199" s="58"/>
+      <c r="M199" s="58"/>
+      <c r="N199" s="58"/>
+      <c r="O199" s="58"/>
+      <c r="P199" s="58"/>
+      <c r="Q199" s="58"/>
       <c r="R199" s="9"/>
       <c r="S199" s="9"/>
       <c r="T199" s="9"/>
@@ -11901,27 +11916,27 @@
       <c r="Z199" s="9"/>
     </row>
     <row r="200">
-      <c r="A200" s="58" t="s">
+      <c r="A200" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="B200" s="58" t="s">
+      <c r="B200" s="59" t="s">
         <v>517</v>
       </c>
-      <c r="C200" s="59"/>
-      <c r="D200" s="59"/>
-      <c r="E200" s="59"/>
-      <c r="F200" s="59"/>
-      <c r="G200" s="59"/>
-      <c r="H200" s="59"/>
-      <c r="I200" s="59"/>
-      <c r="J200" s="59"/>
-      <c r="K200" s="59"/>
-      <c r="L200" s="59"/>
-      <c r="M200" s="59"/>
-      <c r="N200" s="59"/>
-      <c r="O200" s="59"/>
-      <c r="P200" s="59"/>
-      <c r="Q200" s="59"/>
+      <c r="C200" s="58"/>
+      <c r="D200" s="58"/>
+      <c r="E200" s="58"/>
+      <c r="F200" s="58"/>
+      <c r="G200" s="58"/>
+      <c r="H200" s="58"/>
+      <c r="I200" s="58"/>
+      <c r="J200" s="58"/>
+      <c r="K200" s="58"/>
+      <c r="L200" s="58"/>
+      <c r="M200" s="58"/>
+      <c r="N200" s="58"/>
+      <c r="O200" s="58"/>
+      <c r="P200" s="58"/>
+      <c r="Q200" s="58"/>
       <c r="R200" s="9"/>
       <c r="S200" s="9"/>
       <c r="T200" s="9"/>
@@ -11933,35 +11948,35 @@
       <c r="Z200" s="9"/>
     </row>
     <row r="201">
-      <c r="A201" s="58" t="s">
+      <c r="A201" s="59" t="s">
         <v>105</v>
       </c>
-      <c r="B201" s="58" t="s">
+      <c r="B201" s="59" t="s">
         <v>560</v>
       </c>
-      <c r="C201" s="58" t="s">
+      <c r="C201" s="59" t="s">
         <v>561</v>
       </c>
-      <c r="D201" s="58" t="s">
+      <c r="D201" s="59" t="s">
         <v>562</v>
       </c>
-      <c r="E201" s="58"/>
+      <c r="E201" s="59"/>
       <c r="F201" s="35" t="b">
         <v>0</v>
       </c>
-      <c r="G201" s="58" t="s">
+      <c r="G201" s="59" t="s">
         <v>117</v>
       </c>
-      <c r="H201" s="59"/>
-      <c r="I201" s="59"/>
-      <c r="J201" s="59"/>
-      <c r="K201" s="59"/>
-      <c r="L201" s="59"/>
-      <c r="M201" s="59"/>
-      <c r="N201" s="59"/>
-      <c r="O201" s="59"/>
-      <c r="P201" s="59"/>
-      <c r="Q201" s="59"/>
+      <c r="H201" s="58"/>
+      <c r="I201" s="58"/>
+      <c r="J201" s="58"/>
+      <c r="K201" s="58"/>
+      <c r="L201" s="58"/>
+      <c r="M201" s="58"/>
+      <c r="N201" s="58"/>
+      <c r="O201" s="58"/>
+      <c r="P201" s="58"/>
+      <c r="Q201" s="58"/>
       <c r="R201" s="9"/>
       <c r="S201" s="9"/>
       <c r="T201" s="9"/>
@@ -11973,37 +11988,37 @@
       <c r="Z201" s="9"/>
     </row>
     <row r="202">
-      <c r="A202" s="58" t="s">
+      <c r="A202" s="59" t="s">
         <v>563</v>
       </c>
-      <c r="B202" s="58" t="s">
+      <c r="B202" s="59" t="s">
         <v>564</v>
       </c>
-      <c r="C202" s="58" t="s">
+      <c r="C202" s="59" t="s">
         <v>565</v>
       </c>
-      <c r="D202" s="58" t="s">
+      <c r="D202" s="59" t="s">
         <v>566</v>
       </c>
-      <c r="E202" s="58" t="s">
+      <c r="E202" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="F202" s="59"/>
-      <c r="G202" s="58"/>
-      <c r="H202" s="59"/>
+      <c r="F202" s="58"/>
+      <c r="G202" s="59"/>
+      <c r="H202" s="58"/>
       <c r="I202" s="10" t="s">
         <v>567</v>
       </c>
-      <c r="J202" s="58" t="s">
+      <c r="J202" s="59" t="s">
         <v>568</v>
       </c>
-      <c r="K202" s="59"/>
-      <c r="L202" s="59"/>
-      <c r="M202" s="59"/>
-      <c r="N202" s="59"/>
-      <c r="O202" s="59"/>
-      <c r="P202" s="59"/>
-      <c r="Q202" s="59"/>
+      <c r="K202" s="58"/>
+      <c r="L202" s="58"/>
+      <c r="M202" s="58"/>
+      <c r="N202" s="58"/>
+      <c r="O202" s="58"/>
+      <c r="P202" s="58"/>
+      <c r="Q202" s="58"/>
       <c r="R202" s="9"/>
       <c r="S202" s="9"/>
       <c r="T202" s="9"/>
@@ -12015,10 +12030,10 @@
       <c r="Z202" s="9"/>
     </row>
     <row r="203">
-      <c r="A203" s="58" t="s">
+      <c r="A203" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B203" s="58" t="s">
+      <c r="B203" s="59" t="s">
         <v>569</v>
       </c>
       <c r="C203" s="52" t="s">
@@ -12028,20 +12043,20 @@
         <v>571</v>
       </c>
       <c r="E203" s="52"/>
-      <c r="F203" s="58" t="s">
+      <c r="F203" s="59" t="s">
         <v>572</v>
       </c>
-      <c r="G203" s="58"/>
-      <c r="H203" s="59"/>
-      <c r="I203" s="59"/>
-      <c r="J203" s="59"/>
-      <c r="K203" s="59"/>
-      <c r="L203" s="59"/>
-      <c r="M203" s="59"/>
-      <c r="N203" s="59"/>
-      <c r="O203" s="59"/>
-      <c r="P203" s="59"/>
-      <c r="Q203" s="59"/>
+      <c r="G203" s="59"/>
+      <c r="H203" s="58"/>
+      <c r="I203" s="58"/>
+      <c r="J203" s="58"/>
+      <c r="K203" s="58"/>
+      <c r="L203" s="58"/>
+      <c r="M203" s="58"/>
+      <c r="N203" s="58"/>
+      <c r="O203" s="58"/>
+      <c r="P203" s="58"/>
+      <c r="Q203" s="58"/>
       <c r="R203" s="9"/>
       <c r="S203" s="9"/>
       <c r="T203" s="9"/>
@@ -12053,27 +12068,27 @@
       <c r="Z203" s="9"/>
     </row>
     <row r="204">
-      <c r="A204" s="58" t="s">
+      <c r="A204" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="B204" s="58" t="s">
+      <c r="B204" s="59" t="s">
         <v>560</v>
       </c>
-      <c r="C204" s="58"/>
-      <c r="D204" s="58"/>
-      <c r="E204" s="58"/>
+      <c r="C204" s="59"/>
+      <c r="D204" s="59"/>
+      <c r="E204" s="59"/>
       <c r="F204" s="9"/>
-      <c r="G204" s="58"/>
-      <c r="H204" s="59"/>
-      <c r="I204" s="59"/>
-      <c r="J204" s="59"/>
-      <c r="K204" s="59"/>
-      <c r="L204" s="59"/>
-      <c r="M204" s="59"/>
-      <c r="N204" s="59"/>
-      <c r="O204" s="59"/>
-      <c r="P204" s="59"/>
-      <c r="Q204" s="59"/>
+      <c r="G204" s="59"/>
+      <c r="H204" s="58"/>
+      <c r="I204" s="58"/>
+      <c r="J204" s="58"/>
+      <c r="K204" s="58"/>
+      <c r="L204" s="58"/>
+      <c r="M204" s="58"/>
+      <c r="N204" s="58"/>
+      <c r="O204" s="58"/>
+      <c r="P204" s="58"/>
+      <c r="Q204" s="58"/>
       <c r="R204" s="9"/>
       <c r="S204" s="9"/>
       <c r="T204" s="9"/>
@@ -12085,35 +12100,35 @@
       <c r="Z204" s="9"/>
     </row>
     <row r="205">
-      <c r="A205" s="58" t="s">
+      <c r="A205" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="B205" s="58" t="s">
+      <c r="B205" s="59" t="s">
         <v>573</v>
       </c>
-      <c r="C205" s="58" t="s">
+      <c r="C205" s="59" t="s">
         <v>574</v>
       </c>
-      <c r="D205" s="58" t="s">
+      <c r="D205" s="59" t="s">
         <v>575</v>
       </c>
-      <c r="E205" s="59"/>
+      <c r="E205" s="58"/>
       <c r="F205" s="35" t="s">
         <v>576</v>
       </c>
-      <c r="G205" s="58" t="s">
+      <c r="G205" s="59" t="s">
         <v>117</v>
       </c>
-      <c r="H205" s="59"/>
-      <c r="I205" s="59"/>
-      <c r="J205" s="59"/>
-      <c r="K205" s="59"/>
-      <c r="L205" s="59"/>
-      <c r="M205" s="59"/>
-      <c r="N205" s="59"/>
-      <c r="O205" s="59"/>
-      <c r="P205" s="59"/>
-      <c r="Q205" s="59"/>
+      <c r="H205" s="58"/>
+      <c r="I205" s="58"/>
+      <c r="J205" s="58"/>
+      <c r="K205" s="58"/>
+      <c r="L205" s="58"/>
+      <c r="M205" s="58"/>
+      <c r="N205" s="58"/>
+      <c r="O205" s="58"/>
+      <c r="P205" s="58"/>
+      <c r="Q205" s="58"/>
       <c r="R205" s="9"/>
       <c r="S205" s="9"/>
       <c r="T205" s="9"/>
@@ -12125,39 +12140,39 @@
       <c r="Z205" s="9"/>
     </row>
     <row r="206">
-      <c r="A206" s="58" t="s">
+      <c r="A206" s="59" t="s">
         <v>238</v>
       </c>
       <c r="B206" s="13" t="s">
         <v>577</v>
       </c>
-      <c r="C206" s="58" t="s">
+      <c r="C206" s="59" t="s">
         <v>578</v>
       </c>
-      <c r="D206" s="58" t="s">
+      <c r="D206" s="59" t="s">
         <v>579</v>
       </c>
-      <c r="E206" s="58" t="s">
+      <c r="E206" s="59" t="s">
         <v>139</v>
       </c>
       <c r="F206" s="48"/>
-      <c r="G206" s="59"/>
-      <c r="H206" s="59"/>
+      <c r="G206" s="58"/>
+      <c r="H206" s="58"/>
       <c r="I206" s="7" t="s">
         <v>580</v>
       </c>
-      <c r="J206" s="58" t="s">
+      <c r="J206" s="59" t="s">
         <v>581</v>
       </c>
-      <c r="K206" s="58" t="s">
+      <c r="K206" s="59" t="s">
         <v>582</v>
       </c>
-      <c r="L206" s="59"/>
-      <c r="M206" s="59"/>
-      <c r="N206" s="59"/>
-      <c r="O206" s="59"/>
-      <c r="P206" s="58"/>
-      <c r="Q206" s="59"/>
+      <c r="L206" s="58"/>
+      <c r="M206" s="58"/>
+      <c r="N206" s="58"/>
+      <c r="O206" s="58"/>
+      <c r="P206" s="59"/>
+      <c r="Q206" s="58"/>
       <c r="R206" s="9"/>
       <c r="S206" s="9"/>
       <c r="T206" s="9"/>
@@ -12169,34 +12184,34 @@
       <c r="Z206" s="9"/>
     </row>
     <row r="207">
-      <c r="A207" s="58" t="s">
+      <c r="A207" s="59" t="s">
         <v>583</v>
       </c>
-      <c r="B207" s="58" t="s">
+      <c r="B207" s="59" t="s">
         <v>584</v>
       </c>
-      <c r="C207" s="58" t="s">
+      <c r="C207" s="59" t="s">
         <v>585</v>
       </c>
-      <c r="D207" s="58" t="s">
+      <c r="D207" s="59" t="s">
         <v>586</v>
       </c>
-      <c r="E207" s="58" t="s">
+      <c r="E207" s="59" t="s">
         <v>139</v>
       </c>
       <c r="F207" s="35" t="s">
         <v>587</v>
       </c>
-      <c r="G207" s="59"/>
-      <c r="H207" s="59"/>
-      <c r="J207" s="59"/>
-      <c r="K207" s="59"/>
-      <c r="L207" s="59"/>
-      <c r="M207" s="59"/>
-      <c r="N207" s="59"/>
-      <c r="O207" s="59"/>
-      <c r="P207" s="59"/>
-      <c r="Q207" s="59"/>
+      <c r="G207" s="58"/>
+      <c r="H207" s="58"/>
+      <c r="J207" s="58"/>
+      <c r="K207" s="58"/>
+      <c r="L207" s="58"/>
+      <c r="M207" s="58"/>
+      <c r="N207" s="58"/>
+      <c r="O207" s="58"/>
+      <c r="P207" s="58"/>
+      <c r="Q207" s="58"/>
       <c r="R207" s="9"/>
       <c r="S207" s="9"/>
       <c r="T207" s="9"/>
@@ -12208,10 +12223,10 @@
       <c r="Z207" s="9"/>
     </row>
     <row r="208">
-      <c r="A208" s="58" t="s">
+      <c r="A208" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B208" s="58" t="s">
+      <c r="B208" s="59" t="s">
         <v>588</v>
       </c>
       <c r="C208" s="7" t="s">
@@ -12224,17 +12239,17 @@
       <c r="F208" s="35" t="s">
         <v>591</v>
       </c>
-      <c r="G208" s="59"/>
-      <c r="H208" s="59"/>
-      <c r="I208" s="59"/>
-      <c r="J208" s="59"/>
-      <c r="K208" s="59"/>
-      <c r="L208" s="59"/>
-      <c r="M208" s="59"/>
-      <c r="N208" s="59"/>
-      <c r="O208" s="59"/>
-      <c r="P208" s="59"/>
-      <c r="Q208" s="59"/>
+      <c r="G208" s="58"/>
+      <c r="H208" s="58"/>
+      <c r="I208" s="58"/>
+      <c r="J208" s="58"/>
+      <c r="K208" s="58"/>
+      <c r="L208" s="58"/>
+      <c r="M208" s="58"/>
+      <c r="N208" s="58"/>
+      <c r="O208" s="58"/>
+      <c r="P208" s="58"/>
+      <c r="Q208" s="58"/>
       <c r="R208" s="9"/>
       <c r="S208" s="9"/>
       <c r="T208" s="9"/>
@@ -12246,27 +12261,27 @@
       <c r="Z208" s="9"/>
     </row>
     <row r="209">
-      <c r="A209" s="58" t="s">
+      <c r="A209" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="B209" s="58" t="s">
+      <c r="B209" s="59" t="s">
         <v>573</v>
       </c>
-      <c r="C209" s="59"/>
-      <c r="D209" s="59"/>
-      <c r="E209" s="59"/>
-      <c r="F209" s="59"/>
-      <c r="G209" s="59"/>
-      <c r="H209" s="59"/>
-      <c r="I209" s="59"/>
-      <c r="J209" s="59"/>
-      <c r="K209" s="59"/>
-      <c r="L209" s="59"/>
-      <c r="M209" s="59"/>
-      <c r="N209" s="59"/>
-      <c r="O209" s="59"/>
-      <c r="P209" s="59"/>
-      <c r="Q209" s="59"/>
+      <c r="C209" s="58"/>
+      <c r="D209" s="58"/>
+      <c r="E209" s="58"/>
+      <c r="F209" s="58"/>
+      <c r="G209" s="58"/>
+      <c r="H209" s="58"/>
+      <c r="I209" s="58"/>
+      <c r="J209" s="58"/>
+      <c r="K209" s="58"/>
+      <c r="L209" s="58"/>
+      <c r="M209" s="58"/>
+      <c r="N209" s="58"/>
+      <c r="O209" s="58"/>
+      <c r="P209" s="58"/>
+      <c r="Q209" s="58"/>
       <c r="R209" s="9"/>
       <c r="S209" s="9"/>
       <c r="T209" s="9"/>
@@ -12278,31 +12293,31 @@
       <c r="Z209" s="9"/>
     </row>
     <row r="210">
-      <c r="A210" s="58" t="s">
+      <c r="A210" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="B210" s="58" t="s">
+      <c r="B210" s="59" t="s">
         <v>592</v>
       </c>
-      <c r="C210" s="58" t="s">
+      <c r="C210" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="D210" s="59"/>
-      <c r="E210" s="59"/>
+      <c r="D210" s="58"/>
+      <c r="E210" s="58"/>
       <c r="F210" s="35" t="s">
         <v>576</v>
       </c>
-      <c r="G210" s="58"/>
-      <c r="H210" s="59"/>
-      <c r="I210" s="59"/>
-      <c r="J210" s="59"/>
-      <c r="K210" s="59"/>
-      <c r="L210" s="59"/>
-      <c r="M210" s="59"/>
-      <c r="N210" s="59"/>
-      <c r="O210" s="59"/>
-      <c r="P210" s="59"/>
-      <c r="Q210" s="59"/>
+      <c r="G210" s="59"/>
+      <c r="H210" s="58"/>
+      <c r="I210" s="58"/>
+      <c r="J210" s="58"/>
+      <c r="K210" s="58"/>
+      <c r="L210" s="58"/>
+      <c r="M210" s="58"/>
+      <c r="N210" s="58"/>
+      <c r="O210" s="58"/>
+      <c r="P210" s="58"/>
+      <c r="Q210" s="58"/>
       <c r="R210" s="9"/>
       <c r="S210" s="9"/>
       <c r="T210" s="9"/>
@@ -12314,33 +12329,33 @@
       <c r="Z210" s="9"/>
     </row>
     <row r="211">
-      <c r="A211" s="58" t="s">
+      <c r="A211" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="B211" s="58" t="s">
+      <c r="B211" s="59" t="s">
         <v>593</v>
       </c>
-      <c r="C211" s="58" t="s">
+      <c r="C211" s="59" t="s">
         <v>594</v>
       </c>
-      <c r="D211" s="58" t="s">
+      <c r="D211" s="59" t="s">
         <v>595</v>
       </c>
-      <c r="E211" s="59"/>
+      <c r="E211" s="58"/>
       <c r="F211" s="35"/>
-      <c r="G211" s="58" t="s">
+      <c r="G211" s="59" t="s">
         <v>117</v>
       </c>
-      <c r="H211" s="59"/>
-      <c r="I211" s="59"/>
-      <c r="J211" s="59"/>
-      <c r="K211" s="59"/>
-      <c r="L211" s="59"/>
-      <c r="M211" s="59"/>
-      <c r="N211" s="59"/>
-      <c r="O211" s="59"/>
-      <c r="P211" s="59"/>
-      <c r="Q211" s="59"/>
+      <c r="H211" s="58"/>
+      <c r="I211" s="58"/>
+      <c r="J211" s="58"/>
+      <c r="K211" s="58"/>
+      <c r="L211" s="58"/>
+      <c r="M211" s="58"/>
+      <c r="N211" s="58"/>
+      <c r="O211" s="58"/>
+      <c r="P211" s="58"/>
+      <c r="Q211" s="58"/>
       <c r="R211" s="9"/>
       <c r="S211" s="9"/>
       <c r="T211" s="9"/>
@@ -12352,32 +12367,32 @@
       <c r="Z211" s="9"/>
     </row>
     <row r="212">
-      <c r="A212" s="58" t="s">
+      <c r="A212" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B212" s="58" t="s">
+      <c r="B212" s="59" t="s">
         <v>596</v>
       </c>
-      <c r="C212" s="58" t="s">
+      <c r="C212" s="59" t="s">
         <v>597</v>
       </c>
-      <c r="D212" s="58" t="s">
+      <c r="D212" s="59" t="s">
         <v>598</v>
       </c>
-      <c r="E212" s="58"/>
-      <c r="F212" s="58"/>
-      <c r="G212" s="58"/>
-      <c r="H212" s="58"/>
-      <c r="I212" s="58"/>
-      <c r="J212" s="58"/>
-      <c r="K212" s="58"/>
-      <c r="L212" s="58"/>
-      <c r="M212" s="58"/>
-      <c r="N212" s="58"/>
-      <c r="O212" s="58"/>
-      <c r="P212" s="58"/>
-      <c r="Q212" s="58"/>
-      <c r="R212" s="58"/>
+      <c r="E212" s="59"/>
+      <c r="F212" s="59"/>
+      <c r="G212" s="59"/>
+      <c r="H212" s="59"/>
+      <c r="I212" s="59"/>
+      <c r="J212" s="59"/>
+      <c r="K212" s="59"/>
+      <c r="L212" s="59"/>
+      <c r="M212" s="59"/>
+      <c r="N212" s="59"/>
+      <c r="O212" s="59"/>
+      <c r="P212" s="59"/>
+      <c r="Q212" s="59"/>
+      <c r="R212" s="59"/>
       <c r="S212" s="9"/>
       <c r="T212" s="9"/>
       <c r="U212" s="9"/>
@@ -12388,27 +12403,27 @@
       <c r="Z212" s="9"/>
     </row>
     <row r="213">
-      <c r="A213" s="58" t="s">
+      <c r="A213" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="B213" s="58" t="s">
+      <c r="B213" s="59" t="s">
         <v>593</v>
       </c>
-      <c r="C213" s="58"/>
-      <c r="D213" s="59"/>
-      <c r="E213" s="59"/>
-      <c r="F213" s="59"/>
-      <c r="G213" s="59"/>
-      <c r="H213" s="59"/>
-      <c r="I213" s="59"/>
-      <c r="J213" s="59"/>
-      <c r="K213" s="59"/>
-      <c r="L213" s="59"/>
-      <c r="M213" s="59"/>
-      <c r="N213" s="59"/>
-      <c r="O213" s="59"/>
-      <c r="P213" s="59"/>
-      <c r="Q213" s="59"/>
+      <c r="C213" s="59"/>
+      <c r="D213" s="58"/>
+      <c r="E213" s="58"/>
+      <c r="F213" s="58"/>
+      <c r="G213" s="58"/>
+      <c r="H213" s="58"/>
+      <c r="I213" s="58"/>
+      <c r="J213" s="58"/>
+      <c r="K213" s="58"/>
+      <c r="L213" s="58"/>
+      <c r="M213" s="58"/>
+      <c r="N213" s="58"/>
+      <c r="O213" s="58"/>
+      <c r="P213" s="58"/>
+      <c r="Q213" s="58"/>
       <c r="R213" s="9"/>
       <c r="S213" s="9"/>
       <c r="T213" s="9"/>
@@ -12420,33 +12435,33 @@
       <c r="Z213" s="9"/>
     </row>
     <row r="214">
-      <c r="A214" s="58" t="s">
+      <c r="A214" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="B214" s="58" t="s">
+      <c r="B214" s="59" t="s">
         <v>599</v>
       </c>
-      <c r="C214" s="58" t="s">
+      <c r="C214" s="59" t="s">
         <v>600</v>
       </c>
       <c r="D214" s="60" t="s">
         <v>601</v>
       </c>
-      <c r="E214" s="59"/>
-      <c r="F214" s="59"/>
-      <c r="G214" s="58" t="s">
+      <c r="E214" s="58"/>
+      <c r="F214" s="58"/>
+      <c r="G214" s="59" t="s">
         <v>117</v>
       </c>
-      <c r="H214" s="59"/>
-      <c r="I214" s="59"/>
-      <c r="J214" s="59"/>
-      <c r="K214" s="59"/>
-      <c r="L214" s="59"/>
-      <c r="M214" s="59"/>
-      <c r="N214" s="59"/>
-      <c r="O214" s="59"/>
-      <c r="P214" s="59"/>
-      <c r="Q214" s="59"/>
+      <c r="H214" s="58"/>
+      <c r="I214" s="58"/>
+      <c r="J214" s="58"/>
+      <c r="K214" s="58"/>
+      <c r="L214" s="58"/>
+      <c r="M214" s="58"/>
+      <c r="N214" s="58"/>
+      <c r="O214" s="58"/>
+      <c r="P214" s="58"/>
+      <c r="Q214" s="58"/>
       <c r="R214" s="9"/>
       <c r="S214" s="9"/>
       <c r="T214" s="9"/>
@@ -12458,31 +12473,31 @@
       <c r="Z214" s="9"/>
     </row>
     <row r="215">
-      <c r="A215" s="58" t="s">
+      <c r="A215" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B215" s="58" t="s">
+      <c r="B215" s="59" t="s">
         <v>602</v>
       </c>
-      <c r="C215" s="58" t="s">
+      <c r="C215" s="59" t="s">
         <v>603</v>
       </c>
-      <c r="D215" s="58" t="s">
+      <c r="D215" s="59" t="s">
         <v>604</v>
       </c>
-      <c r="E215" s="59"/>
-      <c r="F215" s="59"/>
-      <c r="G215" s="59"/>
-      <c r="H215" s="59"/>
-      <c r="I215" s="59"/>
-      <c r="J215" s="59"/>
-      <c r="K215" s="59"/>
-      <c r="L215" s="59"/>
-      <c r="M215" s="59"/>
-      <c r="N215" s="59"/>
-      <c r="O215" s="59"/>
-      <c r="P215" s="59"/>
-      <c r="Q215" s="59"/>
+      <c r="E215" s="58"/>
+      <c r="F215" s="58"/>
+      <c r="G215" s="58"/>
+      <c r="H215" s="58"/>
+      <c r="I215" s="58"/>
+      <c r="J215" s="58"/>
+      <c r="K215" s="58"/>
+      <c r="L215" s="58"/>
+      <c r="M215" s="58"/>
+      <c r="N215" s="58"/>
+      <c r="O215" s="58"/>
+      <c r="P215" s="58"/>
+      <c r="Q215" s="58"/>
       <c r="R215" s="9"/>
       <c r="S215" s="9"/>
       <c r="T215" s="9"/>
@@ -12494,27 +12509,27 @@
       <c r="Z215" s="9"/>
     </row>
     <row r="216">
-      <c r="A216" s="58" t="s">
+      <c r="A216" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="B216" s="58" t="s">
+      <c r="B216" s="59" t="s">
         <v>599</v>
       </c>
-      <c r="C216" s="58"/>
-      <c r="D216" s="59"/>
-      <c r="E216" s="59"/>
-      <c r="F216" s="59"/>
-      <c r="G216" s="59"/>
-      <c r="H216" s="59"/>
-      <c r="I216" s="59"/>
-      <c r="J216" s="59"/>
-      <c r="K216" s="59"/>
-      <c r="L216" s="59"/>
-      <c r="M216" s="59"/>
-      <c r="N216" s="59"/>
-      <c r="O216" s="59"/>
-      <c r="P216" s="59"/>
-      <c r="Q216" s="59"/>
+      <c r="C216" s="59"/>
+      <c r="D216" s="58"/>
+      <c r="E216" s="58"/>
+      <c r="F216" s="58"/>
+      <c r="G216" s="58"/>
+      <c r="H216" s="58"/>
+      <c r="I216" s="58"/>
+      <c r="J216" s="58"/>
+      <c r="K216" s="58"/>
+      <c r="L216" s="58"/>
+      <c r="M216" s="58"/>
+      <c r="N216" s="58"/>
+      <c r="O216" s="58"/>
+      <c r="P216" s="58"/>
+      <c r="Q216" s="58"/>
       <c r="R216" s="9"/>
       <c r="S216" s="9"/>
       <c r="T216" s="9"/>
@@ -12526,33 +12541,33 @@
       <c r="Z216" s="9"/>
     </row>
     <row r="217">
-      <c r="A217" s="58" t="s">
+      <c r="A217" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="B217" s="58" t="s">
+      <c r="B217" s="59" t="s">
         <v>605</v>
       </c>
-      <c r="C217" s="58" t="s">
+      <c r="C217" s="59" t="s">
         <v>606</v>
       </c>
-      <c r="D217" s="58" t="s">
+      <c r="D217" s="59" t="s">
         <v>607</v>
       </c>
-      <c r="E217" s="59"/>
-      <c r="F217" s="59"/>
-      <c r="G217" s="58" t="s">
+      <c r="E217" s="58"/>
+      <c r="F217" s="58"/>
+      <c r="G217" s="59" t="s">
         <v>117</v>
       </c>
-      <c r="H217" s="59"/>
-      <c r="I217" s="59"/>
-      <c r="J217" s="59"/>
-      <c r="K217" s="59"/>
-      <c r="L217" s="59"/>
-      <c r="M217" s="59"/>
-      <c r="N217" s="59"/>
-      <c r="O217" s="59"/>
-      <c r="P217" s="59"/>
-      <c r="Q217" s="59"/>
+      <c r="H217" s="58"/>
+      <c r="I217" s="58"/>
+      <c r="J217" s="58"/>
+      <c r="K217" s="58"/>
+      <c r="L217" s="58"/>
+      <c r="M217" s="58"/>
+      <c r="N217" s="58"/>
+      <c r="O217" s="58"/>
+      <c r="P217" s="58"/>
+      <c r="Q217" s="58"/>
       <c r="R217" s="9"/>
       <c r="S217" s="9"/>
       <c r="T217" s="9"/>
@@ -12564,31 +12579,31 @@
       <c r="Z217" s="9"/>
     </row>
     <row r="218">
-      <c r="A218" s="58" t="s">
+      <c r="A218" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B218" s="58" t="s">
+      <c r="B218" s="59" t="s">
         <v>608</v>
       </c>
-      <c r="C218" s="58" t="s">
+      <c r="C218" s="59" t="s">
         <v>609</v>
       </c>
-      <c r="D218" s="58" t="s">
+      <c r="D218" s="59" t="s">
         <v>610</v>
       </c>
-      <c r="E218" s="59"/>
-      <c r="F218" s="59"/>
-      <c r="G218" s="59"/>
-      <c r="H218" s="59"/>
-      <c r="I218" s="59"/>
-      <c r="J218" s="59"/>
-      <c r="K218" s="59"/>
-      <c r="L218" s="59"/>
-      <c r="M218" s="59"/>
-      <c r="N218" s="59"/>
-      <c r="O218" s="59"/>
-      <c r="P218" s="59"/>
-      <c r="Q218" s="59"/>
+      <c r="E218" s="58"/>
+      <c r="F218" s="58"/>
+      <c r="G218" s="58"/>
+      <c r="H218" s="58"/>
+      <c r="I218" s="58"/>
+      <c r="J218" s="58"/>
+      <c r="K218" s="58"/>
+      <c r="L218" s="58"/>
+      <c r="M218" s="58"/>
+      <c r="N218" s="58"/>
+      <c r="O218" s="58"/>
+      <c r="P218" s="58"/>
+      <c r="Q218" s="58"/>
       <c r="R218" s="9"/>
       <c r="S218" s="9"/>
       <c r="T218" s="9"/>
@@ -12600,27 +12615,27 @@
       <c r="Z218" s="9"/>
     </row>
     <row r="219">
-      <c r="A219" s="58" t="s">
+      <c r="A219" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="B219" s="58" t="s">
+      <c r="B219" s="59" t="s">
         <v>605</v>
       </c>
-      <c r="C219" s="58"/>
-      <c r="D219" s="59"/>
-      <c r="E219" s="59"/>
+      <c r="C219" s="59"/>
+      <c r="D219" s="58"/>
+      <c r="E219" s="58"/>
       <c r="F219" s="61"/>
-      <c r="G219" s="59"/>
-      <c r="H219" s="59"/>
-      <c r="I219" s="59"/>
-      <c r="J219" s="59"/>
-      <c r="K219" s="59"/>
-      <c r="L219" s="59"/>
-      <c r="M219" s="59"/>
-      <c r="N219" s="59"/>
-      <c r="O219" s="59"/>
-      <c r="P219" s="59"/>
-      <c r="Q219" s="59"/>
+      <c r="G219" s="58"/>
+      <c r="H219" s="58"/>
+      <c r="I219" s="58"/>
+      <c r="J219" s="58"/>
+      <c r="K219" s="58"/>
+      <c r="L219" s="58"/>
+      <c r="M219" s="58"/>
+      <c r="N219" s="58"/>
+      <c r="O219" s="58"/>
+      <c r="P219" s="58"/>
+      <c r="Q219" s="58"/>
       <c r="R219" s="9"/>
       <c r="S219" s="9"/>
       <c r="T219" s="9"/>
@@ -12632,33 +12647,33 @@
       <c r="Z219" s="9"/>
     </row>
     <row r="220">
-      <c r="A220" s="58" t="s">
+      <c r="A220" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="B220" s="58" t="s">
+      <c r="B220" s="59" t="s">
         <v>611</v>
       </c>
-      <c r="C220" s="58" t="s">
+      <c r="C220" s="59" t="s">
         <v>612</v>
       </c>
       <c r="D220" s="60" t="s">
         <v>613</v>
       </c>
-      <c r="E220" s="59"/>
+      <c r="E220" s="58"/>
       <c r="F220" s="61"/>
-      <c r="G220" s="58" t="s">
+      <c r="G220" s="59" t="s">
         <v>117</v>
       </c>
-      <c r="H220" s="59"/>
-      <c r="I220" s="59"/>
-      <c r="J220" s="59"/>
-      <c r="K220" s="59"/>
-      <c r="L220" s="59"/>
-      <c r="M220" s="59"/>
-      <c r="N220" s="59"/>
-      <c r="O220" s="59"/>
-      <c r="P220" s="59"/>
-      <c r="Q220" s="59"/>
+      <c r="H220" s="58"/>
+      <c r="I220" s="58"/>
+      <c r="J220" s="58"/>
+      <c r="K220" s="58"/>
+      <c r="L220" s="58"/>
+      <c r="M220" s="58"/>
+      <c r="N220" s="58"/>
+      <c r="O220" s="58"/>
+      <c r="P220" s="58"/>
+      <c r="Q220" s="58"/>
       <c r="R220" s="9"/>
       <c r="S220" s="9"/>
       <c r="T220" s="9"/>
@@ -12670,31 +12685,31 @@
       <c r="Z220" s="9"/>
     </row>
     <row r="221">
-      <c r="A221" s="58" t="s">
+      <c r="A221" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B221" s="58" t="s">
+      <c r="B221" s="59" t="s">
         <v>614</v>
       </c>
-      <c r="C221" s="58" t="s">
+      <c r="C221" s="59" t="s">
         <v>615</v>
       </c>
-      <c r="D221" s="58" t="s">
+      <c r="D221" s="59" t="s">
         <v>616</v>
       </c>
-      <c r="E221" s="59"/>
+      <c r="E221" s="58"/>
       <c r="F221" s="61"/>
-      <c r="G221" s="59"/>
-      <c r="H221" s="59"/>
-      <c r="I221" s="59"/>
-      <c r="J221" s="59"/>
-      <c r="K221" s="59"/>
-      <c r="L221" s="59"/>
-      <c r="M221" s="59"/>
-      <c r="N221" s="59"/>
-      <c r="O221" s="59"/>
-      <c r="P221" s="59"/>
-      <c r="Q221" s="59"/>
+      <c r="G221" s="58"/>
+      <c r="H221" s="58"/>
+      <c r="I221" s="58"/>
+      <c r="J221" s="58"/>
+      <c r="K221" s="58"/>
+      <c r="L221" s="58"/>
+      <c r="M221" s="58"/>
+      <c r="N221" s="58"/>
+      <c r="O221" s="58"/>
+      <c r="P221" s="58"/>
+      <c r="Q221" s="58"/>
       <c r="R221" s="9"/>
       <c r="S221" s="9"/>
       <c r="T221" s="9"/>
@@ -12706,31 +12721,31 @@
       <c r="Z221" s="9"/>
     </row>
     <row r="222">
-      <c r="A222" s="58" t="s">
+      <c r="A222" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B222" s="58" t="s">
+      <c r="B222" s="59" t="s">
         <v>617</v>
       </c>
-      <c r="C222" s="58" t="s">
+      <c r="C222" s="59" t="s">
         <v>618</v>
       </c>
-      <c r="D222" s="58" t="s">
+      <c r="D222" s="59" t="s">
         <v>619</v>
       </c>
-      <c r="E222" s="59"/>
-      <c r="F222" s="59"/>
-      <c r="G222" s="59"/>
-      <c r="H222" s="59"/>
-      <c r="I222" s="59"/>
-      <c r="J222" s="59"/>
-      <c r="K222" s="59"/>
-      <c r="L222" s="59"/>
-      <c r="M222" s="59"/>
-      <c r="N222" s="59"/>
-      <c r="O222" s="59"/>
-      <c r="P222" s="59"/>
-      <c r="Q222" s="59"/>
+      <c r="E222" s="58"/>
+      <c r="F222" s="58"/>
+      <c r="G222" s="58"/>
+      <c r="H222" s="58"/>
+      <c r="I222" s="58"/>
+      <c r="J222" s="58"/>
+      <c r="K222" s="58"/>
+      <c r="L222" s="58"/>
+      <c r="M222" s="58"/>
+      <c r="N222" s="58"/>
+      <c r="O222" s="58"/>
+      <c r="P222" s="58"/>
+      <c r="Q222" s="58"/>
       <c r="R222" s="9"/>
       <c r="S222" s="9"/>
       <c r="T222" s="9"/>
@@ -12742,27 +12757,27 @@
       <c r="Z222" s="9"/>
     </row>
     <row r="223">
-      <c r="A223" s="58" t="s">
+      <c r="A223" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="B223" s="58" t="s">
+      <c r="B223" s="59" t="s">
         <v>611</v>
       </c>
-      <c r="C223" s="59"/>
-      <c r="D223" s="59"/>
-      <c r="E223" s="59"/>
-      <c r="F223" s="59"/>
-      <c r="G223" s="59"/>
-      <c r="H223" s="59"/>
-      <c r="I223" s="59"/>
-      <c r="J223" s="59"/>
-      <c r="K223" s="59"/>
-      <c r="L223" s="59"/>
-      <c r="M223" s="59"/>
-      <c r="N223" s="59"/>
-      <c r="O223" s="59"/>
-      <c r="P223" s="59"/>
-      <c r="Q223" s="59"/>
+      <c r="C223" s="58"/>
+      <c r="D223" s="58"/>
+      <c r="E223" s="58"/>
+      <c r="F223" s="58"/>
+      <c r="G223" s="58"/>
+      <c r="H223" s="58"/>
+      <c r="I223" s="58"/>
+      <c r="J223" s="58"/>
+      <c r="K223" s="58"/>
+      <c r="L223" s="58"/>
+      <c r="M223" s="58"/>
+      <c r="N223" s="58"/>
+      <c r="O223" s="58"/>
+      <c r="P223" s="58"/>
+      <c r="Q223" s="58"/>
       <c r="R223" s="9"/>
       <c r="S223" s="9"/>
       <c r="T223" s="9"/>
@@ -12831,33 +12846,33 @@
       <c r="Z225" s="4"/>
     </row>
     <row r="226">
-      <c r="A226" s="58" t="s">
+      <c r="A226" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="B226" s="58" t="s">
+      <c r="B226" s="59" t="s">
         <v>622</v>
       </c>
-      <c r="C226" s="58" t="s">
+      <c r="C226" s="59" t="s">
         <v>623</v>
       </c>
-      <c r="D226" s="58" t="s">
+      <c r="D226" s="59" t="s">
         <v>624</v>
       </c>
-      <c r="E226" s="59"/>
+      <c r="E226" s="58"/>
       <c r="F226" s="35" t="s">
         <v>625</v>
       </c>
-      <c r="G226" s="59"/>
-      <c r="H226" s="59"/>
-      <c r="I226" s="59"/>
-      <c r="J226" s="59"/>
-      <c r="K226" s="59"/>
-      <c r="L226" s="59"/>
-      <c r="M226" s="59"/>
-      <c r="N226" s="59"/>
-      <c r="O226" s="59"/>
-      <c r="P226" s="59"/>
-      <c r="Q226" s="59"/>
+      <c r="G226" s="58"/>
+      <c r="H226" s="58"/>
+      <c r="I226" s="58"/>
+      <c r="J226" s="58"/>
+      <c r="K226" s="58"/>
+      <c r="L226" s="58"/>
+      <c r="M226" s="58"/>
+      <c r="N226" s="58"/>
+      <c r="O226" s="58"/>
+      <c r="P226" s="58"/>
+      <c r="Q226" s="58"/>
       <c r="R226" s="9"/>
       <c r="S226" s="9"/>
       <c r="T226" s="9"/>
@@ -12869,31 +12884,31 @@
       <c r="Z226" s="9"/>
     </row>
     <row r="227">
-      <c r="A227" s="58" t="s">
+      <c r="A227" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B227" s="58" t="s">
+      <c r="B227" s="59" t="s">
         <v>626</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="D227" s="58" t="s">
+      <c r="D227" s="59" t="s">
         <v>628</v>
       </c>
-      <c r="E227" s="59"/>
-      <c r="F227" s="59"/>
-      <c r="G227" s="59"/>
-      <c r="H227" s="59"/>
-      <c r="I227" s="59"/>
-      <c r="J227" s="59"/>
-      <c r="K227" s="59"/>
-      <c r="L227" s="59"/>
-      <c r="M227" s="59"/>
-      <c r="N227" s="59"/>
-      <c r="O227" s="59"/>
-      <c r="P227" s="59"/>
-      <c r="Q227" s="59"/>
+      <c r="E227" s="58"/>
+      <c r="F227" s="58"/>
+      <c r="G227" s="58"/>
+      <c r="H227" s="58"/>
+      <c r="I227" s="58"/>
+      <c r="J227" s="58"/>
+      <c r="K227" s="58"/>
+      <c r="L227" s="58"/>
+      <c r="M227" s="58"/>
+      <c r="N227" s="58"/>
+      <c r="O227" s="58"/>
+      <c r="P227" s="58"/>
+      <c r="Q227" s="58"/>
       <c r="R227" s="9"/>
       <c r="S227" s="9"/>
       <c r="T227" s="9"/>
@@ -12905,31 +12920,31 @@
       <c r="Z227" s="9"/>
     </row>
     <row r="228">
-      <c r="A228" s="58" t="s">
+      <c r="A228" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B228" s="58" t="s">
+      <c r="B228" s="59" t="s">
         <v>629</v>
       </c>
-      <c r="C228" s="58" t="s">
+      <c r="C228" s="59" t="s">
         <v>630</v>
       </c>
-      <c r="D228" s="58" t="s">
+      <c r="D228" s="59" t="s">
         <v>631</v>
       </c>
-      <c r="E228" s="59"/>
-      <c r="F228" s="59"/>
-      <c r="G228" s="59"/>
-      <c r="H228" s="59"/>
-      <c r="I228" s="59"/>
-      <c r="J228" s="59"/>
-      <c r="K228" s="59"/>
-      <c r="L228" s="59"/>
-      <c r="M228" s="59"/>
-      <c r="N228" s="59"/>
-      <c r="O228" s="59"/>
-      <c r="P228" s="59"/>
-      <c r="Q228" s="59"/>
+      <c r="E228" s="58"/>
+      <c r="F228" s="58"/>
+      <c r="G228" s="58"/>
+      <c r="H228" s="58"/>
+      <c r="I228" s="58"/>
+      <c r="J228" s="58"/>
+      <c r="K228" s="58"/>
+      <c r="L228" s="58"/>
+      <c r="M228" s="58"/>
+      <c r="N228" s="58"/>
+      <c r="O228" s="58"/>
+      <c r="P228" s="58"/>
+      <c r="Q228" s="58"/>
       <c r="R228" s="9"/>
       <c r="S228" s="9"/>
       <c r="T228" s="9"/>
@@ -12941,31 +12956,31 @@
       <c r="Z228" s="9"/>
     </row>
     <row r="229">
-      <c r="A229" s="58" t="s">
+      <c r="A229" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B229" s="58" t="s">
+      <c r="B229" s="59" t="s">
         <v>632</v>
       </c>
-      <c r="C229" s="58" t="s">
+      <c r="C229" s="59" t="s">
         <v>633</v>
       </c>
-      <c r="D229" s="58" t="s">
+      <c r="D229" s="59" t="s">
         <v>634</v>
       </c>
-      <c r="E229" s="59"/>
-      <c r="F229" s="59"/>
-      <c r="G229" s="59"/>
-      <c r="H229" s="59"/>
-      <c r="I229" s="59"/>
-      <c r="J229" s="59"/>
-      <c r="K229" s="59"/>
-      <c r="L229" s="59"/>
-      <c r="M229" s="59"/>
-      <c r="N229" s="59"/>
-      <c r="O229" s="59"/>
-      <c r="P229" s="59"/>
-      <c r="Q229" s="59"/>
+      <c r="E229" s="58"/>
+      <c r="F229" s="58"/>
+      <c r="G229" s="58"/>
+      <c r="H229" s="58"/>
+      <c r="I229" s="58"/>
+      <c r="J229" s="58"/>
+      <c r="K229" s="58"/>
+      <c r="L229" s="58"/>
+      <c r="M229" s="58"/>
+      <c r="N229" s="58"/>
+      <c r="O229" s="58"/>
+      <c r="P229" s="58"/>
+      <c r="Q229" s="58"/>
       <c r="R229" s="9"/>
       <c r="S229" s="9"/>
       <c r="T229" s="9"/>
@@ -12977,31 +12992,31 @@
       <c r="Z229" s="9"/>
     </row>
     <row r="230">
-      <c r="A230" s="58" t="s">
+      <c r="A230" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B230" s="58" t="s">
+      <c r="B230" s="59" t="s">
         <v>635</v>
       </c>
-      <c r="C230" s="58" t="s">
+      <c r="C230" s="59" t="s">
         <v>636</v>
       </c>
-      <c r="D230" s="58" t="s">
+      <c r="D230" s="59" t="s">
         <v>637</v>
       </c>
-      <c r="E230" s="59"/>
+      <c r="E230" s="58"/>
       <c r="F230" s="61"/>
-      <c r="G230" s="59"/>
-      <c r="H230" s="59"/>
-      <c r="I230" s="59"/>
-      <c r="J230" s="59"/>
-      <c r="K230" s="59"/>
-      <c r="L230" s="59"/>
-      <c r="M230" s="59"/>
-      <c r="N230" s="59"/>
-      <c r="O230" s="59"/>
-      <c r="P230" s="59"/>
-      <c r="Q230" s="59"/>
+      <c r="G230" s="58"/>
+      <c r="H230" s="58"/>
+      <c r="I230" s="58"/>
+      <c r="J230" s="58"/>
+      <c r="K230" s="58"/>
+      <c r="L230" s="58"/>
+      <c r="M230" s="58"/>
+      <c r="N230" s="58"/>
+      <c r="O230" s="58"/>
+      <c r="P230" s="58"/>
+      <c r="Q230" s="58"/>
       <c r="R230" s="9"/>
       <c r="S230" s="9"/>
       <c r="T230" s="9"/>
@@ -13013,31 +13028,31 @@
       <c r="Z230" s="9"/>
     </row>
     <row r="231">
-      <c r="A231" s="58" t="s">
+      <c r="A231" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B231" s="58" t="s">
+      <c r="B231" s="59" t="s">
         <v>638</v>
       </c>
-      <c r="C231" s="58" t="s">
+      <c r="C231" s="59" t="s">
         <v>639</v>
       </c>
-      <c r="D231" s="58" t="s">
+      <c r="D231" s="59" t="s">
         <v>640</v>
       </c>
-      <c r="E231" s="59"/>
-      <c r="F231" s="59"/>
-      <c r="G231" s="59"/>
-      <c r="H231" s="59"/>
-      <c r="I231" s="59"/>
-      <c r="J231" s="59"/>
-      <c r="K231" s="59"/>
-      <c r="L231" s="59"/>
-      <c r="M231" s="59"/>
-      <c r="N231" s="59"/>
-      <c r="O231" s="59"/>
-      <c r="P231" s="59"/>
-      <c r="Q231" s="59"/>
+      <c r="E231" s="58"/>
+      <c r="F231" s="58"/>
+      <c r="G231" s="58"/>
+      <c r="H231" s="58"/>
+      <c r="I231" s="58"/>
+      <c r="J231" s="58"/>
+      <c r="K231" s="58"/>
+      <c r="L231" s="58"/>
+      <c r="M231" s="58"/>
+      <c r="N231" s="58"/>
+      <c r="O231" s="58"/>
+      <c r="P231" s="58"/>
+      <c r="Q231" s="58"/>
       <c r="R231" s="9"/>
       <c r="S231" s="9"/>
       <c r="T231" s="9"/>
@@ -13049,31 +13064,31 @@
       <c r="Z231" s="9"/>
     </row>
     <row r="232">
-      <c r="A232" s="58" t="s">
+      <c r="A232" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B232" s="58" t="s">
+      <c r="B232" s="59" t="s">
         <v>641</v>
       </c>
-      <c r="C232" s="58" t="s">
+      <c r="C232" s="59" t="s">
         <v>642</v>
       </c>
-      <c r="D232" s="58" t="s">
+      <c r="D232" s="59" t="s">
         <v>643</v>
       </c>
-      <c r="E232" s="59"/>
-      <c r="F232" s="59"/>
-      <c r="G232" s="59"/>
-      <c r="H232" s="59"/>
-      <c r="I232" s="59"/>
-      <c r="J232" s="59"/>
-      <c r="K232" s="59"/>
-      <c r="L232" s="59"/>
-      <c r="M232" s="59"/>
-      <c r="N232" s="59"/>
-      <c r="O232" s="59"/>
-      <c r="P232" s="59"/>
-      <c r="Q232" s="59"/>
+      <c r="E232" s="58"/>
+      <c r="F232" s="58"/>
+      <c r="G232" s="58"/>
+      <c r="H232" s="58"/>
+      <c r="I232" s="58"/>
+      <c r="J232" s="58"/>
+      <c r="K232" s="58"/>
+      <c r="L232" s="58"/>
+      <c r="M232" s="58"/>
+      <c r="N232" s="58"/>
+      <c r="O232" s="58"/>
+      <c r="P232" s="58"/>
+      <c r="Q232" s="58"/>
       <c r="R232" s="9"/>
       <c r="S232" s="9"/>
       <c r="T232" s="9"/>
@@ -13085,31 +13100,31 @@
       <c r="Z232" s="9"/>
     </row>
     <row r="233">
-      <c r="A233" s="58" t="s">
+      <c r="A233" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B233" s="58" t="s">
+      <c r="B233" s="59" t="s">
         <v>644</v>
       </c>
-      <c r="C233" s="58" t="s">
+      <c r="C233" s="59" t="s">
         <v>645</v>
       </c>
-      <c r="D233" s="58" t="s">
+      <c r="D233" s="59" t="s">
         <v>646</v>
       </c>
-      <c r="E233" s="59"/>
-      <c r="F233" s="59"/>
-      <c r="G233" s="59"/>
-      <c r="H233" s="59"/>
-      <c r="I233" s="59"/>
-      <c r="J233" s="59"/>
-      <c r="K233" s="59"/>
-      <c r="L233" s="59"/>
-      <c r="M233" s="59"/>
-      <c r="N233" s="59"/>
-      <c r="O233" s="59"/>
-      <c r="P233" s="59"/>
-      <c r="Q233" s="59"/>
+      <c r="E233" s="58"/>
+      <c r="F233" s="58"/>
+      <c r="G233" s="58"/>
+      <c r="H233" s="58"/>
+      <c r="I233" s="58"/>
+      <c r="J233" s="58"/>
+      <c r="K233" s="58"/>
+      <c r="L233" s="58"/>
+      <c r="M233" s="58"/>
+      <c r="N233" s="58"/>
+      <c r="O233" s="58"/>
+      <c r="P233" s="58"/>
+      <c r="Q233" s="58"/>
       <c r="R233" s="9"/>
       <c r="S233" s="9"/>
       <c r="T233" s="9"/>
@@ -13121,10 +13136,10 @@
       <c r="Z233" s="9"/>
     </row>
     <row r="234">
-      <c r="A234" s="58" t="s">
+      <c r="A234" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="B234" s="58" t="s">
+      <c r="B234" s="59" t="s">
         <v>622</v>
       </c>
       <c r="C234" s="8"/>
@@ -13153,33 +13168,33 @@
       <c r="Z234" s="9"/>
     </row>
     <row r="235">
-      <c r="A235" s="58" t="s">
+      <c r="A235" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="B235" s="58" t="s">
+      <c r="B235" s="59" t="s">
         <v>647</v>
       </c>
-      <c r="C235" s="58" t="s">
+      <c r="C235" s="59" t="s">
         <v>648</v>
       </c>
-      <c r="D235" s="58" t="s">
+      <c r="D235" s="59" t="s">
         <v>649</v>
       </c>
-      <c r="E235" s="59"/>
+      <c r="E235" s="58"/>
       <c r="F235" s="35" t="s">
         <v>576</v>
       </c>
-      <c r="G235" s="59"/>
-      <c r="H235" s="59"/>
-      <c r="I235" s="59"/>
-      <c r="J235" s="59"/>
-      <c r="K235" s="59"/>
-      <c r="L235" s="59"/>
-      <c r="M235" s="59"/>
-      <c r="N235" s="59"/>
-      <c r="O235" s="59"/>
-      <c r="P235" s="59"/>
-      <c r="Q235" s="59"/>
+      <c r="G235" s="58"/>
+      <c r="H235" s="58"/>
+      <c r="I235" s="58"/>
+      <c r="J235" s="58"/>
+      <c r="K235" s="58"/>
+      <c r="L235" s="58"/>
+      <c r="M235" s="58"/>
+      <c r="N235" s="58"/>
+      <c r="O235" s="58"/>
+      <c r="P235" s="58"/>
+      <c r="Q235" s="58"/>
       <c r="R235" s="9"/>
       <c r="S235" s="9"/>
       <c r="T235" s="9"/>
@@ -13191,35 +13206,35 @@
       <c r="Z235" s="9"/>
     </row>
     <row r="236">
-      <c r="A236" s="58" t="s">
+      <c r="A236" s="59" t="s">
         <v>135</v>
       </c>
-      <c r="B236" s="58" t="s">
+      <c r="B236" s="59" t="s">
         <v>650</v>
       </c>
-      <c r="C236" s="58" t="s">
+      <c r="C236" s="59" t="s">
         <v>651</v>
       </c>
-      <c r="D236" s="58" t="s">
+      <c r="D236" s="59" t="s">
         <v>652</v>
       </c>
-      <c r="E236" s="58" t="s">
+      <c r="E236" s="59" t="s">
         <v>139</v>
       </c>
       <c r="F236" s="35" t="s">
         <v>302</v>
       </c>
-      <c r="G236" s="59"/>
-      <c r="H236" s="59"/>
-      <c r="I236" s="59"/>
-      <c r="J236" s="59"/>
-      <c r="K236" s="59"/>
-      <c r="L236" s="59"/>
-      <c r="M236" s="59"/>
-      <c r="N236" s="59"/>
-      <c r="O236" s="59"/>
-      <c r="P236" s="59"/>
-      <c r="Q236" s="59"/>
+      <c r="G236" s="58"/>
+      <c r="H236" s="58"/>
+      <c r="I236" s="58"/>
+      <c r="J236" s="58"/>
+      <c r="K236" s="58"/>
+      <c r="L236" s="58"/>
+      <c r="M236" s="58"/>
+      <c r="N236" s="58"/>
+      <c r="O236" s="58"/>
+      <c r="P236" s="58"/>
+      <c r="Q236" s="58"/>
       <c r="R236" s="9"/>
       <c r="S236" s="9"/>
       <c r="T236" s="9"/>
@@ -13231,31 +13246,31 @@
       <c r="Z236" s="9"/>
     </row>
     <row r="237">
-      <c r="A237" s="58" t="s">
+      <c r="A237" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B237" s="58" t="s">
+      <c r="B237" s="59" t="s">
         <v>653</v>
       </c>
-      <c r="C237" s="58" t="s">
+      <c r="C237" s="59" t="s">
         <v>654</v>
       </c>
-      <c r="D237" s="58" t="s">
+      <c r="D237" s="59" t="s">
         <v>655</v>
       </c>
-      <c r="E237" s="59"/>
-      <c r="F237" s="59"/>
-      <c r="G237" s="59"/>
-      <c r="H237" s="59"/>
-      <c r="I237" s="59"/>
-      <c r="J237" s="59"/>
-      <c r="K237" s="59"/>
-      <c r="L237" s="59"/>
-      <c r="M237" s="59"/>
-      <c r="N237" s="59"/>
-      <c r="O237" s="59"/>
-      <c r="P237" s="59"/>
-      <c r="Q237" s="59"/>
+      <c r="E237" s="58"/>
+      <c r="F237" s="58"/>
+      <c r="G237" s="58"/>
+      <c r="H237" s="58"/>
+      <c r="I237" s="58"/>
+      <c r="J237" s="58"/>
+      <c r="K237" s="58"/>
+      <c r="L237" s="58"/>
+      <c r="M237" s="58"/>
+      <c r="N237" s="58"/>
+      <c r="O237" s="58"/>
+      <c r="P237" s="58"/>
+      <c r="Q237" s="58"/>
       <c r="R237" s="9"/>
       <c r="S237" s="9"/>
       <c r="T237" s="9"/>
@@ -13267,31 +13282,31 @@
       <c r="Z237" s="9"/>
     </row>
     <row r="238">
-      <c r="A238" s="58" t="s">
+      <c r="A238" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B238" s="58" t="s">
+      <c r="B238" s="59" t="s">
         <v>656</v>
       </c>
-      <c r="C238" s="58" t="s">
+      <c r="C238" s="59" t="s">
         <v>657</v>
       </c>
-      <c r="D238" s="58" t="s">
+      <c r="D238" s="59" t="s">
         <v>658</v>
       </c>
-      <c r="E238" s="58"/>
-      <c r="F238" s="58"/>
-      <c r="G238" s="58"/>
-      <c r="H238" s="58"/>
-      <c r="I238" s="59"/>
-      <c r="J238" s="59"/>
-      <c r="K238" s="59"/>
-      <c r="L238" s="59"/>
-      <c r="M238" s="59"/>
-      <c r="N238" s="59"/>
-      <c r="O238" s="59"/>
-      <c r="P238" s="59"/>
-      <c r="Q238" s="59"/>
+      <c r="E238" s="59"/>
+      <c r="F238" s="59"/>
+      <c r="G238" s="59"/>
+      <c r="H238" s="59"/>
+      <c r="I238" s="58"/>
+      <c r="J238" s="58"/>
+      <c r="K238" s="58"/>
+      <c r="L238" s="58"/>
+      <c r="M238" s="58"/>
+      <c r="N238" s="58"/>
+      <c r="O238" s="58"/>
+      <c r="P238" s="58"/>
+      <c r="Q238" s="58"/>
       <c r="R238" s="9"/>
       <c r="S238" s="9"/>
       <c r="T238" s="9"/>
@@ -13303,31 +13318,31 @@
       <c r="Z238" s="9"/>
     </row>
     <row r="239">
-      <c r="A239" s="58" t="s">
+      <c r="A239" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B239" s="58" t="s">
+      <c r="B239" s="59" t="s">
         <v>659</v>
       </c>
-      <c r="C239" s="58" t="s">
+      <c r="C239" s="59" t="s">
         <v>660</v>
       </c>
-      <c r="D239" s="58" t="s">
+      <c r="D239" s="59" t="s">
         <v>661</v>
       </c>
-      <c r="E239" s="59"/>
-      <c r="F239" s="59"/>
-      <c r="G239" s="59"/>
-      <c r="H239" s="59"/>
-      <c r="I239" s="59"/>
-      <c r="J239" s="59"/>
-      <c r="K239" s="59"/>
-      <c r="L239" s="59"/>
-      <c r="M239" s="59"/>
-      <c r="N239" s="59"/>
-      <c r="O239" s="59"/>
-      <c r="P239" s="59"/>
-      <c r="Q239" s="59"/>
+      <c r="E239" s="58"/>
+      <c r="F239" s="58"/>
+      <c r="G239" s="58"/>
+      <c r="H239" s="58"/>
+      <c r="I239" s="58"/>
+      <c r="J239" s="58"/>
+      <c r="K239" s="58"/>
+      <c r="L239" s="58"/>
+      <c r="M239" s="58"/>
+      <c r="N239" s="58"/>
+      <c r="O239" s="58"/>
+      <c r="P239" s="58"/>
+      <c r="Q239" s="58"/>
       <c r="R239" s="9"/>
       <c r="S239" s="9"/>
       <c r="T239" s="9"/>
@@ -13339,31 +13354,31 @@
       <c r="Z239" s="9"/>
     </row>
     <row r="240">
-      <c r="A240" s="58" t="s">
+      <c r="A240" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B240" s="58" t="s">
+      <c r="B240" s="59" t="s">
         <v>662</v>
       </c>
-      <c r="C240" s="58" t="s">
+      <c r="C240" s="59" t="s">
         <v>663</v>
       </c>
-      <c r="D240" s="58" t="s">
+      <c r="D240" s="59" t="s">
         <v>664</v>
       </c>
-      <c r="E240" s="59"/>
-      <c r="F240" s="59"/>
-      <c r="G240" s="59"/>
-      <c r="H240" s="59"/>
-      <c r="I240" s="59"/>
-      <c r="J240" s="59"/>
-      <c r="K240" s="59"/>
-      <c r="L240" s="59"/>
-      <c r="M240" s="59"/>
-      <c r="N240" s="59"/>
-      <c r="O240" s="59"/>
-      <c r="P240" s="59"/>
-      <c r="Q240" s="59"/>
+      <c r="E240" s="58"/>
+      <c r="F240" s="58"/>
+      <c r="G240" s="58"/>
+      <c r="H240" s="58"/>
+      <c r="I240" s="58"/>
+      <c r="J240" s="58"/>
+      <c r="K240" s="58"/>
+      <c r="L240" s="58"/>
+      <c r="M240" s="58"/>
+      <c r="N240" s="58"/>
+      <c r="O240" s="58"/>
+      <c r="P240" s="58"/>
+      <c r="Q240" s="58"/>
       <c r="R240" s="9"/>
       <c r="S240" s="9"/>
       <c r="T240" s="9"/>
@@ -13375,35 +13390,35 @@
       <c r="Z240" s="9"/>
     </row>
     <row r="241">
-      <c r="A241" s="58" t="s">
+      <c r="A241" s="59" t="s">
         <v>135</v>
       </c>
-      <c r="B241" s="58" t="s">
+      <c r="B241" s="59" t="s">
         <v>665</v>
       </c>
-      <c r="C241" s="58" t="s">
+      <c r="C241" s="59" t="s">
         <v>666</v>
       </c>
-      <c r="D241" s="58" t="s">
+      <c r="D241" s="59" t="s">
         <v>667</v>
       </c>
-      <c r="E241" s="58" t="s">
+      <c r="E241" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="F241" s="58" t="s">
+      <c r="F241" s="59" t="s">
         <v>302</v>
       </c>
-      <c r="G241" s="59"/>
-      <c r="H241" s="59"/>
-      <c r="I241" s="59"/>
-      <c r="J241" s="59"/>
-      <c r="K241" s="59"/>
-      <c r="L241" s="59"/>
-      <c r="M241" s="59"/>
-      <c r="N241" s="59"/>
-      <c r="O241" s="59"/>
-      <c r="P241" s="59"/>
-      <c r="Q241" s="59"/>
+      <c r="G241" s="58"/>
+      <c r="H241" s="58"/>
+      <c r="I241" s="58"/>
+      <c r="J241" s="58"/>
+      <c r="K241" s="58"/>
+      <c r="L241" s="58"/>
+      <c r="M241" s="58"/>
+      <c r="N241" s="58"/>
+      <c r="O241" s="58"/>
+      <c r="P241" s="58"/>
+      <c r="Q241" s="58"/>
       <c r="R241" s="9"/>
       <c r="S241" s="9"/>
       <c r="T241" s="9"/>
@@ -13415,33 +13430,33 @@
       <c r="Z241" s="9"/>
     </row>
     <row r="242">
-      <c r="A242" s="58" t="s">
+      <c r="A242" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B242" s="58" t="s">
+      <c r="B242" s="59" t="s">
         <v>668</v>
       </c>
-      <c r="C242" s="58" t="s">
+      <c r="C242" s="59" t="s">
         <v>669</v>
       </c>
-      <c r="D242" s="58" t="s">
+      <c r="D242" s="59" t="s">
         <v>670</v>
       </c>
-      <c r="E242" s="58"/>
-      <c r="F242" s="58" t="s">
+      <c r="E242" s="59"/>
+      <c r="F242" s="59" t="s">
         <v>671</v>
       </c>
-      <c r="G242" s="59"/>
-      <c r="H242" s="59"/>
-      <c r="I242" s="59"/>
-      <c r="J242" s="59"/>
-      <c r="K242" s="59"/>
-      <c r="L242" s="59"/>
-      <c r="M242" s="59"/>
-      <c r="N242" s="59"/>
-      <c r="O242" s="59"/>
-      <c r="P242" s="59"/>
-      <c r="Q242" s="59"/>
+      <c r="G242" s="58"/>
+      <c r="H242" s="58"/>
+      <c r="I242" s="58"/>
+      <c r="J242" s="58"/>
+      <c r="K242" s="58"/>
+      <c r="L242" s="58"/>
+      <c r="M242" s="58"/>
+      <c r="N242" s="58"/>
+      <c r="O242" s="58"/>
+      <c r="P242" s="58"/>
+      <c r="Q242" s="58"/>
       <c r="R242" s="9"/>
       <c r="S242" s="9"/>
       <c r="T242" s="9"/>
@@ -13453,35 +13468,35 @@
       <c r="Z242" s="9"/>
     </row>
     <row r="243">
-      <c r="A243" s="58" t="s">
+      <c r="A243" s="59" t="s">
         <v>672</v>
       </c>
-      <c r="B243" s="58" t="s">
+      <c r="B243" s="59" t="s">
         <v>673</v>
       </c>
-      <c r="C243" s="58" t="s">
+      <c r="C243" s="59" t="s">
         <v>674</v>
       </c>
-      <c r="D243" s="58" t="s">
+      <c r="D243" s="59" t="s">
         <v>675</v>
       </c>
-      <c r="E243" s="58" t="s">
+      <c r="E243" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="F243" s="58" t="s">
+      <c r="F243" s="59" t="s">
         <v>676</v>
       </c>
-      <c r="G243" s="59"/>
-      <c r="H243" s="59"/>
-      <c r="I243" s="59"/>
-      <c r="J243" s="59"/>
-      <c r="K243" s="59"/>
-      <c r="L243" s="59"/>
-      <c r="M243" s="59"/>
-      <c r="N243" s="59"/>
-      <c r="O243" s="59"/>
-      <c r="P243" s="59"/>
-      <c r="Q243" s="59"/>
+      <c r="G243" s="58"/>
+      <c r="H243" s="58"/>
+      <c r="I243" s="58"/>
+      <c r="J243" s="58"/>
+      <c r="K243" s="58"/>
+      <c r="L243" s="58"/>
+      <c r="M243" s="58"/>
+      <c r="N243" s="58"/>
+      <c r="O243" s="58"/>
+      <c r="P243" s="58"/>
+      <c r="Q243" s="58"/>
       <c r="R243" s="9"/>
       <c r="S243" s="9"/>
       <c r="T243" s="9"/>
@@ -13493,31 +13508,31 @@
       <c r="Z243" s="9"/>
     </row>
     <row r="244">
-      <c r="A244" s="58" t="s">
+      <c r="A244" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B244" s="58" t="s">
+      <c r="B244" s="59" t="s">
         <v>677</v>
       </c>
-      <c r="C244" s="58" t="s">
+      <c r="C244" s="59" t="s">
         <v>678</v>
       </c>
-      <c r="D244" s="58" t="s">
+      <c r="D244" s="59" t="s">
         <v>679</v>
       </c>
-      <c r="E244" s="59"/>
+      <c r="E244" s="58"/>
       <c r="F244" s="61"/>
-      <c r="G244" s="59"/>
-      <c r="H244" s="59"/>
-      <c r="I244" s="59"/>
-      <c r="J244" s="59"/>
-      <c r="K244" s="59"/>
-      <c r="L244" s="59"/>
-      <c r="M244" s="59"/>
-      <c r="N244" s="59"/>
-      <c r="O244" s="59"/>
-      <c r="P244" s="59"/>
-      <c r="Q244" s="59"/>
+      <c r="G244" s="58"/>
+      <c r="H244" s="58"/>
+      <c r="I244" s="58"/>
+      <c r="J244" s="58"/>
+      <c r="K244" s="58"/>
+      <c r="L244" s="58"/>
+      <c r="M244" s="58"/>
+      <c r="N244" s="58"/>
+      <c r="O244" s="58"/>
+      <c r="P244" s="58"/>
+      <c r="Q244" s="58"/>
       <c r="R244" s="9"/>
       <c r="S244" s="9"/>
       <c r="T244" s="9"/>
@@ -13529,31 +13544,31 @@
       <c r="Z244" s="9"/>
     </row>
     <row r="245">
-      <c r="A245" s="58" t="s">
+      <c r="A245" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B245" s="58" t="s">
+      <c r="B245" s="59" t="s">
         <v>680</v>
       </c>
-      <c r="C245" s="58" t="s">
+      <c r="C245" s="59" t="s">
         <v>681</v>
       </c>
-      <c r="D245" s="58" t="s">
+      <c r="D245" s="59" t="s">
         <v>682</v>
       </c>
-      <c r="E245" s="59"/>
+      <c r="E245" s="58"/>
       <c r="F245" s="61"/>
-      <c r="G245" s="59"/>
-      <c r="H245" s="59"/>
-      <c r="I245" s="59"/>
-      <c r="J245" s="59"/>
-      <c r="K245" s="59"/>
-      <c r="L245" s="59"/>
-      <c r="M245" s="59"/>
-      <c r="N245" s="59"/>
-      <c r="O245" s="59"/>
-      <c r="P245" s="59"/>
-      <c r="Q245" s="59"/>
+      <c r="G245" s="58"/>
+      <c r="H245" s="58"/>
+      <c r="I245" s="58"/>
+      <c r="J245" s="58"/>
+      <c r="K245" s="58"/>
+      <c r="L245" s="58"/>
+      <c r="M245" s="58"/>
+      <c r="N245" s="58"/>
+      <c r="O245" s="58"/>
+      <c r="P245" s="58"/>
+      <c r="Q245" s="58"/>
       <c r="R245" s="9"/>
       <c r="S245" s="9"/>
       <c r="T245" s="9"/>
@@ -13565,31 +13580,31 @@
       <c r="Z245" s="9"/>
     </row>
     <row r="246">
-      <c r="A246" s="58" t="s">
+      <c r="A246" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B246" s="58" t="s">
+      <c r="B246" s="59" t="s">
         <v>683</v>
       </c>
-      <c r="C246" s="58" t="s">
+      <c r="C246" s="59" t="s">
         <v>684</v>
       </c>
-      <c r="D246" s="58" t="s">
+      <c r="D246" s="59" t="s">
         <v>305</v>
       </c>
-      <c r="E246" s="59"/>
-      <c r="F246" s="59"/>
-      <c r="G246" s="59"/>
-      <c r="H246" s="59"/>
-      <c r="I246" s="59"/>
-      <c r="J246" s="59"/>
-      <c r="K246" s="59"/>
-      <c r="L246" s="59"/>
-      <c r="M246" s="59"/>
-      <c r="N246" s="59"/>
-      <c r="O246" s="59"/>
-      <c r="P246" s="59"/>
-      <c r="Q246" s="59"/>
+      <c r="E246" s="58"/>
+      <c r="F246" s="58"/>
+      <c r="G246" s="58"/>
+      <c r="H246" s="58"/>
+      <c r="I246" s="58"/>
+      <c r="J246" s="58"/>
+      <c r="K246" s="58"/>
+      <c r="L246" s="58"/>
+      <c r="M246" s="58"/>
+      <c r="N246" s="58"/>
+      <c r="O246" s="58"/>
+      <c r="P246" s="58"/>
+      <c r="Q246" s="58"/>
       <c r="R246" s="9"/>
       <c r="S246" s="9"/>
       <c r="T246" s="9"/>
@@ -13601,27 +13616,27 @@
       <c r="Z246" s="9"/>
     </row>
     <row r="247">
-      <c r="A247" s="58" t="s">
+      <c r="A247" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="B247" s="58" t="s">
+      <c r="B247" s="59" t="s">
         <v>647</v>
       </c>
-      <c r="C247" s="59"/>
-      <c r="D247" s="59"/>
-      <c r="E247" s="59"/>
-      <c r="F247" s="59"/>
-      <c r="G247" s="59"/>
-      <c r="H247" s="59"/>
-      <c r="I247" s="59"/>
-      <c r="J247" s="59"/>
-      <c r="K247" s="59"/>
-      <c r="L247" s="59"/>
-      <c r="M247" s="59"/>
-      <c r="N247" s="59"/>
-      <c r="O247" s="59"/>
-      <c r="P247" s="59"/>
-      <c r="Q247" s="59"/>
+      <c r="C247" s="58"/>
+      <c r="D247" s="58"/>
+      <c r="E247" s="58"/>
+      <c r="F247" s="58"/>
+      <c r="G247" s="58"/>
+      <c r="H247" s="58"/>
+      <c r="I247" s="58"/>
+      <c r="J247" s="58"/>
+      <c r="K247" s="58"/>
+      <c r="L247" s="58"/>
+      <c r="M247" s="58"/>
+      <c r="N247" s="58"/>
+      <c r="O247" s="58"/>
+      <c r="P247" s="58"/>
+      <c r="Q247" s="58"/>
       <c r="R247" s="9"/>
       <c r="S247" s="9"/>
       <c r="T247" s="9"/>
@@ -13633,33 +13648,33 @@
       <c r="Z247" s="9"/>
     </row>
     <row r="248">
-      <c r="A248" s="58" t="s">
+      <c r="A248" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="B248" s="58" t="s">
+      <c r="B248" s="59" t="s">
         <v>685</v>
       </c>
-      <c r="C248" s="58" t="s">
+      <c r="C248" s="59" t="s">
         <v>686</v>
       </c>
-      <c r="D248" s="58" t="s">
+      <c r="D248" s="59" t="s">
         <v>687</v>
       </c>
-      <c r="E248" s="59"/>
+      <c r="E248" s="58"/>
       <c r="F248" s="35" t="s">
         <v>576</v>
       </c>
-      <c r="G248" s="59"/>
-      <c r="H248" s="59"/>
-      <c r="I248" s="59"/>
-      <c r="J248" s="59"/>
-      <c r="K248" s="59"/>
-      <c r="L248" s="59"/>
-      <c r="M248" s="59"/>
-      <c r="N248" s="59"/>
-      <c r="O248" s="59"/>
-      <c r="P248" s="59"/>
-      <c r="Q248" s="59"/>
+      <c r="G248" s="58"/>
+      <c r="H248" s="58"/>
+      <c r="I248" s="58"/>
+      <c r="J248" s="58"/>
+      <c r="K248" s="58"/>
+      <c r="L248" s="58"/>
+      <c r="M248" s="58"/>
+      <c r="N248" s="58"/>
+      <c r="O248" s="58"/>
+      <c r="P248" s="58"/>
+      <c r="Q248" s="58"/>
       <c r="R248" s="9"/>
       <c r="S248" s="9"/>
       <c r="T248" s="9"/>
@@ -13671,31 +13686,31 @@
       <c r="Z248" s="9"/>
     </row>
     <row r="249">
-      <c r="A249" s="58" t="s">
+      <c r="A249" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B249" s="58" t="s">
+      <c r="B249" s="59" t="s">
         <v>688</v>
       </c>
-      <c r="C249" s="58" t="s">
+      <c r="C249" s="59" t="s">
         <v>689</v>
       </c>
-      <c r="D249" s="58" t="s">
+      <c r="D249" s="59" t="s">
         <v>690</v>
       </c>
-      <c r="E249" s="58"/>
-      <c r="F249" s="58"/>
-      <c r="G249" s="58"/>
-      <c r="H249" s="58"/>
-      <c r="I249" s="58"/>
-      <c r="J249" s="58"/>
-      <c r="K249" s="58"/>
-      <c r="L249" s="59"/>
-      <c r="M249" s="59"/>
-      <c r="N249" s="59"/>
-      <c r="O249" s="59"/>
-      <c r="P249" s="59"/>
-      <c r="Q249" s="59"/>
+      <c r="E249" s="59"/>
+      <c r="F249" s="59"/>
+      <c r="G249" s="59"/>
+      <c r="H249" s="59"/>
+      <c r="I249" s="59"/>
+      <c r="J249" s="59"/>
+      <c r="K249" s="59"/>
+      <c r="L249" s="58"/>
+      <c r="M249" s="58"/>
+      <c r="N249" s="58"/>
+      <c r="O249" s="58"/>
+      <c r="P249" s="58"/>
+      <c r="Q249" s="58"/>
       <c r="R249" s="9"/>
       <c r="S249" s="9"/>
       <c r="T249" s="9"/>
@@ -13707,31 +13722,31 @@
       <c r="Z249" s="9"/>
     </row>
     <row r="250">
-      <c r="A250" s="58" t="s">
+      <c r="A250" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="B250" s="58" t="s">
+      <c r="B250" s="59" t="s">
         <v>691</v>
       </c>
-      <c r="C250" s="58" t="s">
+      <c r="C250" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="D250" s="59"/>
-      <c r="E250" s="59"/>
-      <c r="F250" s="59"/>
-      <c r="G250" s="58" t="s">
+      <c r="D250" s="58"/>
+      <c r="E250" s="58"/>
+      <c r="F250" s="58"/>
+      <c r="G250" s="59" t="s">
         <v>164</v>
       </c>
-      <c r="H250" s="59"/>
-      <c r="I250" s="59"/>
-      <c r="J250" s="59"/>
-      <c r="K250" s="59"/>
-      <c r="L250" s="59"/>
-      <c r="M250" s="59"/>
-      <c r="N250" s="59"/>
-      <c r="O250" s="59"/>
-      <c r="P250" s="59"/>
-      <c r="Q250" s="59"/>
+      <c r="H250" s="58"/>
+      <c r="I250" s="58"/>
+      <c r="J250" s="58"/>
+      <c r="K250" s="58"/>
+      <c r="L250" s="58"/>
+      <c r="M250" s="58"/>
+      <c r="N250" s="58"/>
+      <c r="O250" s="58"/>
+      <c r="P250" s="58"/>
+      <c r="Q250" s="58"/>
       <c r="R250" s="9"/>
       <c r="S250" s="9"/>
       <c r="T250" s="9"/>
@@ -13743,33 +13758,33 @@
       <c r="Z250" s="9"/>
     </row>
     <row r="251">
-      <c r="A251" s="58" t="s">
+      <c r="A251" s="59" t="s">
         <v>135</v>
       </c>
-      <c r="B251" s="58" t="s">
+      <c r="B251" s="59" t="s">
         <v>692</v>
       </c>
-      <c r="C251" s="58" t="s">
+      <c r="C251" s="59" t="s">
         <v>693</v>
       </c>
-      <c r="D251" s="58" t="s">
+      <c r="D251" s="59" t="s">
         <v>694</v>
       </c>
-      <c r="E251" s="58" t="s">
+      <c r="E251" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="F251" s="59"/>
-      <c r="G251" s="58"/>
-      <c r="H251" s="59"/>
-      <c r="I251" s="59"/>
-      <c r="J251" s="59"/>
-      <c r="K251" s="59"/>
-      <c r="L251" s="59"/>
-      <c r="M251" s="59"/>
-      <c r="N251" s="59"/>
-      <c r="O251" s="59"/>
-      <c r="P251" s="59"/>
-      <c r="Q251" s="59"/>
+      <c r="F251" s="58"/>
+      <c r="G251" s="59"/>
+      <c r="H251" s="58"/>
+      <c r="I251" s="58"/>
+      <c r="J251" s="58"/>
+      <c r="K251" s="58"/>
+      <c r="L251" s="58"/>
+      <c r="M251" s="58"/>
+      <c r="N251" s="58"/>
+      <c r="O251" s="58"/>
+      <c r="P251" s="58"/>
+      <c r="Q251" s="58"/>
       <c r="R251" s="9"/>
       <c r="S251" s="9"/>
       <c r="T251" s="9"/>
@@ -13781,33 +13796,33 @@
       <c r="Z251" s="9"/>
     </row>
     <row r="252">
-      <c r="A252" s="58" t="s">
+      <c r="A252" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B252" s="58" t="s">
+      <c r="B252" s="59" t="s">
         <v>695</v>
       </c>
-      <c r="C252" s="58" t="s">
+      <c r="C252" s="59" t="s">
         <v>696</v>
       </c>
-      <c r="D252" s="58" t="s">
+      <c r="D252" s="59" t="s">
         <v>697</v>
       </c>
-      <c r="E252" s="59"/>
-      <c r="F252" s="58" t="s">
+      <c r="E252" s="58"/>
+      <c r="F252" s="59" t="s">
         <v>698</v>
       </c>
-      <c r="G252" s="59"/>
-      <c r="H252" s="59"/>
-      <c r="I252" s="59"/>
-      <c r="J252" s="59"/>
-      <c r="K252" s="59"/>
-      <c r="L252" s="59"/>
-      <c r="M252" s="59"/>
-      <c r="N252" s="59"/>
-      <c r="O252" s="59"/>
-      <c r="P252" s="59"/>
-      <c r="Q252" s="59"/>
+      <c r="G252" s="58"/>
+      <c r="H252" s="58"/>
+      <c r="I252" s="58"/>
+      <c r="J252" s="58"/>
+      <c r="K252" s="58"/>
+      <c r="L252" s="58"/>
+      <c r="M252" s="58"/>
+      <c r="N252" s="58"/>
+      <c r="O252" s="58"/>
+      <c r="P252" s="58"/>
+      <c r="Q252" s="58"/>
       <c r="R252" s="9"/>
       <c r="S252" s="9"/>
       <c r="T252" s="9"/>
@@ -13819,27 +13834,27 @@
       <c r="Z252" s="9"/>
     </row>
     <row r="253">
-      <c r="A253" s="58" t="s">
+      <c r="A253" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="B253" s="58" t="s">
+      <c r="B253" s="59" t="s">
         <v>691</v>
       </c>
-      <c r="C253" s="59"/>
-      <c r="D253" s="59"/>
-      <c r="E253" s="59"/>
-      <c r="F253" s="59"/>
-      <c r="G253" s="59"/>
-      <c r="H253" s="59"/>
-      <c r="I253" s="59"/>
-      <c r="J253" s="59"/>
-      <c r="K253" s="59"/>
-      <c r="L253" s="59"/>
-      <c r="M253" s="59"/>
-      <c r="N253" s="59"/>
-      <c r="O253" s="59"/>
-      <c r="P253" s="59"/>
-      <c r="Q253" s="59"/>
+      <c r="C253" s="58"/>
+      <c r="D253" s="58"/>
+      <c r="E253" s="58"/>
+      <c r="F253" s="58"/>
+      <c r="G253" s="58"/>
+      <c r="H253" s="58"/>
+      <c r="I253" s="58"/>
+      <c r="J253" s="58"/>
+      <c r="K253" s="58"/>
+      <c r="L253" s="58"/>
+      <c r="M253" s="58"/>
+      <c r="N253" s="58"/>
+      <c r="O253" s="58"/>
+      <c r="P253" s="58"/>
+      <c r="Q253" s="58"/>
       <c r="R253" s="9"/>
       <c r="S253" s="9"/>
       <c r="T253" s="9"/>
@@ -13851,27 +13866,27 @@
       <c r="Z253" s="9"/>
     </row>
     <row r="254">
-      <c r="A254" s="58" t="s">
+      <c r="A254" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="B254" s="58" t="s">
+      <c r="B254" s="59" t="s">
         <v>685</v>
       </c>
-      <c r="C254" s="59"/>
-      <c r="D254" s="59"/>
-      <c r="E254" s="59"/>
-      <c r="F254" s="59"/>
-      <c r="G254" s="59"/>
-      <c r="H254" s="59"/>
-      <c r="I254" s="59"/>
-      <c r="J254" s="59"/>
-      <c r="K254" s="59"/>
-      <c r="L254" s="59"/>
-      <c r="M254" s="59"/>
-      <c r="N254" s="59"/>
-      <c r="O254" s="59"/>
-      <c r="P254" s="59"/>
-      <c r="Q254" s="59"/>
+      <c r="C254" s="58"/>
+      <c r="D254" s="58"/>
+      <c r="E254" s="58"/>
+      <c r="F254" s="58"/>
+      <c r="G254" s="58"/>
+      <c r="H254" s="58"/>
+      <c r="I254" s="58"/>
+      <c r="J254" s="58"/>
+      <c r="K254" s="58"/>
+      <c r="L254" s="58"/>
+      <c r="M254" s="58"/>
+      <c r="N254" s="58"/>
+      <c r="O254" s="58"/>
+      <c r="P254" s="58"/>
+      <c r="Q254" s="58"/>
       <c r="R254" s="9"/>
       <c r="S254" s="9"/>
       <c r="T254" s="9"/>
@@ -13883,35 +13898,35 @@
       <c r="Z254" s="9"/>
     </row>
     <row r="255">
-      <c r="A255" s="58" t="s">
+      <c r="A255" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="B255" s="58" t="s">
+      <c r="B255" s="59" t="s">
         <v>699</v>
       </c>
-      <c r="C255" s="58" t="s">
+      <c r="C255" s="59" t="s">
         <v>700</v>
       </c>
-      <c r="D255" s="58" t="s">
+      <c r="D255" s="59" t="s">
         <v>701</v>
       </c>
-      <c r="E255" s="59"/>
+      <c r="E255" s="58"/>
       <c r="F255" s="13" t="s">
         <v>702</v>
       </c>
-      <c r="G255" s="58" t="s">
+      <c r="G255" s="59" t="s">
         <v>164</v>
       </c>
-      <c r="H255" s="59"/>
-      <c r="I255" s="59"/>
-      <c r="J255" s="59"/>
-      <c r="K255" s="59"/>
-      <c r="L255" s="59"/>
-      <c r="M255" s="59"/>
-      <c r="N255" s="59"/>
-      <c r="O255" s="59"/>
-      <c r="P255" s="59"/>
-      <c r="Q255" s="59"/>
+      <c r="H255" s="58"/>
+      <c r="I255" s="58"/>
+      <c r="J255" s="58"/>
+      <c r="K255" s="58"/>
+      <c r="L255" s="58"/>
+      <c r="M255" s="58"/>
+      <c r="N255" s="58"/>
+      <c r="O255" s="58"/>
+      <c r="P255" s="58"/>
+      <c r="Q255" s="58"/>
       <c r="R255" s="9"/>
       <c r="S255" s="9"/>
       <c r="T255" s="9"/>
@@ -13923,31 +13938,31 @@
       <c r="Z255" s="9"/>
     </row>
     <row r="256">
-      <c r="A256" s="58" t="s">
+      <c r="A256" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B256" s="58" t="s">
+      <c r="B256" s="59" t="s">
         <v>703</v>
       </c>
-      <c r="C256" s="58" t="s">
+      <c r="C256" s="59" t="s">
         <v>704</v>
       </c>
       <c r="D256" s="2" t="s">
         <v>705</v>
       </c>
-      <c r="E256" s="59"/>
+      <c r="E256" s="58"/>
       <c r="F256" s="35"/>
-      <c r="G256" s="59"/>
-      <c r="H256" s="59"/>
-      <c r="I256" s="59"/>
-      <c r="J256" s="59"/>
-      <c r="K256" s="59"/>
-      <c r="L256" s="59"/>
-      <c r="M256" s="59"/>
-      <c r="N256" s="59"/>
-      <c r="O256" s="59"/>
-      <c r="P256" s="59"/>
-      <c r="Q256" s="59"/>
+      <c r="G256" s="58"/>
+      <c r="H256" s="58"/>
+      <c r="I256" s="58"/>
+      <c r="J256" s="58"/>
+      <c r="K256" s="58"/>
+      <c r="L256" s="58"/>
+      <c r="M256" s="58"/>
+      <c r="N256" s="58"/>
+      <c r="O256" s="58"/>
+      <c r="P256" s="58"/>
+      <c r="Q256" s="58"/>
       <c r="R256" s="9"/>
       <c r="S256" s="9"/>
       <c r="T256" s="9"/>
@@ -13959,27 +13974,27 @@
       <c r="Z256" s="9"/>
     </row>
     <row r="257">
-      <c r="A257" s="58" t="s">
+      <c r="A257" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="B257" s="58" t="s">
+      <c r="B257" s="59" t="s">
         <v>706</v>
       </c>
-      <c r="C257" s="58"/>
-      <c r="D257" s="58"/>
-      <c r="E257" s="59"/>
+      <c r="C257" s="59"/>
+      <c r="D257" s="59"/>
+      <c r="E257" s="58"/>
       <c r="F257" s="35"/>
-      <c r="G257" s="59"/>
-      <c r="H257" s="59"/>
-      <c r="I257" s="59"/>
-      <c r="J257" s="59"/>
-      <c r="K257" s="59"/>
-      <c r="L257" s="59"/>
-      <c r="M257" s="59"/>
-      <c r="N257" s="59"/>
-      <c r="O257" s="59"/>
-      <c r="P257" s="59"/>
-      <c r="Q257" s="59"/>
+      <c r="G257" s="58"/>
+      <c r="H257" s="58"/>
+      <c r="I257" s="58"/>
+      <c r="J257" s="58"/>
+      <c r="K257" s="58"/>
+      <c r="L257" s="58"/>
+      <c r="M257" s="58"/>
+      <c r="N257" s="58"/>
+      <c r="O257" s="58"/>
+      <c r="P257" s="58"/>
+      <c r="Q257" s="58"/>
       <c r="R257" s="9"/>
       <c r="S257" s="9"/>
       <c r="T257" s="9"/>
@@ -13991,33 +14006,33 @@
       <c r="Z257" s="9"/>
     </row>
     <row r="258">
-      <c r="A258" s="58" t="s">
+      <c r="A258" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="B258" s="58" t="s">
+      <c r="B258" s="59" t="s">
         <v>707</v>
       </c>
-      <c r="C258" s="58" t="s">
+      <c r="C258" s="59" t="s">
         <v>708</v>
       </c>
-      <c r="D258" s="58" t="s">
+      <c r="D258" s="59" t="s">
         <v>709</v>
       </c>
-      <c r="E258" s="59"/>
+      <c r="E258" s="58"/>
       <c r="F258" s="35" t="s">
         <v>710</v>
       </c>
-      <c r="G258" s="59"/>
-      <c r="H258" s="59"/>
-      <c r="I258" s="59"/>
-      <c r="J258" s="59"/>
-      <c r="K258" s="59"/>
-      <c r="L258" s="59"/>
-      <c r="M258" s="59"/>
-      <c r="N258" s="59"/>
-      <c r="O258" s="59"/>
-      <c r="P258" s="59"/>
-      <c r="Q258" s="59"/>
+      <c r="G258" s="58"/>
+      <c r="H258" s="58"/>
+      <c r="I258" s="58"/>
+      <c r="J258" s="58"/>
+      <c r="K258" s="58"/>
+      <c r="L258" s="58"/>
+      <c r="M258" s="58"/>
+      <c r="N258" s="58"/>
+      <c r="O258" s="58"/>
+      <c r="P258" s="58"/>
+      <c r="Q258" s="58"/>
       <c r="R258" s="9"/>
       <c r="S258" s="9"/>
       <c r="T258" s="9"/>
@@ -14029,33 +14044,33 @@
       <c r="Z258" s="9"/>
     </row>
     <row r="259">
-      <c r="A259" s="58" t="s">
+      <c r="A259" s="59" t="s">
         <v>135</v>
       </c>
-      <c r="B259" s="58" t="s">
+      <c r="B259" s="59" t="s">
         <v>711</v>
       </c>
-      <c r="C259" s="58" t="s">
+      <c r="C259" s="59" t="s">
         <v>712</v>
       </c>
-      <c r="D259" s="58" t="s">
+      <c r="D259" s="59" t="s">
         <v>713</v>
       </c>
-      <c r="E259" s="58" t="s">
+      <c r="E259" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="F259" s="59"/>
-      <c r="G259" s="59"/>
-      <c r="H259" s="59"/>
-      <c r="I259" s="59"/>
-      <c r="J259" s="59"/>
-      <c r="K259" s="59"/>
-      <c r="L259" s="59"/>
-      <c r="M259" s="59"/>
-      <c r="N259" s="59"/>
-      <c r="O259" s="59"/>
-      <c r="P259" s="59"/>
-      <c r="Q259" s="59"/>
+      <c r="F259" s="58"/>
+      <c r="G259" s="58"/>
+      <c r="H259" s="58"/>
+      <c r="I259" s="58"/>
+      <c r="J259" s="58"/>
+      <c r="K259" s="58"/>
+      <c r="L259" s="58"/>
+      <c r="M259" s="58"/>
+      <c r="N259" s="58"/>
+      <c r="O259" s="58"/>
+      <c r="P259" s="58"/>
+      <c r="Q259" s="58"/>
       <c r="R259" s="9"/>
       <c r="S259" s="9"/>
       <c r="T259" s="9"/>
@@ -14067,35 +14082,35 @@
       <c r="Z259" s="9"/>
     </row>
     <row r="260">
-      <c r="A260" s="58" t="s">
+      <c r="A260" s="59" t="s">
         <v>714</v>
       </c>
-      <c r="B260" s="58" t="s">
+      <c r="B260" s="59" t="s">
         <v>715</v>
       </c>
-      <c r="C260" s="58" t="s">
+      <c r="C260" s="59" t="s">
         <v>716</v>
       </c>
-      <c r="D260" s="58" t="s">
+      <c r="D260" s="59" t="s">
         <v>717</v>
       </c>
-      <c r="E260" s="58" t="s">
+      <c r="E260" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="F260" s="58" t="s">
+      <c r="F260" s="59" t="s">
         <v>718</v>
       </c>
-      <c r="G260" s="59"/>
-      <c r="H260" s="59"/>
-      <c r="I260" s="59"/>
-      <c r="J260" s="59"/>
-      <c r="K260" s="59"/>
-      <c r="L260" s="59"/>
-      <c r="M260" s="59"/>
-      <c r="N260" s="59"/>
-      <c r="O260" s="59"/>
-      <c r="P260" s="59"/>
-      <c r="Q260" s="59"/>
+      <c r="G260" s="58"/>
+      <c r="H260" s="58"/>
+      <c r="I260" s="58"/>
+      <c r="J260" s="58"/>
+      <c r="K260" s="58"/>
+      <c r="L260" s="58"/>
+      <c r="M260" s="58"/>
+      <c r="N260" s="58"/>
+      <c r="O260" s="58"/>
+      <c r="P260" s="58"/>
+      <c r="Q260" s="58"/>
       <c r="R260" s="9"/>
       <c r="S260" s="9"/>
       <c r="T260" s="9"/>
@@ -14107,37 +14122,37 @@
       <c r="Z260" s="9"/>
     </row>
     <row r="261">
-      <c r="A261" s="58" t="s">
+      <c r="A261" s="59" t="s">
         <v>719</v>
       </c>
-      <c r="B261" s="58" t="s">
+      <c r="B261" s="59" t="s">
         <v>720</v>
       </c>
-      <c r="C261" s="58" t="s">
+      <c r="C261" s="59" t="s">
         <v>721</v>
       </c>
-      <c r="D261" s="58" t="s">
+      <c r="D261" s="59" t="s">
         <v>722</v>
       </c>
-      <c r="E261" s="58" t="s">
+      <c r="E261" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="F261" s="58" t="s">
+      <c r="F261" s="59" t="s">
         <v>723</v>
       </c>
-      <c r="G261" s="59"/>
-      <c r="H261" s="59"/>
-      <c r="I261" s="59"/>
-      <c r="J261" s="59"/>
-      <c r="K261" s="59"/>
-      <c r="L261" s="59"/>
+      <c r="G261" s="58"/>
+      <c r="H261" s="58"/>
+      <c r="I261" s="58"/>
+      <c r="J261" s="58"/>
+      <c r="K261" s="58"/>
+      <c r="L261" s="58"/>
       <c r="M261" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="N261" s="59"/>
-      <c r="O261" s="59"/>
-      <c r="P261" s="59"/>
-      <c r="Q261" s="59"/>
+      <c r="N261" s="58"/>
+      <c r="O261" s="58"/>
+      <c r="P261" s="58"/>
+      <c r="Q261" s="58"/>
       <c r="R261" s="9"/>
       <c r="S261" s="9"/>
       <c r="T261" s="9"/>
@@ -14149,33 +14164,33 @@
       <c r="Z261" s="9"/>
     </row>
     <row r="262">
-      <c r="A262" s="58" t="s">
+      <c r="A262" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="B262" s="58" t="s">
+      <c r="B262" s="59" t="s">
         <v>725</v>
       </c>
-      <c r="C262" s="58" t="s">
+      <c r="C262" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="D262" s="58" t="s">
+      <c r="D262" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="E262" s="58"/>
-      <c r="F262" s="58"/>
-      <c r="G262" s="58" t="s">
+      <c r="E262" s="59"/>
+      <c r="F262" s="59"/>
+      <c r="G262" s="59" t="s">
         <v>117</v>
       </c>
-      <c r="H262" s="59"/>
+      <c r="H262" s="58"/>
       <c r="I262" s="65"/>
       <c r="J262" s="65"/>
-      <c r="K262" s="59"/>
-      <c r="L262" s="59"/>
+      <c r="K262" s="58"/>
+      <c r="L262" s="58"/>
       <c r="M262" s="2"/>
-      <c r="N262" s="59"/>
-      <c r="O262" s="59"/>
-      <c r="P262" s="59"/>
-      <c r="Q262" s="59"/>
+      <c r="N262" s="58"/>
+      <c r="O262" s="58"/>
+      <c r="P262" s="58"/>
+      <c r="Q262" s="58"/>
       <c r="R262" s="9"/>
       <c r="S262" s="9"/>
       <c r="T262" s="9"/>
@@ -14187,37 +14202,37 @@
       <c r="Z262" s="9"/>
     </row>
     <row r="263">
-      <c r="A263" s="58" t="s">
+      <c r="A263" s="59" t="s">
         <v>726</v>
       </c>
-      <c r="B263" s="58" t="s">
+      <c r="B263" s="59" t="s">
         <v>727</v>
       </c>
-      <c r="C263" s="58" t="s">
+      <c r="C263" s="59" t="s">
         <v>728</v>
       </c>
-      <c r="D263" s="58" t="s">
+      <c r="D263" s="59" t="s">
         <v>729</v>
       </c>
-      <c r="E263" s="58" t="s">
+      <c r="E263" s="59" t="s">
         <v>256</v>
       </c>
-      <c r="F263" s="58" t="s">
+      <c r="F263" s="59" t="s">
         <v>730</v>
       </c>
-      <c r="G263" s="59"/>
-      <c r="H263" s="59"/>
+      <c r="G263" s="58"/>
+      <c r="H263" s="58"/>
       <c r="I263" s="65"/>
       <c r="J263" s="65"/>
-      <c r="K263" s="59"/>
-      <c r="L263" s="59"/>
+      <c r="K263" s="58"/>
+      <c r="L263" s="58"/>
       <c r="M263" s="2" t="s">
         <v>731</v>
       </c>
-      <c r="N263" s="59"/>
-      <c r="O263" s="59"/>
-      <c r="P263" s="59"/>
-      <c r="Q263" s="59"/>
+      <c r="N263" s="58"/>
+      <c r="O263" s="58"/>
+      <c r="P263" s="58"/>
+      <c r="Q263" s="58"/>
       <c r="R263" s="9"/>
       <c r="S263" s="9"/>
       <c r="T263" s="9"/>
@@ -14229,35 +14244,35 @@
       <c r="Z263" s="9"/>
     </row>
     <row r="264">
-      <c r="A264" s="58" t="s">
+      <c r="A264" s="59" t="s">
         <v>732</v>
       </c>
-      <c r="B264" s="58" t="s">
+      <c r="B264" s="59" t="s">
         <v>733</v>
       </c>
-      <c r="C264" s="58" t="s">
+      <c r="C264" s="59" t="s">
         <v>734</v>
       </c>
-      <c r="D264" s="58" t="s">
+      <c r="D264" s="59" t="s">
         <v>735</v>
       </c>
-      <c r="E264" s="58" t="s">
+      <c r="E264" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="F264" s="58" t="s">
+      <c r="F264" s="59" t="s">
         <v>736</v>
       </c>
-      <c r="G264" s="59"/>
-      <c r="H264" s="59"/>
-      <c r="I264" s="59"/>
-      <c r="J264" s="59"/>
-      <c r="K264" s="59"/>
-      <c r="L264" s="59"/>
-      <c r="M264" s="59"/>
-      <c r="N264" s="59"/>
-      <c r="O264" s="59"/>
-      <c r="P264" s="59"/>
-      <c r="Q264" s="59"/>
+      <c r="G264" s="58"/>
+      <c r="H264" s="58"/>
+      <c r="I264" s="58"/>
+      <c r="J264" s="58"/>
+      <c r="K264" s="58"/>
+      <c r="L264" s="58"/>
+      <c r="M264" s="58"/>
+      <c r="N264" s="58"/>
+      <c r="O264" s="58"/>
+      <c r="P264" s="58"/>
+      <c r="Q264" s="58"/>
       <c r="R264" s="9"/>
       <c r="S264" s="9"/>
       <c r="T264" s="9"/>
@@ -14269,27 +14284,27 @@
       <c r="Z264" s="9"/>
     </row>
     <row r="265">
-      <c r="A265" s="58" t="s">
+      <c r="A265" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="B265" s="58" t="s">
+      <c r="B265" s="59" t="s">
         <v>725</v>
       </c>
-      <c r="C265" s="58"/>
-      <c r="D265" s="59"/>
-      <c r="E265" s="58"/>
-      <c r="F265" s="58"/>
-      <c r="G265" s="59"/>
-      <c r="H265" s="59"/>
-      <c r="I265" s="59"/>
-      <c r="J265" s="59"/>
-      <c r="K265" s="59"/>
-      <c r="L265" s="59"/>
-      <c r="M265" s="59"/>
-      <c r="N265" s="59"/>
-      <c r="O265" s="59"/>
-      <c r="P265" s="59"/>
-      <c r="Q265" s="59"/>
+      <c r="C265" s="59"/>
+      <c r="D265" s="58"/>
+      <c r="E265" s="59"/>
+      <c r="F265" s="59"/>
+      <c r="G265" s="58"/>
+      <c r="H265" s="58"/>
+      <c r="I265" s="58"/>
+      <c r="J265" s="58"/>
+      <c r="K265" s="58"/>
+      <c r="L265" s="58"/>
+      <c r="M265" s="58"/>
+      <c r="N265" s="58"/>
+      <c r="O265" s="58"/>
+      <c r="P265" s="58"/>
+      <c r="Q265" s="58"/>
       <c r="R265" s="9"/>
       <c r="S265" s="9"/>
       <c r="T265" s="9"/>
@@ -14301,35 +14316,35 @@
       <c r="Z265" s="9"/>
     </row>
     <row r="266">
-      <c r="A266" s="58" t="s">
+      <c r="A266" s="59" t="s">
         <v>737</v>
       </c>
-      <c r="B266" s="58" t="s">
+      <c r="B266" s="59" t="s">
         <v>738</v>
       </c>
-      <c r="C266" s="58" t="s">
+      <c r="C266" s="59" t="s">
         <v>739</v>
       </c>
-      <c r="D266" s="58" t="s">
+      <c r="D266" s="59" t="s">
         <v>740</v>
       </c>
-      <c r="E266" s="58" t="s">
+      <c r="E266" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="F266" s="58" t="s">
+      <c r="F266" s="59" t="s">
         <v>718</v>
       </c>
-      <c r="G266" s="59"/>
-      <c r="H266" s="59"/>
-      <c r="I266" s="59"/>
-      <c r="J266" s="59"/>
-      <c r="K266" s="59"/>
-      <c r="L266" s="59"/>
-      <c r="M266" s="59"/>
-      <c r="N266" s="59"/>
-      <c r="O266" s="59"/>
-      <c r="P266" s="59"/>
-      <c r="Q266" s="59"/>
+      <c r="G266" s="58"/>
+      <c r="H266" s="58"/>
+      <c r="I266" s="58"/>
+      <c r="J266" s="58"/>
+      <c r="K266" s="58"/>
+      <c r="L266" s="58"/>
+      <c r="M266" s="58"/>
+      <c r="N266" s="58"/>
+      <c r="O266" s="58"/>
+      <c r="P266" s="58"/>
+      <c r="Q266" s="58"/>
       <c r="R266" s="9"/>
       <c r="S266" s="9"/>
       <c r="T266" s="9"/>
@@ -14341,35 +14356,35 @@
       <c r="Z266" s="9"/>
     </row>
     <row r="267">
-      <c r="A267" s="58" t="s">
+      <c r="A267" s="59" t="s">
         <v>741</v>
       </c>
-      <c r="B267" s="58" t="s">
+      <c r="B267" s="59" t="s">
         <v>742</v>
       </c>
-      <c r="C267" s="58" t="s">
+      <c r="C267" s="59" t="s">
         <v>743</v>
       </c>
       <c r="D267" s="7" t="s">
         <v>744</v>
       </c>
-      <c r="E267" s="58" t="s">
+      <c r="E267" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="F267" s="58" t="s">
+      <c r="F267" s="59" t="s">
         <v>745</v>
       </c>
-      <c r="G267" s="59"/>
-      <c r="H267" s="59"/>
-      <c r="I267" s="59"/>
-      <c r="J267" s="59"/>
-      <c r="K267" s="59"/>
-      <c r="L267" s="59"/>
-      <c r="M267" s="59"/>
-      <c r="N267" s="59"/>
-      <c r="O267" s="59"/>
-      <c r="P267" s="59"/>
-      <c r="Q267" s="59"/>
+      <c r="G267" s="58"/>
+      <c r="H267" s="58"/>
+      <c r="I267" s="58"/>
+      <c r="J267" s="58"/>
+      <c r="K267" s="58"/>
+      <c r="L267" s="58"/>
+      <c r="M267" s="58"/>
+      <c r="N267" s="58"/>
+      <c r="O267" s="58"/>
+      <c r="P267" s="58"/>
+      <c r="Q267" s="58"/>
       <c r="R267" s="9"/>
       <c r="S267" s="9"/>
       <c r="T267" s="9"/>
@@ -14381,35 +14396,35 @@
       <c r="Z267" s="9"/>
     </row>
     <row r="268">
-      <c r="A268" s="58" t="s">
+      <c r="A268" s="59" t="s">
         <v>746</v>
       </c>
-      <c r="B268" s="58" t="s">
+      <c r="B268" s="59" t="s">
         <v>747</v>
       </c>
       <c r="C268" s="66" t="s">
         <v>748</v>
       </c>
-      <c r="D268" s="58" t="s">
+      <c r="D268" s="59" t="s">
         <v>749</v>
       </c>
-      <c r="E268" s="58" t="s">
+      <c r="E268" s="59" t="s">
         <v>139</v>
       </c>
       <c r="F268" s="13" t="s">
         <v>750</v>
       </c>
-      <c r="G268" s="59"/>
-      <c r="H268" s="59"/>
-      <c r="I268" s="59"/>
-      <c r="J268" s="59"/>
-      <c r="K268" s="59"/>
-      <c r="L268" s="59"/>
-      <c r="M268" s="59"/>
-      <c r="N268" s="59"/>
-      <c r="O268" s="59"/>
-      <c r="P268" s="59"/>
-      <c r="Q268" s="59"/>
+      <c r="G268" s="58"/>
+      <c r="H268" s="58"/>
+      <c r="I268" s="58"/>
+      <c r="J268" s="58"/>
+      <c r="K268" s="58"/>
+      <c r="L268" s="58"/>
+      <c r="M268" s="58"/>
+      <c r="N268" s="58"/>
+      <c r="O268" s="58"/>
+      <c r="P268" s="58"/>
+      <c r="Q268" s="58"/>
       <c r="R268" s="9"/>
       <c r="S268" s="9"/>
       <c r="T268" s="9"/>
@@ -14421,35 +14436,35 @@
       <c r="Z268" s="9"/>
     </row>
     <row r="269">
-      <c r="A269" s="58" t="s">
+      <c r="A269" s="59" t="s">
         <v>751</v>
       </c>
-      <c r="B269" s="58" t="s">
+      <c r="B269" s="59" t="s">
         <v>752</v>
       </c>
-      <c r="C269" s="58" t="s">
+      <c r="C269" s="59" t="s">
         <v>753</v>
       </c>
-      <c r="D269" s="58" t="s">
+      <c r="D269" s="59" t="s">
         <v>754</v>
       </c>
-      <c r="E269" s="58" t="s">
+      <c r="E269" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="F269" s="58" t="s">
+      <c r="F269" s="59" t="s">
         <v>755</v>
       </c>
-      <c r="G269" s="59"/>
-      <c r="H269" s="59"/>
-      <c r="I269" s="59"/>
-      <c r="J269" s="59"/>
-      <c r="K269" s="59"/>
-      <c r="L269" s="59"/>
-      <c r="M269" s="59"/>
-      <c r="N269" s="59"/>
-      <c r="O269" s="59"/>
-      <c r="P269" s="59"/>
-      <c r="Q269" s="59"/>
+      <c r="G269" s="58"/>
+      <c r="H269" s="58"/>
+      <c r="I269" s="58"/>
+      <c r="J269" s="58"/>
+      <c r="K269" s="58"/>
+      <c r="L269" s="58"/>
+      <c r="M269" s="58"/>
+      <c r="N269" s="58"/>
+      <c r="O269" s="58"/>
+      <c r="P269" s="58"/>
+      <c r="Q269" s="58"/>
       <c r="R269" s="9"/>
       <c r="S269" s="9"/>
       <c r="T269" s="9"/>
@@ -14461,35 +14476,35 @@
       <c r="Z269" s="9"/>
     </row>
     <row r="270">
-      <c r="A270" s="58" t="s">
+      <c r="A270" s="59" t="s">
         <v>135</v>
       </c>
-      <c r="B270" s="58" t="s">
+      <c r="B270" s="59" t="s">
         <v>756</v>
       </c>
-      <c r="C270" s="58" t="s">
+      <c r="C270" s="59" t="s">
         <v>757</v>
       </c>
-      <c r="D270" s="58" t="s">
+      <c r="D270" s="59" t="s">
         <v>758</v>
       </c>
-      <c r="E270" s="58" t="s">
+      <c r="E270" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="F270" s="58" t="s">
+      <c r="F270" s="59" t="s">
         <v>718</v>
       </c>
-      <c r="G270" s="59"/>
-      <c r="H270" s="59"/>
-      <c r="I270" s="59"/>
-      <c r="J270" s="59"/>
-      <c r="K270" s="59"/>
-      <c r="L270" s="59"/>
-      <c r="M270" s="59"/>
-      <c r="N270" s="59"/>
-      <c r="O270" s="59"/>
-      <c r="P270" s="59"/>
-      <c r="Q270" s="59"/>
+      <c r="G270" s="58"/>
+      <c r="H270" s="58"/>
+      <c r="I270" s="58"/>
+      <c r="J270" s="58"/>
+      <c r="K270" s="58"/>
+      <c r="L270" s="58"/>
+      <c r="M270" s="58"/>
+      <c r="N270" s="58"/>
+      <c r="O270" s="58"/>
+      <c r="P270" s="58"/>
+      <c r="Q270" s="58"/>
       <c r="R270" s="9"/>
       <c r="S270" s="9"/>
       <c r="T270" s="9"/>
@@ -14501,41 +14516,41 @@
       <c r="Z270" s="9"/>
     </row>
     <row r="271">
-      <c r="A271" s="58" t="s">
+      <c r="A271" s="59" t="s">
         <v>238</v>
       </c>
-      <c r="B271" s="58" t="s">
+      <c r="B271" s="59" t="s">
         <v>759</v>
       </c>
-      <c r="C271" s="58" t="s">
+      <c r="C271" s="59" t="s">
         <v>760</v>
       </c>
-      <c r="D271" s="58" t="s">
+      <c r="D271" s="59" t="s">
         <v>761</v>
       </c>
-      <c r="E271" s="58" t="s">
+      <c r="E271" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="F271" s="58" t="s">
+      <c r="F271" s="59" t="s">
         <v>762</v>
       </c>
-      <c r="G271" s="59"/>
-      <c r="H271" s="59"/>
-      <c r="I271" s="58" t="s">
+      <c r="G271" s="58"/>
+      <c r="H271" s="58"/>
+      <c r="I271" s="59" t="s">
         <v>763</v>
       </c>
-      <c r="J271" s="58" t="s">
+      <c r="J271" s="59" t="s">
         <v>764</v>
       </c>
-      <c r="K271" s="58" t="s">
+      <c r="K271" s="59" t="s">
         <v>765</v>
       </c>
-      <c r="L271" s="59"/>
-      <c r="M271" s="59"/>
-      <c r="N271" s="59"/>
-      <c r="O271" s="59"/>
-      <c r="P271" s="59"/>
-      <c r="Q271" s="59"/>
+      <c r="L271" s="58"/>
+      <c r="M271" s="58"/>
+      <c r="N271" s="58"/>
+      <c r="O271" s="58"/>
+      <c r="P271" s="58"/>
+      <c r="Q271" s="58"/>
       <c r="R271" s="9"/>
       <c r="S271" s="9"/>
       <c r="T271" s="9"/>
@@ -14547,35 +14562,35 @@
       <c r="Z271" s="9"/>
     </row>
     <row r="272">
-      <c r="A272" s="58" t="s">
+      <c r="A272" s="59" t="s">
         <v>766</v>
       </c>
-      <c r="B272" s="58" t="s">
+      <c r="B272" s="59" t="s">
         <v>767</v>
       </c>
-      <c r="C272" s="58" t="s">
+      <c r="C272" s="59" t="s">
         <v>768</v>
       </c>
       <c r="D272" s="60" t="s">
         <v>769</v>
       </c>
-      <c r="E272" s="58" t="s">
+      <c r="E272" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="F272" s="58" t="s">
+      <c r="F272" s="59" t="s">
         <v>762</v>
       </c>
-      <c r="G272" s="59"/>
-      <c r="H272" s="59"/>
-      <c r="I272" s="59"/>
-      <c r="J272" s="59"/>
-      <c r="K272" s="59"/>
-      <c r="L272" s="59"/>
-      <c r="M272" s="59"/>
-      <c r="N272" s="59"/>
-      <c r="O272" s="59"/>
-      <c r="P272" s="59"/>
-      <c r="Q272" s="59"/>
+      <c r="G272" s="58"/>
+      <c r="H272" s="58"/>
+      <c r="I272" s="58"/>
+      <c r="J272" s="58"/>
+      <c r="K272" s="58"/>
+      <c r="L272" s="58"/>
+      <c r="M272" s="58"/>
+      <c r="N272" s="58"/>
+      <c r="O272" s="58"/>
+      <c r="P272" s="58"/>
+      <c r="Q272" s="58"/>
       <c r="R272" s="9"/>
       <c r="S272" s="9"/>
       <c r="T272" s="9"/>
@@ -14587,35 +14602,35 @@
       <c r="Z272" s="9"/>
     </row>
     <row r="273">
-      <c r="A273" s="58" t="s">
+      <c r="A273" s="59" t="s">
         <v>770</v>
       </c>
-      <c r="B273" s="58" t="s">
+      <c r="B273" s="59" t="s">
         <v>771</v>
       </c>
-      <c r="C273" s="58" t="s">
+      <c r="C273" s="59" t="s">
         <v>772</v>
       </c>
-      <c r="D273" s="58" t="s">
+      <c r="D273" s="59" t="s">
         <v>773</v>
       </c>
-      <c r="E273" s="58" t="s">
+      <c r="E273" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="F273" s="58" t="s">
+      <c r="F273" s="59" t="s">
         <v>718</v>
       </c>
-      <c r="G273" s="59"/>
-      <c r="H273" s="59"/>
-      <c r="I273" s="59"/>
-      <c r="J273" s="59"/>
-      <c r="K273" s="59"/>
-      <c r="L273" s="59"/>
-      <c r="M273" s="59"/>
-      <c r="N273" s="59"/>
-      <c r="O273" s="59"/>
-      <c r="P273" s="59"/>
-      <c r="Q273" s="59"/>
+      <c r="G273" s="58"/>
+      <c r="H273" s="58"/>
+      <c r="I273" s="58"/>
+      <c r="J273" s="58"/>
+      <c r="K273" s="58"/>
+      <c r="L273" s="58"/>
+      <c r="M273" s="58"/>
+      <c r="N273" s="58"/>
+      <c r="O273" s="58"/>
+      <c r="P273" s="58"/>
+      <c r="Q273" s="58"/>
       <c r="R273" s="9"/>
       <c r="S273" s="9"/>
       <c r="T273" s="9"/>
@@ -14627,35 +14642,35 @@
       <c r="Z273" s="9"/>
     </row>
     <row r="274">
-      <c r="A274" s="58" t="s">
+      <c r="A274" s="59" t="s">
         <v>135</v>
       </c>
-      <c r="B274" s="58" t="s">
+      <c r="B274" s="59" t="s">
         <v>774</v>
       </c>
       <c r="C274" s="7" t="s">
         <v>775</v>
       </c>
-      <c r="D274" s="58" t="s">
+      <c r="D274" s="59" t="s">
         <v>776</v>
       </c>
-      <c r="E274" s="58" t="s">
+      <c r="E274" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="F274" s="58" t="s">
+      <c r="F274" s="59" t="s">
         <v>718</v>
       </c>
-      <c r="G274" s="59"/>
-      <c r="H274" s="59"/>
-      <c r="I274" s="59"/>
-      <c r="J274" s="59"/>
-      <c r="K274" s="59"/>
-      <c r="L274" s="59"/>
-      <c r="M274" s="59"/>
-      <c r="N274" s="59"/>
-      <c r="O274" s="59"/>
-      <c r="P274" s="59"/>
-      <c r="Q274" s="59"/>
+      <c r="G274" s="58"/>
+      <c r="H274" s="58"/>
+      <c r="I274" s="58"/>
+      <c r="J274" s="58"/>
+      <c r="K274" s="58"/>
+      <c r="L274" s="58"/>
+      <c r="M274" s="58"/>
+      <c r="N274" s="58"/>
+      <c r="O274" s="58"/>
+      <c r="P274" s="58"/>
+      <c r="Q274" s="58"/>
       <c r="R274" s="9"/>
       <c r="S274" s="9"/>
       <c r="T274" s="9"/>
@@ -14667,27 +14682,27 @@
       <c r="Z274" s="9"/>
     </row>
     <row r="275">
-      <c r="A275" s="58" t="s">
+      <c r="A275" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="B275" s="58" t="s">
+      <c r="B275" s="59" t="s">
         <v>707</v>
       </c>
-      <c r="C275" s="59"/>
-      <c r="D275" s="59"/>
-      <c r="E275" s="59"/>
-      <c r="F275" s="59"/>
-      <c r="G275" s="59"/>
-      <c r="H275" s="59"/>
-      <c r="I275" s="59"/>
-      <c r="J275" s="59"/>
-      <c r="K275" s="59"/>
-      <c r="L275" s="59"/>
-      <c r="M275" s="59"/>
-      <c r="N275" s="59"/>
-      <c r="O275" s="59"/>
-      <c r="P275" s="59"/>
-      <c r="Q275" s="59"/>
+      <c r="C275" s="58"/>
+      <c r="D275" s="58"/>
+      <c r="E275" s="58"/>
+      <c r="F275" s="58"/>
+      <c r="G275" s="58"/>
+      <c r="H275" s="58"/>
+      <c r="I275" s="58"/>
+      <c r="J275" s="58"/>
+      <c r="K275" s="58"/>
+      <c r="L275" s="58"/>
+      <c r="M275" s="58"/>
+      <c r="N275" s="58"/>
+      <c r="O275" s="58"/>
+      <c r="P275" s="58"/>
+      <c r="Q275" s="58"/>
       <c r="R275" s="9"/>
       <c r="S275" s="9"/>
       <c r="T275" s="9"/>
@@ -20548,7 +20563,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="58" t="s">
+      <c r="A219" s="59" t="s">
         <v>285</v>
       </c>
       <c r="B219" s="2" t="s">
@@ -20618,7 +20633,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="58" t="s">
+      <c r="A224" s="59" t="s">
         <v>1309</v>
       </c>
       <c r="B224" s="2" t="s">
@@ -20632,7 +20647,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="58" t="s">
+      <c r="A225" s="59" t="s">
         <v>673</v>
       </c>
       <c r="B225" s="2" t="s">
@@ -20646,7 +20661,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="58" t="s">
+      <c r="A226" s="59" t="s">
         <v>673</v>
       </c>
       <c r="B226" s="2" t="s">
@@ -20660,8 +20675,8 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="7" t="s">
-        <v>410</v>
+      <c r="A227" s="59" t="s">
+        <v>673</v>
       </c>
       <c r="B227" s="2" t="s">
         <v>1328</v>
@@ -20674,8 +20689,8 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="s">
-        <v>410</v>
+      <c r="A228" s="7" t="s">
+        <v>673</v>
       </c>
       <c r="B228" s="2" t="s">
         <v>1331</v>
@@ -20689,30 +20704,30 @@
     </row>
     <row r="229">
       <c r="A229" s="7" t="s">
-        <v>329</v>
+        <v>410</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>139</v>
+        <v>1334</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>871</v>
+        <v>1335</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="7" t="s">
-        <v>329</v>
+      <c r="A230" s="2" t="s">
+        <v>410</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="231">
@@ -20720,10 +20735,10 @@
         <v>329</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>1338</v>
+        <v>139</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>1339</v>
+        <v>871</v>
       </c>
       <c r="D231" s="2" t="s">
         <v>1340</v>
@@ -20741,6 +20756,34 @@
       </c>
       <c r="D232" s="2" t="s">
         <v>1343</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>1348</v>
+      </c>
+      <c r="D234" s="2" t="s">
+        <v>1349</v>
       </c>
     </row>
   </sheetData>
@@ -20760,39 +20803,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="79" t="s">
-        <v>1344</v>
+        <v>1350</v>
       </c>
       <c r="B1" s="79" t="s">
-        <v>1345</v>
+        <v>1351</v>
       </c>
       <c r="C1" s="79" t="s">
-        <v>1346</v>
+        <v>1352</v>
       </c>
       <c r="D1" s="79" t="s">
-        <v>1347</v>
+        <v>1353</v>
       </c>
       <c r="E1" s="79" t="s">
-        <v>1348</v>
+        <v>1354</v>
       </c>
       <c r="F1" s="79" t="s">
-        <v>1349</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="88" t="s">
-        <v>1350</v>
+        <v>1356</v>
       </c>
       <c r="B2" s="88" t="s">
-        <v>1351</v>
+        <v>1357</v>
       </c>
       <c r="C2" s="89" t="s">
-        <v>1352</v>
+        <v>1358</v>
       </c>
       <c r="D2" s="80" t="s">
-        <v>1353</v>
+        <v>1359</v>
       </c>
       <c r="E2" s="80" t="s">
-        <v>1354</v>
+        <v>1360</v>
       </c>
       <c r="F2" s="80"/>
     </row>

--- a/forms/app/pregnancy.xlsx
+++ b/forms/app/pregnancy.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2437" uniqueCount="1426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2477" uniqueCount="1432">
   <si>
     <t>type</t>
   </si>
@@ -4273,18 +4273,6 @@
     <t>previous_stillbirth_risk</t>
   </si>
   <si>
-    <t>delivery_complications_risk</t>
-  </si>
-  <si>
-    <t>selected(${delivery_complications},'prolonged_labor') or 
-selected(${delivery_complications},'large_perineal_tear') or 
-selected(${delivery_complications},'retained_placenta') or 
-selected(${delivery_complications},'aph') or 
-selected(${delivery_complications},'postpartum_hemorrage') or 
-selected(${delivery_complications},'enclampsia') or 
-selected(${delivery_complications},'big_baby')</t>
-  </si>
-  <si>
     <t xml:space="preserve">previous_miscarriage_risk </t>
   </si>
   <si>
@@ -4301,12 +4289,6 @@
   </si>
   <si>
     <t>big_baby_risk</t>
-  </si>
-  <si>
-    <t>Big Baby</t>
-  </si>
-  <si>
-    <t>selected(${big_baby},"yes")</t>
   </si>
   <si>
     <t>Malpresentation</t>
@@ -4328,12 +4310,6 @@
     <t>selected(${breech_position},"yes")</t>
   </si>
   <si>
-    <t>medical_conditions_risk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">selected(${medical_conditions},"diabetes") or selected(${medical_conditions},"sickle_cell") or  selected(${medical_conditions},"cardiac_disease") </t>
-  </si>
-  <si>
     <t>Recommended to deliver at a higher level facility</t>
   </si>
   <si>
@@ -4420,9 +4396,6 @@
     <t xml:space="preserve">Kutarajia kuwa na mapacha </t>
   </si>
   <si>
-    <t xml:space="preserve">Kujifungua mtoto mkubwa ( zaidi ya kilo 4) (mimba hii au kabla) </t>
-  </si>
-  <si>
     <t>Milalo mibaya</t>
   </si>
   <si>
@@ -4445,21 +4418,6 @@
   </si>
   <si>
     <t>Hatari za kutumia dawa za mitishamba</t>
-  </si>
-  <si>
-    <t>${medical_conditions}</t>
-  </si>
-  <si>
-    <t>contains(${medical_conditions}, name) or name = 'none'</t>
-  </si>
-  <si>
-    <t>delivery_complications_risk_note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${delivery_complications_risk} </t>
-  </si>
-  <si>
-    <t>jr:choice-name(${delivery_complications}, '${delivery_complications}')</t>
   </si>
   <si>
     <t>${enabel} = "true"  and selected(${first_time_pregnant},'no') and ${previous_pregnancies} &gt; ${previous_miscarriages}</t>
@@ -4491,6 +4449,60 @@
   <si>
     <t xml:space="preserve">As soon as you are aware you are pregnant, it is important to go to the nearest health facility for antenatal care (ANC). You should go to ANC 8 times throughout your pregnancy as directed by the health worker.
 </t>
+  </si>
+  <si>
+    <t>prolonged_labor_risk</t>
+  </si>
+  <si>
+    <t>selected(${delivery_complications},'prolonged_labor')</t>
+  </si>
+  <si>
+    <t>selected(${delivery_complications},'large_perineal_tear')</t>
+  </si>
+  <si>
+    <t>selected(${delivery_complications},'retained_placenta')</t>
+  </si>
+  <si>
+    <t>selected(${delivery_complications},'aph')</t>
+  </si>
+  <si>
+    <t>selected(${delivery_complications},'postpartum_hemorrage')</t>
+  </si>
+  <si>
+    <t>selected(${delivery_complications},'enclampsia')</t>
+  </si>
+  <si>
+    <t>Uchungu wa muda mrefu ( Zaidi ya masaa 12)</t>
+  </si>
+  <si>
+    <t>large_perineal_tear_risk</t>
+  </si>
+  <si>
+    <t>retained_placenta_risk</t>
+  </si>
+  <si>
+    <t>aph_risk</t>
+  </si>
+  <si>
+    <t>postpartum_hemorrage_risk</t>
+  </si>
+  <si>
+    <t>enclampsia_risk</t>
+  </si>
+  <si>
+    <t>selected(${medical_conditions},"diabetes")</t>
+  </si>
+  <si>
+    <t>selected(${medical_conditions},"high_blood_pressure")</t>
+  </si>
+  <si>
+    <t>selected(${medical_conditions},"sickle_cell")</t>
+  </si>
+  <si>
+    <t>selected(${medical_conditions},"cardiac_disease")</t>
+  </si>
+  <si>
+    <t>selected(${delivery_complications},'big_baby') or selected(${big_baby},"yes")</t>
   </si>
 </sst>
 </file>
@@ -5109,7 +5121,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z332"/>
+  <dimension ref="A1:Z339"/>
   <sheetFormatPr defaultColWidth="14.40625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.1328125" customWidth="1"/>
@@ -7612,10 +7624,10 @@
         <v>165</v>
       </c>
       <c r="C75" s="88" t="s">
-        <v>1425</v>
+        <v>1413</v>
       </c>
       <c r="D75" s="46" t="s">
-        <v>1424</v>
+        <v>1412</v>
       </c>
       <c r="E75" s="6"/>
       <c r="F75" s="4"/>
@@ -8658,7 +8670,7 @@
         <v>139</v>
       </c>
       <c r="F103" s="34" t="s">
-        <v>1416</v>
+        <v>1404</v>
       </c>
       <c r="G103" s="20"/>
       <c r="H103" s="8"/>
@@ -8698,7 +8710,7 @@
         <v>139</v>
       </c>
       <c r="F104" s="34" t="s">
-        <v>1417</v>
+        <v>1405</v>
       </c>
       <c r="G104" s="20"/>
       <c r="H104" s="8"/>
@@ -8738,7 +8750,7 @@
         <v>139</v>
       </c>
       <c r="F105" s="34" t="s">
-        <v>1418</v>
+        <v>1406</v>
       </c>
       <c r="G105" s="20"/>
       <c r="H105" s="8"/>
@@ -8824,7 +8836,7 @@
         <v>139</v>
       </c>
       <c r="F107" s="34" t="s">
-        <v>1416</v>
+        <v>1404</v>
       </c>
       <c r="G107" s="20"/>
       <c r="H107" s="8"/>
@@ -9098,7 +9110,7 @@
         <v>139</v>
       </c>
       <c r="F114" s="47" t="s">
-        <v>1419</v>
+        <v>1407</v>
       </c>
       <c r="G114" s="20"/>
       <c r="H114" s="8"/>
@@ -9920,7 +9932,7 @@
         <v>384</v>
       </c>
       <c r="D135" s="46" t="s">
-        <v>1422</v>
+        <v>1410</v>
       </c>
       <c r="E135" s="7" t="s">
         <v>139</v>
@@ -9960,9 +9972,11 @@
         <v>386</v>
       </c>
       <c r="D136" s="102" t="s">
-        <v>1421</v>
-      </c>
-      <c r="E136" s="20"/>
+        <v>1409</v>
+      </c>
+      <c r="E136" s="46" t="s">
+        <v>139</v>
+      </c>
       <c r="F136" s="34" t="s">
         <v>380</v>
       </c>
@@ -9998,9 +10012,11 @@
         <v>388</v>
       </c>
       <c r="D137" s="46" t="s">
-        <v>1423</v>
-      </c>
-      <c r="E137" s="20"/>
+        <v>1411</v>
+      </c>
+      <c r="E137" s="46" t="s">
+        <v>139</v>
+      </c>
       <c r="F137" s="34" t="s">
         <v>380</v>
       </c>
@@ -10038,7 +10054,9 @@
       <c r="D138" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="E138" s="20"/>
+      <c r="E138" s="46" t="s">
+        <v>139</v>
+      </c>
       <c r="F138" s="34" t="s">
         <v>390</v>
       </c>
@@ -13806,7 +13824,7 @@
         <v>139</v>
       </c>
       <c r="F241" s="57" t="s">
-        <v>1420</v>
+        <v>1408</v>
       </c>
       <c r="G241" s="56"/>
       <c r="H241" s="56"/>
@@ -15695,7 +15713,7 @@
         <v>1346</v>
       </c>
       <c r="C303" s="88" t="s">
-        <v>1396</v>
+        <v>1390</v>
       </c>
       <c r="D303" s="46"/>
       <c r="F303" s="46"/>
@@ -15712,14 +15730,14 @@
         <v>1348</v>
       </c>
       <c r="D304" s="46" t="s">
-        <v>1397</v>
+        <v>1391</v>
       </c>
       <c r="F304" s="46" t="s">
         <v>1349</v>
       </c>
       <c r="G304" s="46"/>
     </row>
-    <row r="305" spans="1:26" s="87" customFormat="1" ht="13">
+    <row r="305" spans="1:12" s="87" customFormat="1" ht="13">
       <c r="A305" s="46" t="s">
         <v>109</v>
       </c>
@@ -15730,14 +15748,14 @@
         <v>1350</v>
       </c>
       <c r="D305" s="101" t="s">
-        <v>1398</v>
+        <v>1392</v>
       </c>
       <c r="F305" s="46" t="s">
         <v>1352</v>
       </c>
       <c r="G305" s="46"/>
     </row>
-    <row r="306" spans="1:26" s="87" customFormat="1" ht="13">
+    <row r="306" spans="1:12" s="87" customFormat="1" ht="13">
       <c r="A306" s="46" t="s">
         <v>109</v>
       </c>
@@ -15748,507 +15766,403 @@
         <v>1353</v>
       </c>
       <c r="D306" s="101" t="s">
-        <v>1399</v>
+        <v>1393</v>
       </c>
       <c r="F306" s="46" t="s">
         <v>1354</v>
       </c>
       <c r="G306" s="46"/>
     </row>
-    <row r="307" spans="1:26" s="87" customFormat="1" ht="19.75" customHeight="1">
+    <row r="307" spans="1:12" s="87" customFormat="1" ht="19.75" customHeight="1">
       <c r="A307" s="46" t="s">
-        <v>41</v>
+        <v>109</v>
       </c>
       <c r="B307" s="46" t="s">
-        <v>1356</v>
-      </c>
-      <c r="C307" s="88"/>
-      <c r="D307" s="88"/>
+        <v>1414</v>
+      </c>
+      <c r="C307" s="46" t="s">
+        <v>1276</v>
+      </c>
+      <c r="D307" s="46" t="s">
+        <v>1421</v>
+      </c>
       <c r="F307" s="88" t="s">
-        <v>1357</v>
+        <v>1415</v>
       </c>
       <c r="G307" s="46"/>
-      <c r="L307" s="101" t="s">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="308" spans="1:26" s="97" customFormat="1" ht="19.75" customHeight="1">
+      <c r="L307" s="101"/>
+    </row>
+    <row r="308" spans="1:12" s="97" customFormat="1" ht="19.75" customHeight="1">
       <c r="A308" s="46" t="s">
         <v>109</v>
       </c>
       <c r="B308" s="46" t="s">
-        <v>1413</v>
-      </c>
-      <c r="C308" s="88" t="s">
-        <v>1414</v>
-      </c>
-      <c r="D308" s="88"/>
-      <c r="F308" s="88"/>
+        <v>1422</v>
+      </c>
+      <c r="C308" s="46" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D308" s="46" t="s">
+        <v>1280</v>
+      </c>
+      <c r="F308" s="88" t="s">
+        <v>1416</v>
+      </c>
       <c r="G308" s="46"/>
       <c r="L308" s="101"/>
     </row>
-    <row r="309" spans="1:26" s="87" customFormat="1" ht="13">
+    <row r="309" spans="1:12" s="97" customFormat="1" ht="19.75" customHeight="1">
       <c r="A309" s="46" t="s">
         <v>109</v>
       </c>
       <c r="B309" s="46" t="s">
-        <v>1358</v>
-      </c>
-      <c r="C309" s="88" t="s">
-        <v>1359</v>
-      </c>
-      <c r="D309" s="101" t="s">
-        <v>1400</v>
-      </c>
-      <c r="F309" s="46" t="s">
-        <v>255</v>
+        <v>1423</v>
+      </c>
+      <c r="C309" s="46" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D309" s="46" t="s">
+        <v>1283</v>
+      </c>
+      <c r="F309" s="88" t="s">
+        <v>1417</v>
       </c>
       <c r="G309" s="46"/>
-    </row>
-    <row r="310" spans="1:26" s="87" customFormat="1" ht="13">
+      <c r="L309" s="101"/>
+    </row>
+    <row r="310" spans="1:12" s="97" customFormat="1" ht="19.75" customHeight="1">
       <c r="A310" s="46" t="s">
         <v>109</v>
       </c>
       <c r="B310" s="46" t="s">
-        <v>1360</v>
-      </c>
-      <c r="C310" s="88" t="s">
-        <v>1361</v>
-      </c>
-      <c r="D310" s="101" t="s">
-        <v>1401</v>
-      </c>
-      <c r="F310" s="46" t="s">
-        <v>1362</v>
+        <v>1424</v>
+      </c>
+      <c r="C310" s="46" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D310" s="46" t="s">
+        <v>1286</v>
+      </c>
+      <c r="F310" s="88" t="s">
+        <v>1418</v>
       </c>
       <c r="G310" s="46"/>
-    </row>
-    <row r="311" spans="1:26" s="87" customFormat="1" ht="13">
+      <c r="L310" s="101"/>
+    </row>
+    <row r="311" spans="1:12" s="97" customFormat="1" ht="19.75" customHeight="1">
       <c r="A311" s="46" t="s">
         <v>109</v>
       </c>
       <c r="B311" s="46" t="s">
-        <v>1363</v>
-      </c>
-      <c r="C311" s="88" t="s">
-        <v>1364</v>
-      </c>
-      <c r="D311" s="101" t="s">
-        <v>1402</v>
-      </c>
-      <c r="F311" s="46" t="s">
-        <v>1365</v>
+        <v>1425</v>
+      </c>
+      <c r="C311" s="46" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D311" s="46" t="s">
+        <v>1289</v>
+      </c>
+      <c r="F311" s="88" t="s">
+        <v>1419</v>
       </c>
       <c r="G311" s="46"/>
-    </row>
-    <row r="312" spans="1:26" s="87" customFormat="1" ht="13">
+      <c r="L311" s="101"/>
+    </row>
+    <row r="312" spans="1:12" s="97" customFormat="1" ht="19.75" customHeight="1">
       <c r="A312" s="46" t="s">
         <v>109</v>
       </c>
       <c r="B312" s="46" t="s">
-        <v>1369</v>
-      </c>
-      <c r="C312" s="88" t="s">
-        <v>1366</v>
-      </c>
-      <c r="D312" s="101" t="s">
-        <v>1403</v>
-      </c>
-      <c r="F312" s="46" t="s">
-        <v>1367</v>
+        <v>1426</v>
+      </c>
+      <c r="C312" s="46" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D312" s="46" t="s">
+        <v>446</v>
+      </c>
+      <c r="F312" s="88" t="s">
+        <v>1420</v>
       </c>
       <c r="G312" s="46"/>
-    </row>
-    <row r="313" spans="1:26" s="87" customFormat="1" ht="26">
+      <c r="L312" s="101"/>
+    </row>
+    <row r="313" spans="1:12" s="97" customFormat="1" ht="19.75" customHeight="1">
       <c r="A313" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="B313" s="88" t="s">
-        <v>1370</v>
-      </c>
-      <c r="C313" s="88" t="s">
-        <v>1368</v>
-      </c>
-      <c r="D313" s="101" t="s">
-        <v>1404</v>
-      </c>
-      <c r="F313" s="46" t="s">
-        <v>1371</v>
+      <c r="B313" s="46" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C313" s="46" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D313" s="46" t="s">
+        <v>1293</v>
+      </c>
+      <c r="F313" s="88" t="s">
+        <v>1431</v>
       </c>
       <c r="G313" s="46"/>
-    </row>
-    <row r="314" spans="1:26" s="87" customFormat="1" ht="13">
+      <c r="L313" s="101"/>
+    </row>
+    <row r="314" spans="1:12" s="87" customFormat="1" ht="13">
       <c r="A314" s="46" t="s">
         <v>109</v>
       </c>
       <c r="B314" s="46" t="s">
-        <v>1372</v>
+        <v>1356</v>
       </c>
       <c r="C314" s="88" t="s">
-        <v>1411</v>
-      </c>
-      <c r="D314" s="88" t="s">
-        <v>1411</v>
+        <v>1357</v>
+      </c>
+      <c r="D314" s="101" t="s">
+        <v>1394</v>
       </c>
       <c r="F314" s="46" t="s">
-        <v>1373</v>
+        <v>255</v>
       </c>
       <c r="G314" s="46"/>
-      <c r="M314" s="101" t="s">
-        <v>1412</v>
-      </c>
-    </row>
-    <row r="315" spans="1:26" s="87" customFormat="1" ht="13">
+    </row>
+    <row r="315" spans="1:12" s="87" customFormat="1" ht="13">
       <c r="A315" s="46" t="s">
         <v>109</v>
       </c>
       <c r="B315" s="46" t="s">
-        <v>1383</v>
+        <v>1358</v>
       </c>
       <c r="C315" s="88" t="s">
-        <v>1374</v>
+        <v>1359</v>
       </c>
       <c r="D315" s="101" t="s">
-        <v>1405</v>
+        <v>1395</v>
       </c>
       <c r="F315" s="46" t="s">
-        <v>1375</v>
+        <v>1360</v>
       </c>
       <c r="G315" s="46"/>
     </row>
-    <row r="316" spans="1:26" s="87" customFormat="1" ht="13">
+    <row r="316" spans="1:12" s="87" customFormat="1" ht="13">
       <c r="A316" s="46" t="s">
         <v>109</v>
       </c>
       <c r="B316" s="46" t="s">
-        <v>1394</v>
+        <v>1365</v>
       </c>
       <c r="C316" s="88" t="s">
-        <v>1406</v>
+        <v>1362</v>
       </c>
       <c r="D316" s="101" t="s">
-        <v>1407</v>
+        <v>1396</v>
       </c>
       <c r="F316" s="46" t="s">
-        <v>1376</v>
+        <v>1363</v>
       </c>
       <c r="G316" s="46"/>
     </row>
-    <row r="317" spans="1:26" s="87" customFormat="1" ht="13">
+    <row r="317" spans="1:12" s="87" customFormat="1" ht="26">
       <c r="A317" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="B317" s="46" t="s">
-        <v>1391</v>
+      <c r="B317" s="88" t="s">
+        <v>1366</v>
       </c>
       <c r="C317" s="88" t="s">
-        <v>1377</v>
+        <v>1364</v>
       </c>
       <c r="D317" s="101" t="s">
-        <v>1408</v>
+        <v>1397</v>
       </c>
       <c r="F317" s="46" t="s">
-        <v>1378</v>
+        <v>1367</v>
       </c>
       <c r="G317" s="46"/>
     </row>
-    <row r="318" spans="1:26" s="91" customFormat="1" ht="13">
+    <row r="318" spans="1:12" s="97" customFormat="1" ht="13">
       <c r="A318" s="46" t="s">
         <v>109</v>
       </c>
       <c r="B318" s="46" t="s">
-        <v>1392</v>
-      </c>
-      <c r="C318" s="88" t="s">
-        <v>1380</v>
-      </c>
-      <c r="D318" s="101" t="s">
-        <v>1409</v>
+        <v>1295</v>
+      </c>
+      <c r="C318" s="46" t="s">
+        <v>1296</v>
+      </c>
+      <c r="D318" s="46" t="s">
+        <v>1297</v>
       </c>
       <c r="F318" s="46" t="s">
-        <v>1382</v>
+        <v>1428</v>
       </c>
       <c r="G318" s="46"/>
     </row>
-    <row r="319" spans="1:26" s="91" customFormat="1" ht="13">
+    <row r="319" spans="1:12" s="97" customFormat="1" ht="13">
       <c r="A319" s="46" t="s">
         <v>109</v>
       </c>
       <c r="B319" s="46" t="s">
-        <v>1393</v>
-      </c>
-      <c r="C319" s="88" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C319" s="46" t="s">
+        <v>1299</v>
+      </c>
+      <c r="D319" s="46" t="s">
+        <v>1300</v>
+      </c>
+      <c r="F319" s="46" t="s">
+        <v>1427</v>
+      </c>
+      <c r="G319" s="46"/>
+    </row>
+    <row r="320" spans="1:12" s="97" customFormat="1" ht="13">
+      <c r="A320" s="46" t="s">
+        <v>109</v>
+      </c>
+      <c r="B320" s="46" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C320" s="46" t="s">
+        <v>1302</v>
+      </c>
+      <c r="D320" s="46" t="s">
+        <v>1303</v>
+      </c>
+      <c r="F320" s="46" t="s">
+        <v>1429</v>
+      </c>
+      <c r="G320" s="46"/>
+    </row>
+    <row r="321" spans="1:26" s="97" customFormat="1" ht="13">
+      <c r="A321" s="46" t="s">
+        <v>109</v>
+      </c>
+      <c r="B321" s="46" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C321" s="46" t="s">
+        <v>1305</v>
+      </c>
+      <c r="D321" s="46" t="s">
+        <v>1306</v>
+      </c>
+      <c r="F321" s="46" t="s">
+        <v>1430</v>
+      </c>
+      <c r="G321" s="46"/>
+    </row>
+    <row r="322" spans="1:26" s="87" customFormat="1" ht="13">
+      <c r="A322" s="46" t="s">
+        <v>109</v>
+      </c>
+      <c r="B322" s="46" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C322" s="88" t="s">
+        <v>1368</v>
+      </c>
+      <c r="D322" s="101" t="s">
+        <v>1398</v>
+      </c>
+      <c r="F322" s="46" t="s">
+        <v>1369</v>
+      </c>
+      <c r="G322" s="46"/>
+    </row>
+    <row r="323" spans="1:26" s="87" customFormat="1" ht="13">
+      <c r="A323" s="46" t="s">
+        <v>109</v>
+      </c>
+      <c r="B323" s="46" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C323" s="88" t="s">
+        <v>1399</v>
+      </c>
+      <c r="D323" s="101" t="s">
+        <v>1400</v>
+      </c>
+      <c r="F323" s="46" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G323" s="46"/>
+    </row>
+    <row r="324" spans="1:26" s="87" customFormat="1" ht="13">
+      <c r="A324" s="46" t="s">
+        <v>109</v>
+      </c>
+      <c r="B324" s="46" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C324" s="88" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D324" s="101" t="s">
+        <v>1401</v>
+      </c>
+      <c r="F324" s="46" t="s">
+        <v>1372</v>
+      </c>
+      <c r="G324" s="46"/>
+    </row>
+    <row r="325" spans="1:26" s="91" customFormat="1" ht="13">
+      <c r="A325" s="46" t="s">
+        <v>109</v>
+      </c>
+      <c r="B325" s="46" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C325" s="88" t="s">
+        <v>1374</v>
+      </c>
+      <c r="D325" s="101" t="s">
+        <v>1402</v>
+      </c>
+      <c r="F325" s="46" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G325" s="46"/>
+    </row>
+    <row r="326" spans="1:26" s="91" customFormat="1" ht="13">
+      <c r="A326" s="46" t="s">
+        <v>109</v>
+      </c>
+      <c r="B326" s="46" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C326" s="88" t="s">
+        <v>1373</v>
+      </c>
+      <c r="D326" s="101" t="s">
+        <v>1403</v>
+      </c>
+      <c r="F326" s="46" t="s">
+        <v>1375</v>
+      </c>
+      <c r="G326" s="46"/>
+    </row>
+    <row r="327" spans="1:26" s="87" customFormat="1" ht="26">
+      <c r="A327" s="92" t="s">
+        <v>109</v>
+      </c>
+      <c r="B327" s="92" t="s">
+        <v>831</v>
+      </c>
+      <c r="C327" s="92" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D327" s="93" t="s">
         <v>1379</v>
       </c>
-      <c r="D319" s="101" t="s">
-        <v>1410</v>
-      </c>
-      <c r="F319" s="46" t="s">
-        <v>1381</v>
-      </c>
-      <c r="G319" s="46"/>
-    </row>
-    <row r="320" spans="1:26" s="87" customFormat="1" ht="26">
-      <c r="A320" s="92" t="s">
-        <v>109</v>
-      </c>
-      <c r="B320" s="92" t="s">
-        <v>831</v>
-      </c>
-      <c r="C320" s="92" t="s">
-        <v>1384</v>
-      </c>
-      <c r="D320" s="93" t="s">
-        <v>1385</v>
-      </c>
-      <c r="E320" s="92"/>
-      <c r="F320" s="93" t="s">
-        <v>1386</v>
-      </c>
-      <c r="G320" s="92"/>
-      <c r="H320" s="92"/>
-      <c r="I320" s="92"/>
-      <c r="J320" s="92"/>
-      <c r="K320" s="92"/>
-      <c r="L320" s="92"/>
-      <c r="M320" s="92"/>
-      <c r="N320" s="92"/>
-      <c r="O320" s="92"/>
-      <c r="P320" s="92"/>
-      <c r="Q320" s="92"/>
-      <c r="R320" s="92"/>
-      <c r="S320" s="92"/>
-      <c r="T320" s="92"/>
-      <c r="U320" s="92"/>
-      <c r="V320" s="92"/>
-      <c r="W320" s="92"/>
-      <c r="X320" s="92"/>
-      <c r="Y320" s="92"/>
-      <c r="Z320" s="92"/>
-    </row>
-    <row r="321" spans="1:26" s="87" customFormat="1" ht="13">
-      <c r="A321" s="92" t="s">
-        <v>109</v>
-      </c>
-      <c r="B321" s="92" t="s">
-        <v>832</v>
-      </c>
-      <c r="C321" s="92" t="s">
-        <v>1395</v>
-      </c>
-      <c r="D321" s="93" t="s">
-        <v>833</v>
-      </c>
-      <c r="E321" s="92"/>
-      <c r="F321" s="92" t="s">
-        <v>834</v>
-      </c>
-      <c r="G321" s="92"/>
-      <c r="H321" s="92"/>
-      <c r="I321" s="92"/>
-      <c r="J321" s="92"/>
-      <c r="K321" s="92"/>
-      <c r="L321" s="92"/>
-      <c r="M321" s="92"/>
-      <c r="N321" s="92"/>
-      <c r="O321" s="92"/>
-      <c r="P321" s="92"/>
-      <c r="Q321" s="92"/>
-      <c r="R321" s="92"/>
-      <c r="S321" s="92"/>
-      <c r="T321" s="92"/>
-      <c r="U321" s="92"/>
-      <c r="V321" s="92"/>
-      <c r="W321" s="92"/>
-      <c r="X321" s="92"/>
-      <c r="Y321" s="92"/>
-      <c r="Z321" s="92"/>
-    </row>
-    <row r="322" spans="1:26" ht="13">
-      <c r="A322" s="92" t="s">
-        <v>109</v>
-      </c>
-      <c r="B322" s="92" t="s">
-        <v>835</v>
-      </c>
-      <c r="C322" s="92" t="s">
-        <v>836</v>
-      </c>
-      <c r="D322" s="94" t="s">
-        <v>837</v>
-      </c>
-      <c r="E322" s="92"/>
-      <c r="F322" s="95" t="s">
-        <v>838</v>
-      </c>
-      <c r="G322" s="92" t="s">
-        <v>839</v>
-      </c>
-      <c r="H322" s="92"/>
-      <c r="I322" s="92"/>
-      <c r="J322" s="92"/>
-      <c r="K322" s="92"/>
-      <c r="L322" s="92"/>
-      <c r="M322" s="92"/>
-      <c r="N322" s="92"/>
-      <c r="O322" s="92"/>
-      <c r="P322" s="92"/>
-      <c r="Q322" s="92"/>
-      <c r="R322" s="92"/>
-      <c r="S322" s="92"/>
-      <c r="T322" s="92"/>
-      <c r="U322" s="92"/>
-      <c r="V322" s="92"/>
-      <c r="W322" s="92"/>
-      <c r="X322" s="92"/>
-      <c r="Y322" s="92"/>
-      <c r="Z322" s="92"/>
-    </row>
-    <row r="323" spans="1:26" ht="28.5">
-      <c r="A323" s="92" t="s">
-        <v>109</v>
-      </c>
-      <c r="B323" s="92" t="s">
-        <v>840</v>
-      </c>
-      <c r="C323" s="92" t="s">
-        <v>1387</v>
-      </c>
-      <c r="D323" s="92" t="s">
-        <v>1388</v>
-      </c>
-      <c r="E323" s="92"/>
-      <c r="F323" s="96" t="s">
-        <v>1389</v>
-      </c>
-      <c r="G323" s="92" t="s">
-        <v>839</v>
-      </c>
-      <c r="H323" s="92"/>
-      <c r="I323" s="92"/>
-      <c r="J323" s="92"/>
-      <c r="K323" s="92"/>
-      <c r="L323" s="92"/>
-      <c r="M323" s="92"/>
-      <c r="N323" s="92"/>
-      <c r="O323" s="92"/>
-      <c r="P323" s="92"/>
-      <c r="Q323" s="92"/>
-      <c r="R323" s="92"/>
-      <c r="S323" s="92"/>
-      <c r="T323" s="92"/>
-      <c r="U323" s="92"/>
-      <c r="V323" s="92"/>
-      <c r="W323" s="92"/>
-      <c r="X323" s="92"/>
-      <c r="Y323" s="92"/>
-      <c r="Z323" s="92"/>
-    </row>
-    <row r="324" spans="1:26" ht="13">
-      <c r="A324" s="92" t="s">
-        <v>109</v>
-      </c>
-      <c r="B324" s="92" t="s">
-        <v>841</v>
-      </c>
-      <c r="C324" s="92" t="s">
-        <v>1390</v>
-      </c>
-      <c r="D324" s="93" t="s">
-        <v>842</v>
-      </c>
-      <c r="E324" s="92"/>
-      <c r="F324" s="92" t="s">
-        <v>843</v>
-      </c>
-      <c r="G324" s="92" t="s">
-        <v>839</v>
-      </c>
-      <c r="H324" s="92"/>
-      <c r="I324" s="92"/>
-      <c r="J324" s="92"/>
-      <c r="K324" s="92"/>
-      <c r="L324" s="92"/>
-      <c r="M324" s="92"/>
-      <c r="N324" s="92"/>
-      <c r="O324" s="92"/>
-      <c r="P324" s="92"/>
-      <c r="Q324" s="92"/>
-      <c r="R324" s="92"/>
-      <c r="S324" s="92"/>
-      <c r="T324" s="92"/>
-      <c r="U324" s="92"/>
-      <c r="V324" s="92"/>
-      <c r="W324" s="92"/>
-      <c r="X324" s="92"/>
-      <c r="Y324" s="92"/>
-      <c r="Z324" s="92"/>
-    </row>
-    <row r="325" spans="1:26" s="89" customFormat="1" ht="13">
-      <c r="A325" s="46" t="s">
-        <v>113</v>
-      </c>
-      <c r="B325" s="46" t="s">
-        <v>827</v>
-      </c>
-      <c r="C325" s="46"/>
-      <c r="D325" s="46"/>
-      <c r="F325" s="46"/>
-      <c r="G325" s="46"/>
-    </row>
-    <row r="326" spans="1:26" s="89" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A326" s="92" t="s">
-        <v>41</v>
-      </c>
-      <c r="B326" s="92" t="s">
-        <v>844</v>
-      </c>
-      <c r="C326" s="92"/>
-      <c r="D326" s="92"/>
-      <c r="E326" s="92"/>
-      <c r="F326" s="92"/>
-      <c r="G326" s="92"/>
-      <c r="H326" s="92"/>
-      <c r="I326" s="92"/>
-      <c r="J326" s="92"/>
-      <c r="K326" s="92"/>
-      <c r="L326" s="92" t="s">
-        <v>845</v>
-      </c>
-      <c r="M326" s="92"/>
-      <c r="N326" s="92"/>
-      <c r="O326" s="92"/>
-      <c r="P326" s="92"/>
-      <c r="Q326" s="92"/>
-      <c r="R326" s="92"/>
-      <c r="S326" s="92"/>
-      <c r="T326" s="92"/>
-      <c r="U326" s="92"/>
-      <c r="V326" s="92"/>
-      <c r="W326" s="92"/>
-      <c r="X326" s="92"/>
-      <c r="Y326" s="92"/>
-      <c r="Z326" s="92"/>
-    </row>
-    <row r="327" spans="1:26" ht="13">
-      <c r="A327" s="92" t="s">
-        <v>41</v>
-      </c>
-      <c r="B327" s="92" t="s">
-        <v>846</v>
-      </c>
-      <c r="C327" s="92"/>
-      <c r="D327" s="92"/>
       <c r="E327" s="92"/>
-      <c r="F327" s="92"/>
+      <c r="F327" s="93" t="s">
+        <v>1380</v>
+      </c>
       <c r="G327" s="92"/>
       <c r="H327" s="92"/>
       <c r="I327" s="92"/>
       <c r="J327" s="92"/>
       <c r="K327" s="92"/>
-      <c r="L327" s="92" t="s">
-        <v>847</v>
-      </c>
+      <c r="L327" s="92"/>
       <c r="M327" s="92"/>
       <c r="N327" s="92"/>
       <c r="O327" s="92"/>
@@ -16264,25 +16178,29 @@
       <c r="Y327" s="92"/>
       <c r="Z327" s="92"/>
     </row>
-    <row r="328" spans="1:26" ht="13">
+    <row r="328" spans="1:26" s="87" customFormat="1" ht="13">
       <c r="A328" s="92" t="s">
-        <v>41</v>
+        <v>109</v>
       </c>
       <c r="B328" s="92" t="s">
-        <v>848</v>
-      </c>
-      <c r="C328" s="92"/>
-      <c r="D328" s="92"/>
+        <v>832</v>
+      </c>
+      <c r="C328" s="92" t="s">
+        <v>1389</v>
+      </c>
+      <c r="D328" s="93" t="s">
+        <v>833</v>
+      </c>
       <c r="E328" s="92"/>
-      <c r="F328" s="92"/>
+      <c r="F328" s="92" t="s">
+        <v>834</v>
+      </c>
       <c r="G328" s="92"/>
       <c r="H328" s="92"/>
       <c r="I328" s="92"/>
       <c r="J328" s="92"/>
       <c r="K328" s="92"/>
-      <c r="L328" s="92" t="s">
-        <v>849</v>
-      </c>
+      <c r="L328" s="92"/>
       <c r="M328" s="92"/>
       <c r="N328" s="92"/>
       <c r="O328" s="92"/>
@@ -16300,23 +16218,29 @@
     </row>
     <row r="329" spans="1:26" ht="13">
       <c r="A329" s="92" t="s">
-        <v>41</v>
+        <v>109</v>
       </c>
       <c r="B329" s="92" t="s">
-        <v>850</v>
-      </c>
-      <c r="C329" s="92"/>
-      <c r="D329" s="92"/>
+        <v>835</v>
+      </c>
+      <c r="C329" s="92" t="s">
+        <v>836</v>
+      </c>
+      <c r="D329" s="94" t="s">
+        <v>837</v>
+      </c>
       <c r="E329" s="92"/>
-      <c r="F329" s="92"/>
-      <c r="G329" s="92"/>
+      <c r="F329" s="95" t="s">
+        <v>838</v>
+      </c>
+      <c r="G329" s="92" t="s">
+        <v>839</v>
+      </c>
       <c r="H329" s="92"/>
       <c r="I329" s="92"/>
       <c r="J329" s="92"/>
       <c r="K329" s="92"/>
-      <c r="L329" s="92" t="s">
-        <v>851</v>
-      </c>
+      <c r="L329" s="92"/>
       <c r="M329" s="92"/>
       <c r="N329" s="92"/>
       <c r="O329" s="92"/>
@@ -16332,25 +16256,31 @@
       <c r="Y329" s="92"/>
       <c r="Z329" s="92"/>
     </row>
-    <row r="330" spans="1:26" ht="13">
+    <row r="330" spans="1:26" ht="28.5">
       <c r="A330" s="92" t="s">
-        <v>41</v>
+        <v>109</v>
       </c>
       <c r="B330" s="92" t="s">
-        <v>852</v>
-      </c>
-      <c r="C330" s="92"/>
-      <c r="D330" s="92"/>
+        <v>840</v>
+      </c>
+      <c r="C330" s="92" t="s">
+        <v>1381</v>
+      </c>
+      <c r="D330" s="92" t="s">
+        <v>1382</v>
+      </c>
       <c r="E330" s="92"/>
-      <c r="F330" s="92"/>
-      <c r="G330" s="92"/>
+      <c r="F330" s="96" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G330" s="92" t="s">
+        <v>839</v>
+      </c>
       <c r="H330" s="92"/>
       <c r="I330" s="92"/>
       <c r="J330" s="92"/>
       <c r="K330" s="92"/>
-      <c r="L330" s="92" t="s">
-        <v>853</v>
-      </c>
+      <c r="L330" s="92"/>
       <c r="M330" s="92"/>
       <c r="N330" s="92"/>
       <c r="O330" s="92"/>
@@ -16367,12 +16297,234 @@
       <c r="Z330" s="92"/>
     </row>
     <row r="331" spans="1:26" ht="13">
-      <c r="A331" s="2"/>
-      <c r="L331" s="2"/>
-    </row>
-    <row r="332" spans="1:26" ht="13">
-      <c r="A332" s="2"/>
-      <c r="L332" s="2"/>
+      <c r="A331" s="92" t="s">
+        <v>109</v>
+      </c>
+      <c r="B331" s="92" t="s">
+        <v>841</v>
+      </c>
+      <c r="C331" s="92" t="s">
+        <v>1384</v>
+      </c>
+      <c r="D331" s="93" t="s">
+        <v>842</v>
+      </c>
+      <c r="E331" s="92"/>
+      <c r="F331" s="92" t="s">
+        <v>843</v>
+      </c>
+      <c r="G331" s="92" t="s">
+        <v>839</v>
+      </c>
+      <c r="H331" s="92"/>
+      <c r="I331" s="92"/>
+      <c r="J331" s="92"/>
+      <c r="K331" s="92"/>
+      <c r="L331" s="92"/>
+      <c r="M331" s="92"/>
+      <c r="N331" s="92"/>
+      <c r="O331" s="92"/>
+      <c r="P331" s="92"/>
+      <c r="Q331" s="92"/>
+      <c r="R331" s="92"/>
+      <c r="S331" s="92"/>
+      <c r="T331" s="92"/>
+      <c r="U331" s="92"/>
+      <c r="V331" s="92"/>
+      <c r="W331" s="92"/>
+      <c r="X331" s="92"/>
+      <c r="Y331" s="92"/>
+      <c r="Z331" s="92"/>
+    </row>
+    <row r="332" spans="1:26" s="89" customFormat="1" ht="13">
+      <c r="A332" s="46" t="s">
+        <v>113</v>
+      </c>
+      <c r="B332" s="46" t="s">
+        <v>827</v>
+      </c>
+      <c r="C332" s="46"/>
+      <c r="D332" s="46"/>
+      <c r="F332" s="46"/>
+      <c r="G332" s="46"/>
+    </row>
+    <row r="333" spans="1:26" s="89" customFormat="1" ht="25.5" customHeight="1">
+      <c r="A333" s="92" t="s">
+        <v>41</v>
+      </c>
+      <c r="B333" s="92" t="s">
+        <v>844</v>
+      </c>
+      <c r="C333" s="92"/>
+      <c r="D333" s="92"/>
+      <c r="E333" s="92"/>
+      <c r="F333" s="92"/>
+      <c r="G333" s="92"/>
+      <c r="H333" s="92"/>
+      <c r="I333" s="92"/>
+      <c r="J333" s="92"/>
+      <c r="K333" s="92"/>
+      <c r="L333" s="92" t="s">
+        <v>845</v>
+      </c>
+      <c r="M333" s="92"/>
+      <c r="N333" s="92"/>
+      <c r="O333" s="92"/>
+      <c r="P333" s="92"/>
+      <c r="Q333" s="92"/>
+      <c r="R333" s="92"/>
+      <c r="S333" s="92"/>
+      <c r="T333" s="92"/>
+      <c r="U333" s="92"/>
+      <c r="V333" s="92"/>
+      <c r="W333" s="92"/>
+      <c r="X333" s="92"/>
+      <c r="Y333" s="92"/>
+      <c r="Z333" s="92"/>
+    </row>
+    <row r="334" spans="1:26" ht="13">
+      <c r="A334" s="92" t="s">
+        <v>41</v>
+      </c>
+      <c r="B334" s="92" t="s">
+        <v>846</v>
+      </c>
+      <c r="C334" s="92"/>
+      <c r="D334" s="92"/>
+      <c r="E334" s="92"/>
+      <c r="F334" s="92"/>
+      <c r="G334" s="92"/>
+      <c r="H334" s="92"/>
+      <c r="I334" s="92"/>
+      <c r="J334" s="92"/>
+      <c r="K334" s="92"/>
+      <c r="L334" s="92" t="s">
+        <v>847</v>
+      </c>
+      <c r="M334" s="92"/>
+      <c r="N334" s="92"/>
+      <c r="O334" s="92"/>
+      <c r="P334" s="92"/>
+      <c r="Q334" s="92"/>
+      <c r="R334" s="92"/>
+      <c r="S334" s="92"/>
+      <c r="T334" s="92"/>
+      <c r="U334" s="92"/>
+      <c r="V334" s="92"/>
+      <c r="W334" s="92"/>
+      <c r="X334" s="92"/>
+      <c r="Y334" s="92"/>
+      <c r="Z334" s="92"/>
+    </row>
+    <row r="335" spans="1:26" ht="13">
+      <c r="A335" s="92" t="s">
+        <v>41</v>
+      </c>
+      <c r="B335" s="92" t="s">
+        <v>848</v>
+      </c>
+      <c r="C335" s="92"/>
+      <c r="D335" s="92"/>
+      <c r="E335" s="92"/>
+      <c r="F335" s="92"/>
+      <c r="G335" s="92"/>
+      <c r="H335" s="92"/>
+      <c r="I335" s="92"/>
+      <c r="J335" s="92"/>
+      <c r="K335" s="92"/>
+      <c r="L335" s="92" t="s">
+        <v>849</v>
+      </c>
+      <c r="M335" s="92"/>
+      <c r="N335" s="92"/>
+      <c r="O335" s="92"/>
+      <c r="P335" s="92"/>
+      <c r="Q335" s="92"/>
+      <c r="R335" s="92"/>
+      <c r="S335" s="92"/>
+      <c r="T335" s="92"/>
+      <c r="U335" s="92"/>
+      <c r="V335" s="92"/>
+      <c r="W335" s="92"/>
+      <c r="X335" s="92"/>
+      <c r="Y335" s="92"/>
+      <c r="Z335" s="92"/>
+    </row>
+    <row r="336" spans="1:26" ht="13">
+      <c r="A336" s="92" t="s">
+        <v>41</v>
+      </c>
+      <c r="B336" s="92" t="s">
+        <v>850</v>
+      </c>
+      <c r="C336" s="92"/>
+      <c r="D336" s="92"/>
+      <c r="E336" s="92"/>
+      <c r="F336" s="92"/>
+      <c r="G336" s="92"/>
+      <c r="H336" s="92"/>
+      <c r="I336" s="92"/>
+      <c r="J336" s="92"/>
+      <c r="K336" s="92"/>
+      <c r="L336" s="92" t="s">
+        <v>851</v>
+      </c>
+      <c r="M336" s="92"/>
+      <c r="N336" s="92"/>
+      <c r="O336" s="92"/>
+      <c r="P336" s="92"/>
+      <c r="Q336" s="92"/>
+      <c r="R336" s="92"/>
+      <c r="S336" s="92"/>
+      <c r="T336" s="92"/>
+      <c r="U336" s="92"/>
+      <c r="V336" s="92"/>
+      <c r="W336" s="92"/>
+      <c r="X336" s="92"/>
+      <c r="Y336" s="92"/>
+      <c r="Z336" s="92"/>
+    </row>
+    <row r="337" spans="1:26" ht="13">
+      <c r="A337" s="92" t="s">
+        <v>41</v>
+      </c>
+      <c r="B337" s="92" t="s">
+        <v>852</v>
+      </c>
+      <c r="C337" s="92"/>
+      <c r="D337" s="92"/>
+      <c r="E337" s="92"/>
+      <c r="F337" s="92"/>
+      <c r="G337" s="92"/>
+      <c r="H337" s="92"/>
+      <c r="I337" s="92"/>
+      <c r="J337" s="92"/>
+      <c r="K337" s="92"/>
+      <c r="L337" s="92" t="s">
+        <v>853</v>
+      </c>
+      <c r="M337" s="92"/>
+      <c r="N337" s="92"/>
+      <c r="O337" s="92"/>
+      <c r="P337" s="92"/>
+      <c r="Q337" s="92"/>
+      <c r="R337" s="92"/>
+      <c r="S337" s="92"/>
+      <c r="T337" s="92"/>
+      <c r="U337" s="92"/>
+      <c r="V337" s="92"/>
+      <c r="W337" s="92"/>
+      <c r="X337" s="92"/>
+      <c r="Y337" s="92"/>
+      <c r="Z337" s="92"/>
+    </row>
+    <row r="338" spans="1:26" ht="13">
+      <c r="A338" s="2"/>
+      <c r="L338" s="2"/>
+    </row>
+    <row r="339" spans="1:26" ht="13">
+      <c r="A339" s="2"/>
+      <c r="L339" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -21292,7 +21444,7 @@
       </c>
     </row>
     <row r="212" spans="1:4" ht="13">
-      <c r="A212" s="7" t="s">
+      <c r="A212" s="46" t="s">
         <v>281</v>
       </c>
       <c r="B212" s="2" t="s">

--- a/forms/app/pregnancy.xlsx
+++ b/forms/app/pregnancy.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2477" uniqueCount="1432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2478" uniqueCount="1433">
   <si>
     <t>type</t>
   </si>
@@ -4503,6 +4503,9 @@
   </si>
   <si>
     <t>selected(${delivery_complications},'big_baby') or selected(${big_baby},"yes")</t>
+  </si>
+  <si>
+    <t>selected(${local_herbs},'no')</t>
   </si>
 </sst>
 </file>
@@ -14011,7 +14014,9 @@
         <v>301</v>
       </c>
       <c r="E246" s="56"/>
-      <c r="F246" s="56"/>
+      <c r="F246" s="69" t="s">
+        <v>1432</v>
+      </c>
       <c r="G246" s="56"/>
       <c r="H246" s="56"/>
       <c r="I246" s="56"/>
@@ -21767,6 +21772,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/forms/app/pregnancy.xlsx
+++ b/forms/app/pregnancy.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2478" uniqueCount="1433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2481" uniqueCount="1436">
   <si>
     <t>type</t>
   </si>
@@ -1025,9 +1025,6 @@
   </si>
   <si>
     <t xml:space="preserve">Is the client's partner present during this visit? </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Je, </t>
   </si>
   <si>
     <t>allow_partner_to_deliver_facility</t>
@@ -2694,9 +2691,6 @@
     <t>needs_referral_note</t>
   </si>
   <si>
-    <t>Unatakiwa uende kituo cha afya kutokana na sababu zifuatazo:</t>
-  </si>
-  <si>
     <t>${has_referral}=1</t>
   </si>
   <si>
@@ -4506,6 +4500,23 @@
   </si>
   <si>
     <t>selected(${local_herbs},'no')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je, mwenza wa mteja wako amehudhuria katika tembeleo hili? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je, mwenza wako kakuruhusu kujifungulia katika kituo cha afya na je atakusaidia kupata usafiri na pia kuhifadhi/kutunza pesa ya kulipia usafiri na gharama nyengine? </t>
+  </si>
+  <si>
+    <t>Muulize mwenza: Je, utamruhusu ${client_name} kujifungulia katika kituo cha afya? 
+Hii inamaanisha kumsaidia kupata usafiri na pia katika kuhifadhi/kutunza pesa ya kulipia usafiri na gharama nyingine pia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;strong&gt; Una hali hatarish za wajawazito zifuatazo:&lt;/strong&gt;
+</t>
+  </si>
+  <si>
+    <t>&lt;strong&gt;Unatakiwa uende kituo cha afya kutokana na sababu zifuatazo:&lt;/strong&gt;</t>
   </si>
 </sst>
 </file>
@@ -7627,10 +7638,10 @@
         <v>165</v>
       </c>
       <c r="C75" s="88" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="D75" s="46" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="E75" s="6"/>
       <c r="F75" s="4"/>
@@ -8673,7 +8684,7 @@
         <v>139</v>
       </c>
       <c r="F103" s="34" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="G103" s="20"/>
       <c r="H103" s="8"/>
@@ -8713,7 +8724,7 @@
         <v>139</v>
       </c>
       <c r="F104" s="34" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="G104" s="20"/>
       <c r="H104" s="8"/>
@@ -8753,7 +8764,7 @@
         <v>139</v>
       </c>
       <c r="F105" s="34" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="G105" s="20"/>
       <c r="H105" s="8"/>
@@ -8839,7 +8850,7 @@
         <v>139</v>
       </c>
       <c r="F107" s="34" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="G107" s="20"/>
       <c r="H107" s="8"/>
@@ -9113,7 +9124,7 @@
         <v>139</v>
       </c>
       <c r="F114" s="47" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="G114" s="20"/>
       <c r="H114" s="8"/>
@@ -9262,8 +9273,8 @@
       <c r="C118" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="D118" s="7" t="s">
-        <v>320</v>
+      <c r="D118" s="46" t="s">
+        <v>1431</v>
       </c>
       <c r="E118" s="7" t="s">
         <v>139</v>
@@ -9292,22 +9303,24 @@
       <c r="Y118" s="9"/>
       <c r="Z118" s="9"/>
     </row>
-    <row r="119" spans="1:26" ht="13">
+    <row r="119" spans="1:26" ht="65">
       <c r="A119" s="7" t="s">
         <v>135</v>
       </c>
       <c r="B119" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="C119" s="88" t="s">
         <v>321</v>
       </c>
-      <c r="C119" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="D119" s="20"/>
+      <c r="D119" s="88" t="s">
+        <v>1433</v>
+      </c>
       <c r="E119" s="7" t="s">
         <v>139</v>
       </c>
       <c r="F119" s="34" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G119" s="20"/>
       <c r="H119" s="8"/>
@@ -9332,20 +9345,22 @@
     </row>
     <row r="120" spans="1:26" ht="13">
       <c r="A120" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="B120" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="B120" s="7" t="s">
+      <c r="C120" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="C120" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="D120" s="20"/>
+      <c r="D120" s="46" t="s">
+        <v>1432</v>
+      </c>
       <c r="E120" s="7" t="s">
         <v>139</v>
       </c>
       <c r="F120" s="34" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G120" s="20"/>
       <c r="H120" s="8"/>
@@ -9373,7 +9388,7 @@
         <v>109</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C121" s="7" t="s">
         <v>292</v>
@@ -9383,7 +9398,7 @@
       </c>
       <c r="E121" s="7"/>
       <c r="F121" s="34" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G121" s="20"/>
       <c r="H121" s="8"/>
@@ -9411,17 +9426,17 @@
         <v>109</v>
       </c>
       <c r="B122" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="C122" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="C122" s="7" t="s">
+      <c r="D122" s="7" t="s">
         <v>331</v>
-      </c>
-      <c r="D122" s="7" t="s">
-        <v>332</v>
       </c>
       <c r="E122" s="20"/>
       <c r="F122" s="34" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G122" s="20"/>
       <c r="H122" s="8"/>
@@ -9481,16 +9496,16 @@
         <v>19</v>
       </c>
       <c r="B124" s="20" t="s">
+        <v>333</v>
+      </c>
+      <c r="C124" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="C124" s="7" t="s">
+      <c r="D124" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="D124" s="7" t="s">
+      <c r="F124" s="34" t="s">
         <v>336</v>
-      </c>
-      <c r="F124" s="34" t="s">
-        <v>337</v>
       </c>
       <c r="G124" s="20" t="s">
         <v>117</v>
@@ -9520,13 +9535,13 @@
         <v>109</v>
       </c>
       <c r="B125" s="27" t="s">
+        <v>337</v>
+      </c>
+      <c r="C125" s="48" t="s">
         <v>338</v>
       </c>
-      <c r="C125" s="48" t="s">
+      <c r="D125" s="49" t="s">
         <v>339</v>
-      </c>
-      <c r="D125" s="49" t="s">
-        <v>340</v>
       </c>
       <c r="E125" s="27"/>
       <c r="F125" s="27"/>
@@ -9556,13 +9571,13 @@
         <v>135</v>
       </c>
       <c r="B126" s="20" t="s">
+        <v>340</v>
+      </c>
+      <c r="C126" s="20" t="s">
         <v>341</v>
       </c>
-      <c r="C126" s="20" t="s">
+      <c r="D126" s="7" t="s">
         <v>342</v>
-      </c>
-      <c r="D126" s="7" t="s">
-        <v>343</v>
       </c>
       <c r="E126" s="20" t="s">
         <v>139</v>
@@ -9594,19 +9609,19 @@
         <v>135</v>
       </c>
       <c r="B127" s="20" t="s">
+        <v>343</v>
+      </c>
+      <c r="C127" s="20" t="s">
         <v>344</v>
       </c>
-      <c r="C127" s="20" t="s">
+      <c r="D127" s="7" t="s">
         <v>345</v>
-      </c>
-      <c r="D127" s="7" t="s">
-        <v>346</v>
       </c>
       <c r="E127" s="20" t="s">
         <v>139</v>
       </c>
       <c r="F127" s="34" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G127" s="20"/>
       <c r="H127" s="8"/>
@@ -9634,30 +9649,30 @@
         <v>220</v>
       </c>
       <c r="B128" s="20" t="s">
+        <v>347</v>
+      </c>
+      <c r="C128" s="20" t="s">
         <v>348</v>
       </c>
-      <c r="C128" s="20" t="s">
+      <c r="D128" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="D128" s="7" t="s">
-        <v>350</v>
       </c>
       <c r="E128" s="20" t="s">
         <v>139</v>
       </c>
       <c r="F128" s="47" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G128" s="20"/>
       <c r="H128" s="8"/>
       <c r="I128" s="13" t="s">
+        <v>351</v>
+      </c>
+      <c r="J128" s="8" t="s">
         <v>352</v>
       </c>
-      <c r="J128" s="8" t="s">
+      <c r="K128" s="7" t="s">
         <v>353</v>
-      </c>
-      <c r="K128" s="7" t="s">
-        <v>354</v>
       </c>
       <c r="L128" s="8"/>
       <c r="M128" s="8"/>
@@ -9680,19 +9695,19 @@
         <v>135</v>
       </c>
       <c r="B129" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="C129" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="C129" s="7" t="s">
+      <c r="D129" s="7" t="s">
         <v>356</v>
-      </c>
-      <c r="D129" s="7" t="s">
-        <v>357</v>
       </c>
       <c r="E129" s="7" t="s">
         <v>139</v>
       </c>
       <c r="F129" s="34" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G129" s="20"/>
       <c r="H129" s="8"/>
@@ -9720,29 +9735,29 @@
         <v>220</v>
       </c>
       <c r="B130" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="C130" s="7" t="s">
         <v>359</v>
       </c>
-      <c r="C130" s="7" t="s">
+      <c r="D130" s="7" t="s">
         <v>360</v>
-      </c>
-      <c r="D130" s="7" t="s">
-        <v>361</v>
       </c>
       <c r="E130" s="7" t="s">
         <v>139</v>
       </c>
       <c r="F130" s="34" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H130" s="8"/>
       <c r="I130" s="13" t="s">
+        <v>362</v>
+      </c>
+      <c r="J130" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="J130" s="7" t="s">
+      <c r="K130" s="7" t="s">
         <v>364</v>
-      </c>
-      <c r="K130" s="7" t="s">
-        <v>365</v>
       </c>
       <c r="L130" s="8"/>
       <c r="M130" s="8"/>
@@ -9765,30 +9780,30 @@
         <v>236</v>
       </c>
       <c r="B131" s="20" t="s">
+        <v>365</v>
+      </c>
+      <c r="C131" s="7" t="s">
         <v>366</v>
       </c>
-      <c r="C131" s="7" t="s">
+      <c r="D131" s="7" t="s">
         <v>367</v>
-      </c>
-      <c r="D131" s="7" t="s">
-        <v>368</v>
       </c>
       <c r="E131" s="20" t="s">
         <v>139</v>
       </c>
       <c r="F131" s="34" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G131" s="20"/>
       <c r="H131" s="8"/>
       <c r="I131" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="J131" s="8" t="s">
         <v>370</v>
       </c>
-      <c r="J131" s="8" t="s">
+      <c r="K131" s="7" t="s">
         <v>371</v>
-      </c>
-      <c r="K131" s="7" t="s">
-        <v>372</v>
       </c>
       <c r="L131" s="8"/>
       <c r="M131" s="8"/>
@@ -9811,17 +9826,17 @@
         <v>109</v>
       </c>
       <c r="B132" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="C132" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="C132" s="2" t="s">
+      <c r="D132" s="2" t="s">
         <v>374</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>375</v>
       </c>
       <c r="E132" s="7"/>
       <c r="F132" s="34" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G132" s="7"/>
       <c r="H132" s="8"/>
@@ -9849,19 +9864,19 @@
         <v>135</v>
       </c>
       <c r="B133" s="46" t="s">
+        <v>376</v>
+      </c>
+      <c r="C133" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="C133" s="7" t="s">
+      <c r="D133" s="7" t="s">
         <v>378</v>
-      </c>
-      <c r="D133" s="7" t="s">
-        <v>379</v>
       </c>
       <c r="E133" s="7" t="s">
         <v>139</v>
       </c>
       <c r="F133" s="34" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G133" s="20"/>
       <c r="H133" s="8"/>
@@ -9892,7 +9907,7 @@
         <v>251</v>
       </c>
       <c r="C134" s="7" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D134" s="7" t="s">
         <v>253</v>
@@ -9901,7 +9916,7 @@
         <v>254</v>
       </c>
       <c r="F134" s="34" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G134" s="20"/>
       <c r="H134" s="8"/>
@@ -9929,19 +9944,19 @@
         <v>135</v>
       </c>
       <c r="B135" s="46" t="s">
+        <v>382</v>
+      </c>
+      <c r="C135" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="C135" s="7" t="s">
-        <v>384</v>
-      </c>
       <c r="D135" s="46" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="E135" s="7" t="s">
         <v>139</v>
       </c>
       <c r="F135" s="34" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G135" s="20"/>
       <c r="H135" s="8"/>
@@ -9969,19 +9984,19 @@
         <v>135</v>
       </c>
       <c r="B136" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="C136" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="C136" s="7" t="s">
-        <v>386</v>
-      </c>
       <c r="D136" s="102" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="E136" s="46" t="s">
         <v>139</v>
       </c>
       <c r="F136" s="34" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G136" s="20"/>
       <c r="H136" s="8"/>
@@ -10009,19 +10024,19 @@
         <v>135</v>
       </c>
       <c r="B137" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="C137" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="C137" s="7" t="s">
-        <v>388</v>
-      </c>
       <c r="D137" s="46" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="E137" s="46" t="s">
         <v>139</v>
       </c>
       <c r="F137" s="34" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G137" s="20"/>
       <c r="H137" s="8"/>
@@ -10049,7 +10064,7 @@
         <v>109</v>
       </c>
       <c r="B138" s="7" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C138" s="7" t="s">
         <v>292</v>
@@ -10061,7 +10076,7 @@
         <v>139</v>
       </c>
       <c r="F138" s="34" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G138" s="20"/>
       <c r="H138" s="8"/>
@@ -10086,22 +10101,22 @@
     </row>
     <row r="139" spans="1:26" ht="13">
       <c r="A139" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="B139" s="7" t="s">
         <v>391</v>
       </c>
-      <c r="B139" s="7" t="s">
+      <c r="C139" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="C139" s="7" t="s">
+      <c r="D139" s="7" t="s">
         <v>393</v>
-      </c>
-      <c r="D139" s="7" t="s">
-        <v>394</v>
       </c>
       <c r="E139" s="7" t="s">
         <v>139</v>
       </c>
       <c r="F139" s="34" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G139" s="20"/>
       <c r="H139" s="8"/>
@@ -10135,13 +10150,13 @@
         <v>135</v>
       </c>
       <c r="B140" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="C140" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="C140" s="7" t="s">
+      <c r="D140" s="7" t="s">
         <v>397</v>
-      </c>
-      <c r="D140" s="7" t="s">
-        <v>398</v>
       </c>
       <c r="E140" s="7" t="s">
         <v>139</v>
@@ -10172,17 +10187,17 @@
         <v>109</v>
       </c>
       <c r="B141" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="C141" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="C141" s="7" t="s">
+      <c r="D141" s="7" t="s">
         <v>400</v>
-      </c>
-      <c r="D141" s="7" t="s">
-        <v>401</v>
       </c>
       <c r="E141" s="20"/>
       <c r="F141" s="34" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G141" s="20"/>
       <c r="H141" s="8"/>
@@ -10204,22 +10219,22 @@
     </row>
     <row r="142" spans="1:26" ht="13">
       <c r="A142" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="B142" s="7" t="s">
         <v>403</v>
       </c>
-      <c r="B142" s="7" t="s">
+      <c r="C142" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="C142" s="7" t="s">
+      <c r="D142" s="7" t="s">
         <v>405</v>
-      </c>
-      <c r="D142" s="7" t="s">
-        <v>406</v>
       </c>
       <c r="E142" s="7" t="s">
         <v>139</v>
       </c>
       <c r="F142" s="34" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G142" s="20"/>
       <c r="H142" s="8"/>
@@ -10247,7 +10262,7 @@
         <v>35</v>
       </c>
       <c r="B143" s="20" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C143" s="20"/>
       <c r="D143" s="20"/>
@@ -10279,7 +10294,7 @@
         <v>41</v>
       </c>
       <c r="B144" s="20" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C144" s="20"/>
       <c r="D144" s="20"/>
@@ -10291,7 +10306,7 @@
       <c r="J144" s="8"/>
       <c r="K144" s="8"/>
       <c r="L144" s="100" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="M144" s="99"/>
       <c r="N144" s="99"/>
@@ -10313,7 +10328,7 @@
         <v>41</v>
       </c>
       <c r="B145" s="20" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C145" s="20"/>
       <c r="D145" s="20"/>
@@ -10325,7 +10340,7 @@
       <c r="J145" s="8"/>
       <c r="K145" s="8"/>
       <c r="L145" s="7" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M145" s="8"/>
       <c r="N145" s="8"/>
@@ -10347,17 +10362,17 @@
         <v>19</v>
       </c>
       <c r="B146" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="C146" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="C146" s="2" t="s">
+      <c r="D146" s="2" t="s">
         <v>413</v>
-      </c>
-      <c r="D146" s="2" t="s">
-        <v>414</v>
       </c>
       <c r="E146" s="7"/>
       <c r="F146" s="34" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G146" s="7" t="s">
         <v>117</v>
@@ -10387,13 +10402,13 @@
         <v>109</v>
       </c>
       <c r="B147" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="C147" s="7" t="s">
         <v>416</v>
       </c>
-      <c r="C147" s="7" t="s">
+      <c r="D147" s="7" t="s">
         <v>417</v>
-      </c>
-      <c r="D147" s="7" t="s">
-        <v>418</v>
       </c>
       <c r="E147" s="7"/>
       <c r="F147" s="8"/>
@@ -10423,14 +10438,14 @@
         <v>19</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E148" s="7"/>
       <c r="G148" s="7" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H148" s="8"/>
       <c r="I148" s="8"/>
@@ -10457,13 +10472,13 @@
         <v>135</v>
       </c>
       <c r="B149" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="C149" s="50" t="s">
         <v>421</v>
       </c>
-      <c r="C149" s="50" t="s">
+      <c r="D149" s="50" t="s">
         <v>422</v>
-      </c>
-      <c r="D149" s="50" t="s">
-        <v>423</v>
       </c>
       <c r="E149" s="7" t="s">
         <v>139</v>
@@ -10495,13 +10510,13 @@
         <v>135</v>
       </c>
       <c r="B150" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="C150" s="50" t="s">
         <v>424</v>
       </c>
-      <c r="C150" s="50" t="s">
+      <c r="D150" s="50" t="s">
         <v>425</v>
-      </c>
-      <c r="D150" s="50" t="s">
-        <v>426</v>
       </c>
       <c r="E150" s="7" t="s">
         <v>139</v>
@@ -10533,13 +10548,13 @@
         <v>135</v>
       </c>
       <c r="B151" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="C151" s="7" t="s">
         <v>427</v>
       </c>
-      <c r="C151" s="7" t="s">
+      <c r="D151" s="7" t="s">
         <v>428</v>
-      </c>
-      <c r="D151" s="7" t="s">
-        <v>429</v>
       </c>
       <c r="E151" s="7" t="s">
         <v>139</v>
@@ -10571,13 +10586,13 @@
         <v>135</v>
       </c>
       <c r="B152" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="C152" s="50" t="s">
         <v>430</v>
       </c>
-      <c r="C152" s="50" t="s">
+      <c r="D152" s="50" t="s">
         <v>431</v>
-      </c>
-      <c r="D152" s="50" t="s">
-        <v>432</v>
       </c>
       <c r="E152" s="7" t="s">
         <v>139</v>
@@ -10609,7 +10624,7 @@
         <v>35</v>
       </c>
       <c r="B153" s="7" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C153" s="13"/>
       <c r="D153" s="7"/>
@@ -10641,7 +10656,7 @@
         <v>109</v>
       </c>
       <c r="B154" s="7" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C154" s="13" t="s">
         <v>186</v>
@@ -10677,13 +10692,13 @@
         <v>109</v>
       </c>
       <c r="B155" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="C155" s="7" t="s">
         <v>434</v>
       </c>
-      <c r="C155" s="7" t="s">
+      <c r="D155" s="7" t="s">
         <v>435</v>
-      </c>
-      <c r="D155" s="7" t="s">
-        <v>436</v>
       </c>
       <c r="E155" s="7"/>
       <c r="F155" s="8"/>
@@ -10713,7 +10728,7 @@
         <v>19</v>
       </c>
       <c r="B156" s="7" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C156" s="50" t="s">
         <v>21</v>
@@ -10722,7 +10737,7 @@
       <c r="E156" s="7"/>
       <c r="F156" s="8"/>
       <c r="G156" s="7" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H156" s="8"/>
       <c r="I156" s="8"/>
@@ -10749,13 +10764,13 @@
         <v>135</v>
       </c>
       <c r="B157" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="C157" s="50" t="s">
         <v>438</v>
       </c>
-      <c r="C157" s="50" t="s">
+      <c r="D157" s="50" t="s">
         <v>439</v>
-      </c>
-      <c r="D157" s="50" t="s">
-        <v>440</v>
       </c>
       <c r="E157" s="7" t="s">
         <v>139</v>
@@ -10787,13 +10802,13 @@
         <v>135</v>
       </c>
       <c r="B158" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="C158" s="50" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="50" t="s">
+      <c r="D158" s="50" t="s">
         <v>442</v>
-      </c>
-      <c r="D158" s="50" t="s">
-        <v>443</v>
       </c>
       <c r="E158" s="7" t="s">
         <v>139</v>
@@ -10825,13 +10840,13 @@
         <v>135</v>
       </c>
       <c r="B159" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="C159" s="50" t="s">
         <v>444</v>
       </c>
-      <c r="C159" s="50" t="s">
+      <c r="D159" s="51" t="s">
         <v>445</v>
-      </c>
-      <c r="D159" s="51" t="s">
-        <v>446</v>
       </c>
       <c r="E159" s="7" t="s">
         <v>139</v>
@@ -10863,7 +10878,7 @@
         <v>35</v>
       </c>
       <c r="B160" s="7" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C160" s="50"/>
       <c r="D160" s="8"/>
@@ -10895,7 +10910,7 @@
         <v>41</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C161" s="52"/>
       <c r="D161" s="8"/>
@@ -10907,7 +10922,7 @@
       <c r="J161" s="8"/>
       <c r="K161" s="8"/>
       <c r="L161" s="53" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="M161" s="8"/>
       <c r="N161" s="8"/>
@@ -10929,19 +10944,19 @@
         <v>109</v>
       </c>
       <c r="B162" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="C162" s="50" t="s">
         <v>449</v>
       </c>
-      <c r="C162" s="50" t="s">
+      <c r="D162" s="50" t="s">
         <v>450</v>
-      </c>
-      <c r="D162" s="50" t="s">
-        <v>451</v>
       </c>
       <c r="E162" s="7" t="s">
         <v>139</v>
       </c>
       <c r="F162" s="7" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G162" s="7"/>
       <c r="H162" s="8"/>
@@ -10969,17 +10984,17 @@
         <v>109</v>
       </c>
       <c r="B163" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="C163" s="7" t="s">
         <v>453</v>
       </c>
-      <c r="C163" s="7" t="s">
+      <c r="D163" s="54" t="s">
         <v>454</v>
-      </c>
-      <c r="D163" s="54" t="s">
-        <v>455</v>
       </c>
       <c r="E163" s="7"/>
       <c r="F163" s="7" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G163" s="7"/>
       <c r="H163" s="7"/>
@@ -11007,7 +11022,7 @@
         <v>35</v>
       </c>
       <c r="B164" s="7" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C164" s="8"/>
       <c r="D164" s="8"/>
@@ -11039,17 +11054,17 @@
         <v>19</v>
       </c>
       <c r="B165" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="C165" s="7" t="s">
         <v>457</v>
       </c>
-      <c r="C165" s="7" t="s">
+      <c r="D165" s="7" t="s">
         <v>458</v>
-      </c>
-      <c r="D165" s="7" t="s">
-        <v>459</v>
       </c>
       <c r="E165" s="8"/>
       <c r="F165" s="34" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="G165" s="7"/>
       <c r="H165" s="8"/>
@@ -11077,7 +11092,7 @@
         <v>19</v>
       </c>
       <c r="B166" s="7" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C166" s="7" t="s">
         <v>21</v>
@@ -11110,22 +11125,22 @@
     </row>
     <row r="167" spans="1:26" ht="13">
       <c r="A167" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="B167" s="7" t="s">
         <v>462</v>
       </c>
-      <c r="B167" s="7" t="s">
+      <c r="C167" s="7" t="s">
         <v>463</v>
       </c>
-      <c r="C167" s="7" t="s">
+      <c r="D167" s="7" t="s">
         <v>464</v>
-      </c>
-      <c r="D167" s="7" t="s">
-        <v>465</v>
       </c>
       <c r="E167" s="7" t="s">
         <v>139</v>
       </c>
       <c r="F167" s="53" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G167" s="7" t="s">
         <v>117</v>
@@ -11159,7 +11174,7 @@
         <v>41</v>
       </c>
       <c r="B168" s="7" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C168" s="13"/>
       <c r="D168" s="7"/>
@@ -11171,7 +11186,7 @@
       <c r="J168" s="8"/>
       <c r="K168" s="8"/>
       <c r="L168" s="7" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="M168" s="8"/>
       <c r="N168" s="8"/>
@@ -11193,17 +11208,17 @@
         <v>109</v>
       </c>
       <c r="B169" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="C169" s="13" t="s">
         <v>469</v>
       </c>
-      <c r="C169" s="13" t="s">
+      <c r="D169" s="7" t="s">
         <v>470</v>
-      </c>
-      <c r="D169" s="7" t="s">
-        <v>471</v>
       </c>
       <c r="E169" s="7"/>
       <c r="F169" s="57" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="G169" s="7"/>
       <c r="H169" s="8"/>
@@ -11231,7 +11246,7 @@
         <v>35</v>
       </c>
       <c r="B170" s="7" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C170" s="7"/>
       <c r="D170" s="7"/>
@@ -11263,7 +11278,7 @@
         <v>19</v>
       </c>
       <c r="B171" s="7" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C171" s="7" t="s">
         <v>21</v>
@@ -11271,7 +11286,7 @@
       <c r="D171" s="7"/>
       <c r="E171" s="7"/>
       <c r="F171" s="53" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G171" s="7" t="s">
         <v>117</v>
@@ -11301,19 +11316,19 @@
         <v>135</v>
       </c>
       <c r="B172" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="C172" s="7" t="s">
         <v>474</v>
       </c>
-      <c r="C172" s="7" t="s">
+      <c r="D172" s="7" t="s">
         <v>475</v>
-      </c>
-      <c r="D172" s="7" t="s">
-        <v>476</v>
       </c>
       <c r="E172" s="7" t="s">
         <v>139</v>
       </c>
       <c r="F172" s="53" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G172" s="8"/>
       <c r="H172" s="8"/>
@@ -11341,17 +11356,17 @@
         <v>109</v>
       </c>
       <c r="B173" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="C173" s="7" t="s">
         <v>478</v>
       </c>
-      <c r="C173" s="7" t="s">
+      <c r="D173" s="7" t="s">
         <v>479</v>
-      </c>
-      <c r="D173" s="7" t="s">
-        <v>480</v>
       </c>
       <c r="E173" s="7"/>
       <c r="F173" s="53" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G173" s="8"/>
       <c r="H173" s="8"/>
@@ -11379,19 +11394,19 @@
         <v>135</v>
       </c>
       <c r="B174" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="C174" s="7" t="s">
         <v>481</v>
       </c>
-      <c r="C174" s="7" t="s">
+      <c r="D174" s="7" t="s">
         <v>482</v>
-      </c>
-      <c r="D174" s="7" t="s">
-        <v>483</v>
       </c>
       <c r="E174" s="7" t="s">
         <v>139</v>
       </c>
       <c r="F174" s="53" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G174" s="8"/>
       <c r="H174" s="8"/>
@@ -11419,7 +11434,7 @@
         <v>41</v>
       </c>
       <c r="B175" s="7" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C175" s="56"/>
       <c r="D175" s="56"/>
@@ -11431,7 +11446,7 @@
       <c r="J175" s="56"/>
       <c r="K175" s="56"/>
       <c r="L175" s="53" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="M175" s="56"/>
       <c r="N175" s="56"/>
@@ -11453,17 +11468,17 @@
         <v>109</v>
       </c>
       <c r="B176" s="7" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C176" s="57" t="s">
+        <v>469</v>
+      </c>
+      <c r="D176" s="57" t="s">
         <v>470</v>
-      </c>
-      <c r="D176" s="57" t="s">
-        <v>471</v>
       </c>
       <c r="E176" s="57"/>
       <c r="F176" s="57" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="G176" s="56"/>
       <c r="H176" s="56"/>
@@ -11491,17 +11506,17 @@
         <v>109</v>
       </c>
       <c r="B177" s="57" t="s">
+        <v>487</v>
+      </c>
+      <c r="C177" s="57" t="s">
         <v>488</v>
       </c>
-      <c r="C177" s="57" t="s">
+      <c r="D177" s="57" t="s">
         <v>489</v>
-      </c>
-      <c r="D177" s="57" t="s">
-        <v>490</v>
       </c>
       <c r="E177" s="56"/>
       <c r="F177" s="57" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="G177" s="56"/>
       <c r="H177" s="56"/>
@@ -11529,7 +11544,7 @@
         <v>35</v>
       </c>
       <c r="B178" s="57" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C178" s="57"/>
       <c r="D178" s="56"/>
@@ -11561,7 +11576,7 @@
         <v>35</v>
       </c>
       <c r="B179" s="57" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C179" s="56"/>
       <c r="D179" s="56"/>
@@ -11593,17 +11608,17 @@
         <v>19</v>
       </c>
       <c r="B180" s="57" t="s">
+        <v>491</v>
+      </c>
+      <c r="C180" s="57" t="s">
         <v>492</v>
       </c>
-      <c r="C180" s="57" t="s">
+      <c r="D180" s="57" t="s">
         <v>493</v>
-      </c>
-      <c r="D180" s="57" t="s">
-        <v>494</v>
       </c>
       <c r="E180" s="56"/>
       <c r="F180" s="57" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G180" s="57" t="s">
         <v>164</v>
@@ -11633,13 +11648,13 @@
         <v>109</v>
       </c>
       <c r="B181" s="57" t="s">
+        <v>495</v>
+      </c>
+      <c r="C181" s="57" t="s">
         <v>496</v>
       </c>
-      <c r="C181" s="57" t="s">
+      <c r="D181" s="57" t="s">
         <v>497</v>
-      </c>
-      <c r="D181" s="57" t="s">
-        <v>498</v>
       </c>
       <c r="E181" s="56"/>
       <c r="G181" s="56"/>
@@ -11668,7 +11683,7 @@
         <v>109</v>
       </c>
       <c r="B182" s="57" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C182" s="56"/>
       <c r="D182" s="56"/>
@@ -11686,10 +11701,10 @@
       <c r="P182" s="56"/>
       <c r="Q182" s="56"/>
       <c r="R182" s="57" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="S182" s="57" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="T182" s="9"/>
       <c r="U182" s="9"/>
@@ -11704,7 +11719,7 @@
         <v>109</v>
       </c>
       <c r="B183" s="57" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D183" s="56"/>
       <c r="E183" s="56"/>
@@ -11721,10 +11736,10 @@
       <c r="P183" s="56"/>
       <c r="Q183" s="56"/>
       <c r="R183" s="57" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="S183" s="57" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="T183" s="9"/>
       <c r="U183" s="9"/>
@@ -11739,7 +11754,7 @@
         <v>109</v>
       </c>
       <c r="B184" s="57" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C184" s="56"/>
       <c r="D184" s="56"/>
@@ -11757,10 +11772,10 @@
       <c r="P184" s="56"/>
       <c r="Q184" s="56"/>
       <c r="R184" s="57" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="S184" s="57" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="T184" s="9"/>
       <c r="U184" s="9"/>
@@ -11775,7 +11790,7 @@
         <v>109</v>
       </c>
       <c r="B185" s="57" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C185" s="56"/>
       <c r="D185" s="56"/>
@@ -11793,10 +11808,10 @@
       <c r="P185" s="56"/>
       <c r="Q185" s="56"/>
       <c r="R185" s="57" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="S185" s="57" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="T185" s="9"/>
       <c r="U185" s="9"/>
@@ -11811,7 +11826,7 @@
         <v>109</v>
       </c>
       <c r="B186" s="57" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C186" s="56"/>
       <c r="D186" s="56"/>
@@ -11829,10 +11844,10 @@
       <c r="P186" s="56"/>
       <c r="Q186" s="56"/>
       <c r="R186" s="57" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="S186" s="57" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="T186" s="9"/>
       <c r="U186" s="9"/>
@@ -11847,7 +11862,7 @@
         <v>109</v>
       </c>
       <c r="B187" s="57" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C187" s="56"/>
       <c r="D187" s="56"/>
@@ -11865,10 +11880,10 @@
       <c r="P187" s="56"/>
       <c r="Q187" s="56"/>
       <c r="R187" s="57" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="S187" s="57" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="T187" s="9"/>
       <c r="U187" s="9"/>
@@ -11883,7 +11898,7 @@
         <v>35</v>
       </c>
       <c r="B188" s="57" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C188" s="56"/>
       <c r="D188" s="56"/>
@@ -11915,17 +11930,17 @@
         <v>19</v>
       </c>
       <c r="B189" s="57" t="s">
+        <v>510</v>
+      </c>
+      <c r="C189" s="57" t="s">
         <v>511</v>
       </c>
-      <c r="C189" s="57" t="s">
+      <c r="D189" s="57" t="s">
         <v>512</v>
-      </c>
-      <c r="D189" s="57" t="s">
-        <v>513</v>
       </c>
       <c r="E189" s="57"/>
       <c r="F189" s="34" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="G189" s="57" t="s">
         <v>117</v>
@@ -11955,13 +11970,13 @@
         <v>135</v>
       </c>
       <c r="B190" s="57" t="s">
+        <v>514</v>
+      </c>
+      <c r="C190" s="57" t="s">
         <v>515</v>
       </c>
-      <c r="C190" s="57" t="s">
+      <c r="D190" s="57" t="s">
         <v>516</v>
-      </c>
-      <c r="D190" s="57" t="s">
-        <v>517</v>
       </c>
       <c r="E190" s="57" t="s">
         <v>139</v>
@@ -11993,17 +12008,17 @@
         <v>109</v>
       </c>
       <c r="B191" s="57" t="s">
+        <v>517</v>
+      </c>
+      <c r="C191" s="50" t="s">
         <v>518</v>
       </c>
-      <c r="C191" s="50" t="s">
+      <c r="D191" s="50" t="s">
         <v>519</v>
-      </c>
-      <c r="D191" s="50" t="s">
-        <v>520</v>
       </c>
       <c r="E191" s="50"/>
       <c r="F191" s="57" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="G191" s="56"/>
       <c r="H191" s="56"/>
@@ -12031,19 +12046,19 @@
         <v>135</v>
       </c>
       <c r="B192" s="57" t="s">
+        <v>521</v>
+      </c>
+      <c r="C192" s="57" t="s">
         <v>522</v>
       </c>
-      <c r="C192" s="57" t="s">
+      <c r="D192" s="57" t="s">
         <v>523</v>
-      </c>
-      <c r="D192" s="57" t="s">
-        <v>524</v>
       </c>
       <c r="E192" s="57" t="s">
         <v>139</v>
       </c>
       <c r="F192" s="57" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="G192" s="56"/>
       <c r="H192" s="56"/>
@@ -12068,22 +12083,22 @@
     </row>
     <row r="193" spans="1:26" ht="13">
       <c r="A193" s="57" t="s">
+        <v>525</v>
+      </c>
+      <c r="B193" s="57" t="s">
         <v>526</v>
       </c>
-      <c r="B193" s="57" t="s">
+      <c r="C193" s="57" t="s">
         <v>527</v>
       </c>
-      <c r="C193" s="57" t="s">
+      <c r="D193" s="57" t="s">
         <v>528</v>
-      </c>
-      <c r="D193" s="57" t="s">
-        <v>529</v>
       </c>
       <c r="E193" s="57" t="s">
         <v>139</v>
       </c>
       <c r="F193" s="57" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="G193" s="56"/>
       <c r="H193" s="56"/>
@@ -12111,17 +12126,17 @@
         <v>109</v>
       </c>
       <c r="B194" s="57" t="s">
+        <v>530</v>
+      </c>
+      <c r="C194" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="C194" s="7" t="s">
+      <c r="D194" s="7" t="s">
         <v>532</v>
-      </c>
-      <c r="D194" s="7" t="s">
-        <v>533</v>
       </c>
       <c r="E194" s="7"/>
       <c r="F194" s="57" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="G194" s="56"/>
       <c r="H194" s="56"/>
@@ -12149,19 +12164,19 @@
         <v>135</v>
       </c>
       <c r="B195" s="57" t="s">
+        <v>534</v>
+      </c>
+      <c r="C195" s="57" t="s">
         <v>535</v>
       </c>
-      <c r="C195" s="57" t="s">
+      <c r="D195" s="57" t="s">
         <v>536</v>
-      </c>
-      <c r="D195" s="57" t="s">
-        <v>537</v>
       </c>
       <c r="E195" s="57" t="s">
         <v>139</v>
       </c>
       <c r="F195" s="57" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="G195" s="56"/>
       <c r="H195" s="56"/>
@@ -12189,17 +12204,17 @@
         <v>109</v>
       </c>
       <c r="B196" s="57" t="s">
+        <v>538</v>
+      </c>
+      <c r="C196" s="50" t="s">
         <v>539</v>
       </c>
-      <c r="C196" s="50" t="s">
+      <c r="D196" s="50" t="s">
         <v>540</v>
-      </c>
-      <c r="D196" s="50" t="s">
-        <v>541</v>
       </c>
       <c r="E196" s="50"/>
       <c r="F196" s="57" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="G196" s="56"/>
       <c r="H196" s="56"/>
@@ -12227,17 +12242,17 @@
         <v>109</v>
       </c>
       <c r="B197" s="57" t="s">
+        <v>542</v>
+      </c>
+      <c r="C197" s="50" t="s">
         <v>543</v>
       </c>
-      <c r="C197" s="50" t="s">
+      <c r="D197" s="50" t="s">
         <v>544</v>
-      </c>
-      <c r="D197" s="50" t="s">
-        <v>545</v>
       </c>
       <c r="E197" s="50"/>
       <c r="F197" s="57" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="G197" s="56"/>
       <c r="H197" s="56"/>
@@ -12265,17 +12280,17 @@
         <v>109</v>
       </c>
       <c r="B198" s="57" t="s">
+        <v>546</v>
+      </c>
+      <c r="C198" s="7" t="s">
         <v>547</v>
       </c>
-      <c r="C198" s="7" t="s">
+      <c r="D198" s="7" t="s">
         <v>548</v>
-      </c>
-      <c r="D198" s="7" t="s">
-        <v>549</v>
       </c>
       <c r="E198" s="7"/>
       <c r="F198" s="57" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="G198" s="56"/>
       <c r="H198" s="56"/>
@@ -12303,17 +12318,17 @@
         <v>109</v>
       </c>
       <c r="B199" s="57" t="s">
+        <v>549</v>
+      </c>
+      <c r="C199" s="7" t="s">
         <v>550</v>
       </c>
-      <c r="C199" s="7" t="s">
+      <c r="D199" s="7" t="s">
         <v>551</v>
-      </c>
-      <c r="D199" s="7" t="s">
-        <v>552</v>
       </c>
       <c r="E199" s="7"/>
       <c r="F199" s="57" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G199" s="56"/>
       <c r="H199" s="56"/>
@@ -12341,7 +12356,7 @@
         <v>35</v>
       </c>
       <c r="B200" s="57" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C200" s="56"/>
       <c r="D200" s="56"/>
@@ -12373,13 +12388,13 @@
         <v>105</v>
       </c>
       <c r="B201" s="57" t="s">
+        <v>553</v>
+      </c>
+      <c r="C201" s="57" t="s">
         <v>554</v>
       </c>
-      <c r="C201" s="57" t="s">
+      <c r="D201" s="57" t="s">
         <v>555</v>
-      </c>
-      <c r="D201" s="57" t="s">
-        <v>556</v>
       </c>
       <c r="E201" s="57"/>
       <c r="F201" s="34" t="b">
@@ -12410,16 +12425,16 @@
     </row>
     <row r="202" spans="1:26" ht="13">
       <c r="A202" s="57" t="s">
+        <v>556</v>
+      </c>
+      <c r="B202" s="57" t="s">
         <v>557</v>
       </c>
-      <c r="B202" s="57" t="s">
+      <c r="C202" s="57" t="s">
         <v>558</v>
       </c>
-      <c r="C202" s="57" t="s">
+      <c r="D202" s="57" t="s">
         <v>559</v>
-      </c>
-      <c r="D202" s="57" t="s">
-        <v>560</v>
       </c>
       <c r="E202" s="57" t="s">
         <v>139</v>
@@ -12428,10 +12443,10 @@
       <c r="G202" s="57"/>
       <c r="H202" s="56"/>
       <c r="I202" s="10" t="s">
+        <v>560</v>
+      </c>
+      <c r="J202" s="57" t="s">
         <v>561</v>
-      </c>
-      <c r="J202" s="57" t="s">
-        <v>562</v>
       </c>
       <c r="K202" s="56"/>
       <c r="L202" s="56"/>
@@ -12455,17 +12470,17 @@
         <v>109</v>
       </c>
       <c r="B203" s="57" t="s">
+        <v>562</v>
+      </c>
+      <c r="C203" s="50" t="s">
         <v>563</v>
       </c>
-      <c r="C203" s="50" t="s">
+      <c r="D203" s="50" t="s">
         <v>564</v>
-      </c>
-      <c r="D203" s="50" t="s">
-        <v>565</v>
       </c>
       <c r="E203" s="50"/>
       <c r="F203" s="57" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G203" s="57"/>
       <c r="H203" s="56"/>
@@ -12493,7 +12508,7 @@
         <v>35</v>
       </c>
       <c r="B204" s="57" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C204" s="57"/>
       <c r="D204" s="57"/>
@@ -12525,17 +12540,17 @@
         <v>19</v>
       </c>
       <c r="B205" s="57" t="s">
+        <v>566</v>
+      </c>
+      <c r="C205" s="57" t="s">
         <v>567</v>
       </c>
-      <c r="C205" s="57" t="s">
+      <c r="D205" s="57" t="s">
         <v>568</v>
-      </c>
-      <c r="D205" s="57" t="s">
-        <v>569</v>
       </c>
       <c r="E205" s="56"/>
       <c r="F205" s="34" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G205" s="57" t="s">
         <v>117</v>
@@ -12565,13 +12580,13 @@
         <v>236</v>
       </c>
       <c r="B206" s="13" t="s">
+        <v>570</v>
+      </c>
+      <c r="C206" s="57" t="s">
         <v>571</v>
       </c>
-      <c r="C206" s="57" t="s">
+      <c r="D206" s="57" t="s">
         <v>572</v>
-      </c>
-      <c r="D206" s="57" t="s">
-        <v>573</v>
       </c>
       <c r="E206" s="57" t="s">
         <v>139</v>
@@ -12580,13 +12595,13 @@
       <c r="G206" s="56"/>
       <c r="H206" s="56"/>
       <c r="I206" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="J206" s="57" t="s">
         <v>574</v>
       </c>
-      <c r="J206" s="57" t="s">
+      <c r="K206" s="57" t="s">
         <v>575</v>
-      </c>
-      <c r="K206" s="57" t="s">
-        <v>576</v>
       </c>
       <c r="L206" s="56"/>
       <c r="M206" s="56"/>
@@ -12606,22 +12621,22 @@
     </row>
     <row r="207" spans="1:26" ht="13">
       <c r="A207" s="57" t="s">
+        <v>576</v>
+      </c>
+      <c r="B207" s="57" t="s">
         <v>577</v>
       </c>
-      <c r="B207" s="57" t="s">
+      <c r="C207" s="57" t="s">
         <v>578</v>
       </c>
-      <c r="C207" s="57" t="s">
+      <c r="D207" s="57" t="s">
         <v>579</v>
-      </c>
-      <c r="D207" s="57" t="s">
-        <v>580</v>
       </c>
       <c r="E207" s="57" t="s">
         <v>139</v>
       </c>
       <c r="F207" s="34" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G207" s="56"/>
       <c r="H207" s="56"/>
@@ -12648,17 +12663,17 @@
         <v>109</v>
       </c>
       <c r="B208" s="57" t="s">
+        <v>581</v>
+      </c>
+      <c r="C208" s="7" t="s">
         <v>582</v>
       </c>
-      <c r="C208" s="7" t="s">
+      <c r="D208" s="7" t="s">
         <v>583</v>
-      </c>
-      <c r="D208" s="7" t="s">
-        <v>584</v>
       </c>
       <c r="E208" s="7"/>
       <c r="F208" s="34" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="G208" s="56"/>
       <c r="H208" s="56"/>
@@ -12686,7 +12701,7 @@
         <v>35</v>
       </c>
       <c r="B209" s="57" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C209" s="56"/>
       <c r="D209" s="56"/>
@@ -12718,7 +12733,7 @@
         <v>19</v>
       </c>
       <c r="B210" s="57" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C210" s="57" t="s">
         <v>21</v>
@@ -12726,7 +12741,7 @@
       <c r="D210" s="56"/>
       <c r="E210" s="56"/>
       <c r="F210" s="34" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G210" s="57"/>
       <c r="H210" s="56"/>
@@ -12754,13 +12769,13 @@
         <v>19</v>
       </c>
       <c r="B211" s="57" t="s">
+        <v>586</v>
+      </c>
+      <c r="C211" s="57" t="s">
         <v>587</v>
       </c>
-      <c r="C211" s="57" t="s">
+      <c r="D211" s="57" t="s">
         <v>588</v>
-      </c>
-      <c r="D211" s="57" t="s">
-        <v>589</v>
       </c>
       <c r="E211" s="56"/>
       <c r="F211" s="34"/>
@@ -12792,13 +12807,13 @@
         <v>109</v>
       </c>
       <c r="B212" s="57" t="s">
+        <v>589</v>
+      </c>
+      <c r="C212" s="57" t="s">
         <v>590</v>
       </c>
-      <c r="C212" s="57" t="s">
+      <c r="D212" s="57" t="s">
         <v>591</v>
-      </c>
-      <c r="D212" s="57" t="s">
-        <v>592</v>
       </c>
       <c r="E212" s="57"/>
       <c r="F212" s="57"/>
@@ -12828,7 +12843,7 @@
         <v>35</v>
       </c>
       <c r="B213" s="57" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C213" s="57"/>
       <c r="D213" s="56"/>
@@ -12860,13 +12875,13 @@
         <v>19</v>
       </c>
       <c r="B214" s="57" t="s">
+        <v>592</v>
+      </c>
+      <c r="C214" s="57" t="s">
         <v>593</v>
       </c>
-      <c r="C214" s="57" t="s">
+      <c r="D214" s="58" t="s">
         <v>594</v>
-      </c>
-      <c r="D214" s="58" t="s">
-        <v>595</v>
       </c>
       <c r="E214" s="56"/>
       <c r="F214" s="56"/>
@@ -12898,13 +12913,13 @@
         <v>109</v>
       </c>
       <c r="B215" s="57" t="s">
+        <v>595</v>
+      </c>
+      <c r="C215" s="57" t="s">
         <v>596</v>
       </c>
-      <c r="C215" s="57" t="s">
+      <c r="D215" s="57" t="s">
         <v>597</v>
-      </c>
-      <c r="D215" s="57" t="s">
-        <v>598</v>
       </c>
       <c r="E215" s="56"/>
       <c r="F215" s="56"/>
@@ -12934,7 +12949,7 @@
         <v>35</v>
       </c>
       <c r="B216" s="57" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C216" s="57"/>
       <c r="D216" s="56"/>
@@ -12966,13 +12981,13 @@
         <v>19</v>
       </c>
       <c r="B217" s="57" t="s">
+        <v>598</v>
+      </c>
+      <c r="C217" s="57" t="s">
         <v>599</v>
       </c>
-      <c r="C217" s="57" t="s">
+      <c r="D217" s="57" t="s">
         <v>600</v>
-      </c>
-      <c r="D217" s="57" t="s">
-        <v>601</v>
       </c>
       <c r="E217" s="56"/>
       <c r="F217" s="56"/>
@@ -13004,13 +13019,13 @@
         <v>109</v>
       </c>
       <c r="B218" s="57" t="s">
+        <v>601</v>
+      </c>
+      <c r="C218" s="57" t="s">
         <v>602</v>
       </c>
-      <c r="C218" s="57" t="s">
+      <c r="D218" s="57" t="s">
         <v>603</v>
-      </c>
-      <c r="D218" s="57" t="s">
-        <v>604</v>
       </c>
       <c r="E218" s="56"/>
       <c r="F218" s="56"/>
@@ -13040,7 +13055,7 @@
         <v>35</v>
       </c>
       <c r="B219" s="57" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C219" s="57"/>
       <c r="D219" s="56"/>
@@ -13072,13 +13087,13 @@
         <v>19</v>
       </c>
       <c r="B220" s="57" t="s">
+        <v>604</v>
+      </c>
+      <c r="C220" s="57" t="s">
         <v>605</v>
       </c>
-      <c r="C220" s="57" t="s">
+      <c r="D220" s="58" t="s">
         <v>606</v>
-      </c>
-      <c r="D220" s="58" t="s">
-        <v>607</v>
       </c>
       <c r="E220" s="56"/>
       <c r="F220" s="59"/>
@@ -13110,13 +13125,13 @@
         <v>109</v>
       </c>
       <c r="B221" s="57" t="s">
+        <v>607</v>
+      </c>
+      <c r="C221" s="57" t="s">
         <v>608</v>
       </c>
-      <c r="C221" s="57" t="s">
+      <c r="D221" s="57" t="s">
         <v>609</v>
-      </c>
-      <c r="D221" s="57" t="s">
-        <v>610</v>
       </c>
       <c r="E221" s="56"/>
       <c r="F221" s="59"/>
@@ -13146,13 +13161,13 @@
         <v>109</v>
       </c>
       <c r="B222" s="57" t="s">
+        <v>610</v>
+      </c>
+      <c r="C222" s="57" t="s">
         <v>611</v>
       </c>
-      <c r="C222" s="57" t="s">
+      <c r="D222" s="57" t="s">
         <v>612</v>
-      </c>
-      <c r="D222" s="57" t="s">
-        <v>613</v>
       </c>
       <c r="E222" s="56"/>
       <c r="F222" s="56"/>
@@ -13182,7 +13197,7 @@
         <v>35</v>
       </c>
       <c r="B223" s="57" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C223" s="56"/>
       <c r="D223" s="56"/>
@@ -13214,7 +13229,7 @@
         <v>35</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C224" s="60"/>
       <c r="D224" s="61"/>
@@ -13237,7 +13252,7 @@
         <v>41</v>
       </c>
       <c r="B225" s="10" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C225" s="6"/>
       <c r="D225" s="4"/>
@@ -13249,7 +13264,7 @@
       <c r="J225" s="4"/>
       <c r="K225" s="4"/>
       <c r="L225" s="62" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="M225" s="4"/>
       <c r="N225" s="4"/>
@@ -13271,17 +13286,17 @@
         <v>19</v>
       </c>
       <c r="B226" s="57" t="s">
+        <v>615</v>
+      </c>
+      <c r="C226" s="57" t="s">
         <v>616</v>
       </c>
-      <c r="C226" s="57" t="s">
+      <c r="D226" s="57" t="s">
         <v>617</v>
-      </c>
-      <c r="D226" s="57" t="s">
-        <v>618</v>
       </c>
       <c r="E226" s="56"/>
       <c r="F226" s="34" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="G226" s="56"/>
       <c r="H226" s="56"/>
@@ -13309,13 +13324,13 @@
         <v>109</v>
       </c>
       <c r="B227" s="57" t="s">
+        <v>619</v>
+      </c>
+      <c r="C227" s="2" t="s">
         <v>620</v>
       </c>
-      <c r="C227" s="2" t="s">
+      <c r="D227" s="57" t="s">
         <v>621</v>
-      </c>
-      <c r="D227" s="57" t="s">
-        <v>622</v>
       </c>
       <c r="E227" s="56"/>
       <c r="F227" s="56"/>
@@ -13345,13 +13360,13 @@
         <v>109</v>
       </c>
       <c r="B228" s="57" t="s">
+        <v>622</v>
+      </c>
+      <c r="C228" s="57" t="s">
         <v>623</v>
       </c>
-      <c r="C228" s="57" t="s">
+      <c r="D228" s="57" t="s">
         <v>624</v>
-      </c>
-      <c r="D228" s="57" t="s">
-        <v>625</v>
       </c>
       <c r="E228" s="56"/>
       <c r="F228" s="56"/>
@@ -13381,13 +13396,13 @@
         <v>109</v>
       </c>
       <c r="B229" s="57" t="s">
+        <v>625</v>
+      </c>
+      <c r="C229" s="57" t="s">
         <v>626</v>
       </c>
-      <c r="C229" s="57" t="s">
+      <c r="D229" s="57" t="s">
         <v>627</v>
-      </c>
-      <c r="D229" s="57" t="s">
-        <v>628</v>
       </c>
       <c r="E229" s="56"/>
       <c r="F229" s="56"/>
@@ -13417,13 +13432,13 @@
         <v>109</v>
       </c>
       <c r="B230" s="57" t="s">
+        <v>628</v>
+      </c>
+      <c r="C230" s="57" t="s">
         <v>629</v>
       </c>
-      <c r="C230" s="57" t="s">
+      <c r="D230" s="57" t="s">
         <v>630</v>
-      </c>
-      <c r="D230" s="57" t="s">
-        <v>631</v>
       </c>
       <c r="E230" s="56"/>
       <c r="F230" s="59"/>
@@ -13453,13 +13468,13 @@
         <v>109</v>
       </c>
       <c r="B231" s="57" t="s">
+        <v>631</v>
+      </c>
+      <c r="C231" s="57" t="s">
         <v>632</v>
       </c>
-      <c r="C231" s="57" t="s">
+      <c r="D231" s="57" t="s">
         <v>633</v>
-      </c>
-      <c r="D231" s="57" t="s">
-        <v>634</v>
       </c>
       <c r="E231" s="56"/>
       <c r="F231" s="56"/>
@@ -13489,13 +13504,13 @@
         <v>109</v>
       </c>
       <c r="B232" s="57" t="s">
+        <v>634</v>
+      </c>
+      <c r="C232" s="57" t="s">
         <v>635</v>
       </c>
-      <c r="C232" s="57" t="s">
+      <c r="D232" s="57" t="s">
         <v>636</v>
-      </c>
-      <c r="D232" s="57" t="s">
-        <v>637</v>
       </c>
       <c r="E232" s="56"/>
       <c r="F232" s="56"/>
@@ -13525,13 +13540,13 @@
         <v>109</v>
       </c>
       <c r="B233" s="57" t="s">
+        <v>637</v>
+      </c>
+      <c r="C233" s="57" t="s">
         <v>638</v>
       </c>
-      <c r="C233" s="57" t="s">
+      <c r="D233" s="57" t="s">
         <v>639</v>
-      </c>
-      <c r="D233" s="57" t="s">
-        <v>640</v>
       </c>
       <c r="E233" s="56"/>
       <c r="F233" s="56"/>
@@ -13561,7 +13576,7 @@
         <v>35</v>
       </c>
       <c r="B234" s="57" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C234" s="8"/>
       <c r="D234" s="8"/>
@@ -13593,17 +13608,17 @@
         <v>19</v>
       </c>
       <c r="B235" s="57" t="s">
+        <v>640</v>
+      </c>
+      <c r="C235" s="57" t="s">
         <v>641</v>
       </c>
-      <c r="C235" s="57" t="s">
+      <c r="D235" s="57" t="s">
         <v>642</v>
-      </c>
-      <c r="D235" s="57" t="s">
-        <v>643</v>
       </c>
       <c r="E235" s="56"/>
       <c r="F235" s="34" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G235" s="56"/>
       <c r="H235" s="56"/>
@@ -13631,13 +13646,13 @@
         <v>135</v>
       </c>
       <c r="B236" s="57" t="s">
+        <v>643</v>
+      </c>
+      <c r="C236" s="57" t="s">
         <v>644</v>
       </c>
-      <c r="C236" s="57" t="s">
+      <c r="D236" s="57" t="s">
         <v>645</v>
-      </c>
-      <c r="D236" s="57" t="s">
-        <v>646</v>
       </c>
       <c r="E236" s="57" t="s">
         <v>139</v>
@@ -13671,13 +13686,13 @@
         <v>109</v>
       </c>
       <c r="B237" s="57" t="s">
+        <v>646</v>
+      </c>
+      <c r="C237" s="57" t="s">
         <v>647</v>
       </c>
-      <c r="C237" s="57" t="s">
+      <c r="D237" s="57" t="s">
         <v>648</v>
-      </c>
-      <c r="D237" s="57" t="s">
-        <v>649</v>
       </c>
       <c r="E237" s="56"/>
       <c r="F237" s="56"/>
@@ -13707,13 +13722,13 @@
         <v>109</v>
       </c>
       <c r="B238" s="57" t="s">
+        <v>649</v>
+      </c>
+      <c r="C238" s="57" t="s">
         <v>650</v>
       </c>
-      <c r="C238" s="57" t="s">
+      <c r="D238" s="57" t="s">
         <v>651</v>
-      </c>
-      <c r="D238" s="57" t="s">
-        <v>652</v>
       </c>
       <c r="E238" s="57"/>
       <c r="F238" s="57"/>
@@ -13743,13 +13758,13 @@
         <v>109</v>
       </c>
       <c r="B239" s="57" t="s">
+        <v>652</v>
+      </c>
+      <c r="C239" s="57" t="s">
         <v>653</v>
       </c>
-      <c r="C239" s="57" t="s">
+      <c r="D239" s="57" t="s">
         <v>654</v>
-      </c>
-      <c r="D239" s="57" t="s">
-        <v>655</v>
       </c>
       <c r="E239" s="56"/>
       <c r="F239" s="56"/>
@@ -13779,13 +13794,13 @@
         <v>109</v>
       </c>
       <c r="B240" s="57" t="s">
+        <v>655</v>
+      </c>
+      <c r="C240" s="57" t="s">
         <v>656</v>
       </c>
-      <c r="C240" s="57" t="s">
+      <c r="D240" s="57" t="s">
         <v>657</v>
-      </c>
-      <c r="D240" s="57" t="s">
-        <v>658</v>
       </c>
       <c r="E240" s="56"/>
       <c r="F240" s="56"/>
@@ -13815,19 +13830,19 @@
         <v>135</v>
       </c>
       <c r="B241" s="57" t="s">
+        <v>658</v>
+      </c>
+      <c r="C241" s="57" t="s">
         <v>659</v>
       </c>
-      <c r="C241" s="57" t="s">
+      <c r="D241" s="57" t="s">
         <v>660</v>
-      </c>
-      <c r="D241" s="57" t="s">
-        <v>661</v>
       </c>
       <c r="E241" s="57" t="s">
         <v>139</v>
       </c>
       <c r="F241" s="57" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="G241" s="56"/>
       <c r="H241" s="56"/>
@@ -13855,17 +13870,17 @@
         <v>109</v>
       </c>
       <c r="B242" s="57" t="s">
+        <v>661</v>
+      </c>
+      <c r="C242" s="57" t="s">
         <v>662</v>
       </c>
-      <c r="C242" s="57" t="s">
+      <c r="D242" s="57" t="s">
         <v>663</v>
-      </c>
-      <c r="D242" s="57" t="s">
-        <v>664</v>
       </c>
       <c r="E242" s="57"/>
       <c r="F242" s="57" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G242" s="56"/>
       <c r="H242" s="56"/>
@@ -13890,22 +13905,22 @@
     </row>
     <row r="243" spans="1:26" ht="13">
       <c r="A243" s="57" t="s">
+        <v>665</v>
+      </c>
+      <c r="B243" s="57" t="s">
         <v>666</v>
       </c>
-      <c r="B243" s="57" t="s">
+      <c r="C243" s="57" t="s">
         <v>667</v>
       </c>
-      <c r="C243" s="57" t="s">
+      <c r="D243" s="57" t="s">
         <v>668</v>
-      </c>
-      <c r="D243" s="57" t="s">
-        <v>669</v>
       </c>
       <c r="E243" s="57" t="s">
         <v>139</v>
       </c>
       <c r="F243" s="57" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="G243" s="56"/>
       <c r="H243" s="56"/>
@@ -13933,13 +13948,13 @@
         <v>109</v>
       </c>
       <c r="B244" s="57" t="s">
+        <v>670</v>
+      </c>
+      <c r="C244" s="57" t="s">
         <v>671</v>
       </c>
-      <c r="C244" s="57" t="s">
+      <c r="D244" s="57" t="s">
         <v>672</v>
-      </c>
-      <c r="D244" s="57" t="s">
-        <v>673</v>
       </c>
       <c r="E244" s="56"/>
       <c r="F244" s="59"/>
@@ -13969,13 +13984,13 @@
         <v>109</v>
       </c>
       <c r="B245" s="57" t="s">
+        <v>673</v>
+      </c>
+      <c r="C245" s="57" t="s">
         <v>674</v>
       </c>
-      <c r="C245" s="57" t="s">
+      <c r="D245" s="57" t="s">
         <v>675</v>
-      </c>
-      <c r="D245" s="57" t="s">
-        <v>676</v>
       </c>
       <c r="E245" s="56"/>
       <c r="F245" s="59"/>
@@ -14005,17 +14020,17 @@
         <v>109</v>
       </c>
       <c r="B246" s="57" t="s">
+        <v>676</v>
+      </c>
+      <c r="C246" s="57" t="s">
         <v>677</v>
-      </c>
-      <c r="C246" s="57" t="s">
-        <v>678</v>
       </c>
       <c r="D246" s="57" t="s">
         <v>301</v>
       </c>
       <c r="E246" s="56"/>
       <c r="F246" s="69" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="G246" s="56"/>
       <c r="H246" s="56"/>
@@ -14043,7 +14058,7 @@
         <v>35</v>
       </c>
       <c r="B247" s="57" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C247" s="56"/>
       <c r="D247" s="56"/>
@@ -14075,17 +14090,17 @@
         <v>19</v>
       </c>
       <c r="B248" s="57" t="s">
+        <v>678</v>
+      </c>
+      <c r="C248" s="57" t="s">
         <v>679</v>
       </c>
-      <c r="C248" s="57" t="s">
+      <c r="D248" s="57" t="s">
         <v>680</v>
-      </c>
-      <c r="D248" s="57" t="s">
-        <v>681</v>
       </c>
       <c r="E248" s="56"/>
       <c r="F248" s="34" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G248" s="56"/>
       <c r="H248" s="56"/>
@@ -14113,13 +14128,13 @@
         <v>109</v>
       </c>
       <c r="B249" s="57" t="s">
+        <v>681</v>
+      </c>
+      <c r="C249" s="57" t="s">
         <v>682</v>
       </c>
-      <c r="C249" s="57" t="s">
+      <c r="D249" s="57" t="s">
         <v>683</v>
-      </c>
-      <c r="D249" s="57" t="s">
-        <v>684</v>
       </c>
       <c r="E249" s="57"/>
       <c r="F249" s="57"/>
@@ -14149,7 +14164,7 @@
         <v>19</v>
       </c>
       <c r="B250" s="57" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C250" s="57" t="s">
         <v>21</v>
@@ -14185,13 +14200,13 @@
         <v>135</v>
       </c>
       <c r="B251" s="57" t="s">
+        <v>685</v>
+      </c>
+      <c r="C251" s="57" t="s">
         <v>686</v>
       </c>
-      <c r="C251" s="57" t="s">
+      <c r="D251" s="57" t="s">
         <v>687</v>
-      </c>
-      <c r="D251" s="57" t="s">
-        <v>688</v>
       </c>
       <c r="E251" s="57" t="s">
         <v>139</v>
@@ -14223,17 +14238,17 @@
         <v>109</v>
       </c>
       <c r="B252" s="57" t="s">
+        <v>688</v>
+      </c>
+      <c r="C252" s="57" t="s">
         <v>689</v>
       </c>
-      <c r="C252" s="57" t="s">
+      <c r="D252" s="57" t="s">
         <v>690</v>
-      </c>
-      <c r="D252" s="57" t="s">
-        <v>691</v>
       </c>
       <c r="E252" s="56"/>
       <c r="F252" s="57" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="G252" s="56"/>
       <c r="H252" s="56"/>
@@ -14261,7 +14276,7 @@
         <v>35</v>
       </c>
       <c r="B253" s="57" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C253" s="56"/>
       <c r="D253" s="56"/>
@@ -14293,7 +14308,7 @@
         <v>35</v>
       </c>
       <c r="B254" s="57" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C254" s="56"/>
       <c r="D254" s="56"/>
@@ -14325,17 +14340,17 @@
         <v>19</v>
       </c>
       <c r="B255" s="57" t="s">
+        <v>692</v>
+      </c>
+      <c r="C255" s="57" t="s">
         <v>693</v>
       </c>
-      <c r="C255" s="57" t="s">
+      <c r="D255" s="57" t="s">
         <v>694</v>
-      </c>
-      <c r="D255" s="57" t="s">
-        <v>695</v>
       </c>
       <c r="E255" s="56"/>
       <c r="F255" s="13" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="G255" s="57" t="s">
         <v>164</v>
@@ -14365,13 +14380,13 @@
         <v>109</v>
       </c>
       <c r="B256" s="57" t="s">
+        <v>696</v>
+      </c>
+      <c r="C256" s="57" t="s">
         <v>697</v>
       </c>
-      <c r="C256" s="57" t="s">
+      <c r="D256" s="2" t="s">
         <v>698</v>
-      </c>
-      <c r="D256" s="2" t="s">
-        <v>699</v>
       </c>
       <c r="E256" s="56"/>
       <c r="F256" s="34"/>
@@ -14401,7 +14416,7 @@
         <v>35</v>
       </c>
       <c r="B257" s="57" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C257" s="57"/>
       <c r="D257" s="57"/>
@@ -14433,17 +14448,17 @@
         <v>19</v>
       </c>
       <c r="B258" s="57" t="s">
+        <v>700</v>
+      </c>
+      <c r="C258" s="57" t="s">
         <v>701</v>
       </c>
-      <c r="C258" s="57" t="s">
+      <c r="D258" s="57" t="s">
         <v>702</v>
-      </c>
-      <c r="D258" s="57" t="s">
-        <v>703</v>
       </c>
       <c r="E258" s="56"/>
       <c r="F258" s="34" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="G258" s="56"/>
       <c r="H258" s="56"/>
@@ -14471,13 +14486,13 @@
         <v>135</v>
       </c>
       <c r="B259" s="57" t="s">
+        <v>704</v>
+      </c>
+      <c r="C259" s="57" t="s">
         <v>705</v>
       </c>
-      <c r="C259" s="57" t="s">
+      <c r="D259" s="57" t="s">
         <v>706</v>
-      </c>
-      <c r="D259" s="57" t="s">
-        <v>707</v>
       </c>
       <c r="E259" s="57" t="s">
         <v>139</v>
@@ -14506,22 +14521,22 @@
     </row>
     <row r="260" spans="1:26" ht="13">
       <c r="A260" s="57" t="s">
+        <v>707</v>
+      </c>
+      <c r="B260" s="57" t="s">
         <v>708</v>
       </c>
-      <c r="B260" s="57" t="s">
+      <c r="C260" s="57" t="s">
         <v>709</v>
       </c>
-      <c r="C260" s="57" t="s">
+      <c r="D260" s="57" t="s">
         <v>710</v>
-      </c>
-      <c r="D260" s="57" t="s">
-        <v>711</v>
       </c>
       <c r="E260" s="57" t="s">
         <v>139</v>
       </c>
       <c r="F260" s="57" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="G260" s="56"/>
       <c r="H260" s="56"/>
@@ -14546,22 +14561,22 @@
     </row>
     <row r="261" spans="1:26" ht="13">
       <c r="A261" s="57" t="s">
+        <v>712</v>
+      </c>
+      <c r="B261" s="57" t="s">
         <v>713</v>
       </c>
-      <c r="B261" s="57" t="s">
+      <c r="C261" s="57" t="s">
         <v>714</v>
       </c>
-      <c r="C261" s="57" t="s">
+      <c r="D261" s="57" t="s">
         <v>715</v>
-      </c>
-      <c r="D261" s="57" t="s">
-        <v>716</v>
       </c>
       <c r="E261" s="57" t="s">
         <v>139</v>
       </c>
       <c r="F261" s="57" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="G261" s="56"/>
       <c r="H261" s="56"/>
@@ -14570,7 +14585,7 @@
       <c r="K261" s="56"/>
       <c r="L261" s="56"/>
       <c r="M261" s="2" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="N261" s="56"/>
       <c r="O261" s="56"/>
@@ -14591,7 +14606,7 @@
         <v>19</v>
       </c>
       <c r="B262" s="57" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C262" s="57" t="s">
         <v>21</v>
@@ -14626,22 +14641,22 @@
     </row>
     <row r="263" spans="1:26" ht="13">
       <c r="A263" s="57" t="s">
+        <v>719</v>
+      </c>
+      <c r="B263" s="57" t="s">
         <v>720</v>
       </c>
-      <c r="B263" s="57" t="s">
+      <c r="C263" s="57" t="s">
         <v>721</v>
       </c>
-      <c r="C263" s="57" t="s">
+      <c r="D263" s="57" t="s">
         <v>722</v>
-      </c>
-      <c r="D263" s="57" t="s">
-        <v>723</v>
       </c>
       <c r="E263" s="57" t="s">
         <v>254</v>
       </c>
       <c r="F263" s="57" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="G263" s="56"/>
       <c r="H263" s="56"/>
@@ -14650,7 +14665,7 @@
       <c r="K263" s="56"/>
       <c r="L263" s="56"/>
       <c r="M263" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="N263" s="56"/>
       <c r="O263" s="56"/>
@@ -14668,22 +14683,22 @@
     </row>
     <row r="264" spans="1:26" ht="13">
       <c r="A264" s="57" t="s">
+        <v>725</v>
+      </c>
+      <c r="B264" s="57" t="s">
         <v>726</v>
       </c>
-      <c r="B264" s="57" t="s">
+      <c r="C264" s="57" t="s">
         <v>727</v>
       </c>
-      <c r="C264" s="57" t="s">
+      <c r="D264" s="57" t="s">
         <v>728</v>
-      </c>
-      <c r="D264" s="57" t="s">
-        <v>729</v>
       </c>
       <c r="E264" s="57" t="s">
         <v>139</v>
       </c>
       <c r="F264" s="57" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="G264" s="56"/>
       <c r="H264" s="56"/>
@@ -14711,7 +14726,7 @@
         <v>35</v>
       </c>
       <c r="B265" s="57" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C265" s="57"/>
       <c r="D265" s="56"/>
@@ -14740,22 +14755,22 @@
     </row>
     <row r="266" spans="1:26" ht="13">
       <c r="A266" s="57" t="s">
+        <v>730</v>
+      </c>
+      <c r="B266" s="57" t="s">
         <v>731</v>
       </c>
-      <c r="B266" s="57" t="s">
+      <c r="C266" s="57" t="s">
         <v>732</v>
       </c>
-      <c r="C266" s="57" t="s">
+      <c r="D266" s="57" t="s">
         <v>733</v>
-      </c>
-      <c r="D266" s="57" t="s">
-        <v>734</v>
       </c>
       <c r="E266" s="57" t="s">
         <v>139</v>
       </c>
       <c r="F266" s="57" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="G266" s="56"/>
       <c r="H266" s="56"/>
@@ -14780,22 +14795,22 @@
     </row>
     <row r="267" spans="1:26" ht="13">
       <c r="A267" s="57" t="s">
+        <v>734</v>
+      </c>
+      <c r="B267" s="57" t="s">
         <v>735</v>
       </c>
-      <c r="B267" s="57" t="s">
+      <c r="C267" s="57" t="s">
         <v>736</v>
       </c>
-      <c r="C267" s="57" t="s">
+      <c r="D267" s="7" t="s">
         <v>737</v>
-      </c>
-      <c r="D267" s="7" t="s">
-        <v>738</v>
       </c>
       <c r="E267" s="57" t="s">
         <v>139</v>
       </c>
       <c r="F267" s="57" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="G267" s="56"/>
       <c r="H267" s="56"/>
@@ -14820,22 +14835,22 @@
     </row>
     <row r="268" spans="1:26" ht="14.25">
       <c r="A268" s="57" t="s">
+        <v>739</v>
+      </c>
+      <c r="B268" s="57" t="s">
         <v>740</v>
       </c>
-      <c r="B268" s="57" t="s">
+      <c r="C268" s="64" t="s">
         <v>741</v>
       </c>
-      <c r="C268" s="64" t="s">
+      <c r="D268" s="57" t="s">
         <v>742</v>
-      </c>
-      <c r="D268" s="57" t="s">
-        <v>743</v>
       </c>
       <c r="E268" s="57" t="s">
         <v>139</v>
       </c>
       <c r="F268" s="13" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="G268" s="56"/>
       <c r="H268" s="56"/>
@@ -14860,22 +14875,22 @@
     </row>
     <row r="269" spans="1:26" ht="13">
       <c r="A269" s="57" t="s">
+        <v>744</v>
+      </c>
+      <c r="B269" s="57" t="s">
         <v>745</v>
       </c>
-      <c r="B269" s="57" t="s">
+      <c r="C269" s="57" t="s">
         <v>746</v>
       </c>
-      <c r="C269" s="57" t="s">
+      <c r="D269" s="57" t="s">
         <v>747</v>
-      </c>
-      <c r="D269" s="57" t="s">
-        <v>748</v>
       </c>
       <c r="E269" s="57" t="s">
         <v>139</v>
       </c>
       <c r="F269" s="57" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="G269" s="56"/>
       <c r="H269" s="56"/>
@@ -14903,19 +14918,19 @@
         <v>135</v>
       </c>
       <c r="B270" s="57" t="s">
+        <v>749</v>
+      </c>
+      <c r="C270" s="57" t="s">
         <v>750</v>
       </c>
-      <c r="C270" s="57" t="s">
+      <c r="D270" s="57" t="s">
         <v>751</v>
-      </c>
-      <c r="D270" s="57" t="s">
-        <v>752</v>
       </c>
       <c r="E270" s="57" t="s">
         <v>139</v>
       </c>
       <c r="F270" s="57" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="G270" s="56"/>
       <c r="H270" s="56"/>
@@ -14943,30 +14958,30 @@
         <v>236</v>
       </c>
       <c r="B271" s="57" t="s">
+        <v>752</v>
+      </c>
+      <c r="C271" s="57" t="s">
         <v>753</v>
       </c>
-      <c r="C271" s="57" t="s">
+      <c r="D271" s="57" t="s">
         <v>754</v>
-      </c>
-      <c r="D271" s="57" t="s">
-        <v>755</v>
       </c>
       <c r="E271" s="57" t="s">
         <v>139</v>
       </c>
       <c r="F271" s="57" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="G271" s="56"/>
       <c r="H271" s="56"/>
       <c r="I271" s="57" t="s">
+        <v>756</v>
+      </c>
+      <c r="J271" s="57" t="s">
         <v>757</v>
       </c>
-      <c r="J271" s="57" t="s">
+      <c r="K271" s="57" t="s">
         <v>758</v>
-      </c>
-      <c r="K271" s="57" t="s">
-        <v>759</v>
       </c>
       <c r="L271" s="56"/>
       <c r="M271" s="56"/>
@@ -14986,22 +15001,22 @@
     </row>
     <row r="272" spans="1:26" ht="13">
       <c r="A272" s="57" t="s">
+        <v>759</v>
+      </c>
+      <c r="B272" s="57" t="s">
         <v>760</v>
       </c>
-      <c r="B272" s="57" t="s">
+      <c r="C272" s="57" t="s">
         <v>761</v>
       </c>
-      <c r="C272" s="57" t="s">
+      <c r="D272" s="58" t="s">
         <v>762</v>
-      </c>
-      <c r="D272" s="58" t="s">
-        <v>763</v>
       </c>
       <c r="E272" s="57" t="s">
         <v>139</v>
       </c>
       <c r="F272" s="57" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="G272" s="56"/>
       <c r="H272" s="56"/>
@@ -15026,22 +15041,22 @@
     </row>
     <row r="273" spans="1:26" ht="13">
       <c r="A273" s="57" t="s">
+        <v>763</v>
+      </c>
+      <c r="B273" s="57" t="s">
         <v>764</v>
       </c>
-      <c r="B273" s="57" t="s">
+      <c r="C273" s="57" t="s">
         <v>765</v>
       </c>
-      <c r="C273" s="57" t="s">
+      <c r="D273" s="57" t="s">
         <v>766</v>
-      </c>
-      <c r="D273" s="57" t="s">
-        <v>767</v>
       </c>
       <c r="E273" s="57" t="s">
         <v>139</v>
       </c>
       <c r="F273" s="57" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="G273" s="56"/>
       <c r="H273" s="56"/>
@@ -15069,19 +15084,19 @@
         <v>135</v>
       </c>
       <c r="B274" s="57" t="s">
+        <v>767</v>
+      </c>
+      <c r="C274" s="7" t="s">
         <v>768</v>
       </c>
-      <c r="C274" s="7" t="s">
+      <c r="D274" s="57" t="s">
         <v>769</v>
-      </c>
-      <c r="D274" s="57" t="s">
-        <v>770</v>
       </c>
       <c r="E274" s="57" t="s">
         <v>139</v>
       </c>
       <c r="F274" s="57" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="G274" s="56"/>
       <c r="H274" s="56"/>
@@ -15109,7 +15124,7 @@
         <v>35</v>
       </c>
       <c r="B275" s="57" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C275" s="56"/>
       <c r="D275" s="56"/>
@@ -15141,17 +15156,17 @@
         <v>105</v>
       </c>
       <c r="B276" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="C276" s="65" t="s">
         <v>771</v>
       </c>
-      <c r="C276" s="65" t="s">
+      <c r="D276" s="66" t="s">
         <v>772</v>
-      </c>
-      <c r="D276" s="66" t="s">
-        <v>773</v>
       </c>
       <c r="E276" s="67"/>
       <c r="F276" s="68" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="277" spans="1:26" ht="13">
@@ -15159,13 +15174,13 @@
         <v>135</v>
       </c>
       <c r="B277" s="7" t="s">
+        <v>774</v>
+      </c>
+      <c r="C277" s="7" t="s">
         <v>775</v>
       </c>
-      <c r="C277" s="7" t="s">
+      <c r="D277" s="7" t="s">
         <v>776</v>
-      </c>
-      <c r="D277" s="7" t="s">
-        <v>777</v>
       </c>
       <c r="E277" s="7" t="s">
         <v>139</v>
@@ -15194,22 +15209,22 @@
     </row>
     <row r="278" spans="1:26" ht="13">
       <c r="A278" s="7" t="s">
+        <v>777</v>
+      </c>
+      <c r="B278" s="7" t="s">
         <v>778</v>
       </c>
-      <c r="B278" s="7" t="s">
+      <c r="C278" s="70" t="s">
         <v>779</v>
       </c>
-      <c r="C278" s="70" t="s">
+      <c r="D278" s="7" t="s">
         <v>780</v>
-      </c>
-      <c r="D278" s="7" t="s">
-        <v>781</v>
       </c>
       <c r="E278" s="7" t="s">
         <v>139</v>
       </c>
       <c r="F278" s="7" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="G278" s="69"/>
       <c r="H278" s="9"/>
@@ -15237,7 +15252,7 @@
         <v>19</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C279" s="71" t="s">
         <v>21</v>
@@ -15250,42 +15265,42 @@
     </row>
     <row r="280" spans="1:26" ht="13">
       <c r="A280" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="B280" s="2" t="s">
         <v>784</v>
       </c>
-      <c r="B280" s="2" t="s">
+      <c r="C280" s="71" t="s">
         <v>785</v>
       </c>
-      <c r="C280" s="71" t="s">
+      <c r="D280" s="2" t="s">
         <v>786</v>
-      </c>
-      <c r="D280" s="2" t="s">
-        <v>787</v>
       </c>
       <c r="E280" s="2" t="s">
         <v>139</v>
       </c>
       <c r="F280" s="72" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="281" spans="1:26" ht="13">
       <c r="A281" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C281" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="D281" s="2" t="s">
         <v>728</v>
-      </c>
-      <c r="D281" s="2" t="s">
-        <v>729</v>
       </c>
       <c r="E281" s="2" t="s">
         <v>139</v>
       </c>
       <c r="F281" s="72" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="282" spans="1:26" ht="13">
@@ -15293,7 +15308,7 @@
         <v>35</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C282" s="73"/>
       <c r="E282" s="2"/>
@@ -15304,7 +15319,7 @@
         <v>19</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C283" s="73" t="s">
         <v>21</v>
@@ -15317,42 +15332,42 @@
     </row>
     <row r="284" spans="1:26" ht="13">
       <c r="A284" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="B284" s="2" t="s">
         <v>791</v>
       </c>
-      <c r="B284" s="2" t="s">
+      <c r="C284" s="71" t="s">
         <v>792</v>
       </c>
-      <c r="C284" s="71" t="s">
+      <c r="D284" s="2" t="s">
         <v>793</v>
-      </c>
-      <c r="D284" s="2" t="s">
-        <v>794</v>
       </c>
       <c r="E284" s="2" t="s">
         <v>139</v>
       </c>
       <c r="F284" s="72" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="285" spans="1:26" ht="13">
       <c r="A285" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="C285" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="D285" s="2" t="s">
         <v>728</v>
-      </c>
-      <c r="D285" s="2" t="s">
-        <v>729</v>
       </c>
       <c r="E285" s="2" t="s">
         <v>139</v>
       </c>
       <c r="F285" s="72" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="286" spans="1:26" ht="13">
@@ -15360,7 +15375,7 @@
         <v>35</v>
       </c>
       <c r="B286" s="10" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C286" s="74"/>
       <c r="D286" s="75"/>
@@ -15392,7 +15407,7 @@
         <v>19</v>
       </c>
       <c r="B287" s="10" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C287" s="74" t="s">
         <v>21</v>
@@ -15425,22 +15440,22 @@
     </row>
     <row r="288" spans="1:26" ht="13">
       <c r="A288" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="B288" s="2" t="s">
         <v>798</v>
       </c>
-      <c r="B288" s="2" t="s">
+      <c r="C288" s="2" t="s">
         <v>799</v>
       </c>
-      <c r="C288" s="2" t="s">
+      <c r="D288" s="2" t="s">
         <v>800</v>
-      </c>
-      <c r="D288" s="2" t="s">
-        <v>801</v>
       </c>
       <c r="E288" s="2" t="s">
         <v>139</v>
       </c>
       <c r="F288" s="72" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="289" spans="1:26" ht="13">
@@ -15448,7 +15463,7 @@
         <v>35</v>
       </c>
       <c r="B289" s="10" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C289" s="74"/>
       <c r="D289" s="75"/>
@@ -15480,7 +15495,7 @@
         <v>19</v>
       </c>
       <c r="B290" s="10" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="C290" s="74" t="s">
         <v>21</v>
@@ -15516,19 +15531,19 @@
         <v>174</v>
       </c>
       <c r="B291" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="C291" s="2" t="s">
         <v>803</v>
       </c>
-      <c r="C291" s="2" t="s">
+      <c r="D291" s="2" t="s">
         <v>804</v>
-      </c>
-      <c r="D291" s="2" t="s">
-        <v>805</v>
       </c>
       <c r="E291" s="2" t="s">
         <v>139</v>
       </c>
       <c r="F291" s="72" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="292" spans="1:26" ht="13">
@@ -15536,7 +15551,7 @@
         <v>35</v>
       </c>
       <c r="B292" s="10" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="C292" s="2"/>
       <c r="E292" s="2"/>
@@ -15547,7 +15562,7 @@
         <v>19</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="C293" s="2" t="s">
         <v>21</v>
@@ -15565,42 +15580,42 @@
         <v>236</v>
       </c>
       <c r="B294" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="C294" s="2" t="s">
         <v>808</v>
       </c>
-      <c r="C294" s="2" t="s">
+      <c r="D294" s="2" t="s">
         <v>809</v>
       </c>
-      <c r="D294" s="2" t="s">
+      <c r="F294" s="72" t="s">
+        <v>805</v>
+      </c>
+      <c r="I294" s="2" t="s">
         <v>810</v>
       </c>
-      <c r="F294" s="72" t="s">
-        <v>806</v>
-      </c>
-      <c r="I294" s="2" t="s">
+      <c r="J294" s="2" t="s">
         <v>811</v>
-      </c>
-      <c r="J294" s="2" t="s">
-        <v>812</v>
       </c>
     </row>
     <row r="295" spans="1:26" ht="13">
       <c r="A295" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="B295" s="2" t="s">
         <v>813</v>
       </c>
-      <c r="B295" s="2" t="s">
+      <c r="C295" s="2" t="s">
         <v>814</v>
       </c>
-      <c r="C295" s="2" t="s">
+      <c r="D295" s="2" t="s">
         <v>815</v>
-      </c>
-      <c r="D295" s="2" t="s">
-        <v>816</v>
       </c>
       <c r="E295" s="2" t="s">
         <v>139</v>
       </c>
       <c r="F295" s="72" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="296" spans="1:26" ht="13">
@@ -15608,7 +15623,7 @@
         <v>35</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C296" s="2"/>
       <c r="E296" s="2"/>
@@ -15620,7 +15635,7 @@
         <v>19</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C297" s="2" t="s">
         <v>21</v>
@@ -15636,19 +15651,19 @@
         <v>174</v>
       </c>
       <c r="B298" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="C298" s="2" t="s">
         <v>818</v>
       </c>
-      <c r="C298" s="2" t="s">
+      <c r="D298" s="2" t="s">
         <v>819</v>
-      </c>
-      <c r="D298" s="2" t="s">
-        <v>820</v>
       </c>
       <c r="E298" s="2" t="s">
         <v>139</v>
       </c>
       <c r="F298" s="72" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="299" spans="1:26" ht="13">
@@ -15656,22 +15671,22 @@
         <v>236</v>
       </c>
       <c r="B299" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="C299" s="2" t="s">
         <v>821</v>
       </c>
-      <c r="C299" s="2" t="s">
+      <c r="D299" s="2" t="s">
         <v>822</v>
       </c>
-      <c r="D299" s="2" t="s">
+      <c r="F299" s="72" t="s">
         <v>823</v>
       </c>
-      <c r="F299" s="72" t="s">
+      <c r="I299" s="2" t="s">
         <v>824</v>
       </c>
-      <c r="I299" s="2" t="s">
+      <c r="J299" s="2" t="s">
         <v>825</v>
-      </c>
-      <c r="J299" s="2" t="s">
-        <v>826</v>
       </c>
     </row>
     <row r="300" spans="1:26" ht="13">
@@ -15679,7 +15694,7 @@
         <v>35</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="301" spans="1:26" ht="13">
@@ -15687,7 +15702,7 @@
         <v>35</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="302" spans="1:26" ht="13">
@@ -15695,32 +15710,34 @@
         <v>19</v>
       </c>
       <c r="B302" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="C302" s="2" t="s">
         <v>827</v>
       </c>
-      <c r="C302" s="2" t="s">
+      <c r="D302" s="2" t="s">
         <v>828</v>
       </c>
-      <c r="D302" s="2" t="s">
+      <c r="F302" s="2" t="s">
         <v>829</v>
-      </c>
-      <c r="F302" s="2" t="s">
-        <v>830</v>
       </c>
       <c r="G302" s="2" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="303" spans="1:26" ht="26">
+    <row r="303" spans="1:26" ht="39">
       <c r="A303" s="46" t="s">
         <v>109</v>
       </c>
       <c r="B303" s="46" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="C303" s="88" t="s">
-        <v>1390</v>
-      </c>
-      <c r="D303" s="46"/>
+        <v>1388</v>
+      </c>
+      <c r="D303" s="88" t="s">
+        <v>1434</v>
+      </c>
       <c r="F303" s="46"/>
       <c r="G303" s="46"/>
     </row>
@@ -15729,16 +15746,16 @@
         <v>109</v>
       </c>
       <c r="B304" s="46" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C304" s="88" t="s">
+        <v>1346</v>
+      </c>
+      <c r="D304" s="46" t="s">
+        <v>1389</v>
+      </c>
+      <c r="F304" s="46" t="s">
         <v>1347</v>
-      </c>
-      <c r="C304" s="88" t="s">
-        <v>1348</v>
-      </c>
-      <c r="D304" s="46" t="s">
-        <v>1391</v>
-      </c>
-      <c r="F304" s="46" t="s">
-        <v>1349</v>
       </c>
       <c r="G304" s="46"/>
     </row>
@@ -15747,16 +15764,16 @@
         <v>109</v>
       </c>
       <c r="B305" s="46" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="C305" s="88" t="s">
+        <v>1348</v>
+      </c>
+      <c r="D305" s="101" t="s">
+        <v>1390</v>
+      </c>
+      <c r="F305" s="46" t="s">
         <v>1350</v>
-      </c>
-      <c r="D305" s="101" t="s">
-        <v>1392</v>
-      </c>
-      <c r="F305" s="46" t="s">
-        <v>1352</v>
       </c>
       <c r="G305" s="46"/>
     </row>
@@ -15765,16 +15782,16 @@
         <v>109</v>
       </c>
       <c r="B306" s="46" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="C306" s="88" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="D306" s="101" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="F306" s="46" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="G306" s="46"/>
     </row>
@@ -15783,16 +15800,16 @@
         <v>109</v>
       </c>
       <c r="B307" s="46" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="C307" s="46" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="D307" s="46" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="F307" s="88" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="G307" s="46"/>
       <c r="L307" s="101"/>
@@ -15802,16 +15819,16 @@
         <v>109</v>
       </c>
       <c r="B308" s="46" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="C308" s="46" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="D308" s="46" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="F308" s="88" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="G308" s="46"/>
       <c r="L308" s="101"/>
@@ -15821,16 +15838,16 @@
         <v>109</v>
       </c>
       <c r="B309" s="46" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="C309" s="46" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="D309" s="46" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="F309" s="88" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="G309" s="46"/>
       <c r="L309" s="101"/>
@@ -15840,16 +15857,16 @@
         <v>109</v>
       </c>
       <c r="B310" s="46" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="C310" s="46" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="D310" s="46" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="F310" s="88" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="G310" s="46"/>
       <c r="L310" s="101"/>
@@ -15859,16 +15876,16 @@
         <v>109</v>
       </c>
       <c r="B311" s="46" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="C311" s="46" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="D311" s="46" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="F311" s="88" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="G311" s="46"/>
       <c r="L311" s="101"/>
@@ -15878,16 +15895,16 @@
         <v>109</v>
       </c>
       <c r="B312" s="46" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="C312" s="46" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="D312" s="46" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F312" s="88" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="G312" s="46"/>
       <c r="L312" s="101"/>
@@ -15897,16 +15914,16 @@
         <v>109</v>
       </c>
       <c r="B313" s="46" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="C313" s="46" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="D313" s="46" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="F313" s="88" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="G313" s="46"/>
       <c r="L313" s="101"/>
@@ -15916,13 +15933,13 @@
         <v>109</v>
       </c>
       <c r="B314" s="46" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="C314" s="88" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="D314" s="101" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="F314" s="46" t="s">
         <v>255</v>
@@ -15934,16 +15951,16 @@
         <v>109</v>
       </c>
       <c r="B315" s="46" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C315" s="88" t="s">
+        <v>1357</v>
+      </c>
+      <c r="D315" s="101" t="s">
+        <v>1393</v>
+      </c>
+      <c r="F315" s="46" t="s">
         <v>1358</v>
-      </c>
-      <c r="C315" s="88" t="s">
-        <v>1359</v>
-      </c>
-      <c r="D315" s="101" t="s">
-        <v>1395</v>
-      </c>
-      <c r="F315" s="46" t="s">
-        <v>1360</v>
       </c>
       <c r="G315" s="46"/>
     </row>
@@ -15952,16 +15969,16 @@
         <v>109</v>
       </c>
       <c r="B316" s="46" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="C316" s="88" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="D316" s="101" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="F316" s="46" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="G316" s="46"/>
     </row>
@@ -15970,16 +15987,16 @@
         <v>109</v>
       </c>
       <c r="B317" s="88" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="C317" s="88" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="D317" s="101" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="F317" s="46" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="G317" s="46"/>
     </row>
@@ -15988,16 +16005,16 @@
         <v>109</v>
       </c>
       <c r="B318" s="46" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C318" s="46" t="s">
+        <v>1294</v>
+      </c>
+      <c r="D318" s="46" t="s">
         <v>1295</v>
       </c>
-      <c r="C318" s="46" t="s">
-        <v>1296</v>
-      </c>
-      <c r="D318" s="46" t="s">
-        <v>1297</v>
-      </c>
       <c r="F318" s="46" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="G318" s="46"/>
     </row>
@@ -16006,16 +16023,16 @@
         <v>109</v>
       </c>
       <c r="B319" s="46" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C319" s="46" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D319" s="46" t="s">
         <v>1298</v>
       </c>
-      <c r="C319" s="46" t="s">
-        <v>1299</v>
-      </c>
-      <c r="D319" s="46" t="s">
-        <v>1300</v>
-      </c>
       <c r="F319" s="46" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="G319" s="46"/>
     </row>
@@ -16024,16 +16041,16 @@
         <v>109</v>
       </c>
       <c r="B320" s="46" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C320" s="46" t="s">
+        <v>1300</v>
+      </c>
+      <c r="D320" s="46" t="s">
         <v>1301</v>
       </c>
-      <c r="C320" s="46" t="s">
-        <v>1302</v>
-      </c>
-      <c r="D320" s="46" t="s">
-        <v>1303</v>
-      </c>
       <c r="F320" s="46" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="G320" s="46"/>
     </row>
@@ -16042,16 +16059,16 @@
         <v>109</v>
       </c>
       <c r="B321" s="46" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C321" s="46" t="s">
+        <v>1303</v>
+      </c>
+      <c r="D321" s="46" t="s">
         <v>1304</v>
       </c>
-      <c r="C321" s="46" t="s">
-        <v>1305</v>
-      </c>
-      <c r="D321" s="46" t="s">
-        <v>1306</v>
-      </c>
       <c r="F321" s="46" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="G321" s="46"/>
     </row>
@@ -16060,16 +16077,16 @@
         <v>109</v>
       </c>
       <c r="B322" s="46" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="C322" s="88" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="D322" s="101" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="F322" s="46" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="G322" s="46"/>
     </row>
@@ -16078,16 +16095,16 @@
         <v>109</v>
       </c>
       <c r="B323" s="46" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="C323" s="88" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="D323" s="101" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="F323" s="46" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="G323" s="46"/>
     </row>
@@ -16096,16 +16113,16 @@
         <v>109</v>
       </c>
       <c r="B324" s="46" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="C324" s="88" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="D324" s="101" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="F324" s="46" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="G324" s="46"/>
     </row>
@@ -16114,16 +16131,16 @@
         <v>109</v>
       </c>
       <c r="B325" s="46" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="C325" s="88" t="s">
+        <v>1372</v>
+      </c>
+      <c r="D325" s="101" t="s">
+        <v>1400</v>
+      </c>
+      <c r="F325" s="46" t="s">
         <v>1374</v>
-      </c>
-      <c r="D325" s="101" t="s">
-        <v>1402</v>
-      </c>
-      <c r="F325" s="46" t="s">
-        <v>1376</v>
       </c>
       <c r="G325" s="46"/>
     </row>
@@ -16132,16 +16149,16 @@
         <v>109</v>
       </c>
       <c r="B326" s="46" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="C326" s="88" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D326" s="101" t="s">
+        <v>1401</v>
+      </c>
+      <c r="F326" s="46" t="s">
         <v>1373</v>
-      </c>
-      <c r="D326" s="101" t="s">
-        <v>1403</v>
-      </c>
-      <c r="F326" s="46" t="s">
-        <v>1375</v>
       </c>
       <c r="G326" s="46"/>
     </row>
@@ -16150,17 +16167,17 @@
         <v>109</v>
       </c>
       <c r="B327" s="92" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="C327" s="92" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="D327" s="93" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="E327" s="92"/>
       <c r="F327" s="93" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="G327" s="92"/>
       <c r="H327" s="92"/>
@@ -16188,17 +16205,17 @@
         <v>109</v>
       </c>
       <c r="B328" s="92" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C328" s="92" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="D328" s="93" t="s">
-        <v>833</v>
+        <v>1435</v>
       </c>
       <c r="E328" s="92"/>
       <c r="F328" s="92" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="G328" s="92"/>
       <c r="H328" s="92"/>
@@ -16226,20 +16243,20 @@
         <v>109</v>
       </c>
       <c r="B329" s="92" t="s">
+        <v>833</v>
+      </c>
+      <c r="C329" s="92" t="s">
+        <v>834</v>
+      </c>
+      <c r="D329" s="94" t="s">
         <v>835</v>
-      </c>
-      <c r="C329" s="92" t="s">
-        <v>836</v>
-      </c>
-      <c r="D329" s="94" t="s">
-        <v>837</v>
       </c>
       <c r="E329" s="92"/>
       <c r="F329" s="95" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="G329" s="92" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="H329" s="92"/>
       <c r="I329" s="92"/>
@@ -16266,20 +16283,20 @@
         <v>109</v>
       </c>
       <c r="B330" s="92" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="C330" s="92" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="D330" s="92" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="E330" s="92"/>
       <c r="F330" s="96" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="G330" s="92" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="H330" s="92"/>
       <c r="I330" s="92"/>
@@ -16306,20 +16323,20 @@
         <v>109</v>
       </c>
       <c r="B331" s="92" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="C331" s="92" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="D331" s="93" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="E331" s="92"/>
       <c r="F331" s="92" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="G331" s="92" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="H331" s="92"/>
       <c r="I331" s="92"/>
@@ -16346,7 +16363,7 @@
         <v>113</v>
       </c>
       <c r="B332" s="46" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C332" s="46"/>
       <c r="D332" s="46"/>
@@ -16358,7 +16375,7 @@
         <v>41</v>
       </c>
       <c r="B333" s="92" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="C333" s="92"/>
       <c r="D333" s="92"/>
@@ -16370,7 +16387,7 @@
       <c r="J333" s="92"/>
       <c r="K333" s="92"/>
       <c r="L333" s="92" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="M333" s="92"/>
       <c r="N333" s="92"/>
@@ -16392,7 +16409,7 @@
         <v>41</v>
       </c>
       <c r="B334" s="92" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="C334" s="92"/>
       <c r="D334" s="92"/>
@@ -16404,7 +16421,7 @@
       <c r="J334" s="92"/>
       <c r="K334" s="92"/>
       <c r="L334" s="92" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="M334" s="92"/>
       <c r="N334" s="92"/>
@@ -16426,7 +16443,7 @@
         <v>41</v>
       </c>
       <c r="B335" s="92" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="C335" s="92"/>
       <c r="D335" s="92"/>
@@ -16438,7 +16455,7 @@
       <c r="J335" s="92"/>
       <c r="K335" s="92"/>
       <c r="L335" s="92" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="M335" s="92"/>
       <c r="N335" s="92"/>
@@ -16460,7 +16477,7 @@
         <v>41</v>
       </c>
       <c r="B336" s="92" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="C336" s="92"/>
       <c r="D336" s="92"/>
@@ -16472,7 +16489,7 @@
       <c r="J336" s="92"/>
       <c r="K336" s="92"/>
       <c r="L336" s="92" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="M336" s="92"/>
       <c r="N336" s="92"/>
@@ -16494,7 +16511,7 @@
         <v>41</v>
       </c>
       <c r="B337" s="92" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="C337" s="92"/>
       <c r="D337" s="92"/>
@@ -16506,7 +16523,7 @@
       <c r="J337" s="92"/>
       <c r="K337" s="92"/>
       <c r="L337" s="92" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="M337" s="92"/>
       <c r="N337" s="92"/>
@@ -16556,7 +16573,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1" s="76" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="B1" s="76" t="s">
         <v>1</v>
@@ -16573,464 +16590,464 @@
     </row>
     <row r="2" spans="1:5" ht="14.75">
       <c r="A2" s="77" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="B2" s="77" t="s">
         <v>139</v>
       </c>
       <c r="C2" s="77" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="D2" s="77" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="14.75">
       <c r="A3" s="77" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="B3" s="77" t="s">
+        <v>856</v>
+      </c>
+      <c r="C3" s="77" t="s">
+        <v>857</v>
+      </c>
+      <c r="D3" s="77" t="s">
         <v>858</v>
-      </c>
-      <c r="C3" s="77" t="s">
-        <v>859</v>
-      </c>
-      <c r="D3" s="77" t="s">
-        <v>860</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1">
       <c r="A4" s="45" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B4" s="16" t="s">
+        <v>859</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>860</v>
+      </c>
+      <c r="D4" s="78" t="s">
         <v>861</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>862</v>
-      </c>
-      <c r="D4" s="78" t="s">
-        <v>863</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1">
       <c r="A5" s="45" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B5" s="16" t="s">
+        <v>862</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>863</v>
+      </c>
+      <c r="D5" s="78" t="s">
         <v>864</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>865</v>
-      </c>
-      <c r="D5" s="78" t="s">
-        <v>866</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1">
       <c r="A6" s="45" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B6" s="16" t="s">
+        <v>865</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>866</v>
+      </c>
+      <c r="D6" s="40" t="s">
         <v>867</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>868</v>
-      </c>
-      <c r="D6" s="40" t="s">
-        <v>869</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1">
       <c r="A7" s="45" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B7" s="16" t="s">
+        <v>868</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>869</v>
+      </c>
+      <c r="D7" s="38" t="s">
         <v>870</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>871</v>
-      </c>
-      <c r="D7" s="38" t="s">
-        <v>872</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1">
       <c r="A8" s="45" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B8" s="16" t="s">
+        <v>871</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>872</v>
+      </c>
+      <c r="D8" s="78" t="s">
         <v>873</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>874</v>
-      </c>
-      <c r="D8" s="78" t="s">
-        <v>875</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1">
       <c r="A9" s="45" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B9" s="16" t="s">
+        <v>874</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>875</v>
+      </c>
+      <c r="D9" s="78" t="s">
         <v>876</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>877</v>
-      </c>
-      <c r="D9" s="78" t="s">
-        <v>878</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" customHeight="1">
       <c r="A10" s="45" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B10" s="16" t="s">
+        <v>877</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>878</v>
+      </c>
+      <c r="D10" s="78" t="s">
         <v>879</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>880</v>
-      </c>
-      <c r="D10" s="78" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.75" customHeight="1">
       <c r="A11" s="45" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B11" s="16" t="s">
+        <v>880</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>881</v>
+      </c>
+      <c r="D11" s="78" t="s">
         <v>882</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>883</v>
-      </c>
-      <c r="D11" s="78" t="s">
-        <v>884</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.75" customHeight="1">
       <c r="A12" s="45" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B12" s="16" t="s">
+        <v>883</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>884</v>
+      </c>
+      <c r="D12" s="78" t="s">
         <v>885</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>886</v>
-      </c>
-      <c r="D12" s="78" t="s">
-        <v>887</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.75" customHeight="1">
       <c r="A13" s="45" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B13" s="16" t="s">
+        <v>886</v>
+      </c>
+      <c r="C13" s="60" t="s">
+        <v>887</v>
+      </c>
+      <c r="D13" s="78" t="s">
         <v>888</v>
-      </c>
-      <c r="C13" s="60" t="s">
-        <v>889</v>
-      </c>
-      <c r="D13" s="78" t="s">
-        <v>890</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.75" customHeight="1">
       <c r="A14" s="45" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B14" s="16" t="s">
+        <v>889</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>890</v>
+      </c>
+      <c r="D14" s="78" t="s">
         <v>891</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>892</v>
-      </c>
-      <c r="D14" s="78" t="s">
-        <v>893</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.75" customHeight="1">
       <c r="A15" s="45" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B15" s="16" t="s">
+        <v>892</v>
+      </c>
+      <c r="C15" s="60" t="s">
+        <v>893</v>
+      </c>
+      <c r="D15" s="78" t="s">
         <v>894</v>
-      </c>
-      <c r="C15" s="60" t="s">
-        <v>895</v>
-      </c>
-      <c r="D15" s="78" t="s">
-        <v>896</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.75" customHeight="1">
       <c r="A16" s="45" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B16" s="16" t="s">
+        <v>895</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>896</v>
+      </c>
+      <c r="D16" s="78" t="s">
         <v>897</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>898</v>
-      </c>
-      <c r="D16" s="78" t="s">
-        <v>899</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75" customHeight="1">
       <c r="A17" s="45" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B17" s="5" t="s">
+        <v>898</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>899</v>
+      </c>
+      <c r="D17" s="78" t="s">
         <v>900</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>901</v>
-      </c>
-      <c r="D17" s="78" t="s">
-        <v>902</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="13">
       <c r="A18" s="16" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B18" s="16" t="s">
+        <v>901</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>902</v>
+      </c>
+      <c r="D18" s="38" t="s">
         <v>903</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>904</v>
-      </c>
-      <c r="D18" s="38" t="s">
-        <v>905</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="13">
       <c r="A19" s="16" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B19" s="16" t="s">
+        <v>904</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>905</v>
+      </c>
+      <c r="D19" s="38" t="s">
         <v>906</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>907</v>
-      </c>
-      <c r="D19" s="38" t="s">
-        <v>908</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="13">
       <c r="A20" s="16" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B20" s="16" t="s">
+        <v>907</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>908</v>
+      </c>
+      <c r="D20" s="78" t="s">
         <v>909</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>910</v>
-      </c>
-      <c r="D20" s="78" t="s">
-        <v>911</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="13">
       <c r="A21" s="16" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B21" s="16" t="s">
+        <v>910</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>911</v>
+      </c>
+      <c r="D21" s="78" t="s">
         <v>912</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>913</v>
-      </c>
-      <c r="D21" s="78" t="s">
-        <v>914</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="13">
       <c r="A22" s="16" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B22" s="16" t="s">
+        <v>913</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>914</v>
+      </c>
+      <c r="D22" s="78" t="s">
         <v>915</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>916</v>
-      </c>
-      <c r="D22" s="78" t="s">
-        <v>917</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="13">
       <c r="A23" s="16" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B23" s="16" t="s">
+        <v>916</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>917</v>
+      </c>
+      <c r="D23" s="78" t="s">
         <v>918</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>919</v>
-      </c>
-      <c r="D23" s="78" t="s">
-        <v>920</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="13">
       <c r="A24" s="16" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B24" s="16" t="s">
+        <v>919</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>920</v>
+      </c>
+      <c r="D24" s="78" t="s">
         <v>921</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>922</v>
-      </c>
-      <c r="D24" s="78" t="s">
-        <v>923</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="13">
       <c r="A25" s="16" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B25" s="16" t="s">
+        <v>922</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>923</v>
+      </c>
+      <c r="D25" s="78" t="s">
         <v>924</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>925</v>
-      </c>
-      <c r="D25" s="78" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="13">
       <c r="A26" s="16" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B26" s="16" t="s">
+        <v>925</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>926</v>
+      </c>
+      <c r="D26" s="78" t="s">
         <v>927</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>928</v>
-      </c>
-      <c r="D26" s="78" t="s">
-        <v>929</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="13">
       <c r="A27" s="16" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B27" s="45" t="s">
+        <v>928</v>
+      </c>
+      <c r="C27" s="38" t="s">
+        <v>929</v>
+      </c>
+      <c r="D27" s="78" t="s">
         <v>930</v>
-      </c>
-      <c r="C27" s="38" t="s">
-        <v>931</v>
-      </c>
-      <c r="D27" s="78" t="s">
-        <v>932</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="13">
       <c r="A28" s="16" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B28" s="45" t="s">
+        <v>931</v>
+      </c>
+      <c r="C28" s="79" t="s">
+        <v>932</v>
+      </c>
+      <c r="D28" s="80" t="s">
         <v>933</v>
-      </c>
-      <c r="C28" s="79" t="s">
-        <v>934</v>
-      </c>
-      <c r="D28" s="80" t="s">
-        <v>935</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="13">
       <c r="A29" s="16" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B29" s="45" t="s">
+        <v>934</v>
+      </c>
+      <c r="C29" s="79" t="s">
+        <v>935</v>
+      </c>
+      <c r="D29" s="78" t="s">
         <v>936</v>
-      </c>
-      <c r="C29" s="79" t="s">
-        <v>937</v>
-      </c>
-      <c r="D29" s="78" t="s">
-        <v>938</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="13">
       <c r="A30" s="16" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B30" s="45" t="s">
+        <v>937</v>
+      </c>
+      <c r="C30" s="45" t="s">
+        <v>938</v>
+      </c>
+      <c r="D30" s="78" t="s">
         <v>939</v>
-      </c>
-      <c r="C30" s="45" t="s">
-        <v>940</v>
-      </c>
-      <c r="D30" s="78" t="s">
-        <v>941</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="13">
       <c r="A31" s="16" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B31" s="45" t="s">
+        <v>940</v>
+      </c>
+      <c r="C31" s="79" t="s">
+        <v>941</v>
+      </c>
+      <c r="D31" s="80" t="s">
         <v>942</v>
-      </c>
-      <c r="C31" s="79" t="s">
-        <v>943</v>
-      </c>
-      <c r="D31" s="80" t="s">
-        <v>944</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="13">
       <c r="A32" s="16" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B32" s="45" t="s">
+        <v>943</v>
+      </c>
+      <c r="C32" s="79" t="s">
+        <v>944</v>
+      </c>
+      <c r="D32" s="38" t="s">
         <v>945</v>
-      </c>
-      <c r="C32" s="79" t="s">
-        <v>946</v>
-      </c>
-      <c r="D32" s="38" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="33" spans="1:26" ht="13">
       <c r="A33" s="16" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B33" s="45" t="s">
+        <v>946</v>
+      </c>
+      <c r="C33" s="45" t="s">
+        <v>947</v>
+      </c>
+      <c r="D33" s="78" t="s">
         <v>948</v>
-      </c>
-      <c r="C33" s="45" t="s">
-        <v>949</v>
-      </c>
-      <c r="D33" s="78" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="34" spans="1:26" ht="13">
       <c r="A34" s="16" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B34" s="5" t="s">
+        <v>949</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>950</v>
+      </c>
+      <c r="D34" s="78" t="s">
         <v>951</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>952</v>
-      </c>
-      <c r="D34" s="78" t="s">
-        <v>953</v>
       </c>
     </row>
     <row r="35" spans="1:26" ht="13">
@@ -17038,13 +17055,13 @@
         <v>308</v>
       </c>
       <c r="B35" s="16" t="s">
+        <v>952</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>953</v>
+      </c>
+      <c r="D35" s="78" t="s">
         <v>954</v>
-      </c>
-      <c r="C35" s="16" t="s">
-        <v>955</v>
-      </c>
-      <c r="D35" s="78" t="s">
-        <v>956</v>
       </c>
     </row>
     <row r="36" spans="1:26" ht="13">
@@ -17052,13 +17069,13 @@
         <v>308</v>
       </c>
       <c r="B36" s="16" t="s">
+        <v>955</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>956</v>
+      </c>
+      <c r="D36" s="38" t="s">
         <v>957</v>
-      </c>
-      <c r="C36" s="16" t="s">
-        <v>958</v>
-      </c>
-      <c r="D36" s="38" t="s">
-        <v>959</v>
       </c>
     </row>
     <row r="37" spans="1:26" ht="13">
@@ -17066,27 +17083,27 @@
         <v>308</v>
       </c>
       <c r="B37" s="5" t="s">
+        <v>958</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>959</v>
+      </c>
+      <c r="D37" s="78" t="s">
         <v>960</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>961</v>
-      </c>
-      <c r="D37" s="78" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="38" spans="1:26" ht="13">
       <c r="A38" s="4" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
@@ -17113,16 +17130,16 @@
     </row>
     <row r="39" spans="1:26" ht="13">
       <c r="A39" s="4" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
@@ -17149,16 +17166,16 @@
     </row>
     <row r="40" spans="1:26" ht="13">
       <c r="A40" s="4" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B40" s="4" t="s">
+        <v>965</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>966</v>
+      </c>
+      <c r="D40" s="10" t="s">
         <v>967</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>968</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>969</v>
       </c>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
@@ -17185,19 +17202,19 @@
     </row>
     <row r="41" spans="1:26" ht="13">
       <c r="A41" s="4" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
@@ -17223,19 +17240,19 @@
     </row>
     <row r="42" spans="1:26" ht="13">
       <c r="A42" s="4" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
@@ -17261,19 +17278,19 @@
     </row>
     <row r="43" spans="1:26" ht="13">
       <c r="A43" s="4" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
@@ -17299,19 +17316,19 @@
     </row>
     <row r="44" spans="1:26" ht="13">
       <c r="A44" s="4" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="F44" s="4"/>
       <c r="G44" s="4"/>
@@ -17337,19 +17354,19 @@
     </row>
     <row r="45" spans="1:26" ht="13">
       <c r="A45" s="4" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
@@ -17375,19 +17392,19 @@
     </row>
     <row r="46" spans="1:26" ht="13">
       <c r="A46" s="4" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
@@ -17413,19 +17430,19 @@
     </row>
     <row r="47" spans="1:26" ht="13">
       <c r="A47" s="4" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
@@ -17451,19 +17468,19 @@
     </row>
     <row r="48" spans="1:26" ht="13">
       <c r="A48" s="4" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
@@ -17489,19 +17506,19 @@
     </row>
     <row r="49" spans="1:26" ht="13">
       <c r="A49" s="4" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
@@ -17527,19 +17544,19 @@
     </row>
     <row r="50" spans="1:26" ht="13">
       <c r="A50" s="4" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="F50" s="4"/>
       <c r="G50" s="4"/>
@@ -17565,19 +17582,19 @@
     </row>
     <row r="51" spans="1:26" ht="13">
       <c r="A51" s="4" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
@@ -17603,20 +17620,20 @@
     </row>
     <row r="52" spans="1:26" ht="13">
       <c r="A52" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B52" s="4" t="str">
         <f t="shared" ref="B52:B115" si="0">LOWER(SUBSTITUTE(C52," ",""))</f>
         <v>chakechakedistricthospital</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
@@ -17642,20 +17659,20 @@
     </row>
     <row r="53" spans="1:26" ht="13">
       <c r="A53" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B53" s="4" t="str">
         <f t="shared" si="0"/>
         <v>pujiniphcu+</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
@@ -17681,20 +17698,20 @@
     </row>
     <row r="54" spans="1:26" ht="13">
       <c r="A54" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B54" s="4" t="str">
         <f t="shared" si="0"/>
         <v>tundauwaphcu+</v>
       </c>
       <c r="C54" s="21" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="D54" s="21" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="F54" s="4"/>
       <c r="G54" s="4"/>
@@ -17720,20 +17737,20 @@
     </row>
     <row r="55" spans="1:26" ht="13">
       <c r="A55" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B55" s="4" t="str">
         <f t="shared" si="0"/>
         <v>vitongojiphcc</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
@@ -17759,20 +17776,20 @@
     </row>
     <row r="56" spans="1:26" ht="13">
       <c r="A56" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B56" s="4" t="str">
         <f t="shared" si="0"/>
         <v>weshaphcu+</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
@@ -17798,20 +17815,20 @@
     </row>
     <row r="57" spans="1:26" ht="13">
       <c r="A57" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B57" s="4" t="str">
         <f t="shared" si="0"/>
         <v>kondephcu+</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
@@ -17837,20 +17854,20 @@
     </row>
     <row r="58" spans="1:26" ht="13">
       <c r="A58" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B58" s="4" t="str">
         <f t="shared" si="0"/>
         <v>makangalephcu+</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="F58" s="4"/>
       <c r="G58" s="4"/>
@@ -17876,20 +17893,20 @@
     </row>
     <row r="59" spans="1:26" ht="13">
       <c r="A59" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B59" s="4" t="str">
         <f t="shared" si="0"/>
         <v>maziwangombephcu+</v>
       </c>
       <c r="C59" s="21" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="D59" s="21" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="F59" s="4"/>
       <c r="G59" s="4"/>
@@ -17915,20 +17932,20 @@
     </row>
     <row r="60" spans="1:26" ht="13">
       <c r="A60" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B60" s="4" t="str">
         <f t="shared" si="0"/>
         <v>micheweniphcc</v>
       </c>
       <c r="C60" s="21" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="D60" s="21" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="F60" s="4"/>
       <c r="G60" s="4"/>
@@ -17954,20 +17971,20 @@
     </row>
     <row r="61" spans="1:26" ht="13">
       <c r="A61" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B61" s="4" t="str">
         <f t="shared" si="0"/>
         <v>wingwiphcu+</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="F61" s="4"/>
       <c r="G61" s="4"/>
@@ -17993,20 +18010,20 @@
     </row>
     <row r="62" spans="1:26" ht="13">
       <c r="A62" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B62" s="4" t="str">
         <f t="shared" si="0"/>
         <v>kiuyumbuyuniphcu+</v>
       </c>
       <c r="C62" s="21" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="D62" s="21" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="F62" s="4"/>
       <c r="G62" s="4"/>
@@ -18032,20 +18049,20 @@
     </row>
     <row r="63" spans="1:26" ht="13">
       <c r="A63" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B63" s="4" t="str">
         <f t="shared" si="0"/>
         <v>bogoaphcu+</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="F63" s="4"/>
       <c r="G63" s="4"/>
@@ -18071,20 +18088,20 @@
     </row>
     <row r="64" spans="1:26" ht="13">
       <c r="A64" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B64" s="4" t="str">
         <f t="shared" si="0"/>
         <v>kengejaphcu+</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="F64" s="4"/>
       <c r="G64" s="4"/>
@@ -18110,20 +18127,20 @@
     </row>
     <row r="65" spans="1:26" ht="13">
       <c r="A65" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B65" s="4" t="str">
         <f t="shared" si="0"/>
         <v>abdallahmzeedistricthospital</v>
       </c>
       <c r="C65" s="21" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="D65" s="14" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="F65" s="4"/>
       <c r="G65" s="4"/>
@@ -18149,20 +18166,20 @@
     </row>
     <row r="66" spans="1:26" ht="13">
       <c r="A66" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B66" s="4" t="str">
         <f t="shared" si="0"/>
         <v>michenzaniphcu+</v>
       </c>
       <c r="C66" s="21" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="D66" s="21" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="F66" s="4"/>
       <c r="G66" s="4"/>
@@ -18188,20 +18205,20 @@
     </row>
     <row r="67" spans="1:26" ht="13">
       <c r="A67" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B67" s="4" t="str">
         <f t="shared" si="0"/>
         <v>fundophcu+</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="F67" s="4"/>
       <c r="G67" s="4"/>
@@ -18227,20 +18244,20 @@
     </row>
     <row r="68" spans="1:26" ht="13">
       <c r="A68" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B68" s="4" t="str">
         <f t="shared" si="0"/>
         <v>kojaniphcu+</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="F68" s="4"/>
       <c r="G68" s="4"/>
@@ -18266,20 +18283,20 @@
     </row>
     <row r="69" spans="1:26" ht="13">
       <c r="A69" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B69" s="4" t="str">
         <f t="shared" si="0"/>
         <v>makongeniphcu+</v>
       </c>
       <c r="C69" s="21" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="D69" s="21" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="F69" s="4"/>
       <c r="G69" s="4"/>
@@ -18305,20 +18322,20 @@
     </row>
     <row r="70" spans="1:26" ht="13">
       <c r="A70" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B70" s="4" t="str">
         <f t="shared" si="0"/>
         <v>wetedistricthospital</v>
       </c>
       <c r="C70" s="21" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="F70" s="4"/>
       <c r="G70" s="4"/>
@@ -18344,20 +18361,20 @@
     </row>
     <row r="71" spans="1:26" ht="13">
       <c r="A71" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B71" s="4" t="str">
         <f t="shared" si="0"/>
         <v>mzambarauniphcu+</v>
       </c>
       <c r="C71" s="21" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="D71" s="21" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="F71" s="4"/>
       <c r="G71" s="4"/>
@@ -18383,20 +18400,20 @@
     </row>
     <row r="72" spans="1:26" ht="13">
       <c r="A72" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B72" s="4" t="str">
         <f t="shared" si="0"/>
         <v>junguniphcu+</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="F72" s="4"/>
       <c r="G72" s="4"/>
@@ -18422,20 +18439,20 @@
     </row>
     <row r="73" spans="1:26" ht="13">
       <c r="A73" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B73" s="4" t="str">
         <f t="shared" si="0"/>
         <v>ukunjwiphcu+</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="F73" s="4"/>
       <c r="G73" s="4"/>
@@ -18461,20 +18478,20 @@
     </row>
     <row r="74" spans="1:26" ht="13">
       <c r="A74" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B74" s="4" t="str">
         <f t="shared" si="0"/>
         <v>uondwephcu+</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="F74" s="4"/>
       <c r="G74" s="4"/>
@@ -18500,20 +18517,20 @@
     </row>
     <row r="75" spans="1:26" ht="13">
       <c r="A75" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B75" s="4" t="str">
         <f t="shared" si="0"/>
         <v>chwakaphcu+</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="F75" s="4"/>
       <c r="G75" s="4"/>
@@ -18539,20 +18556,20 @@
     </row>
     <row r="76" spans="1:26" ht="13">
       <c r="A76" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B76" s="4" t="str">
         <f t="shared" si="0"/>
         <v>mweraphcu+</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="F76" s="4"/>
       <c r="G76" s="4"/>
@@ -18578,20 +18595,20 @@
     </row>
     <row r="77" spans="1:26" ht="13">
       <c r="A77" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B77" s="4" t="str">
         <f t="shared" si="0"/>
         <v>ungujaukuuphcu+</v>
       </c>
       <c r="C77" s="21" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="D77" s="21" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="F77" s="4"/>
       <c r="G77" s="4"/>
@@ -18617,20 +18634,20 @@
     </row>
     <row r="78" spans="1:26" ht="13">
       <c r="A78" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B78" s="4" t="str">
         <f t="shared" si="0"/>
         <v>uziniphcu+</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="F78" s="4"/>
       <c r="G78" s="4"/>
@@ -18656,20 +18673,20 @@
     </row>
     <row r="79" spans="1:26" ht="13">
       <c r="A79" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B79" s="4" t="str">
         <f t="shared" si="0"/>
         <v>uroaphcu+</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="F79" s="4"/>
       <c r="G79" s="4"/>
@@ -18695,20 +18712,20 @@
     </row>
     <row r="80" spans="1:26" ht="13">
       <c r="A80" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B80" s="4" t="str">
         <f t="shared" si="0"/>
         <v>kivungedistricthospital</v>
       </c>
       <c r="C80" s="21" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="F80" s="4"/>
       <c r="G80" s="4"/>
@@ -18734,20 +18751,20 @@
     </row>
     <row r="81" spans="1:26" ht="13">
       <c r="A81" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B81" s="4" t="str">
         <f t="shared" si="0"/>
         <v>matemwephcu+</v>
       </c>
       <c r="C81" s="21" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="D81" s="21" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="F81" s="4"/>
       <c r="G81" s="4"/>
@@ -18773,20 +18790,20 @@
     </row>
     <row r="82" spans="1:26" ht="13">
       <c r="A82" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B82" s="4" t="str">
         <f t="shared" si="0"/>
         <v>nungwiphcu+</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="F82" s="4"/>
       <c r="G82" s="4"/>
@@ -18812,20 +18829,20 @@
     </row>
     <row r="83" spans="1:26" ht="13">
       <c r="A83" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B83" s="4" t="str">
         <f t="shared" si="0"/>
         <v>pwanimchanganiphcu+</v>
       </c>
       <c r="C83" s="21" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="D83" s="21" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="F83" s="4"/>
       <c r="G83" s="4"/>
@@ -18851,20 +18868,20 @@
     </row>
     <row r="84" spans="1:26" ht="13">
       <c r="A84" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B84" s="4" t="str">
         <f t="shared" si="0"/>
         <v>tumbatugomaniphcu+</v>
       </c>
       <c r="C84" s="21" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="D84" s="21" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="F84" s="4"/>
       <c r="G84" s="4"/>
@@ -18890,20 +18907,20 @@
     </row>
     <row r="85" spans="1:26" ht="13">
       <c r="A85" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B85" s="4" t="str">
         <f t="shared" si="0"/>
         <v>kendwaphcu+</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="F85" s="4"/>
       <c r="G85" s="4"/>
@@ -18929,20 +18946,20 @@
     </row>
     <row r="86" spans="1:26" ht="13">
       <c r="A86" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B86" s="4" t="str">
         <f t="shared" si="0"/>
         <v>bumbwinimisufiniphcu+</v>
       </c>
       <c r="C86" s="21" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="D86" s="21" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="F86" s="4"/>
       <c r="G86" s="4"/>
@@ -18968,20 +18985,20 @@
     </row>
     <row r="87" spans="1:26" ht="13">
       <c r="A87" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B87" s="4" t="str">
         <f t="shared" si="0"/>
         <v>dongevijibweniphcu+</v>
       </c>
       <c r="C87" s="21" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="D87" s="21" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="F87" s="4"/>
       <c r="G87" s="4"/>
@@ -19007,20 +19024,20 @@
     </row>
     <row r="88" spans="1:26" ht="13">
       <c r="A88" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B88" s="4" t="str">
         <f t="shared" si="0"/>
         <v>kiongwephcu</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="F88" s="4"/>
       <c r="G88" s="4"/>
@@ -19046,20 +19063,20 @@
     </row>
     <row r="89" spans="1:26" ht="13">
       <c r="A89" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B89" s="4" t="str">
         <f t="shared" si="0"/>
         <v>kitopephcu</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="F89" s="4"/>
       <c r="G89" s="4"/>
@@ -19085,20 +19102,20 @@
     </row>
     <row r="90" spans="1:26" ht="13">
       <c r="A90" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B90" s="4" t="str">
         <f t="shared" si="0"/>
         <v>mahondaphcu+</v>
       </c>
       <c r="C90" s="21" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="D90" s="21" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="F90" s="4"/>
       <c r="G90" s="4"/>
@@ -19124,20 +19141,20 @@
     </row>
     <row r="91" spans="1:26" ht="13">
       <c r="A91" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B91" s="4" t="str">
         <f t="shared" si="0"/>
         <v>jambianiphcu+</v>
       </c>
       <c r="C91" s="21" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="D91" s="21" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="F91" s="4"/>
       <c r="G91" s="4"/>
@@ -19163,20 +19180,20 @@
     </row>
     <row r="92" spans="1:26" ht="13">
       <c r="A92" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B92" s="4" t="str">
         <f t="shared" si="0"/>
         <v>makunduchidistricthospital</v>
       </c>
       <c r="C92" s="21" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="F92" s="4"/>
       <c r="G92" s="4"/>
@@ -19202,20 +19219,20 @@
     </row>
     <row r="93" spans="1:26" ht="13">
       <c r="A93" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B93" s="4" t="str">
         <f t="shared" si="0"/>
         <v>muyuniphcu+</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="F93" s="4"/>
       <c r="G93" s="4"/>
@@ -19241,20 +19258,20 @@
     </row>
     <row r="94" spans="1:26" ht="13">
       <c r="A94" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B94" s="4" t="str">
         <f t="shared" si="0"/>
         <v>bwejuuphcu+</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="F94" s="4"/>
       <c r="G94" s="4"/>
@@ -19280,20 +19297,20 @@
     </row>
     <row r="95" spans="1:26" ht="13">
       <c r="A95" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B95" s="4" t="str">
         <f t="shared" si="0"/>
         <v>chumbuniphcu+</v>
       </c>
       <c r="C95" s="21" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="D95" s="21" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="F95" s="4"/>
       <c r="G95" s="4"/>
@@ -19319,20 +19336,20 @@
     </row>
     <row r="96" spans="1:26" ht="13">
       <c r="A96" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B96" s="4" t="str">
         <f t="shared" si="0"/>
         <v>mnazimmojahospital</v>
       </c>
       <c r="C96" s="21" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="D96" s="10" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="F96" s="4"/>
       <c r="G96" s="4"/>
@@ -19358,20 +19375,20 @@
     </row>
     <row r="97" spans="1:26" ht="13">
       <c r="A97" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B97" s="4" t="str">
         <f t="shared" si="0"/>
         <v>mwembeladumchclinic</v>
       </c>
       <c r="C97" s="21" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="F97" s="4"/>
       <c r="G97" s="4"/>
@@ -19397,20 +19414,20 @@
     </row>
     <row r="98" spans="1:26" ht="13">
       <c r="A98" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B98" s="4" t="str">
         <f t="shared" si="0"/>
         <v>sebleniphcu+</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="F98" s="4"/>
       <c r="G98" s="4"/>
@@ -19436,20 +19453,20 @@
     </row>
     <row r="99" spans="1:26" ht="13">
       <c r="A99" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B99" s="4" t="str">
         <f t="shared" si="0"/>
         <v>chukwaniphcu+</v>
       </c>
       <c r="C99" s="21" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="D99" s="21" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="F99" s="4"/>
       <c r="G99" s="4"/>
@@ -19475,20 +19492,20 @@
     </row>
     <row r="100" spans="1:26" ht="13">
       <c r="A100" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B100" s="4" t="str">
         <f t="shared" si="0"/>
         <v>fuoniphcu+</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="F100" s="4"/>
       <c r="G100" s="4"/>
@@ -19514,20 +19531,20 @@
     </row>
     <row r="101" spans="1:26" ht="13">
       <c r="A101" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B101" s="4" t="str">
         <f t="shared" si="0"/>
         <v>kombeniphcu+</v>
       </c>
       <c r="C101" s="21" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="D101" s="21" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="F101" s="4"/>
       <c r="G101" s="4"/>
@@ -19553,20 +19570,20 @@
     </row>
     <row r="102" spans="1:26" ht="13">
       <c r="A102" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B102" s="4" t="str">
         <f t="shared" si="0"/>
         <v>mtofaaniphcu+(kinuni)</v>
       </c>
       <c r="C102" s="21" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="D102" s="21" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="F102" s="4"/>
       <c r="G102" s="4"/>
@@ -19592,20 +19609,20 @@
     </row>
     <row r="103" spans="1:26" ht="13">
       <c r="A103" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B103" s="4" t="str">
         <f t="shared" si="0"/>
         <v>bumbwisudiphcu+</v>
       </c>
       <c r="C103" s="21" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="D103" s="21" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="F103" s="4"/>
       <c r="G103" s="4"/>
@@ -19631,20 +19648,20 @@
     </row>
     <row r="104" spans="1:26" ht="13">
       <c r="A104" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B104" s="4" t="str">
         <f t="shared" si="0"/>
         <v>selemphcu+</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="F104" s="4"/>
       <c r="G104" s="4"/>
@@ -19670,20 +19687,20 @@
     </row>
     <row r="105" spans="1:26" ht="13">
       <c r="A105" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B105" s="4" t="str">
         <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="F105" s="4"/>
       <c r="G105" s="4"/>
@@ -19709,20 +19726,20 @@
     </row>
     <row r="106" spans="1:26" ht="13">
       <c r="A106" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B106" s="4" t="str">
         <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="F106" s="4"/>
       <c r="G106" s="4"/>
@@ -19748,20 +19765,20 @@
     </row>
     <row r="107" spans="1:26" ht="13">
       <c r="A107" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B107" s="4" t="str">
         <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="F107" s="4"/>
       <c r="G107" s="4"/>
@@ -19787,20 +19804,20 @@
     </row>
     <row r="108" spans="1:26" ht="13">
       <c r="A108" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B108" s="4" t="str">
         <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="F108" s="4"/>
       <c r="G108" s="4"/>
@@ -19826,20 +19843,20 @@
     </row>
     <row r="109" spans="1:26" ht="13">
       <c r="A109" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B109" s="4" t="str">
         <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="F109" s="4"/>
       <c r="G109" s="4"/>
@@ -19865,20 +19882,20 @@
     </row>
     <row r="110" spans="1:26" ht="13">
       <c r="A110" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B110" s="4" t="str">
         <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C110" s="4" t="s">
+        <v>966</v>
+      </c>
+      <c r="D110" s="10" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E110" s="4" t="s">
         <v>968</v>
-      </c>
-      <c r="D110" s="10" t="s">
-        <v>1052</v>
-      </c>
-      <c r="E110" s="4" t="s">
-        <v>970</v>
       </c>
       <c r="F110" s="4"/>
       <c r="G110" s="4"/>
@@ -19904,20 +19921,20 @@
     </row>
     <row r="111" spans="1:26" ht="13">
       <c r="A111" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B111" s="4" t="str">
         <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="F111" s="4"/>
       <c r="G111" s="4"/>
@@ -19943,20 +19960,20 @@
     </row>
     <row r="112" spans="1:26" ht="13">
       <c r="A112" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B112" s="4" t="str">
         <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="F112" s="4"/>
       <c r="G112" s="4"/>
@@ -19982,20 +19999,20 @@
     </row>
     <row r="113" spans="1:26" ht="13">
       <c r="A113" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B113" s="4" t="str">
         <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="D113" s="10" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="F113" s="4"/>
       <c r="G113" s="4"/>
@@ -20021,20 +20038,20 @@
     </row>
     <row r="114" spans="1:26" ht="13">
       <c r="A114" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B114" s="4" t="str">
         <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="D114" s="10" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="F114" s="4"/>
       <c r="G114" s="4"/>
@@ -20060,20 +20077,20 @@
     </row>
     <row r="115" spans="1:26" ht="13">
       <c r="A115" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B115" s="4" t="str">
         <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="D115" s="10" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="F115" s="4"/>
       <c r="G115" s="4"/>
@@ -20099,674 +20116,674 @@
     </row>
     <row r="116" spans="1:26" ht="13">
       <c r="A116" s="16" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B116" s="16" t="s">
         <v>139</v>
       </c>
       <c r="C116" s="16" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D116" s="38" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="117" spans="1:26" ht="13">
       <c r="A117" s="16" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B117" s="16" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C117" s="60" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D117" s="81" t="s">
         <v>1055</v>
-      </c>
-      <c r="C117" s="60" t="s">
-        <v>1056</v>
-      </c>
-      <c r="D117" s="81" t="s">
-        <v>1057</v>
       </c>
     </row>
     <row r="118" spans="1:26" ht="13">
       <c r="A118" s="16" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B118" s="16" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="D118" s="38" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="119" spans="1:26" ht="13">
       <c r="A119" s="16" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B119" s="16" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C119" s="16" t="s">
         <v>1060</v>
       </c>
-      <c r="B119" s="16" t="s">
+      <c r="D119" s="78" t="s">
         <v>1061</v>
-      </c>
-      <c r="C119" s="16" t="s">
-        <v>1062</v>
-      </c>
-      <c r="D119" s="78" t="s">
-        <v>1063</v>
       </c>
     </row>
     <row r="120" spans="1:26" ht="13">
       <c r="A120" s="16" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="B120" s="16" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C120" s="16" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D120" s="38" t="s">
         <v>1064</v>
-      </c>
-      <c r="C120" s="16" t="s">
-        <v>1065</v>
-      </c>
-      <c r="D120" s="38" t="s">
-        <v>1066</v>
       </c>
     </row>
     <row r="121" spans="1:26" ht="13">
       <c r="A121" s="16" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="B121" s="16" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C121" s="60" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D121" s="38" t="s">
         <v>1067</v>
-      </c>
-      <c r="C121" s="60" t="s">
-        <v>1068</v>
-      </c>
-      <c r="D121" s="38" t="s">
-        <v>1069</v>
       </c>
     </row>
     <row r="122" spans="1:26" ht="13">
       <c r="A122" s="16" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="B122" s="16" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C122" s="60" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D122" s="81" t="s">
         <v>1070</v>
-      </c>
-      <c r="C122" s="60" t="s">
-        <v>1071</v>
-      </c>
-      <c r="D122" s="81" t="s">
-        <v>1072</v>
       </c>
     </row>
     <row r="123" spans="1:26" ht="13">
       <c r="A123" s="16" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="B123" s="16" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C123" s="16" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D123" s="78" t="s">
         <v>1073</v>
-      </c>
-      <c r="C123" s="16" t="s">
-        <v>1074</v>
-      </c>
-      <c r="D123" s="78" t="s">
-        <v>1075</v>
       </c>
     </row>
     <row r="124" spans="1:26" ht="13">
       <c r="A124" s="16" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="B124" s="16" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C124" s="16" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="D124" s="78" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="125" spans="1:26" ht="13">
       <c r="A125" s="5" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B125" s="5" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D125" s="78" t="s">
         <v>1077</v>
-      </c>
-      <c r="C125" s="5" t="s">
-        <v>1078</v>
-      </c>
-      <c r="D125" s="78" t="s">
-        <v>1079</v>
       </c>
     </row>
     <row r="126" spans="1:26" ht="13">
       <c r="A126" s="5" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B126" s="5" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D126" s="78" t="s">
         <v>1080</v>
-      </c>
-      <c r="C126" s="5" t="s">
-        <v>1081</v>
-      </c>
-      <c r="D126" s="78" t="s">
-        <v>1082</v>
       </c>
     </row>
     <row r="127" spans="1:26" ht="13">
       <c r="A127" s="5" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B127" s="5" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D127" s="78" t="s">
         <v>1083</v>
-      </c>
-      <c r="C127" s="5" t="s">
-        <v>1084</v>
-      </c>
-      <c r="D127" s="78" t="s">
-        <v>1085</v>
       </c>
     </row>
     <row r="128" spans="1:26" ht="13">
       <c r="A128" s="5" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B128" s="5" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D128" s="78" t="s">
         <v>1086</v>
-      </c>
-      <c r="C128" s="5" t="s">
-        <v>1087</v>
-      </c>
-      <c r="D128" s="78" t="s">
-        <v>1088</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="13">
       <c r="A129" s="5" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B129" s="5" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D129" s="78" t="s">
         <v>1089</v>
-      </c>
-      <c r="C129" s="5" t="s">
-        <v>1090</v>
-      </c>
-      <c r="D129" s="78" t="s">
-        <v>1091</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="13">
       <c r="A130" s="5" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="D130" s="78" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="13">
       <c r="A131" s="5" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="D131" s="78" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="13">
       <c r="A132" s="16" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B132" s="16" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C132" s="16" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D132" s="78" t="s">
         <v>1094</v>
-      </c>
-      <c r="C132" s="16" t="s">
-        <v>1095</v>
-      </c>
-      <c r="D132" s="78" t="s">
-        <v>1096</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="13">
       <c r="A133" s="16" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B133" s="16" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C133" s="16" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D133" s="78" t="s">
         <v>1097</v>
-      </c>
-      <c r="C133" s="16" t="s">
-        <v>1098</v>
-      </c>
-      <c r="D133" s="78" t="s">
-        <v>1099</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="13">
       <c r="A134" s="16" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B134" s="16" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C134" s="16" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D134" s="78" t="s">
         <v>1100</v>
-      </c>
-      <c r="C134" s="16" t="s">
-        <v>1101</v>
-      </c>
-      <c r="D134" s="78" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="13">
       <c r="A135" s="16" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B135" s="16" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C135" s="16" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="D135" s="78" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="13">
       <c r="A136" s="16" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B136" s="16" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C136" s="16" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D136" s="78" t="s">
         <v>1105</v>
-      </c>
-      <c r="C136" s="16" t="s">
-        <v>1106</v>
-      </c>
-      <c r="D136" s="78" t="s">
-        <v>1107</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="13">
       <c r="A137" s="16" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B137" s="16" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C137" s="16" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D137" s="78" t="s">
         <v>1089</v>
-      </c>
-      <c r="C137" s="16" t="s">
-        <v>1108</v>
-      </c>
-      <c r="D137" s="78" t="s">
-        <v>1091</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="13">
       <c r="A138" s="16" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B138" s="16" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="C138" s="16" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="D138" s="78" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="13">
       <c r="A139" s="16" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B139" s="16" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C139" s="16" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D139" s="78" t="s">
         <v>1111</v>
-      </c>
-      <c r="C139" s="16" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D139" s="78" t="s">
-        <v>1113</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="13">
       <c r="A140" s="16" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B140" s="16" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C140" s="16" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D140" s="78" t="s">
         <v>1114</v>
-      </c>
-      <c r="C140" s="16" t="s">
-        <v>1115</v>
-      </c>
-      <c r="D140" s="78" t="s">
-        <v>1116</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="13">
       <c r="A141" s="16" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B141" s="16" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C141" s="16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D141" s="78" t="s">
         <v>1117</v>
-      </c>
-      <c r="C141" s="16" t="s">
-        <v>1118</v>
-      </c>
-      <c r="D141" s="78" t="s">
-        <v>1119</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="13">
       <c r="A142" s="16" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B142" s="16" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C142" s="16" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D142" s="78" t="s">
         <v>1120</v>
-      </c>
-      <c r="C142" s="16" t="s">
-        <v>1121</v>
-      </c>
-      <c r="D142" s="78" t="s">
-        <v>1122</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="13">
       <c r="A143" s="16" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B143" s="16" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C143" s="16" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D143" s="78" t="s">
         <v>1083</v>
-      </c>
-      <c r="C143" s="16" t="s">
-        <v>1123</v>
-      </c>
-      <c r="D143" s="78" t="s">
-        <v>1085</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="13">
       <c r="A144" s="16" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B144" s="16" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C144" s="16" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D144" s="78" t="s">
         <v>1124</v>
-      </c>
-      <c r="C144" s="16" t="s">
-        <v>1125</v>
-      </c>
-      <c r="D144" s="78" t="s">
-        <v>1126</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="13">
       <c r="A145" s="16" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B145" s="16" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C145" s="16" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="D145" s="78" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="13">
       <c r="A146" s="16" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B146" s="16" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C146" s="16" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D146" s="78" t="s">
         <v>1129</v>
-      </c>
-      <c r="C146" s="16" t="s">
-        <v>1130</v>
-      </c>
-      <c r="D146" s="78" t="s">
-        <v>1131</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="13">
       <c r="A147" s="16" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B147" s="16" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C147" s="16" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="D147" s="78" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="13">
       <c r="A148" s="16" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B148" s="16" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="D148" s="38" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="13">
       <c r="A149" s="16" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B149" s="16" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C149" s="16" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D149" s="78" t="s">
         <v>1135</v>
-      </c>
-      <c r="C149" s="16" t="s">
-        <v>1136</v>
-      </c>
-      <c r="D149" s="78" t="s">
-        <v>1137</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="13">
       <c r="A150" s="16" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B150" s="16" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C150" s="16" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D150" s="78" t="s">
         <v>1138</v>
-      </c>
-      <c r="C150" s="16" t="s">
-        <v>1139</v>
-      </c>
-      <c r="D150" s="78" t="s">
-        <v>1140</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="13">
       <c r="A151" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B151" s="2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D151" s="40" t="s">
         <v>1141</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>1142</v>
-      </c>
-      <c r="D151" s="40" t="s">
-        <v>1143</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="13">
       <c r="A152" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B152" s="2" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D152" s="40" t="s">
         <v>1144</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>1145</v>
-      </c>
-      <c r="D152" s="40" t="s">
-        <v>1146</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="13">
       <c r="A153" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B153" s="2" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D153" s="40" t="s">
         <v>1147</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>1148</v>
-      </c>
-      <c r="D153" s="40" t="s">
-        <v>1149</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="13">
       <c r="A154" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B154" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D154" s="40" t="s">
         <v>1150</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>1151</v>
-      </c>
-      <c r="D154" s="40" t="s">
-        <v>1152</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="13">
       <c r="A155" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B155" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D155" s="40" t="s">
         <v>1153</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>1154</v>
-      </c>
-      <c r="D155" s="40" t="s">
-        <v>1155</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="13">
       <c r="A156" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B156" s="2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D156" s="40" t="s">
         <v>1156</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>1157</v>
-      </c>
-      <c r="D156" s="40" t="s">
-        <v>1158</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="13">
       <c r="A157" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B157" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="D157" s="40" t="s">
         <v>1159</v>
-      </c>
-      <c r="C157" s="2" t="s">
-        <v>1160</v>
-      </c>
-      <c r="D157" s="40" t="s">
-        <v>1161</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="13">
       <c r="A158" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B158" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D158" s="40" t="s">
         <v>1162</v>
-      </c>
-      <c r="C158" s="2" t="s">
-        <v>1163</v>
-      </c>
-      <c r="D158" s="40" t="s">
-        <v>1164</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="13">
       <c r="A159" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B159" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D159" s="40" t="s">
         <v>1165</v>
-      </c>
-      <c r="C159" s="2" t="s">
-        <v>1166</v>
-      </c>
-      <c r="D159" s="40" t="s">
-        <v>1167</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="13">
       <c r="A160" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B160" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D160" s="40" t="s">
         <v>1168</v>
-      </c>
-      <c r="C160" s="2" t="s">
-        <v>1169</v>
-      </c>
-      <c r="D160" s="40" t="s">
-        <v>1170</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="13">
       <c r="A161" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B161" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="D161" s="40" t="s">
         <v>1171</v>
-      </c>
-      <c r="C161" s="2" t="s">
-        <v>1172</v>
-      </c>
-      <c r="D161" s="40" t="s">
-        <v>1173</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="13">
       <c r="A162" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="D162" s="40" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="163" spans="1:5" ht="13">
       <c r="A163" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="C163" s="13" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="D163" s="40" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="13">
@@ -20774,13 +20791,13 @@
         <v>171</v>
       </c>
       <c r="B164" s="2" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C164" s="65" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D164" s="40" t="s">
         <v>1177</v>
-      </c>
-      <c r="C164" s="65" t="s">
-        <v>1178</v>
-      </c>
-      <c r="D164" s="40" t="s">
-        <v>1179</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="13">
@@ -20788,13 +20805,13 @@
         <v>171</v>
       </c>
       <c r="B165" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C165" s="65" t="s">
+        <v>1179</v>
+      </c>
+      <c r="D165" s="72" t="s">
         <v>1180</v>
-      </c>
-      <c r="C165" s="65" t="s">
-        <v>1181</v>
-      </c>
-      <c r="D165" s="72" t="s">
-        <v>1182</v>
       </c>
       <c r="E165" s="67"/>
     </row>
@@ -20803,13 +20820,13 @@
         <v>171</v>
       </c>
       <c r="B166" s="2" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C166" s="65" t="s">
+        <v>1182</v>
+      </c>
+      <c r="D166" s="66" t="s">
         <v>1183</v>
-      </c>
-      <c r="C166" s="65" t="s">
-        <v>1184</v>
-      </c>
-      <c r="D166" s="66" t="s">
-        <v>1185</v>
       </c>
       <c r="E166" s="67"/>
     </row>
@@ -20818,13 +20835,13 @@
         <v>171</v>
       </c>
       <c r="B167" s="2" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C167" s="65" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D167" s="66" t="s">
         <v>1186</v>
-      </c>
-      <c r="C167" s="65" t="s">
-        <v>1187</v>
-      </c>
-      <c r="D167" s="66" t="s">
-        <v>1188</v>
       </c>
       <c r="E167" s="67"/>
     </row>
@@ -20833,13 +20850,13 @@
         <v>171</v>
       </c>
       <c r="B168" s="2" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C168" s="65" t="s">
+        <v>1188</v>
+      </c>
+      <c r="D168" s="66" t="s">
         <v>1189</v>
-      </c>
-      <c r="C168" s="65" t="s">
-        <v>1190</v>
-      </c>
-      <c r="D168" s="66" t="s">
-        <v>1191</v>
       </c>
       <c r="E168" s="67"/>
     </row>
@@ -20848,13 +20865,13 @@
         <v>171</v>
       </c>
       <c r="B169" s="2" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C169" s="65" t="s">
+        <v>1191</v>
+      </c>
+      <c r="D169" s="66" t="s">
         <v>1192</v>
-      </c>
-      <c r="C169" s="65" t="s">
-        <v>1193</v>
-      </c>
-      <c r="D169" s="66" t="s">
-        <v>1194</v>
       </c>
       <c r="E169" s="67"/>
     </row>
@@ -20863,13 +20880,13 @@
         <v>171</v>
       </c>
       <c r="B170" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C170" s="65" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D170" s="66" t="s">
         <v>1195</v>
-      </c>
-      <c r="C170" s="65" t="s">
-        <v>1196</v>
-      </c>
-      <c r="D170" s="66" t="s">
-        <v>1197</v>
       </c>
       <c r="E170" s="67"/>
     </row>
@@ -20878,308 +20895,308 @@
         <v>171</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="C171" s="82" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="D171" s="66" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="E171" s="67"/>
     </row>
     <row r="172" spans="1:5" ht="13">
       <c r="A172" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B172" s="2" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C172" s="71" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D172" s="40" t="s">
         <v>1199</v>
-      </c>
-      <c r="C172" s="71" t="s">
-        <v>1200</v>
-      </c>
-      <c r="D172" s="40" t="s">
-        <v>1201</v>
       </c>
     </row>
     <row r="173" spans="1:5" ht="13">
       <c r="A173" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B173" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="C173" s="71" t="s">
+        <v>1200</v>
+      </c>
+      <c r="D173" s="40" t="s">
         <v>909</v>
-      </c>
-      <c r="C173" s="71" t="s">
-        <v>1202</v>
-      </c>
-      <c r="D173" s="40" t="s">
-        <v>911</v>
       </c>
     </row>
     <row r="174" spans="1:5" ht="13">
       <c r="A174" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B174" s="2" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C174" s="71" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D174" s="40" t="s">
         <v>1203</v>
-      </c>
-      <c r="C174" s="71" t="s">
-        <v>1204</v>
-      </c>
-      <c r="D174" s="40" t="s">
-        <v>1205</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="13">
       <c r="A175" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="D175" s="40" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="176" spans="1:5" ht="13">
       <c r="A176" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="C176" s="82" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="D176" s="40" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="13">
       <c r="A177" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B177" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C177" s="73" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D177" s="2" t="s">
         <v>1210</v>
-      </c>
-      <c r="C177" s="73" t="s">
-        <v>1211</v>
-      </c>
-      <c r="D177" s="2" t="s">
-        <v>1212</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="13">
       <c r="A178" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B178" s="2" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C178" s="71" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D178" s="40" t="s">
         <v>1213</v>
-      </c>
-      <c r="C178" s="71" t="s">
-        <v>1214</v>
-      </c>
-      <c r="D178" s="40" t="s">
-        <v>1215</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="13">
       <c r="A179" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B179" s="2" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C179" s="71" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D179" s="40" t="s">
         <v>1216</v>
-      </c>
-      <c r="C179" s="71" t="s">
-        <v>1217</v>
-      </c>
-      <c r="D179" s="40" t="s">
-        <v>1218</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="13">
       <c r="A180" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B180" s="2" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C180" s="71" t="s">
+        <v>1218</v>
+      </c>
+      <c r="D180" s="40" t="s">
         <v>1219</v>
-      </c>
-      <c r="C180" s="71" t="s">
-        <v>1220</v>
-      </c>
-      <c r="D180" s="40" t="s">
-        <v>1221</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="13">
       <c r="A181" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="C181" s="82" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="D181" s="40" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="13">
       <c r="A182" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="C182" s="65" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="D182" s="40" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="13">
       <c r="A183" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="C183" s="65" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="D183" s="40" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="13">
       <c r="A184" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="C184" s="65" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="D184" s="40" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="13">
       <c r="A185" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="C185" s="65" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="D185" s="40" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="13">
       <c r="A186" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="C186" s="65" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="D186" s="40" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="187" spans="1:4" ht="13">
       <c r="A187" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="C187" s="65" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="D187" s="40" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="188" spans="1:4" ht="13">
       <c r="A188" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="C188" s="65" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="D188" s="40" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="189" spans="1:4" ht="13">
       <c r="A189" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="C189" s="82" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="D189" s="40" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="13">
       <c r="A190" s="2" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="B190" s="2" t="s">
         <v>139</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="D190" s="40" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="191" spans="1:4" ht="13">
       <c r="A191" s="2" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="B191" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="D191" s="40" t="s">
         <v>858</v>
-      </c>
-      <c r="C191" s="2" t="s">
-        <v>859</v>
-      </c>
-      <c r="D191" s="40" t="s">
-        <v>860</v>
       </c>
     </row>
     <row r="192" spans="1:4" ht="13">
       <c r="A192" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B192" s="2" t="s">
         <v>1233</v>
       </c>
-      <c r="B192" s="2" t="s">
-        <v>1235</v>
-      </c>
       <c r="C192" s="13" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="D192" s="40" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="193" spans="1:4" ht="14.25">
@@ -21187,13 +21204,13 @@
         <v>182</v>
       </c>
       <c r="B193" s="2" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="D193" s="83" t="s">
         <v>1236</v>
-      </c>
-      <c r="C193" s="2" t="s">
-        <v>1237</v>
-      </c>
-      <c r="D193" s="83" t="s">
-        <v>1238</v>
       </c>
     </row>
     <row r="194" spans="1:4" ht="14.25">
@@ -21201,13 +21218,13 @@
         <v>182</v>
       </c>
       <c r="B194" s="2" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="D194" s="83" t="s">
         <v>1239</v>
-      </c>
-      <c r="C194" s="2" t="s">
-        <v>1240</v>
-      </c>
-      <c r="D194" s="83" t="s">
-        <v>1241</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="14.25">
@@ -21215,13 +21232,13 @@
         <v>182</v>
       </c>
       <c r="B195" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>1241</v>
+      </c>
+      <c r="D195" s="83" t="s">
         <v>1242</v>
-      </c>
-      <c r="C195" s="2" t="s">
-        <v>1243</v>
-      </c>
-      <c r="D195" s="83" t="s">
-        <v>1244</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="14.25">
@@ -21229,13 +21246,13 @@
         <v>182</v>
       </c>
       <c r="B196" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="D196" s="83" t="s">
         <v>1245</v>
-      </c>
-      <c r="C196" s="2" t="s">
-        <v>1246</v>
-      </c>
-      <c r="D196" s="83" t="s">
-        <v>1247</v>
       </c>
     </row>
     <row r="197" spans="1:4" ht="14.25">
@@ -21243,13 +21260,13 @@
         <v>182</v>
       </c>
       <c r="B197" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D197" s="83" t="s">
         <v>1248</v>
-      </c>
-      <c r="C197" s="2" t="s">
-        <v>1249</v>
-      </c>
-      <c r="D197" s="83" t="s">
-        <v>1250</v>
       </c>
     </row>
     <row r="198" spans="1:4" ht="13">
@@ -21257,13 +21274,13 @@
         <v>182</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="D198" s="40" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="199" spans="1:4" ht="13">
@@ -21271,181 +21288,181 @@
         <v>182</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="C199" s="13" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="D199" s="40" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="200" spans="1:4" ht="14.25">
       <c r="A200" s="2" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C200" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="B200" s="2" t="s">
+      <c r="D200" s="83" t="s">
         <v>1252</v>
-      </c>
-      <c r="C200" s="2" t="s">
-        <v>1253</v>
-      </c>
-      <c r="D200" s="83" t="s">
-        <v>1254</v>
       </c>
     </row>
     <row r="201" spans="1:4" ht="14.25">
       <c r="A201" s="2" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B201" s="2" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D201" s="83" t="s">
         <v>1255</v>
-      </c>
-      <c r="C201" s="2" t="s">
-        <v>1256</v>
-      </c>
-      <c r="D201" s="83" t="s">
-        <v>1257</v>
       </c>
     </row>
     <row r="202" spans="1:4" ht="14.25">
       <c r="A202" s="2" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B202" s="2" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D202" s="83" t="s">
         <v>1258</v>
-      </c>
-      <c r="C202" s="2" t="s">
-        <v>1259</v>
-      </c>
-      <c r="D202" s="83" t="s">
-        <v>1260</v>
       </c>
     </row>
     <row r="203" spans="1:4" ht="14.25">
       <c r="A203" s="2" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B203" s="2" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D203" s="83" t="s">
         <v>1261</v>
-      </c>
-      <c r="C203" s="2" t="s">
-        <v>1262</v>
-      </c>
-      <c r="D203" s="83" t="s">
-        <v>1263</v>
       </c>
     </row>
     <row r="204" spans="1:4" ht="13">
       <c r="A204" s="2" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="D204" s="40" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="13">
       <c r="A205" s="2" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="C205" s="13" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="D205" s="40" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="206" spans="1:4" ht="14.25">
       <c r="A206" s="2" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C206" s="2" t="s">
         <v>1264</v>
       </c>
-      <c r="B206" s="2" t="s">
-        <v>1265</v>
-      </c>
-      <c r="C206" s="2" t="s">
-        <v>1266</v>
-      </c>
       <c r="D206" s="83" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="207" spans="1:4" ht="14.25">
       <c r="A207" s="2" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="B207" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>1266</v>
+      </c>
+      <c r="D207" s="83" t="s">
         <v>1267</v>
-      </c>
-      <c r="C207" s="2" t="s">
-        <v>1268</v>
-      </c>
-      <c r="D207" s="83" t="s">
-        <v>1269</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="14.25">
       <c r="A208" s="2" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="B208" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="D208" s="83" t="s">
         <v>1270</v>
-      </c>
-      <c r="C208" s="2" t="s">
-        <v>1271</v>
-      </c>
-      <c r="D208" s="83" t="s">
-        <v>1272</v>
       </c>
     </row>
     <row r="209" spans="1:4" ht="14.25">
       <c r="A209" s="2" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D209" s="83" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="210" spans="1:4" ht="13">
       <c r="A210" s="2" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="D210" s="40" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="211" spans="1:4" ht="13">
       <c r="A211" s="2" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="C211" s="13" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="D211" s="40" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="212" spans="1:4" ht="13">
@@ -21453,13 +21470,13 @@
         <v>281</v>
       </c>
       <c r="B212" s="2" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C212" s="40" t="s">
+        <v>1274</v>
+      </c>
+      <c r="D212" s="2" t="s">
         <v>1275</v>
-      </c>
-      <c r="C212" s="40" t="s">
-        <v>1276</v>
-      </c>
-      <c r="D212" s="2" t="s">
-        <v>1277</v>
       </c>
     </row>
     <row r="213" spans="1:4" ht="13">
@@ -21467,13 +21484,13 @@
         <v>281</v>
       </c>
       <c r="B213" s="2" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>1277</v>
+      </c>
+      <c r="D213" s="2" t="s">
         <v>1278</v>
-      </c>
-      <c r="C213" s="2" t="s">
-        <v>1279</v>
-      </c>
-      <c r="D213" s="2" t="s">
-        <v>1280</v>
       </c>
     </row>
     <row r="214" spans="1:4" ht="13">
@@ -21481,13 +21498,13 @@
         <v>281</v>
       </c>
       <c r="B214" s="2" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>1280</v>
+      </c>
+      <c r="D214" s="2" t="s">
         <v>1281</v>
-      </c>
-      <c r="C214" s="2" t="s">
-        <v>1282</v>
-      </c>
-      <c r="D214" s="2" t="s">
-        <v>1283</v>
       </c>
     </row>
     <row r="215" spans="1:4" ht="13">
@@ -21495,13 +21512,13 @@
         <v>281</v>
       </c>
       <c r="B215" s="2" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>1283</v>
+      </c>
+      <c r="D215" s="2" t="s">
         <v>1284</v>
-      </c>
-      <c r="C215" s="2" t="s">
-        <v>1285</v>
-      </c>
-      <c r="D215" s="2" t="s">
-        <v>1286</v>
       </c>
     </row>
     <row r="216" spans="1:4" ht="13">
@@ -21509,13 +21526,13 @@
         <v>281</v>
       </c>
       <c r="B216" s="2" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="D216" s="2" t="s">
         <v>1287</v>
-      </c>
-      <c r="C216" s="2" t="s">
-        <v>1288</v>
-      </c>
-      <c r="D216" s="2" t="s">
-        <v>1289</v>
       </c>
     </row>
     <row r="217" spans="1:4" ht="13">
@@ -21523,13 +21540,13 @@
         <v>281</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="C217" s="40" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="218" spans="1:4" ht="13">
@@ -21537,13 +21554,13 @@
         <v>281</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="219" spans="1:4" ht="13">
@@ -21551,223 +21568,223 @@
         <v>281</v>
       </c>
       <c r="B219" s="2" t="s">
+        <v>898</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>899</v>
+      </c>
+      <c r="D219" s="2" t="s">
         <v>900</v>
-      </c>
-      <c r="C219" s="2" t="s">
-        <v>901</v>
-      </c>
-      <c r="D219" s="2" t="s">
-        <v>902</v>
       </c>
     </row>
     <row r="220" spans="1:4" ht="13">
       <c r="A220" s="84" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C220" s="2" t="s">
         <v>1294</v>
       </c>
-      <c r="B220" s="2" t="s">
+      <c r="D220" s="2" t="s">
         <v>1295</v>
-      </c>
-      <c r="C220" s="2" t="s">
-        <v>1296</v>
-      </c>
-      <c r="D220" s="2" t="s">
-        <v>1297</v>
       </c>
     </row>
     <row r="221" spans="1:4" ht="13">
       <c r="A221" s="84" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="B221" s="2" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C221" s="40" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D221" s="2" t="s">
         <v>1298</v>
-      </c>
-      <c r="C221" s="40" t="s">
-        <v>1299</v>
-      </c>
-      <c r="D221" s="2" t="s">
-        <v>1300</v>
       </c>
     </row>
     <row r="222" spans="1:4" ht="13">
       <c r="A222" s="84" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="B222" s="2" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>1300</v>
+      </c>
+      <c r="D222" s="2" t="s">
         <v>1301</v>
-      </c>
-      <c r="C222" s="2" t="s">
-        <v>1302</v>
-      </c>
-      <c r="D222" s="2" t="s">
-        <v>1303</v>
       </c>
     </row>
     <row r="223" spans="1:4" ht="13">
       <c r="A223" s="84" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="B223" s="2" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>1303</v>
+      </c>
+      <c r="D223" s="2" t="s">
         <v>1304</v>
-      </c>
-      <c r="C223" s="2" t="s">
-        <v>1305</v>
-      </c>
-      <c r="D223" s="2" t="s">
-        <v>1306</v>
       </c>
     </row>
     <row r="224" spans="1:4" ht="13">
       <c r="A224" s="57" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="B224" s="2" t="s">
+        <v>898</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>899</v>
+      </c>
+      <c r="D224" s="2" t="s">
         <v>900</v>
-      </c>
-      <c r="C224" s="2" t="s">
-        <v>901</v>
-      </c>
-      <c r="D224" s="2" t="s">
-        <v>902</v>
       </c>
     </row>
     <row r="225" spans="1:4" ht="13">
       <c r="A225" s="57" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B225" s="2" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>1306</v>
+      </c>
+      <c r="D225" s="2" t="s">
         <v>1307</v>
-      </c>
-      <c r="C225" s="2" t="s">
-        <v>1308</v>
-      </c>
-      <c r="D225" s="2" t="s">
-        <v>1309</v>
       </c>
     </row>
     <row r="226" spans="1:4" ht="13">
       <c r="A226" s="57" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B226" s="2" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>1309</v>
+      </c>
+      <c r="D226" s="2" t="s">
         <v>1310</v>
-      </c>
-      <c r="C226" s="2" t="s">
-        <v>1311</v>
-      </c>
-      <c r="D226" s="2" t="s">
-        <v>1312</v>
       </c>
     </row>
     <row r="227" spans="1:4" ht="13">
       <c r="A227" s="57" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B227" s="2" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>1312</v>
+      </c>
+      <c r="D227" s="2" t="s">
         <v>1313</v>
-      </c>
-      <c r="C227" s="2" t="s">
-        <v>1314</v>
-      </c>
-      <c r="D227" s="2" t="s">
-        <v>1315</v>
       </c>
     </row>
     <row r="228" spans="1:4" ht="13">
       <c r="A228" s="7" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B228" s="2" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>1315</v>
+      </c>
+      <c r="D228" s="2" t="s">
         <v>1316</v>
-      </c>
-      <c r="C228" s="2" t="s">
-        <v>1317</v>
-      </c>
-      <c r="D228" s="2" t="s">
-        <v>1318</v>
       </c>
     </row>
     <row r="229" spans="1:4" ht="13">
       <c r="A229" s="7" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B229" s="2" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D229" s="2" t="s">
         <v>1319</v>
-      </c>
-      <c r="C229" s="2" t="s">
-        <v>1320</v>
-      </c>
-      <c r="D229" s="2" t="s">
-        <v>1321</v>
       </c>
     </row>
     <row r="230" spans="1:4" ht="13">
       <c r="A230" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B230" s="2" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D230" s="2" t="s">
         <v>1322</v>
-      </c>
-      <c r="C230" s="2" t="s">
-        <v>1323</v>
-      </c>
-      <c r="D230" s="2" t="s">
-        <v>1324</v>
       </c>
     </row>
     <row r="231" spans="1:4" ht="13">
       <c r="A231" s="7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B231" s="2" t="s">
         <v>139</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="232" spans="1:4" ht="13">
       <c r="A232" s="7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B232" s="2" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>1325</v>
+      </c>
+      <c r="D232" s="2" t="s">
         <v>1326</v>
-      </c>
-      <c r="C232" s="2" t="s">
-        <v>1327</v>
-      </c>
-      <c r="D232" s="2" t="s">
-        <v>1328</v>
       </c>
     </row>
     <row r="233" spans="1:4" ht="13">
       <c r="A233" s="7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B233" s="2" t="s">
+        <v>1327</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>1328</v>
+      </c>
+      <c r="D233" s="2" t="s">
         <v>1329</v>
-      </c>
-      <c r="C233" s="2" t="s">
-        <v>1330</v>
-      </c>
-      <c r="D233" s="2" t="s">
-        <v>1331</v>
       </c>
     </row>
     <row r="234" spans="1:4" ht="13">
       <c r="A234" s="7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B234" s="2" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>1331</v>
+      </c>
+      <c r="D234" s="2" t="s">
         <v>1332</v>
-      </c>
-      <c r="C234" s="2" t="s">
-        <v>1333</v>
-      </c>
-      <c r="D234" s="2" t="s">
-        <v>1334</v>
       </c>
     </row>
   </sheetData>
@@ -21789,39 +21806,39 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" customHeight="1">
       <c r="A1" s="76" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B1" s="76" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C1" s="76" t="s">
         <v>1335</v>
       </c>
-      <c r="B1" s="76" t="s">
+      <c r="D1" s="76" t="s">
         <v>1336</v>
       </c>
-      <c r="C1" s="76" t="s">
+      <c r="E1" s="76" t="s">
         <v>1337</v>
       </c>
-      <c r="D1" s="76" t="s">
+      <c r="F1" s="76" t="s">
         <v>1338</v>
-      </c>
-      <c r="E1" s="76" t="s">
-        <v>1339</v>
-      </c>
-      <c r="F1" s="76" t="s">
-        <v>1340</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.75">
       <c r="A2" s="85" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B2" s="85" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C2" s="86" t="s">
         <v>1341</v>
       </c>
-      <c r="B2" s="85" t="s">
+      <c r="D2" s="77" t="s">
         <v>1342</v>
       </c>
-      <c r="C2" s="86" t="s">
+      <c r="E2" s="77" t="s">
         <v>1343</v>
-      </c>
-      <c r="D2" s="77" t="s">
-        <v>1344</v>
-      </c>
-      <c r="E2" s="77" t="s">
-        <v>1345</v>
       </c>
       <c r="F2" s="77"/>
     </row>

--- a/forms/app/pregnancy.xlsx
+++ b/forms/app/pregnancy.xlsx
@@ -4512,11 +4512,11 @@
 Hii inamaanisha kumsaidia kupata usafiri na pia katika kuhifadhi/kutunza pesa ya kulipia usafiri na gharama nyingine pia.</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;strong&gt; Una hali hatarish za wajawazito zifuatazo:&lt;/strong&gt;
+    <t>&lt;strong&gt;Unatakiwa uende kituo cha afya kutokana na sababu zifuatazo:&lt;/strong&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;strong&gt; Una hali hatarishi za wajawazito zifuatazo:&lt;/strong&gt;
 </t>
-  </si>
-  <si>
-    <t>&lt;strong&gt;Unatakiwa uende kituo cha afya kutokana na sababu zifuatazo:&lt;/strong&gt;</t>
   </si>
 </sst>
 </file>
@@ -15736,7 +15736,7 @@
         <v>1388</v>
       </c>
       <c r="D303" s="88" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="F303" s="46"/>
       <c r="G303" s="46"/>
@@ -16211,7 +16211,7 @@
         <v>1387</v>
       </c>
       <c r="D328" s="93" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="E328" s="92"/>
       <c r="F328" s="92" t="s">

--- a/forms/app/pregnancy.xlsx
+++ b/forms/app/pregnancy.xlsx
@@ -934,19 +934,6 @@
     <t>Ni muhimu kwa kila mtu kujifungua kituo cha afya. Kwasababu huwezi kujua kama unaweza kupatwa na tatizo au dharura yoyote wakati wa kujifungua.  Kama umepatwa na tatizo wakati wa kujifungua ni lazima ufike kituo cha afya ili kupata huduma muhimu kwa ajili yako na mtoto ili kuhakikisha usalama wako na mtoto. Kama uliwahi kupata matatizo yoyote kipindi cha nyuma katika ujauzito wako uliopita au wakati wa kujifungua. Pia  ni muhimu zaidi kuenda  kituo cha afya muda huu ili  kuhakikisha usalama wako na mtoto.</t>
   </si>
   <si>
-    <t>selected(${previous_delivery_by_c_section},'yes') or 
-selected(${previous_delivery_by_vacuum},'yes') or 
-selected(${previous_stillbirth},'yes') or  
-selected(${ten_or_more_years},'yes') or 
-selected(${delivery_complications},'prolonged_labor') or 
-selected(${delivery_complications},'large_perineal_tear') or 
-selected(${delivery_complications},'retained_placenta') or 
-selected(${delivery_complications},'aph') or 
-selected(${delivery_complications},'postpartum_hemorrage') or 
-selected(${delivery_complications},'enclampsia') or 
-selected(${delivery_complications},'big_baby')</t>
-  </si>
-  <si>
     <t>local_herbs</t>
   </si>
   <si>
@@ -4067,9 +4054,6 @@
     <t>Kutokwa damu nyingi baada ya kujifungua</t>
   </si>
   <si>
-    <t>enclampsia</t>
-  </si>
-  <si>
     <t>Eclampsia</t>
   </si>
   <si>
@@ -4463,9 +4447,6 @@
     <t>selected(${delivery_complications},'postpartum_hemorrage')</t>
   </si>
   <si>
-    <t>selected(${delivery_complications},'enclampsia')</t>
-  </si>
-  <si>
     <t>Uchungu wa muda mrefu ( Zaidi ya masaa 12)</t>
   </si>
   <si>
@@ -4517,6 +4498,25 @@
   <si>
     <t xml:space="preserve">&lt;strong&gt; Una hali hatarishi za wajawazito zifuatazo:&lt;/strong&gt;
 </t>
+  </si>
+  <si>
+    <t>eclampsia</t>
+  </si>
+  <si>
+    <t>selected(${delivery_complications},'eclampsia')</t>
+  </si>
+  <si>
+    <t>selected(${previous_delivery_by_c_section},'yes') or 
+selected(${previous_delivery_by_vacuum},'yes') or 
+selected(${previous_stillbirth},'yes') or  
+selected(${ten_or_more_years},'yes') or 
+selected(${delivery_complications},'prolonged_labor') or 
+selected(${delivery_complications},'large_perineal_tear') or 
+selected(${delivery_complications},'retained_placenta') or 
+selected(${delivery_complications},'aph') or 
+selected(${delivery_complications},'postpartum_hemorrage') or 
+selected(${delivery_complications},'eclampsia') or 
+selected(${delivery_complications},'big_baby')</t>
   </si>
 </sst>
 </file>
@@ -7638,10 +7638,10 @@
         <v>165</v>
       </c>
       <c r="C75" s="88" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="D75" s="46" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="E75" s="6"/>
       <c r="F75" s="4"/>
@@ -8684,7 +8684,7 @@
         <v>139</v>
       </c>
       <c r="F103" s="34" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="G103" s="20"/>
       <c r="H103" s="8"/>
@@ -8724,7 +8724,7 @@
         <v>139</v>
       </c>
       <c r="F104" s="34" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="G104" s="20"/>
       <c r="H104" s="8"/>
@@ -8764,7 +8764,7 @@
         <v>139</v>
       </c>
       <c r="F105" s="34" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="G105" s="20"/>
       <c r="H105" s="8"/>
@@ -8850,7 +8850,7 @@
         <v>139</v>
       </c>
       <c r="F107" s="34" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="G107" s="20"/>
       <c r="H107" s="8"/>
@@ -8934,7 +8934,7 @@
       </c>
       <c r="E109" s="7"/>
       <c r="F109" s="90" t="s">
-        <v>294</v>
+        <v>1435</v>
       </c>
       <c r="G109" s="20"/>
       <c r="H109" s="8"/>
@@ -8962,19 +8962,19 @@
         <v>135</v>
       </c>
       <c r="B110" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="C110" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="C110" s="7" t="s">
+      <c r="D110" s="7" t="s">
         <v>296</v>
-      </c>
-      <c r="D110" s="7" t="s">
-        <v>297</v>
       </c>
       <c r="E110" s="7" t="s">
         <v>139</v>
       </c>
       <c r="F110" s="34" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G110" s="20"/>
       <c r="H110" s="8"/>
@@ -9002,17 +9002,17 @@
         <v>109</v>
       </c>
       <c r="B111" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="C111" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="C111" s="7" t="s">
+      <c r="D111" s="88" t="s">
         <v>300</v>
-      </c>
-      <c r="D111" s="88" t="s">
-        <v>301</v>
       </c>
       <c r="E111" s="20"/>
       <c r="F111" s="34" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G111" s="20"/>
       <c r="H111" s="8"/>
@@ -9072,17 +9072,17 @@
         <v>19</v>
       </c>
       <c r="B113" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="C113" s="20" t="s">
         <v>303</v>
       </c>
-      <c r="C113" s="20" t="s">
+      <c r="D113" s="7" t="s">
         <v>304</v>
-      </c>
-      <c r="D113" s="7" t="s">
-        <v>305</v>
       </c>
       <c r="E113" s="20"/>
       <c r="F113" s="34" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G113" s="20" t="s">
         <v>117</v>
@@ -9109,22 +9109,22 @@
     </row>
     <row r="114" spans="1:26" ht="13">
       <c r="A114" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="B114" s="20" t="s">
         <v>307</v>
       </c>
-      <c r="B114" s="20" t="s">
+      <c r="C114" s="20" t="s">
         <v>308</v>
       </c>
-      <c r="C114" s="20" t="s">
+      <c r="D114" s="7" t="s">
         <v>309</v>
-      </c>
-      <c r="D114" s="7" t="s">
-        <v>310</v>
       </c>
       <c r="E114" s="20" t="s">
         <v>139</v>
       </c>
       <c r="F114" s="47" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="G114" s="20"/>
       <c r="H114" s="8"/>
@@ -9152,7 +9152,7 @@
         <v>109</v>
       </c>
       <c r="B115" s="20" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C115" s="20" t="s">
         <v>292</v>
@@ -9164,7 +9164,7 @@
         <v>139</v>
       </c>
       <c r="F115" s="47" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G115" s="20"/>
       <c r="H115" s="8"/>
@@ -9192,17 +9192,17 @@
         <v>109</v>
       </c>
       <c r="B116" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="C116" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="C116" s="7" t="s">
+      <c r="D116" s="7" t="s">
         <v>314</v>
-      </c>
-      <c r="D116" s="7" t="s">
-        <v>315</v>
       </c>
       <c r="E116" s="20"/>
       <c r="F116" s="47" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G116" s="20"/>
       <c r="H116" s="8"/>
@@ -9230,7 +9230,7 @@
         <v>109</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C117" s="13" t="s">
         <v>186</v>
@@ -9240,7 +9240,7 @@
       </c>
       <c r="E117" s="7"/>
       <c r="F117" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G117" s="8"/>
       <c r="H117" s="8"/>
@@ -9268,19 +9268,19 @@
         <v>135</v>
       </c>
       <c r="B118" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="C118" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="C118" s="7" t="s">
-        <v>319</v>
-      </c>
       <c r="D118" s="46" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
       <c r="E118" s="7" t="s">
         <v>139</v>
       </c>
       <c r="F118" s="34" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G118" s="20"/>
       <c r="H118" s="8"/>
@@ -9308,19 +9308,19 @@
         <v>135</v>
       </c>
       <c r="B119" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="C119" s="88" t="s">
         <v>320</v>
       </c>
-      <c r="C119" s="88" t="s">
-        <v>321</v>
-      </c>
       <c r="D119" s="88" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
       <c r="E119" s="7" t="s">
         <v>139</v>
       </c>
       <c r="F119" s="34" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G119" s="20"/>
       <c r="H119" s="8"/>
@@ -9345,22 +9345,22 @@
     </row>
     <row r="120" spans="1:26" ht="13">
       <c r="A120" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="B120" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="B120" s="7" t="s">
+      <c r="C120" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="C120" s="7" t="s">
-        <v>325</v>
-      </c>
       <c r="D120" s="46" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
       <c r="E120" s="7" t="s">
         <v>139</v>
       </c>
       <c r="F120" s="34" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G120" s="20"/>
       <c r="H120" s="8"/>
@@ -9388,7 +9388,7 @@
         <v>109</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C121" s="7" t="s">
         <v>292</v>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="E121" s="7"/>
       <c r="F121" s="34" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G121" s="20"/>
       <c r="H121" s="8"/>
@@ -9426,17 +9426,17 @@
         <v>109</v>
       </c>
       <c r="B122" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="C122" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="C122" s="7" t="s">
+      <c r="D122" s="7" t="s">
         <v>330</v>
-      </c>
-      <c r="D122" s="7" t="s">
-        <v>331</v>
       </c>
       <c r="E122" s="20"/>
       <c r="F122" s="34" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G122" s="20"/>
       <c r="H122" s="8"/>
@@ -9464,7 +9464,7 @@
         <v>35</v>
       </c>
       <c r="B123" s="20" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C123" s="20"/>
       <c r="D123" s="20"/>
@@ -9496,16 +9496,16 @@
         <v>19</v>
       </c>
       <c r="B124" s="20" t="s">
+        <v>332</v>
+      </c>
+      <c r="C124" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="C124" s="7" t="s">
+      <c r="D124" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="D124" s="7" t="s">
+      <c r="F124" s="34" t="s">
         <v>335</v>
-      </c>
-      <c r="F124" s="34" t="s">
-        <v>336</v>
       </c>
       <c r="G124" s="20" t="s">
         <v>117</v>
@@ -9535,13 +9535,13 @@
         <v>109</v>
       </c>
       <c r="B125" s="27" t="s">
+        <v>336</v>
+      </c>
+      <c r="C125" s="48" t="s">
         <v>337</v>
       </c>
-      <c r="C125" s="48" t="s">
+      <c r="D125" s="49" t="s">
         <v>338</v>
-      </c>
-      <c r="D125" s="49" t="s">
-        <v>339</v>
       </c>
       <c r="E125" s="27"/>
       <c r="F125" s="27"/>
@@ -9571,13 +9571,13 @@
         <v>135</v>
       </c>
       <c r="B126" s="20" t="s">
+        <v>339</v>
+      </c>
+      <c r="C126" s="20" t="s">
         <v>340</v>
       </c>
-      <c r="C126" s="20" t="s">
+      <c r="D126" s="7" t="s">
         <v>341</v>
-      </c>
-      <c r="D126" s="7" t="s">
-        <v>342</v>
       </c>
       <c r="E126" s="20" t="s">
         <v>139</v>
@@ -9609,19 +9609,19 @@
         <v>135</v>
       </c>
       <c r="B127" s="20" t="s">
+        <v>342</v>
+      </c>
+      <c r="C127" s="20" t="s">
         <v>343</v>
       </c>
-      <c r="C127" s="20" t="s">
+      <c r="D127" s="7" t="s">
         <v>344</v>
-      </c>
-      <c r="D127" s="7" t="s">
-        <v>345</v>
       </c>
       <c r="E127" s="20" t="s">
         <v>139</v>
       </c>
       <c r="F127" s="34" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G127" s="20"/>
       <c r="H127" s="8"/>
@@ -9649,30 +9649,30 @@
         <v>220</v>
       </c>
       <c r="B128" s="20" t="s">
+        <v>346</v>
+      </c>
+      <c r="C128" s="20" t="s">
         <v>347</v>
       </c>
-      <c r="C128" s="20" t="s">
+      <c r="D128" s="7" t="s">
         <v>348</v>
-      </c>
-      <c r="D128" s="7" t="s">
-        <v>349</v>
       </c>
       <c r="E128" s="20" t="s">
         <v>139</v>
       </c>
       <c r="F128" s="47" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G128" s="20"/>
       <c r="H128" s="8"/>
       <c r="I128" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="J128" s="8" t="s">
         <v>351</v>
       </c>
-      <c r="J128" s="8" t="s">
+      <c r="K128" s="7" t="s">
         <v>352</v>
-      </c>
-      <c r="K128" s="7" t="s">
-        <v>353</v>
       </c>
       <c r="L128" s="8"/>
       <c r="M128" s="8"/>
@@ -9695,19 +9695,19 @@
         <v>135</v>
       </c>
       <c r="B129" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="C129" s="7" t="s">
         <v>354</v>
       </c>
-      <c r="C129" s="7" t="s">
+      <c r="D129" s="7" t="s">
         <v>355</v>
-      </c>
-      <c r="D129" s="7" t="s">
-        <v>356</v>
       </c>
       <c r="E129" s="7" t="s">
         <v>139</v>
       </c>
       <c r="F129" s="34" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G129" s="20"/>
       <c r="H129" s="8"/>
@@ -9735,29 +9735,29 @@
         <v>220</v>
       </c>
       <c r="B130" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="C130" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="C130" s="7" t="s">
+      <c r="D130" s="7" t="s">
         <v>359</v>
-      </c>
-      <c r="D130" s="7" t="s">
-        <v>360</v>
       </c>
       <c r="E130" s="7" t="s">
         <v>139</v>
       </c>
       <c r="F130" s="34" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H130" s="8"/>
       <c r="I130" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="J130" s="7" t="s">
         <v>362</v>
       </c>
-      <c r="J130" s="7" t="s">
+      <c r="K130" s="7" t="s">
         <v>363</v>
-      </c>
-      <c r="K130" s="7" t="s">
-        <v>364</v>
       </c>
       <c r="L130" s="8"/>
       <c r="M130" s="8"/>
@@ -9780,30 +9780,30 @@
         <v>236</v>
       </c>
       <c r="B131" s="20" t="s">
+        <v>364</v>
+      </c>
+      <c r="C131" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="C131" s="7" t="s">
+      <c r="D131" s="7" t="s">
         <v>366</v>
-      </c>
-      <c r="D131" s="7" t="s">
-        <v>367</v>
       </c>
       <c r="E131" s="20" t="s">
         <v>139</v>
       </c>
       <c r="F131" s="34" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G131" s="20"/>
       <c r="H131" s="8"/>
       <c r="I131" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="J131" s="8" t="s">
         <v>369</v>
       </c>
-      <c r="J131" s="8" t="s">
+      <c r="K131" s="7" t="s">
         <v>370</v>
-      </c>
-      <c r="K131" s="7" t="s">
-        <v>371</v>
       </c>
       <c r="L131" s="8"/>
       <c r="M131" s="8"/>
@@ -9826,17 +9826,17 @@
         <v>109</v>
       </c>
       <c r="B132" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="C132" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="C132" s="2" t="s">
+      <c r="D132" s="2" t="s">
         <v>373</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>374</v>
       </c>
       <c r="E132" s="7"/>
       <c r="F132" s="34" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G132" s="7"/>
       <c r="H132" s="8"/>
@@ -9864,19 +9864,19 @@
         <v>135</v>
       </c>
       <c r="B133" s="46" t="s">
+        <v>375</v>
+      </c>
+      <c r="C133" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="C133" s="7" t="s">
+      <c r="D133" s="7" t="s">
         <v>377</v>
-      </c>
-      <c r="D133" s="7" t="s">
-        <v>378</v>
       </c>
       <c r="E133" s="7" t="s">
         <v>139</v>
       </c>
       <c r="F133" s="34" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G133" s="20"/>
       <c r="H133" s="8"/>
@@ -9907,7 +9907,7 @@
         <v>251</v>
       </c>
       <c r="C134" s="7" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D134" s="7" t="s">
         <v>253</v>
@@ -9916,7 +9916,7 @@
         <v>254</v>
       </c>
       <c r="F134" s="34" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G134" s="20"/>
       <c r="H134" s="8"/>
@@ -9944,19 +9944,19 @@
         <v>135</v>
       </c>
       <c r="B135" s="46" t="s">
+        <v>381</v>
+      </c>
+      <c r="C135" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="C135" s="7" t="s">
-        <v>383</v>
-      </c>
       <c r="D135" s="46" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="E135" s="7" t="s">
         <v>139</v>
       </c>
       <c r="F135" s="34" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G135" s="20"/>
       <c r="H135" s="8"/>
@@ -9984,19 +9984,19 @@
         <v>135</v>
       </c>
       <c r="B136" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="C136" s="7" t="s">
         <v>384</v>
       </c>
-      <c r="C136" s="7" t="s">
-        <v>385</v>
-      </c>
       <c r="D136" s="102" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="E136" s="46" t="s">
         <v>139</v>
       </c>
       <c r="F136" s="34" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G136" s="20"/>
       <c r="H136" s="8"/>
@@ -10024,19 +10024,19 @@
         <v>135</v>
       </c>
       <c r="B137" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="C137" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="C137" s="7" t="s">
-        <v>387</v>
-      </c>
       <c r="D137" s="46" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="E137" s="46" t="s">
         <v>139</v>
       </c>
       <c r="F137" s="34" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G137" s="20"/>
       <c r="H137" s="8"/>
@@ -10064,7 +10064,7 @@
         <v>109</v>
       </c>
       <c r="B138" s="7" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C138" s="7" t="s">
         <v>292</v>
@@ -10076,7 +10076,7 @@
         <v>139</v>
       </c>
       <c r="F138" s="34" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G138" s="20"/>
       <c r="H138" s="8"/>
@@ -10101,22 +10101,22 @@
     </row>
     <row r="139" spans="1:26" ht="13">
       <c r="A139" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="B139" s="7" t="s">
         <v>390</v>
       </c>
-      <c r="B139" s="7" t="s">
+      <c r="C139" s="7" t="s">
         <v>391</v>
       </c>
-      <c r="C139" s="7" t="s">
+      <c r="D139" s="7" t="s">
         <v>392</v>
-      </c>
-      <c r="D139" s="7" t="s">
-        <v>393</v>
       </c>
       <c r="E139" s="7" t="s">
         <v>139</v>
       </c>
       <c r="F139" s="34" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G139" s="20"/>
       <c r="H139" s="8"/>
@@ -10150,19 +10150,19 @@
         <v>135</v>
       </c>
       <c r="B140" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="C140" s="7" t="s">
         <v>395</v>
       </c>
-      <c r="C140" s="7" t="s">
+      <c r="D140" s="7" t="s">
         <v>396</v>
-      </c>
-      <c r="D140" s="7" t="s">
-        <v>397</v>
       </c>
       <c r="E140" s="7" t="s">
         <v>139</v>
       </c>
       <c r="F140" s="34" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G140" s="20"/>
       <c r="H140" s="8"/>
@@ -10187,17 +10187,17 @@
         <v>109</v>
       </c>
       <c r="B141" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="C141" s="7" t="s">
         <v>398</v>
       </c>
-      <c r="C141" s="7" t="s">
+      <c r="D141" s="7" t="s">
         <v>399</v>
-      </c>
-      <c r="D141" s="7" t="s">
-        <v>400</v>
       </c>
       <c r="E141" s="20"/>
       <c r="F141" s="34" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G141" s="20"/>
       <c r="H141" s="8"/>
@@ -10219,22 +10219,22 @@
     </row>
     <row r="142" spans="1:26" ht="13">
       <c r="A142" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="B142" s="7" t="s">
         <v>402</v>
       </c>
-      <c r="B142" s="7" t="s">
+      <c r="C142" s="7" t="s">
         <v>403</v>
       </c>
-      <c r="C142" s="7" t="s">
+      <c r="D142" s="7" t="s">
         <v>404</v>
-      </c>
-      <c r="D142" s="7" t="s">
-        <v>405</v>
       </c>
       <c r="E142" s="7" t="s">
         <v>139</v>
       </c>
       <c r="F142" s="34" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G142" s="20"/>
       <c r="H142" s="8"/>
@@ -10262,7 +10262,7 @@
         <v>35</v>
       </c>
       <c r="B143" s="20" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C143" s="20"/>
       <c r="D143" s="20"/>
@@ -10294,7 +10294,7 @@
         <v>41</v>
       </c>
       <c r="B144" s="20" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C144" s="20"/>
       <c r="D144" s="20"/>
@@ -10306,7 +10306,7 @@
       <c r="J144" s="8"/>
       <c r="K144" s="8"/>
       <c r="L144" s="100" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="M144" s="99"/>
       <c r="N144" s="99"/>
@@ -10328,7 +10328,7 @@
         <v>41</v>
       </c>
       <c r="B145" s="20" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C145" s="20"/>
       <c r="D145" s="20"/>
@@ -10340,7 +10340,7 @@
       <c r="J145" s="8"/>
       <c r="K145" s="8"/>
       <c r="L145" s="7" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M145" s="8"/>
       <c r="N145" s="8"/>
@@ -10362,17 +10362,17 @@
         <v>19</v>
       </c>
       <c r="B146" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="C146" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="C146" s="2" t="s">
+      <c r="D146" s="2" t="s">
         <v>412</v>
-      </c>
-      <c r="D146" s="2" t="s">
-        <v>413</v>
       </c>
       <c r="E146" s="7"/>
       <c r="F146" s="34" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G146" s="7" t="s">
         <v>117</v>
@@ -10402,13 +10402,13 @@
         <v>109</v>
       </c>
       <c r="B147" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="C147" s="7" t="s">
         <v>415</v>
       </c>
-      <c r="C147" s="7" t="s">
+      <c r="D147" s="7" t="s">
         <v>416</v>
-      </c>
-      <c r="D147" s="7" t="s">
-        <v>417</v>
       </c>
       <c r="E147" s="7"/>
       <c r="F147" s="8"/>
@@ -10438,14 +10438,14 @@
         <v>19</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E148" s="7"/>
       <c r="G148" s="7" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H148" s="8"/>
       <c r="I148" s="8"/>
@@ -10472,13 +10472,13 @@
         <v>135</v>
       </c>
       <c r="B149" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="C149" s="50" t="s">
         <v>420</v>
       </c>
-      <c r="C149" s="50" t="s">
+      <c r="D149" s="50" t="s">
         <v>421</v>
-      </c>
-      <c r="D149" s="50" t="s">
-        <v>422</v>
       </c>
       <c r="E149" s="7" t="s">
         <v>139</v>
@@ -10510,13 +10510,13 @@
         <v>135</v>
       </c>
       <c r="B150" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="C150" s="50" t="s">
         <v>423</v>
       </c>
-      <c r="C150" s="50" t="s">
+      <c r="D150" s="50" t="s">
         <v>424</v>
-      </c>
-      <c r="D150" s="50" t="s">
-        <v>425</v>
       </c>
       <c r="E150" s="7" t="s">
         <v>139</v>
@@ -10548,13 +10548,13 @@
         <v>135</v>
       </c>
       <c r="B151" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="C151" s="7" t="s">
         <v>426</v>
       </c>
-      <c r="C151" s="7" t="s">
+      <c r="D151" s="7" t="s">
         <v>427</v>
-      </c>
-      <c r="D151" s="7" t="s">
-        <v>428</v>
       </c>
       <c r="E151" s="7" t="s">
         <v>139</v>
@@ -10586,13 +10586,13 @@
         <v>135</v>
       </c>
       <c r="B152" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="C152" s="50" t="s">
         <v>429</v>
       </c>
-      <c r="C152" s="50" t="s">
+      <c r="D152" s="50" t="s">
         <v>430</v>
-      </c>
-      <c r="D152" s="50" t="s">
-        <v>431</v>
       </c>
       <c r="E152" s="7" t="s">
         <v>139</v>
@@ -10624,7 +10624,7 @@
         <v>35</v>
       </c>
       <c r="B153" s="7" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C153" s="13"/>
       <c r="D153" s="7"/>
@@ -10656,7 +10656,7 @@
         <v>109</v>
       </c>
       <c r="B154" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C154" s="13" t="s">
         <v>186</v>
@@ -10692,13 +10692,13 @@
         <v>109</v>
       </c>
       <c r="B155" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="C155" s="7" t="s">
         <v>433</v>
       </c>
-      <c r="C155" s="7" t="s">
+      <c r="D155" s="7" t="s">
         <v>434</v>
-      </c>
-      <c r="D155" s="7" t="s">
-        <v>435</v>
       </c>
       <c r="E155" s="7"/>
       <c r="F155" s="8"/>
@@ -10728,7 +10728,7 @@
         <v>19</v>
       </c>
       <c r="B156" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C156" s="50" t="s">
         <v>21</v>
@@ -10737,7 +10737,7 @@
       <c r="E156" s="7"/>
       <c r="F156" s="8"/>
       <c r="G156" s="7" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H156" s="8"/>
       <c r="I156" s="8"/>
@@ -10764,13 +10764,13 @@
         <v>135</v>
       </c>
       <c r="B157" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="C157" s="50" t="s">
         <v>437</v>
       </c>
-      <c r="C157" s="50" t="s">
+      <c r="D157" s="50" t="s">
         <v>438</v>
-      </c>
-      <c r="D157" s="50" t="s">
-        <v>439</v>
       </c>
       <c r="E157" s="7" t="s">
         <v>139</v>
@@ -10802,13 +10802,13 @@
         <v>135</v>
       </c>
       <c r="B158" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="C158" s="50" t="s">
         <v>440</v>
       </c>
-      <c r="C158" s="50" t="s">
+      <c r="D158" s="50" t="s">
         <v>441</v>
-      </c>
-      <c r="D158" s="50" t="s">
-        <v>442</v>
       </c>
       <c r="E158" s="7" t="s">
         <v>139</v>
@@ -10840,13 +10840,13 @@
         <v>135</v>
       </c>
       <c r="B159" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="C159" s="50" t="s">
         <v>443</v>
       </c>
-      <c r="C159" s="50" t="s">
+      <c r="D159" s="51" t="s">
         <v>444</v>
-      </c>
-      <c r="D159" s="51" t="s">
-        <v>445</v>
       </c>
       <c r="E159" s="7" t="s">
         <v>139</v>
@@ -10878,7 +10878,7 @@
         <v>35</v>
       </c>
       <c r="B160" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C160" s="50"/>
       <c r="D160" s="8"/>
@@ -10910,7 +10910,7 @@
         <v>41</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C161" s="52"/>
       <c r="D161" s="8"/>
@@ -10922,7 +10922,7 @@
       <c r="J161" s="8"/>
       <c r="K161" s="8"/>
       <c r="L161" s="53" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="M161" s="8"/>
       <c r="N161" s="8"/>
@@ -10944,19 +10944,19 @@
         <v>109</v>
       </c>
       <c r="B162" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="C162" s="50" t="s">
         <v>448</v>
       </c>
-      <c r="C162" s="50" t="s">
+      <c r="D162" s="50" t="s">
         <v>449</v>
-      </c>
-      <c r="D162" s="50" t="s">
-        <v>450</v>
       </c>
       <c r="E162" s="7" t="s">
         <v>139</v>
       </c>
       <c r="F162" s="7" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G162" s="7"/>
       <c r="H162" s="8"/>
@@ -10984,17 +10984,17 @@
         <v>109</v>
       </c>
       <c r="B163" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="C163" s="7" t="s">
         <v>452</v>
       </c>
-      <c r="C163" s="7" t="s">
+      <c r="D163" s="54" t="s">
         <v>453</v>
-      </c>
-      <c r="D163" s="54" t="s">
-        <v>454</v>
       </c>
       <c r="E163" s="7"/>
       <c r="F163" s="7" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G163" s="7"/>
       <c r="H163" s="7"/>
@@ -11022,7 +11022,7 @@
         <v>35</v>
       </c>
       <c r="B164" s="7" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C164" s="8"/>
       <c r="D164" s="8"/>
@@ -11054,17 +11054,17 @@
         <v>19</v>
       </c>
       <c r="B165" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="C165" s="7" t="s">
         <v>456</v>
       </c>
-      <c r="C165" s="7" t="s">
+      <c r="D165" s="7" t="s">
         <v>457</v>
-      </c>
-      <c r="D165" s="7" t="s">
-        <v>458</v>
       </c>
       <c r="E165" s="8"/>
       <c r="F165" s="34" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="G165" s="7"/>
       <c r="H165" s="8"/>
@@ -11092,7 +11092,7 @@
         <v>19</v>
       </c>
       <c r="B166" s="7" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C166" s="7" t="s">
         <v>21</v>
@@ -11125,22 +11125,22 @@
     </row>
     <row r="167" spans="1:26" ht="13">
       <c r="A167" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="B167" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="B167" s="7" t="s">
+      <c r="C167" s="7" t="s">
         <v>462</v>
       </c>
-      <c r="C167" s="7" t="s">
+      <c r="D167" s="7" t="s">
         <v>463</v>
-      </c>
-      <c r="D167" s="7" t="s">
-        <v>464</v>
       </c>
       <c r="E167" s="7" t="s">
         <v>139</v>
       </c>
       <c r="F167" s="53" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G167" s="7" t="s">
         <v>117</v>
@@ -11174,7 +11174,7 @@
         <v>41</v>
       </c>
       <c r="B168" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C168" s="13"/>
       <c r="D168" s="7"/>
@@ -11186,7 +11186,7 @@
       <c r="J168" s="8"/>
       <c r="K168" s="8"/>
       <c r="L168" s="7" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="M168" s="8"/>
       <c r="N168" s="8"/>
@@ -11208,17 +11208,17 @@
         <v>109</v>
       </c>
       <c r="B169" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="C169" s="13" t="s">
         <v>468</v>
       </c>
-      <c r="C169" s="13" t="s">
+      <c r="D169" s="7" t="s">
         <v>469</v>
-      </c>
-      <c r="D169" s="7" t="s">
-        <v>470</v>
       </c>
       <c r="E169" s="7"/>
       <c r="F169" s="57" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="G169" s="7"/>
       <c r="H169" s="8"/>
@@ -11246,7 +11246,7 @@
         <v>35</v>
       </c>
       <c r="B170" s="7" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C170" s="7"/>
       <c r="D170" s="7"/>
@@ -11278,7 +11278,7 @@
         <v>19</v>
       </c>
       <c r="B171" s="7" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C171" s="7" t="s">
         <v>21</v>
@@ -11286,7 +11286,7 @@
       <c r="D171" s="7"/>
       <c r="E171" s="7"/>
       <c r="F171" s="53" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G171" s="7" t="s">
         <v>117</v>
@@ -11316,19 +11316,19 @@
         <v>135</v>
       </c>
       <c r="B172" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="C172" s="7" t="s">
         <v>473</v>
       </c>
-      <c r="C172" s="7" t="s">
+      <c r="D172" s="7" t="s">
         <v>474</v>
-      </c>
-      <c r="D172" s="7" t="s">
-        <v>475</v>
       </c>
       <c r="E172" s="7" t="s">
         <v>139</v>
       </c>
       <c r="F172" s="53" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="G172" s="8"/>
       <c r="H172" s="8"/>
@@ -11356,17 +11356,17 @@
         <v>109</v>
       </c>
       <c r="B173" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="C173" s="7" t="s">
         <v>477</v>
       </c>
-      <c r="C173" s="7" t="s">
+      <c r="D173" s="7" t="s">
         <v>478</v>
-      </c>
-      <c r="D173" s="7" t="s">
-        <v>479</v>
       </c>
       <c r="E173" s="7"/>
       <c r="F173" s="53" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G173" s="8"/>
       <c r="H173" s="8"/>
@@ -11394,19 +11394,19 @@
         <v>135</v>
       </c>
       <c r="B174" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="C174" s="7" t="s">
         <v>480</v>
       </c>
-      <c r="C174" s="7" t="s">
+      <c r="D174" s="7" t="s">
         <v>481</v>
-      </c>
-      <c r="D174" s="7" t="s">
-        <v>482</v>
       </c>
       <c r="E174" s="7" t="s">
         <v>139</v>
       </c>
       <c r="F174" s="53" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G174" s="8"/>
       <c r="H174" s="8"/>
@@ -11434,7 +11434,7 @@
         <v>41</v>
       </c>
       <c r="B175" s="7" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C175" s="56"/>
       <c r="D175" s="56"/>
@@ -11446,7 +11446,7 @@
       <c r="J175" s="56"/>
       <c r="K175" s="56"/>
       <c r="L175" s="53" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="M175" s="56"/>
       <c r="N175" s="56"/>
@@ -11468,17 +11468,17 @@
         <v>109</v>
       </c>
       <c r="B176" s="7" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C176" s="57" t="s">
+        <v>468</v>
+      </c>
+      <c r="D176" s="57" t="s">
         <v>469</v>
-      </c>
-      <c r="D176" s="57" t="s">
-        <v>470</v>
       </c>
       <c r="E176" s="57"/>
       <c r="F176" s="57" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="G176" s="56"/>
       <c r="H176" s="56"/>
@@ -11506,17 +11506,17 @@
         <v>109</v>
       </c>
       <c r="B177" s="57" t="s">
+        <v>486</v>
+      </c>
+      <c r="C177" s="57" t="s">
         <v>487</v>
       </c>
-      <c r="C177" s="57" t="s">
+      <c r="D177" s="57" t="s">
         <v>488</v>
-      </c>
-      <c r="D177" s="57" t="s">
-        <v>489</v>
       </c>
       <c r="E177" s="56"/>
       <c r="F177" s="57" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="G177" s="56"/>
       <c r="H177" s="56"/>
@@ -11544,7 +11544,7 @@
         <v>35</v>
       </c>
       <c r="B178" s="57" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C178" s="57"/>
       <c r="D178" s="56"/>
@@ -11576,7 +11576,7 @@
         <v>35</v>
       </c>
       <c r="B179" s="57" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C179" s="56"/>
       <c r="D179" s="56"/>
@@ -11608,17 +11608,17 @@
         <v>19</v>
       </c>
       <c r="B180" s="57" t="s">
+        <v>490</v>
+      </c>
+      <c r="C180" s="57" t="s">
         <v>491</v>
       </c>
-      <c r="C180" s="57" t="s">
+      <c r="D180" s="57" t="s">
         <v>492</v>
-      </c>
-      <c r="D180" s="57" t="s">
-        <v>493</v>
       </c>
       <c r="E180" s="56"/>
       <c r="F180" s="57" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="G180" s="57" t="s">
         <v>164</v>
@@ -11648,13 +11648,13 @@
         <v>109</v>
       </c>
       <c r="B181" s="57" t="s">
+        <v>494</v>
+      </c>
+      <c r="C181" s="57" t="s">
         <v>495</v>
       </c>
-      <c r="C181" s="57" t="s">
+      <c r="D181" s="57" t="s">
         <v>496</v>
-      </c>
-      <c r="D181" s="57" t="s">
-        <v>497</v>
       </c>
       <c r="E181" s="56"/>
       <c r="G181" s="56"/>
@@ -11683,7 +11683,7 @@
         <v>109</v>
       </c>
       <c r="B182" s="57" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C182" s="56"/>
       <c r="D182" s="56"/>
@@ -11701,10 +11701,10 @@
       <c r="P182" s="56"/>
       <c r="Q182" s="56"/>
       <c r="R182" s="57" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="S182" s="57" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="T182" s="9"/>
       <c r="U182" s="9"/>
@@ -11719,7 +11719,7 @@
         <v>109</v>
       </c>
       <c r="B183" s="57" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D183" s="56"/>
       <c r="E183" s="56"/>
@@ -11736,10 +11736,10 @@
       <c r="P183" s="56"/>
       <c r="Q183" s="56"/>
       <c r="R183" s="57" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="S183" s="57" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="T183" s="9"/>
       <c r="U183" s="9"/>
@@ -11754,7 +11754,7 @@
         <v>109</v>
       </c>
       <c r="B184" s="57" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C184" s="56"/>
       <c r="D184" s="56"/>
@@ -11772,10 +11772,10 @@
       <c r="P184" s="56"/>
       <c r="Q184" s="56"/>
       <c r="R184" s="57" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="S184" s="57" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="T184" s="9"/>
       <c r="U184" s="9"/>
@@ -11790,7 +11790,7 @@
         <v>109</v>
       </c>
       <c r="B185" s="57" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C185" s="56"/>
       <c r="D185" s="56"/>
@@ -11808,10 +11808,10 @@
       <c r="P185" s="56"/>
       <c r="Q185" s="56"/>
       <c r="R185" s="57" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="S185" s="57" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="T185" s="9"/>
       <c r="U185" s="9"/>
@@ -11826,7 +11826,7 @@
         <v>109</v>
       </c>
       <c r="B186" s="57" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C186" s="56"/>
       <c r="D186" s="56"/>
@@ -11844,10 +11844,10 @@
       <c r="P186" s="56"/>
       <c r="Q186" s="56"/>
       <c r="R186" s="57" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="S186" s="57" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="T186" s="9"/>
       <c r="U186" s="9"/>
@@ -11862,7 +11862,7 @@
         <v>109</v>
       </c>
       <c r="B187" s="57" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C187" s="56"/>
       <c r="D187" s="56"/>
@@ -11880,10 +11880,10 @@
       <c r="P187" s="56"/>
       <c r="Q187" s="56"/>
       <c r="R187" s="57" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="S187" s="57" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="T187" s="9"/>
       <c r="U187" s="9"/>
@@ -11898,7 +11898,7 @@
         <v>35</v>
       </c>
       <c r="B188" s="57" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C188" s="56"/>
       <c r="D188" s="56"/>
@@ -11930,17 +11930,17 @@
         <v>19</v>
       </c>
       <c r="B189" s="57" t="s">
+        <v>509</v>
+      </c>
+      <c r="C189" s="57" t="s">
         <v>510</v>
       </c>
-      <c r="C189" s="57" t="s">
+      <c r="D189" s="57" t="s">
         <v>511</v>
-      </c>
-      <c r="D189" s="57" t="s">
-        <v>512</v>
       </c>
       <c r="E189" s="57"/>
       <c r="F189" s="34" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="G189" s="57" t="s">
         <v>117</v>
@@ -11970,13 +11970,13 @@
         <v>135</v>
       </c>
       <c r="B190" s="57" t="s">
+        <v>513</v>
+      </c>
+      <c r="C190" s="57" t="s">
         <v>514</v>
       </c>
-      <c r="C190" s="57" t="s">
+      <c r="D190" s="57" t="s">
         <v>515</v>
-      </c>
-      <c r="D190" s="57" t="s">
-        <v>516</v>
       </c>
       <c r="E190" s="57" t="s">
         <v>139</v>
@@ -12008,17 +12008,17 @@
         <v>109</v>
       </c>
       <c r="B191" s="57" t="s">
+        <v>516</v>
+      </c>
+      <c r="C191" s="50" t="s">
         <v>517</v>
       </c>
-      <c r="C191" s="50" t="s">
+      <c r="D191" s="50" t="s">
         <v>518</v>
-      </c>
-      <c r="D191" s="50" t="s">
-        <v>519</v>
       </c>
       <c r="E191" s="50"/>
       <c r="F191" s="57" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="G191" s="56"/>
       <c r="H191" s="56"/>
@@ -12046,19 +12046,19 @@
         <v>135</v>
       </c>
       <c r="B192" s="57" t="s">
+        <v>520</v>
+      </c>
+      <c r="C192" s="57" t="s">
         <v>521</v>
       </c>
-      <c r="C192" s="57" t="s">
+      <c r="D192" s="57" t="s">
         <v>522</v>
-      </c>
-      <c r="D192" s="57" t="s">
-        <v>523</v>
       </c>
       <c r="E192" s="57" t="s">
         <v>139</v>
       </c>
       <c r="F192" s="57" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="G192" s="56"/>
       <c r="H192" s="56"/>
@@ -12083,22 +12083,22 @@
     </row>
     <row r="193" spans="1:26" ht="13">
       <c r="A193" s="57" t="s">
+        <v>524</v>
+      </c>
+      <c r="B193" s="57" t="s">
         <v>525</v>
       </c>
-      <c r="B193" s="57" t="s">
+      <c r="C193" s="57" t="s">
         <v>526</v>
       </c>
-      <c r="C193" s="57" t="s">
+      <c r="D193" s="57" t="s">
         <v>527</v>
-      </c>
-      <c r="D193" s="57" t="s">
-        <v>528</v>
       </c>
       <c r="E193" s="57" t="s">
         <v>139</v>
       </c>
       <c r="F193" s="57" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="G193" s="56"/>
       <c r="H193" s="56"/>
@@ -12126,17 +12126,17 @@
         <v>109</v>
       </c>
       <c r="B194" s="57" t="s">
+        <v>529</v>
+      </c>
+      <c r="C194" s="7" t="s">
         <v>530</v>
       </c>
-      <c r="C194" s="7" t="s">
+      <c r="D194" s="7" t="s">
         <v>531</v>
-      </c>
-      <c r="D194" s="7" t="s">
-        <v>532</v>
       </c>
       <c r="E194" s="7"/>
       <c r="F194" s="57" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="G194" s="56"/>
       <c r="H194" s="56"/>
@@ -12164,19 +12164,19 @@
         <v>135</v>
       </c>
       <c r="B195" s="57" t="s">
+        <v>533</v>
+      </c>
+      <c r="C195" s="57" t="s">
         <v>534</v>
       </c>
-      <c r="C195" s="57" t="s">
+      <c r="D195" s="57" t="s">
         <v>535</v>
-      </c>
-      <c r="D195" s="57" t="s">
-        <v>536</v>
       </c>
       <c r="E195" s="57" t="s">
         <v>139</v>
       </c>
       <c r="F195" s="57" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="G195" s="56"/>
       <c r="H195" s="56"/>
@@ -12204,17 +12204,17 @@
         <v>109</v>
       </c>
       <c r="B196" s="57" t="s">
+        <v>537</v>
+      </c>
+      <c r="C196" s="50" t="s">
         <v>538</v>
       </c>
-      <c r="C196" s="50" t="s">
+      <c r="D196" s="50" t="s">
         <v>539</v>
-      </c>
-      <c r="D196" s="50" t="s">
-        <v>540</v>
       </c>
       <c r="E196" s="50"/>
       <c r="F196" s="57" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="G196" s="56"/>
       <c r="H196" s="56"/>
@@ -12242,17 +12242,17 @@
         <v>109</v>
       </c>
       <c r="B197" s="57" t="s">
+        <v>541</v>
+      </c>
+      <c r="C197" s="50" t="s">
         <v>542</v>
       </c>
-      <c r="C197" s="50" t="s">
+      <c r="D197" s="50" t="s">
         <v>543</v>
-      </c>
-      <c r="D197" s="50" t="s">
-        <v>544</v>
       </c>
       <c r="E197" s="50"/>
       <c r="F197" s="57" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="G197" s="56"/>
       <c r="H197" s="56"/>
@@ -12280,17 +12280,17 @@
         <v>109</v>
       </c>
       <c r="B198" s="57" t="s">
+        <v>545</v>
+      </c>
+      <c r="C198" s="7" t="s">
         <v>546</v>
       </c>
-      <c r="C198" s="7" t="s">
+      <c r="D198" s="7" t="s">
         <v>547</v>
-      </c>
-      <c r="D198" s="7" t="s">
-        <v>548</v>
       </c>
       <c r="E198" s="7"/>
       <c r="F198" s="57" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="G198" s="56"/>
       <c r="H198" s="56"/>
@@ -12318,17 +12318,17 @@
         <v>109</v>
       </c>
       <c r="B199" s="57" t="s">
+        <v>548</v>
+      </c>
+      <c r="C199" s="7" t="s">
         <v>549</v>
       </c>
-      <c r="C199" s="7" t="s">
+      <c r="D199" s="7" t="s">
         <v>550</v>
-      </c>
-      <c r="D199" s="7" t="s">
-        <v>551</v>
       </c>
       <c r="E199" s="7"/>
       <c r="F199" s="57" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G199" s="56"/>
       <c r="H199" s="56"/>
@@ -12356,7 +12356,7 @@
         <v>35</v>
       </c>
       <c r="B200" s="57" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C200" s="56"/>
       <c r="D200" s="56"/>
@@ -12388,13 +12388,13 @@
         <v>105</v>
       </c>
       <c r="B201" s="57" t="s">
+        <v>552</v>
+      </c>
+      <c r="C201" s="57" t="s">
         <v>553</v>
       </c>
-      <c r="C201" s="57" t="s">
+      <c r="D201" s="57" t="s">
         <v>554</v>
-      </c>
-      <c r="D201" s="57" t="s">
-        <v>555</v>
       </c>
       <c r="E201" s="57"/>
       <c r="F201" s="34" t="b">
@@ -12425,16 +12425,16 @@
     </row>
     <row r="202" spans="1:26" ht="13">
       <c r="A202" s="57" t="s">
+        <v>555</v>
+      </c>
+      <c r="B202" s="57" t="s">
         <v>556</v>
       </c>
-      <c r="B202" s="57" t="s">
+      <c r="C202" s="57" t="s">
         <v>557</v>
       </c>
-      <c r="C202" s="57" t="s">
+      <c r="D202" s="57" t="s">
         <v>558</v>
-      </c>
-      <c r="D202" s="57" t="s">
-        <v>559</v>
       </c>
       <c r="E202" s="57" t="s">
         <v>139</v>
@@ -12443,10 +12443,10 @@
       <c r="G202" s="57"/>
       <c r="H202" s="56"/>
       <c r="I202" s="10" t="s">
+        <v>559</v>
+      </c>
+      <c r="J202" s="57" t="s">
         <v>560</v>
-      </c>
-      <c r="J202" s="57" t="s">
-        <v>561</v>
       </c>
       <c r="K202" s="56"/>
       <c r="L202" s="56"/>
@@ -12470,17 +12470,17 @@
         <v>109</v>
       </c>
       <c r="B203" s="57" t="s">
+        <v>561</v>
+      </c>
+      <c r="C203" s="50" t="s">
         <v>562</v>
       </c>
-      <c r="C203" s="50" t="s">
+      <c r="D203" s="50" t="s">
         <v>563</v>
-      </c>
-      <c r="D203" s="50" t="s">
-        <v>564</v>
       </c>
       <c r="E203" s="50"/>
       <c r="F203" s="57" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="G203" s="57"/>
       <c r="H203" s="56"/>
@@ -12508,7 +12508,7 @@
         <v>35</v>
       </c>
       <c r="B204" s="57" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C204" s="57"/>
       <c r="D204" s="57"/>
@@ -12540,17 +12540,17 @@
         <v>19</v>
       </c>
       <c r="B205" s="57" t="s">
+        <v>565</v>
+      </c>
+      <c r="C205" s="57" t="s">
         <v>566</v>
       </c>
-      <c r="C205" s="57" t="s">
+      <c r="D205" s="57" t="s">
         <v>567</v>
-      </c>
-      <c r="D205" s="57" t="s">
-        <v>568</v>
       </c>
       <c r="E205" s="56"/>
       <c r="F205" s="34" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="G205" s="57" t="s">
         <v>117</v>
@@ -12580,13 +12580,13 @@
         <v>236</v>
       </c>
       <c r="B206" s="13" t="s">
+        <v>569</v>
+      </c>
+      <c r="C206" s="57" t="s">
         <v>570</v>
       </c>
-      <c r="C206" s="57" t="s">
+      <c r="D206" s="57" t="s">
         <v>571</v>
-      </c>
-      <c r="D206" s="57" t="s">
-        <v>572</v>
       </c>
       <c r="E206" s="57" t="s">
         <v>139</v>
@@ -12595,13 +12595,13 @@
       <c r="G206" s="56"/>
       <c r="H206" s="56"/>
       <c r="I206" s="7" t="s">
+        <v>572</v>
+      </c>
+      <c r="J206" s="57" t="s">
         <v>573</v>
       </c>
-      <c r="J206" s="57" t="s">
+      <c r="K206" s="57" t="s">
         <v>574</v>
-      </c>
-      <c r="K206" s="57" t="s">
-        <v>575</v>
       </c>
       <c r="L206" s="56"/>
       <c r="M206" s="56"/>
@@ -12621,22 +12621,22 @@
     </row>
     <row r="207" spans="1:26" ht="13">
       <c r="A207" s="57" t="s">
+        <v>575</v>
+      </c>
+      <c r="B207" s="57" t="s">
         <v>576</v>
       </c>
-      <c r="B207" s="57" t="s">
+      <c r="C207" s="57" t="s">
         <v>577</v>
       </c>
-      <c r="C207" s="57" t="s">
+      <c r="D207" s="57" t="s">
         <v>578</v>
-      </c>
-      <c r="D207" s="57" t="s">
-        <v>579</v>
       </c>
       <c r="E207" s="57" t="s">
         <v>139</v>
       </c>
       <c r="F207" s="34" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="G207" s="56"/>
       <c r="H207" s="56"/>
@@ -12663,17 +12663,17 @@
         <v>109</v>
       </c>
       <c r="B208" s="57" t="s">
+        <v>580</v>
+      </c>
+      <c r="C208" s="7" t="s">
         <v>581</v>
       </c>
-      <c r="C208" s="7" t="s">
+      <c r="D208" s="7" t="s">
         <v>582</v>
-      </c>
-      <c r="D208" s="7" t="s">
-        <v>583</v>
       </c>
       <c r="E208" s="7"/>
       <c r="F208" s="34" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="G208" s="56"/>
       <c r="H208" s="56"/>
@@ -12701,7 +12701,7 @@
         <v>35</v>
       </c>
       <c r="B209" s="57" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C209" s="56"/>
       <c r="D209" s="56"/>
@@ -12733,7 +12733,7 @@
         <v>19</v>
       </c>
       <c r="B210" s="57" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C210" s="57" t="s">
         <v>21</v>
@@ -12741,7 +12741,7 @@
       <c r="D210" s="56"/>
       <c r="E210" s="56"/>
       <c r="F210" s="34" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="G210" s="57"/>
       <c r="H210" s="56"/>
@@ -12769,13 +12769,13 @@
         <v>19</v>
       </c>
       <c r="B211" s="57" t="s">
+        <v>585</v>
+      </c>
+      <c r="C211" s="57" t="s">
         <v>586</v>
       </c>
-      <c r="C211" s="57" t="s">
+      <c r="D211" s="57" t="s">
         <v>587</v>
-      </c>
-      <c r="D211" s="57" t="s">
-        <v>588</v>
       </c>
       <c r="E211" s="56"/>
       <c r="F211" s="34"/>
@@ -12807,13 +12807,13 @@
         <v>109</v>
       </c>
       <c r="B212" s="57" t="s">
+        <v>588</v>
+      </c>
+      <c r="C212" s="57" t="s">
         <v>589</v>
       </c>
-      <c r="C212" s="57" t="s">
+      <c r="D212" s="57" t="s">
         <v>590</v>
-      </c>
-      <c r="D212" s="57" t="s">
-        <v>591</v>
       </c>
       <c r="E212" s="57"/>
       <c r="F212" s="57"/>
@@ -12843,7 +12843,7 @@
         <v>35</v>
       </c>
       <c r="B213" s="57" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C213" s="57"/>
       <c r="D213" s="56"/>
@@ -12875,13 +12875,13 @@
         <v>19</v>
       </c>
       <c r="B214" s="57" t="s">
+        <v>591</v>
+      </c>
+      <c r="C214" s="57" t="s">
         <v>592</v>
       </c>
-      <c r="C214" s="57" t="s">
+      <c r="D214" s="58" t="s">
         <v>593</v>
-      </c>
-      <c r="D214" s="58" t="s">
-        <v>594</v>
       </c>
       <c r="E214" s="56"/>
       <c r="F214" s="56"/>
@@ -12913,13 +12913,13 @@
         <v>109</v>
       </c>
       <c r="B215" s="57" t="s">
+        <v>594</v>
+      </c>
+      <c r="C215" s="57" t="s">
         <v>595</v>
       </c>
-      <c r="C215" s="57" t="s">
+      <c r="D215" s="57" t="s">
         <v>596</v>
-      </c>
-      <c r="D215" s="57" t="s">
-        <v>597</v>
       </c>
       <c r="E215" s="56"/>
       <c r="F215" s="56"/>
@@ -12949,7 +12949,7 @@
         <v>35</v>
       </c>
       <c r="B216" s="57" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C216" s="57"/>
       <c r="D216" s="56"/>
@@ -12981,13 +12981,13 @@
         <v>19</v>
       </c>
       <c r="B217" s="57" t="s">
+        <v>597</v>
+      </c>
+      <c r="C217" s="57" t="s">
         <v>598</v>
       </c>
-      <c r="C217" s="57" t="s">
+      <c r="D217" s="57" t="s">
         <v>599</v>
-      </c>
-      <c r="D217" s="57" t="s">
-        <v>600</v>
       </c>
       <c r="E217" s="56"/>
       <c r="F217" s="56"/>
@@ -13019,13 +13019,13 @@
         <v>109</v>
       </c>
       <c r="B218" s="57" t="s">
+        <v>600</v>
+      </c>
+      <c r="C218" s="57" t="s">
         <v>601</v>
       </c>
-      <c r="C218" s="57" t="s">
+      <c r="D218" s="57" t="s">
         <v>602</v>
-      </c>
-      <c r="D218" s="57" t="s">
-        <v>603</v>
       </c>
       <c r="E218" s="56"/>
       <c r="F218" s="56"/>
@@ -13055,7 +13055,7 @@
         <v>35</v>
       </c>
       <c r="B219" s="57" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C219" s="57"/>
       <c r="D219" s="56"/>
@@ -13087,13 +13087,13 @@
         <v>19</v>
       </c>
       <c r="B220" s="57" t="s">
+        <v>603</v>
+      </c>
+      <c r="C220" s="57" t="s">
         <v>604</v>
       </c>
-      <c r="C220" s="57" t="s">
+      <c r="D220" s="58" t="s">
         <v>605</v>
-      </c>
-      <c r="D220" s="58" t="s">
-        <v>606</v>
       </c>
       <c r="E220" s="56"/>
       <c r="F220" s="59"/>
@@ -13125,13 +13125,13 @@
         <v>109</v>
       </c>
       <c r="B221" s="57" t="s">
+        <v>606</v>
+      </c>
+      <c r="C221" s="57" t="s">
         <v>607</v>
       </c>
-      <c r="C221" s="57" t="s">
+      <c r="D221" s="57" t="s">
         <v>608</v>
-      </c>
-      <c r="D221" s="57" t="s">
-        <v>609</v>
       </c>
       <c r="E221" s="56"/>
       <c r="F221" s="59"/>
@@ -13161,13 +13161,13 @@
         <v>109</v>
       </c>
       <c r="B222" s="57" t="s">
+        <v>609</v>
+      </c>
+      <c r="C222" s="57" t="s">
         <v>610</v>
       </c>
-      <c r="C222" s="57" t="s">
+      <c r="D222" s="57" t="s">
         <v>611</v>
-      </c>
-      <c r="D222" s="57" t="s">
-        <v>612</v>
       </c>
       <c r="E222" s="56"/>
       <c r="F222" s="56"/>
@@ -13197,7 +13197,7 @@
         <v>35</v>
       </c>
       <c r="B223" s="57" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C223" s="56"/>
       <c r="D223" s="56"/>
@@ -13229,7 +13229,7 @@
         <v>35</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C224" s="60"/>
       <c r="D224" s="61"/>
@@ -13252,7 +13252,7 @@
         <v>41</v>
       </c>
       <c r="B225" s="10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C225" s="6"/>
       <c r="D225" s="4"/>
@@ -13264,7 +13264,7 @@
       <c r="J225" s="4"/>
       <c r="K225" s="4"/>
       <c r="L225" s="62" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="M225" s="4"/>
       <c r="N225" s="4"/>
@@ -13286,17 +13286,17 @@
         <v>19</v>
       </c>
       <c r="B226" s="57" t="s">
+        <v>614</v>
+      </c>
+      <c r="C226" s="57" t="s">
         <v>615</v>
       </c>
-      <c r="C226" s="57" t="s">
+      <c r="D226" s="57" t="s">
         <v>616</v>
-      </c>
-      <c r="D226" s="57" t="s">
-        <v>617</v>
       </c>
       <c r="E226" s="56"/>
       <c r="F226" s="34" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="G226" s="56"/>
       <c r="H226" s="56"/>
@@ -13324,13 +13324,13 @@
         <v>109</v>
       </c>
       <c r="B227" s="57" t="s">
+        <v>618</v>
+      </c>
+      <c r="C227" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="C227" s="2" t="s">
+      <c r="D227" s="57" t="s">
         <v>620</v>
-      </c>
-      <c r="D227" s="57" t="s">
-        <v>621</v>
       </c>
       <c r="E227" s="56"/>
       <c r="F227" s="56"/>
@@ -13360,13 +13360,13 @@
         <v>109</v>
       </c>
       <c r="B228" s="57" t="s">
+        <v>621</v>
+      </c>
+      <c r="C228" s="57" t="s">
         <v>622</v>
       </c>
-      <c r="C228" s="57" t="s">
+      <c r="D228" s="57" t="s">
         <v>623</v>
-      </c>
-      <c r="D228" s="57" t="s">
-        <v>624</v>
       </c>
       <c r="E228" s="56"/>
       <c r="F228" s="56"/>
@@ -13396,13 +13396,13 @@
         <v>109</v>
       </c>
       <c r="B229" s="57" t="s">
+        <v>624</v>
+      </c>
+      <c r="C229" s="57" t="s">
         <v>625</v>
       </c>
-      <c r="C229" s="57" t="s">
+      <c r="D229" s="57" t="s">
         <v>626</v>
-      </c>
-      <c r="D229" s="57" t="s">
-        <v>627</v>
       </c>
       <c r="E229" s="56"/>
       <c r="F229" s="56"/>
@@ -13432,13 +13432,13 @@
         <v>109</v>
       </c>
       <c r="B230" s="57" t="s">
+        <v>627</v>
+      </c>
+      <c r="C230" s="57" t="s">
         <v>628</v>
       </c>
-      <c r="C230" s="57" t="s">
+      <c r="D230" s="57" t="s">
         <v>629</v>
-      </c>
-      <c r="D230" s="57" t="s">
-        <v>630</v>
       </c>
       <c r="E230" s="56"/>
       <c r="F230" s="59"/>
@@ -13468,13 +13468,13 @@
         <v>109</v>
       </c>
       <c r="B231" s="57" t="s">
+        <v>630</v>
+      </c>
+      <c r="C231" s="57" t="s">
         <v>631</v>
       </c>
-      <c r="C231" s="57" t="s">
+      <c r="D231" s="57" t="s">
         <v>632</v>
-      </c>
-      <c r="D231" s="57" t="s">
-        <v>633</v>
       </c>
       <c r="E231" s="56"/>
       <c r="F231" s="56"/>
@@ -13504,13 +13504,13 @@
         <v>109</v>
       </c>
       <c r="B232" s="57" t="s">
+        <v>633</v>
+      </c>
+      <c r="C232" s="57" t="s">
         <v>634</v>
       </c>
-      <c r="C232" s="57" t="s">
+      <c r="D232" s="57" t="s">
         <v>635</v>
-      </c>
-      <c r="D232" s="57" t="s">
-        <v>636</v>
       </c>
       <c r="E232" s="56"/>
       <c r="F232" s="56"/>
@@ -13540,13 +13540,13 @@
         <v>109</v>
       </c>
       <c r="B233" s="57" t="s">
+        <v>636</v>
+      </c>
+      <c r="C233" s="57" t="s">
         <v>637</v>
       </c>
-      <c r="C233" s="57" t="s">
+      <c r="D233" s="57" t="s">
         <v>638</v>
-      </c>
-      <c r="D233" s="57" t="s">
-        <v>639</v>
       </c>
       <c r="E233" s="56"/>
       <c r="F233" s="56"/>
@@ -13576,7 +13576,7 @@
         <v>35</v>
       </c>
       <c r="B234" s="57" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C234" s="8"/>
       <c r="D234" s="8"/>
@@ -13608,17 +13608,17 @@
         <v>19</v>
       </c>
       <c r="B235" s="57" t="s">
+        <v>639</v>
+      </c>
+      <c r="C235" s="57" t="s">
         <v>640</v>
       </c>
-      <c r="C235" s="57" t="s">
+      <c r="D235" s="57" t="s">
         <v>641</v>
-      </c>
-      <c r="D235" s="57" t="s">
-        <v>642</v>
       </c>
       <c r="E235" s="56"/>
       <c r="F235" s="34" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="G235" s="56"/>
       <c r="H235" s="56"/>
@@ -13646,19 +13646,19 @@
         <v>135</v>
       </c>
       <c r="B236" s="57" t="s">
+        <v>642</v>
+      </c>
+      <c r="C236" s="57" t="s">
         <v>643</v>
       </c>
-      <c r="C236" s="57" t="s">
+      <c r="D236" s="57" t="s">
         <v>644</v>
-      </c>
-      <c r="D236" s="57" t="s">
-        <v>645</v>
       </c>
       <c r="E236" s="57" t="s">
         <v>139</v>
       </c>
       <c r="F236" s="34" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G236" s="56"/>
       <c r="H236" s="56"/>
@@ -13686,13 +13686,13 @@
         <v>109</v>
       </c>
       <c r="B237" s="57" t="s">
+        <v>645</v>
+      </c>
+      <c r="C237" s="57" t="s">
         <v>646</v>
       </c>
-      <c r="C237" s="57" t="s">
+      <c r="D237" s="57" t="s">
         <v>647</v>
-      </c>
-      <c r="D237" s="57" t="s">
-        <v>648</v>
       </c>
       <c r="E237" s="56"/>
       <c r="F237" s="56"/>
@@ -13722,13 +13722,13 @@
         <v>109</v>
       </c>
       <c r="B238" s="57" t="s">
+        <v>648</v>
+      </c>
+      <c r="C238" s="57" t="s">
         <v>649</v>
       </c>
-      <c r="C238" s="57" t="s">
+      <c r="D238" s="57" t="s">
         <v>650</v>
-      </c>
-      <c r="D238" s="57" t="s">
-        <v>651</v>
       </c>
       <c r="E238" s="57"/>
       <c r="F238" s="57"/>
@@ -13758,13 +13758,13 @@
         <v>109</v>
       </c>
       <c r="B239" s="57" t="s">
+        <v>651</v>
+      </c>
+      <c r="C239" s="57" t="s">
         <v>652</v>
       </c>
-      <c r="C239" s="57" t="s">
+      <c r="D239" s="57" t="s">
         <v>653</v>
-      </c>
-      <c r="D239" s="57" t="s">
-        <v>654</v>
       </c>
       <c r="E239" s="56"/>
       <c r="F239" s="56"/>
@@ -13794,13 +13794,13 @@
         <v>109</v>
       </c>
       <c r="B240" s="57" t="s">
+        <v>654</v>
+      </c>
+      <c r="C240" s="57" t="s">
         <v>655</v>
       </c>
-      <c r="C240" s="57" t="s">
+      <c r="D240" s="57" t="s">
         <v>656</v>
-      </c>
-      <c r="D240" s="57" t="s">
-        <v>657</v>
       </c>
       <c r="E240" s="56"/>
       <c r="F240" s="56"/>
@@ -13830,19 +13830,19 @@
         <v>135</v>
       </c>
       <c r="B241" s="57" t="s">
+        <v>657</v>
+      </c>
+      <c r="C241" s="57" t="s">
         <v>658</v>
       </c>
-      <c r="C241" s="57" t="s">
+      <c r="D241" s="57" t="s">
         <v>659</v>
-      </c>
-      <c r="D241" s="57" t="s">
-        <v>660</v>
       </c>
       <c r="E241" s="57" t="s">
         <v>139</v>
       </c>
       <c r="F241" s="57" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="G241" s="56"/>
       <c r="H241" s="56"/>
@@ -13870,17 +13870,17 @@
         <v>109</v>
       </c>
       <c r="B242" s="57" t="s">
+        <v>660</v>
+      </c>
+      <c r="C242" s="57" t="s">
         <v>661</v>
       </c>
-      <c r="C242" s="57" t="s">
+      <c r="D242" s="57" t="s">
         <v>662</v>
-      </c>
-      <c r="D242" s="57" t="s">
-        <v>663</v>
       </c>
       <c r="E242" s="57"/>
       <c r="F242" s="57" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="G242" s="56"/>
       <c r="H242" s="56"/>
@@ -13905,22 +13905,22 @@
     </row>
     <row r="243" spans="1:26" ht="13">
       <c r="A243" s="57" t="s">
+        <v>664</v>
+      </c>
+      <c r="B243" s="57" t="s">
         <v>665</v>
       </c>
-      <c r="B243" s="57" t="s">
+      <c r="C243" s="57" t="s">
         <v>666</v>
       </c>
-      <c r="C243" s="57" t="s">
+      <c r="D243" s="57" t="s">
         <v>667</v>
-      </c>
-      <c r="D243" s="57" t="s">
-        <v>668</v>
       </c>
       <c r="E243" s="57" t="s">
         <v>139</v>
       </c>
       <c r="F243" s="57" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="G243" s="56"/>
       <c r="H243" s="56"/>
@@ -13948,13 +13948,13 @@
         <v>109</v>
       </c>
       <c r="B244" s="57" t="s">
+        <v>669</v>
+      </c>
+      <c r="C244" s="57" t="s">
         <v>670</v>
       </c>
-      <c r="C244" s="57" t="s">
+      <c r="D244" s="57" t="s">
         <v>671</v>
-      </c>
-      <c r="D244" s="57" t="s">
-        <v>672</v>
       </c>
       <c r="E244" s="56"/>
       <c r="F244" s="59"/>
@@ -13984,13 +13984,13 @@
         <v>109</v>
       </c>
       <c r="B245" s="57" t="s">
+        <v>672</v>
+      </c>
+      <c r="C245" s="57" t="s">
         <v>673</v>
       </c>
-      <c r="C245" s="57" t="s">
+      <c r="D245" s="57" t="s">
         <v>674</v>
-      </c>
-      <c r="D245" s="57" t="s">
-        <v>675</v>
       </c>
       <c r="E245" s="56"/>
       <c r="F245" s="59"/>
@@ -14020,17 +14020,17 @@
         <v>109</v>
       </c>
       <c r="B246" s="57" t="s">
+        <v>675</v>
+      </c>
+      <c r="C246" s="57" t="s">
         <v>676</v>
       </c>
-      <c r="C246" s="57" t="s">
-        <v>677</v>
-      </c>
       <c r="D246" s="57" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E246" s="56"/>
       <c r="F246" s="69" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="G246" s="56"/>
       <c r="H246" s="56"/>
@@ -14058,7 +14058,7 @@
         <v>35</v>
       </c>
       <c r="B247" s="57" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C247" s="56"/>
       <c r="D247" s="56"/>
@@ -14090,17 +14090,17 @@
         <v>19</v>
       </c>
       <c r="B248" s="57" t="s">
+        <v>677</v>
+      </c>
+      <c r="C248" s="57" t="s">
         <v>678</v>
       </c>
-      <c r="C248" s="57" t="s">
+      <c r="D248" s="57" t="s">
         <v>679</v>
-      </c>
-      <c r="D248" s="57" t="s">
-        <v>680</v>
       </c>
       <c r="E248" s="56"/>
       <c r="F248" s="34" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="G248" s="56"/>
       <c r="H248" s="56"/>
@@ -14128,13 +14128,13 @@
         <v>109</v>
       </c>
       <c r="B249" s="57" t="s">
+        <v>680</v>
+      </c>
+      <c r="C249" s="57" t="s">
         <v>681</v>
       </c>
-      <c r="C249" s="57" t="s">
+      <c r="D249" s="57" t="s">
         <v>682</v>
-      </c>
-      <c r="D249" s="57" t="s">
-        <v>683</v>
       </c>
       <c r="E249" s="57"/>
       <c r="F249" s="57"/>
@@ -14164,7 +14164,7 @@
         <v>19</v>
       </c>
       <c r="B250" s="57" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C250" s="57" t="s">
         <v>21</v>
@@ -14200,13 +14200,13 @@
         <v>135</v>
       </c>
       <c r="B251" s="57" t="s">
+        <v>684</v>
+      </c>
+      <c r="C251" s="57" t="s">
         <v>685</v>
       </c>
-      <c r="C251" s="57" t="s">
+      <c r="D251" s="57" t="s">
         <v>686</v>
-      </c>
-      <c r="D251" s="57" t="s">
-        <v>687</v>
       </c>
       <c r="E251" s="57" t="s">
         <v>139</v>
@@ -14238,17 +14238,17 @@
         <v>109</v>
       </c>
       <c r="B252" s="57" t="s">
+        <v>687</v>
+      </c>
+      <c r="C252" s="57" t="s">
         <v>688</v>
       </c>
-      <c r="C252" s="57" t="s">
+      <c r="D252" s="57" t="s">
         <v>689</v>
-      </c>
-      <c r="D252" s="57" t="s">
-        <v>690</v>
       </c>
       <c r="E252" s="56"/>
       <c r="F252" s="57" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="G252" s="56"/>
       <c r="H252" s="56"/>
@@ -14276,7 +14276,7 @@
         <v>35</v>
       </c>
       <c r="B253" s="57" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C253" s="56"/>
       <c r="D253" s="56"/>
@@ -14308,7 +14308,7 @@
         <v>35</v>
       </c>
       <c r="B254" s="57" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C254" s="56"/>
       <c r="D254" s="56"/>
@@ -14340,17 +14340,17 @@
         <v>19</v>
       </c>
       <c r="B255" s="57" t="s">
+        <v>691</v>
+      </c>
+      <c r="C255" s="57" t="s">
         <v>692</v>
       </c>
-      <c r="C255" s="57" t="s">
+      <c r="D255" s="57" t="s">
         <v>693</v>
-      </c>
-      <c r="D255" s="57" t="s">
-        <v>694</v>
       </c>
       <c r="E255" s="56"/>
       <c r="F255" s="13" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="G255" s="57" t="s">
         <v>164</v>
@@ -14380,13 +14380,13 @@
         <v>109</v>
       </c>
       <c r="B256" s="57" t="s">
+        <v>695</v>
+      </c>
+      <c r="C256" s="57" t="s">
         <v>696</v>
       </c>
-      <c r="C256" s="57" t="s">
+      <c r="D256" s="2" t="s">
         <v>697</v>
-      </c>
-      <c r="D256" s="2" t="s">
-        <v>698</v>
       </c>
       <c r="E256" s="56"/>
       <c r="F256" s="34"/>
@@ -14416,7 +14416,7 @@
         <v>35</v>
       </c>
       <c r="B257" s="57" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="C257" s="57"/>
       <c r="D257" s="57"/>
@@ -14448,17 +14448,17 @@
         <v>19</v>
       </c>
       <c r="B258" s="57" t="s">
+        <v>699</v>
+      </c>
+      <c r="C258" s="57" t="s">
         <v>700</v>
       </c>
-      <c r="C258" s="57" t="s">
+      <c r="D258" s="57" t="s">
         <v>701</v>
-      </c>
-      <c r="D258" s="57" t="s">
-        <v>702</v>
       </c>
       <c r="E258" s="56"/>
       <c r="F258" s="34" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="G258" s="56"/>
       <c r="H258" s="56"/>
@@ -14486,13 +14486,13 @@
         <v>135</v>
       </c>
       <c r="B259" s="57" t="s">
+        <v>703</v>
+      </c>
+      <c r="C259" s="57" t="s">
         <v>704</v>
       </c>
-      <c r="C259" s="57" t="s">
+      <c r="D259" s="57" t="s">
         <v>705</v>
-      </c>
-      <c r="D259" s="57" t="s">
-        <v>706</v>
       </c>
       <c r="E259" s="57" t="s">
         <v>139</v>
@@ -14521,22 +14521,22 @@
     </row>
     <row r="260" spans="1:26" ht="13">
       <c r="A260" s="57" t="s">
+        <v>706</v>
+      </c>
+      <c r="B260" s="57" t="s">
         <v>707</v>
       </c>
-      <c r="B260" s="57" t="s">
+      <c r="C260" s="57" t="s">
         <v>708</v>
       </c>
-      <c r="C260" s="57" t="s">
+      <c r="D260" s="57" t="s">
         <v>709</v>
-      </c>
-      <c r="D260" s="57" t="s">
-        <v>710</v>
       </c>
       <c r="E260" s="57" t="s">
         <v>139</v>
       </c>
       <c r="F260" s="57" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="G260" s="56"/>
       <c r="H260" s="56"/>
@@ -14561,22 +14561,22 @@
     </row>
     <row r="261" spans="1:26" ht="13">
       <c r="A261" s="57" t="s">
+        <v>711</v>
+      </c>
+      <c r="B261" s="57" t="s">
         <v>712</v>
       </c>
-      <c r="B261" s="57" t="s">
+      <c r="C261" s="57" t="s">
         <v>713</v>
       </c>
-      <c r="C261" s="57" t="s">
+      <c r="D261" s="57" t="s">
         <v>714</v>
-      </c>
-      <c r="D261" s="57" t="s">
-        <v>715</v>
       </c>
       <c r="E261" s="57" t="s">
         <v>139</v>
       </c>
       <c r="F261" s="57" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="G261" s="56"/>
       <c r="H261" s="56"/>
@@ -14585,7 +14585,7 @@
       <c r="K261" s="56"/>
       <c r="L261" s="56"/>
       <c r="M261" s="2" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="N261" s="56"/>
       <c r="O261" s="56"/>
@@ -14606,7 +14606,7 @@
         <v>19</v>
       </c>
       <c r="B262" s="57" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C262" s="57" t="s">
         <v>21</v>
@@ -14641,22 +14641,22 @@
     </row>
     <row r="263" spans="1:26" ht="13">
       <c r="A263" s="57" t="s">
+        <v>718</v>
+      </c>
+      <c r="B263" s="57" t="s">
         <v>719</v>
       </c>
-      <c r="B263" s="57" t="s">
+      <c r="C263" s="57" t="s">
         <v>720</v>
       </c>
-      <c r="C263" s="57" t="s">
+      <c r="D263" s="57" t="s">
         <v>721</v>
-      </c>
-      <c r="D263" s="57" t="s">
-        <v>722</v>
       </c>
       <c r="E263" s="57" t="s">
         <v>254</v>
       </c>
       <c r="F263" s="57" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="G263" s="56"/>
       <c r="H263" s="56"/>
@@ -14665,7 +14665,7 @@
       <c r="K263" s="56"/>
       <c r="L263" s="56"/>
       <c r="M263" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="N263" s="56"/>
       <c r="O263" s="56"/>
@@ -14683,22 +14683,22 @@
     </row>
     <row r="264" spans="1:26" ht="13">
       <c r="A264" s="57" t="s">
+        <v>724</v>
+      </c>
+      <c r="B264" s="57" t="s">
         <v>725</v>
       </c>
-      <c r="B264" s="57" t="s">
+      <c r="C264" s="57" t="s">
         <v>726</v>
       </c>
-      <c r="C264" s="57" t="s">
+      <c r="D264" s="57" t="s">
         <v>727</v>
-      </c>
-      <c r="D264" s="57" t="s">
-        <v>728</v>
       </c>
       <c r="E264" s="57" t="s">
         <v>139</v>
       </c>
       <c r="F264" s="57" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="G264" s="56"/>
       <c r="H264" s="56"/>
@@ -14726,7 +14726,7 @@
         <v>35</v>
       </c>
       <c r="B265" s="57" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C265" s="57"/>
       <c r="D265" s="56"/>
@@ -14755,22 +14755,22 @@
     </row>
     <row r="266" spans="1:26" ht="13">
       <c r="A266" s="57" t="s">
+        <v>729</v>
+      </c>
+      <c r="B266" s="57" t="s">
         <v>730</v>
       </c>
-      <c r="B266" s="57" t="s">
+      <c r="C266" s="57" t="s">
         <v>731</v>
       </c>
-      <c r="C266" s="57" t="s">
+      <c r="D266" s="57" t="s">
         <v>732</v>
-      </c>
-      <c r="D266" s="57" t="s">
-        <v>733</v>
       </c>
       <c r="E266" s="57" t="s">
         <v>139</v>
       </c>
       <c r="F266" s="57" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="G266" s="56"/>
       <c r="H266" s="56"/>
@@ -14795,22 +14795,22 @@
     </row>
     <row r="267" spans="1:26" ht="13">
       <c r="A267" s="57" t="s">
+        <v>733</v>
+      </c>
+      <c r="B267" s="57" t="s">
         <v>734</v>
       </c>
-      <c r="B267" s="57" t="s">
+      <c r="C267" s="57" t="s">
         <v>735</v>
       </c>
-      <c r="C267" s="57" t="s">
+      <c r="D267" s="7" t="s">
         <v>736</v>
-      </c>
-      <c r="D267" s="7" t="s">
-        <v>737</v>
       </c>
       <c r="E267" s="57" t="s">
         <v>139</v>
       </c>
       <c r="F267" s="57" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G267" s="56"/>
       <c r="H267" s="56"/>
@@ -14835,22 +14835,22 @@
     </row>
     <row r="268" spans="1:26" ht="14.25">
       <c r="A268" s="57" t="s">
+        <v>738</v>
+      </c>
+      <c r="B268" s="57" t="s">
         <v>739</v>
       </c>
-      <c r="B268" s="57" t="s">
+      <c r="C268" s="64" t="s">
         <v>740</v>
       </c>
-      <c r="C268" s="64" t="s">
+      <c r="D268" s="57" t="s">
         <v>741</v>
-      </c>
-      <c r="D268" s="57" t="s">
-        <v>742</v>
       </c>
       <c r="E268" s="57" t="s">
         <v>139</v>
       </c>
       <c r="F268" s="13" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="G268" s="56"/>
       <c r="H268" s="56"/>
@@ -14875,22 +14875,22 @@
     </row>
     <row r="269" spans="1:26" ht="13">
       <c r="A269" s="57" t="s">
+        <v>743</v>
+      </c>
+      <c r="B269" s="57" t="s">
         <v>744</v>
       </c>
-      <c r="B269" s="57" t="s">
+      <c r="C269" s="57" t="s">
         <v>745</v>
       </c>
-      <c r="C269" s="57" t="s">
+      <c r="D269" s="57" t="s">
         <v>746</v>
-      </c>
-      <c r="D269" s="57" t="s">
-        <v>747</v>
       </c>
       <c r="E269" s="57" t="s">
         <v>139</v>
       </c>
       <c r="F269" s="57" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="G269" s="56"/>
       <c r="H269" s="56"/>
@@ -14918,19 +14918,19 @@
         <v>135</v>
       </c>
       <c r="B270" s="57" t="s">
+        <v>748</v>
+      </c>
+      <c r="C270" s="57" t="s">
         <v>749</v>
       </c>
-      <c r="C270" s="57" t="s">
+      <c r="D270" s="57" t="s">
         <v>750</v>
-      </c>
-      <c r="D270" s="57" t="s">
-        <v>751</v>
       </c>
       <c r="E270" s="57" t="s">
         <v>139</v>
       </c>
       <c r="F270" s="57" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="G270" s="56"/>
       <c r="H270" s="56"/>
@@ -14958,30 +14958,30 @@
         <v>236</v>
       </c>
       <c r="B271" s="57" t="s">
+        <v>751</v>
+      </c>
+      <c r="C271" s="57" t="s">
         <v>752</v>
       </c>
-      <c r="C271" s="57" t="s">
+      <c r="D271" s="57" t="s">
         <v>753</v>
-      </c>
-      <c r="D271" s="57" t="s">
-        <v>754</v>
       </c>
       <c r="E271" s="57" t="s">
         <v>139</v>
       </c>
       <c r="F271" s="57" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="G271" s="56"/>
       <c r="H271" s="56"/>
       <c r="I271" s="57" t="s">
+        <v>755</v>
+      </c>
+      <c r="J271" s="57" t="s">
         <v>756</v>
       </c>
-      <c r="J271" s="57" t="s">
+      <c r="K271" s="57" t="s">
         <v>757</v>
-      </c>
-      <c r="K271" s="57" t="s">
-        <v>758</v>
       </c>
       <c r="L271" s="56"/>
       <c r="M271" s="56"/>
@@ -15001,22 +15001,22 @@
     </row>
     <row r="272" spans="1:26" ht="13">
       <c r="A272" s="57" t="s">
+        <v>758</v>
+      </c>
+      <c r="B272" s="57" t="s">
         <v>759</v>
       </c>
-      <c r="B272" s="57" t="s">
+      <c r="C272" s="57" t="s">
         <v>760</v>
       </c>
-      <c r="C272" s="57" t="s">
+      <c r="D272" s="58" t="s">
         <v>761</v>
-      </c>
-      <c r="D272" s="58" t="s">
-        <v>762</v>
       </c>
       <c r="E272" s="57" t="s">
         <v>139</v>
       </c>
       <c r="F272" s="57" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="G272" s="56"/>
       <c r="H272" s="56"/>
@@ -15041,22 +15041,22 @@
     </row>
     <row r="273" spans="1:26" ht="13">
       <c r="A273" s="57" t="s">
+        <v>762</v>
+      </c>
+      <c r="B273" s="57" t="s">
         <v>763</v>
       </c>
-      <c r="B273" s="57" t="s">
+      <c r="C273" s="57" t="s">
         <v>764</v>
       </c>
-      <c r="C273" s="57" t="s">
+      <c r="D273" s="57" t="s">
         <v>765</v>
-      </c>
-      <c r="D273" s="57" t="s">
-        <v>766</v>
       </c>
       <c r="E273" s="57" t="s">
         <v>139</v>
       </c>
       <c r="F273" s="57" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="G273" s="56"/>
       <c r="H273" s="56"/>
@@ -15084,19 +15084,19 @@
         <v>135</v>
       </c>
       <c r="B274" s="57" t="s">
+        <v>766</v>
+      </c>
+      <c r="C274" s="7" t="s">
         <v>767</v>
       </c>
-      <c r="C274" s="7" t="s">
+      <c r="D274" s="57" t="s">
         <v>768</v>
-      </c>
-      <c r="D274" s="57" t="s">
-        <v>769</v>
       </c>
       <c r="E274" s="57" t="s">
         <v>139</v>
       </c>
       <c r="F274" s="57" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="G274" s="56"/>
       <c r="H274" s="56"/>
@@ -15124,7 +15124,7 @@
         <v>35</v>
       </c>
       <c r="B275" s="57" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C275" s="56"/>
       <c r="D275" s="56"/>
@@ -15156,17 +15156,17 @@
         <v>105</v>
       </c>
       <c r="B276" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="C276" s="65" t="s">
         <v>770</v>
       </c>
-      <c r="C276" s="65" t="s">
+      <c r="D276" s="66" t="s">
         <v>771</v>
-      </c>
-      <c r="D276" s="66" t="s">
-        <v>772</v>
       </c>
       <c r="E276" s="67"/>
       <c r="F276" s="68" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="277" spans="1:26" ht="13">
@@ -15174,13 +15174,13 @@
         <v>135</v>
       </c>
       <c r="B277" s="7" t="s">
+        <v>773</v>
+      </c>
+      <c r="C277" s="7" t="s">
         <v>774</v>
       </c>
-      <c r="C277" s="7" t="s">
+      <c r="D277" s="7" t="s">
         <v>775</v>
-      </c>
-      <c r="D277" s="7" t="s">
-        <v>776</v>
       </c>
       <c r="E277" s="7" t="s">
         <v>139</v>
@@ -15209,22 +15209,22 @@
     </row>
     <row r="278" spans="1:26" ht="13">
       <c r="A278" s="7" t="s">
+        <v>776</v>
+      </c>
+      <c r="B278" s="7" t="s">
         <v>777</v>
       </c>
-      <c r="B278" s="7" t="s">
+      <c r="C278" s="70" t="s">
         <v>778</v>
       </c>
-      <c r="C278" s="70" t="s">
+      <c r="D278" s="7" t="s">
         <v>779</v>
-      </c>
-      <c r="D278" s="7" t="s">
-        <v>780</v>
       </c>
       <c r="E278" s="7" t="s">
         <v>139</v>
       </c>
       <c r="F278" s="7" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="G278" s="69"/>
       <c r="H278" s="9"/>
@@ -15252,7 +15252,7 @@
         <v>19</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C279" s="71" t="s">
         <v>21</v>
@@ -15265,42 +15265,42 @@
     </row>
     <row r="280" spans="1:26" ht="13">
       <c r="A280" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="B280" s="2" t="s">
         <v>783</v>
       </c>
-      <c r="B280" s="2" t="s">
+      <c r="C280" s="71" t="s">
         <v>784</v>
       </c>
-      <c r="C280" s="71" t="s">
+      <c r="D280" s="2" t="s">
         <v>785</v>
-      </c>
-      <c r="D280" s="2" t="s">
-        <v>786</v>
       </c>
       <c r="E280" s="2" t="s">
         <v>139</v>
       </c>
       <c r="F280" s="72" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="281" spans="1:26" ht="13">
       <c r="A281" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C281" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="D281" s="2" t="s">
         <v>727</v>
-      </c>
-      <c r="D281" s="2" t="s">
-        <v>728</v>
       </c>
       <c r="E281" s="2" t="s">
         <v>139</v>
       </c>
       <c r="F281" s="72" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="282" spans="1:26" ht="13">
@@ -15308,7 +15308,7 @@
         <v>35</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C282" s="73"/>
       <c r="E282" s="2"/>
@@ -15319,7 +15319,7 @@
         <v>19</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C283" s="73" t="s">
         <v>21</v>
@@ -15332,42 +15332,42 @@
     </row>
     <row r="284" spans="1:26" ht="13">
       <c r="A284" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="B284" s="2" t="s">
         <v>790</v>
       </c>
-      <c r="B284" s="2" t="s">
+      <c r="C284" s="71" t="s">
         <v>791</v>
       </c>
-      <c r="C284" s="71" t="s">
+      <c r="D284" s="2" t="s">
         <v>792</v>
-      </c>
-      <c r="D284" s="2" t="s">
-        <v>793</v>
       </c>
       <c r="E284" s="2" t="s">
         <v>139</v>
       </c>
       <c r="F284" s="72" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="285" spans="1:26" ht="13">
       <c r="A285" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="C285" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="D285" s="2" t="s">
         <v>727</v>
-      </c>
-      <c r="D285" s="2" t="s">
-        <v>728</v>
       </c>
       <c r="E285" s="2" t="s">
         <v>139</v>
       </c>
       <c r="F285" s="72" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="286" spans="1:26" ht="13">
@@ -15375,7 +15375,7 @@
         <v>35</v>
       </c>
       <c r="B286" s="10" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C286" s="74"/>
       <c r="D286" s="75"/>
@@ -15407,7 +15407,7 @@
         <v>19</v>
       </c>
       <c r="B287" s="10" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="C287" s="74" t="s">
         <v>21</v>
@@ -15440,22 +15440,22 @@
     </row>
     <row r="288" spans="1:26" ht="13">
       <c r="A288" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="B288" s="2" t="s">
         <v>797</v>
       </c>
-      <c r="B288" s="2" t="s">
+      <c r="C288" s="2" t="s">
         <v>798</v>
       </c>
-      <c r="C288" s="2" t="s">
+      <c r="D288" s="2" t="s">
         <v>799</v>
-      </c>
-      <c r="D288" s="2" t="s">
-        <v>800</v>
       </c>
       <c r="E288" s="2" t="s">
         <v>139</v>
       </c>
       <c r="F288" s="72" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="289" spans="1:26" ht="13">
@@ -15463,7 +15463,7 @@
         <v>35</v>
       </c>
       <c r="B289" s="10" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="C289" s="74"/>
       <c r="D289" s="75"/>
@@ -15495,7 +15495,7 @@
         <v>19</v>
       </c>
       <c r="B290" s="10" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="C290" s="74" t="s">
         <v>21</v>
@@ -15531,19 +15531,19 @@
         <v>174</v>
       </c>
       <c r="B291" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="C291" s="2" t="s">
         <v>802</v>
       </c>
-      <c r="C291" s="2" t="s">
+      <c r="D291" s="2" t="s">
         <v>803</v>
-      </c>
-      <c r="D291" s="2" t="s">
-        <v>804</v>
       </c>
       <c r="E291" s="2" t="s">
         <v>139</v>
       </c>
       <c r="F291" s="72" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="292" spans="1:26" ht="13">
@@ -15551,7 +15551,7 @@
         <v>35</v>
       </c>
       <c r="B292" s="10" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="C292" s="2"/>
       <c r="E292" s="2"/>
@@ -15562,7 +15562,7 @@
         <v>19</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="C293" s="2" t="s">
         <v>21</v>
@@ -15580,42 +15580,42 @@
         <v>236</v>
       </c>
       <c r="B294" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="C294" s="2" t="s">
         <v>807</v>
       </c>
-      <c r="C294" s="2" t="s">
+      <c r="D294" s="2" t="s">
         <v>808</v>
       </c>
-      <c r="D294" s="2" t="s">
+      <c r="F294" s="72" t="s">
+        <v>804</v>
+      </c>
+      <c r="I294" s="2" t="s">
         <v>809</v>
       </c>
-      <c r="F294" s="72" t="s">
-        <v>805</v>
-      </c>
-      <c r="I294" s="2" t="s">
+      <c r="J294" s="2" t="s">
         <v>810</v>
-      </c>
-      <c r="J294" s="2" t="s">
-        <v>811</v>
       </c>
     </row>
     <row r="295" spans="1:26" ht="13">
       <c r="A295" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="B295" s="2" t="s">
         <v>812</v>
       </c>
-      <c r="B295" s="2" t="s">
+      <c r="C295" s="2" t="s">
         <v>813</v>
       </c>
-      <c r="C295" s="2" t="s">
+      <c r="D295" s="2" t="s">
         <v>814</v>
-      </c>
-      <c r="D295" s="2" t="s">
-        <v>815</v>
       </c>
       <c r="E295" s="2" t="s">
         <v>139</v>
       </c>
       <c r="F295" s="72" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="296" spans="1:26" ht="13">
@@ -15623,7 +15623,7 @@
         <v>35</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="C296" s="2"/>
       <c r="E296" s="2"/>
@@ -15635,7 +15635,7 @@
         <v>19</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C297" s="2" t="s">
         <v>21</v>
@@ -15651,19 +15651,19 @@
         <v>174</v>
       </c>
       <c r="B298" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="C298" s="2" t="s">
         <v>817</v>
       </c>
-      <c r="C298" s="2" t="s">
+      <c r="D298" s="2" t="s">
         <v>818</v>
-      </c>
-      <c r="D298" s="2" t="s">
-        <v>819</v>
       </c>
       <c r="E298" s="2" t="s">
         <v>139</v>
       </c>
       <c r="F298" s="72" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="299" spans="1:26" ht="13">
@@ -15671,22 +15671,22 @@
         <v>236</v>
       </c>
       <c r="B299" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="C299" s="2" t="s">
         <v>820</v>
       </c>
-      <c r="C299" s="2" t="s">
+      <c r="D299" s="2" t="s">
         <v>821</v>
       </c>
-      <c r="D299" s="2" t="s">
+      <c r="F299" s="72" t="s">
         <v>822</v>
       </c>
-      <c r="F299" s="72" t="s">
+      <c r="I299" s="2" t="s">
         <v>823</v>
       </c>
-      <c r="I299" s="2" t="s">
+      <c r="J299" s="2" t="s">
         <v>824</v>
-      </c>
-      <c r="J299" s="2" t="s">
-        <v>825</v>
       </c>
     </row>
     <row r="300" spans="1:26" ht="13">
@@ -15694,7 +15694,7 @@
         <v>35</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="301" spans="1:26" ht="13">
@@ -15702,7 +15702,7 @@
         <v>35</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="302" spans="1:26" ht="13">
@@ -15710,16 +15710,16 @@
         <v>19</v>
       </c>
       <c r="B302" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="C302" s="2" t="s">
         <v>826</v>
       </c>
-      <c r="C302" s="2" t="s">
+      <c r="D302" s="2" t="s">
         <v>827</v>
       </c>
-      <c r="D302" s="2" t="s">
+      <c r="F302" s="2" t="s">
         <v>828</v>
-      </c>
-      <c r="F302" s="2" t="s">
-        <v>829</v>
       </c>
       <c r="G302" s="2" t="s">
         <v>117</v>
@@ -15730,13 +15730,13 @@
         <v>109</v>
       </c>
       <c r="B303" s="46" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="C303" s="88" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="D303" s="88" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
       <c r="F303" s="46"/>
       <c r="G303" s="46"/>
@@ -15746,16 +15746,16 @@
         <v>109</v>
       </c>
       <c r="B304" s="46" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C304" s="88" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D304" s="46" t="s">
+        <v>1387</v>
+      </c>
+      <c r="F304" s="46" t="s">
         <v>1345</v>
-      </c>
-      <c r="C304" s="88" t="s">
-        <v>1346</v>
-      </c>
-      <c r="D304" s="46" t="s">
-        <v>1389</v>
-      </c>
-      <c r="F304" s="46" t="s">
-        <v>1347</v>
       </c>
       <c r="G304" s="46"/>
     </row>
@@ -15764,16 +15764,16 @@
         <v>109</v>
       </c>
       <c r="B305" s="46" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="C305" s="88" t="s">
+        <v>1346</v>
+      </c>
+      <c r="D305" s="101" t="s">
+        <v>1388</v>
+      </c>
+      <c r="F305" s="46" t="s">
         <v>1348</v>
-      </c>
-      <c r="D305" s="101" t="s">
-        <v>1390</v>
-      </c>
-      <c r="F305" s="46" t="s">
-        <v>1350</v>
       </c>
       <c r="G305" s="46"/>
     </row>
@@ -15782,16 +15782,16 @@
         <v>109</v>
       </c>
       <c r="B306" s="46" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="C306" s="88" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="D306" s="101" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="F306" s="46" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="G306" s="46"/>
     </row>
@@ -15800,16 +15800,16 @@
         <v>109</v>
       </c>
       <c r="B307" s="46" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="C307" s="46" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="D307" s="46" t="s">
-        <v>1419</v>
+        <v>1416</v>
       </c>
       <c r="F307" s="88" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="G307" s="46"/>
       <c r="L307" s="101"/>
@@ -15819,16 +15819,16 @@
         <v>109</v>
       </c>
       <c r="B308" s="46" t="s">
-        <v>1420</v>
+        <v>1417</v>
       </c>
       <c r="C308" s="46" t="s">
+        <v>1276</v>
+      </c>
+      <c r="D308" s="46" t="s">
         <v>1277</v>
       </c>
-      <c r="D308" s="46" t="s">
-        <v>1278</v>
-      </c>
       <c r="F308" s="88" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="G308" s="46"/>
       <c r="L308" s="101"/>
@@ -15838,16 +15838,16 @@
         <v>109</v>
       </c>
       <c r="B309" s="46" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
       <c r="C309" s="46" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D309" s="46" t="s">
         <v>1280</v>
       </c>
-      <c r="D309" s="46" t="s">
-        <v>1281</v>
-      </c>
       <c r="F309" s="88" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="G309" s="46"/>
       <c r="L309" s="101"/>
@@ -15857,16 +15857,16 @@
         <v>109</v>
       </c>
       <c r="B310" s="46" t="s">
-        <v>1422</v>
+        <v>1419</v>
       </c>
       <c r="C310" s="46" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D310" s="46" t="s">
         <v>1283</v>
       </c>
-      <c r="D310" s="46" t="s">
-        <v>1284</v>
-      </c>
       <c r="F310" s="88" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="G310" s="46"/>
       <c r="L310" s="101"/>
@@ -15876,16 +15876,16 @@
         <v>109</v>
       </c>
       <c r="B311" s="46" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
       <c r="C311" s="46" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D311" s="46" t="s">
         <v>1286</v>
       </c>
-      <c r="D311" s="46" t="s">
-        <v>1287</v>
-      </c>
       <c r="F311" s="88" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="G311" s="46"/>
       <c r="L311" s="101"/>
@@ -15895,16 +15895,16 @@
         <v>109</v>
       </c>
       <c r="B312" s="46" t="s">
-        <v>1424</v>
+        <v>1421</v>
       </c>
       <c r="C312" s="46" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="D312" s="46" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F312" s="88" t="s">
-        <v>1418</v>
+        <v>1434</v>
       </c>
       <c r="G312" s="46"/>
       <c r="L312" s="101"/>
@@ -15914,16 +15914,16 @@
         <v>109</v>
       </c>
       <c r="B313" s="46" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="C313" s="46" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="D313" s="46" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="F313" s="88" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
       <c r="G313" s="46"/>
       <c r="L313" s="101"/>
@@ -15933,13 +15933,13 @@
         <v>109</v>
       </c>
       <c r="B314" s="46" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="C314" s="88" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="D314" s="101" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="F314" s="46" t="s">
         <v>255</v>
@@ -15951,16 +15951,16 @@
         <v>109</v>
       </c>
       <c r="B315" s="46" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C315" s="88" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D315" s="101" t="s">
+        <v>1391</v>
+      </c>
+      <c r="F315" s="46" t="s">
         <v>1356</v>
-      </c>
-      <c r="C315" s="88" t="s">
-        <v>1357</v>
-      </c>
-      <c r="D315" s="101" t="s">
-        <v>1393</v>
-      </c>
-      <c r="F315" s="46" t="s">
-        <v>1358</v>
       </c>
       <c r="G315" s="46"/>
     </row>
@@ -15969,16 +15969,16 @@
         <v>109</v>
       </c>
       <c r="B316" s="46" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="C316" s="88" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="D316" s="101" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="F316" s="46" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="G316" s="46"/>
     </row>
@@ -15987,16 +15987,16 @@
         <v>109</v>
       </c>
       <c r="B317" s="88" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="C317" s="88" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="D317" s="101" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="F317" s="46" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="G317" s="46"/>
     </row>
@@ -16005,16 +16005,16 @@
         <v>109</v>
       </c>
       <c r="B318" s="46" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C318" s="46" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D318" s="46" t="s">
         <v>1293</v>
       </c>
-      <c r="C318" s="46" t="s">
-        <v>1294</v>
-      </c>
-      <c r="D318" s="46" t="s">
-        <v>1295</v>
-      </c>
       <c r="F318" s="46" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
       <c r="G318" s="46"/>
     </row>
@@ -16023,16 +16023,16 @@
         <v>109</v>
       </c>
       <c r="B319" s="46" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C319" s="46" t="s">
+        <v>1295</v>
+      </c>
+      <c r="D319" s="46" t="s">
         <v>1296</v>
       </c>
-      <c r="C319" s="46" t="s">
-        <v>1297</v>
-      </c>
-      <c r="D319" s="46" t="s">
-        <v>1298</v>
-      </c>
       <c r="F319" s="46" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
       <c r="G319" s="46"/>
     </row>
@@ -16041,16 +16041,16 @@
         <v>109</v>
       </c>
       <c r="B320" s="46" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C320" s="46" t="s">
+        <v>1298</v>
+      </c>
+      <c r="D320" s="46" t="s">
         <v>1299</v>
       </c>
-      <c r="C320" s="46" t="s">
-        <v>1300</v>
-      </c>
-      <c r="D320" s="46" t="s">
-        <v>1301</v>
-      </c>
       <c r="F320" s="46" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
       <c r="G320" s="46"/>
     </row>
@@ -16059,16 +16059,16 @@
         <v>109</v>
       </c>
       <c r="B321" s="46" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C321" s="46" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D321" s="46" t="s">
         <v>1302</v>
       </c>
-      <c r="C321" s="46" t="s">
-        <v>1303</v>
-      </c>
-      <c r="D321" s="46" t="s">
-        <v>1304</v>
-      </c>
       <c r="F321" s="46" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
       <c r="G321" s="46"/>
     </row>
@@ -16077,16 +16077,16 @@
         <v>109</v>
       </c>
       <c r="B322" s="46" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="C322" s="88" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D322" s="101" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="F322" s="46" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="G322" s="46"/>
     </row>
@@ -16095,16 +16095,16 @@
         <v>109</v>
       </c>
       <c r="B323" s="46" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="C323" s="88" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="D323" s="101" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="F323" s="46" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="G323" s="46"/>
     </row>
@@ -16113,16 +16113,16 @@
         <v>109</v>
       </c>
       <c r="B324" s="46" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="C324" s="88" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="D324" s="101" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="F324" s="46" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="G324" s="46"/>
     </row>
@@ -16131,16 +16131,16 @@
         <v>109</v>
       </c>
       <c r="B325" s="46" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="C325" s="88" t="s">
+        <v>1370</v>
+      </c>
+      <c r="D325" s="101" t="s">
+        <v>1398</v>
+      </c>
+      <c r="F325" s="46" t="s">
         <v>1372</v>
-      </c>
-      <c r="D325" s="101" t="s">
-        <v>1400</v>
-      </c>
-      <c r="F325" s="46" t="s">
-        <v>1374</v>
       </c>
       <c r="G325" s="46"/>
     </row>
@@ -16149,16 +16149,16 @@
         <v>109</v>
       </c>
       <c r="B326" s="46" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="C326" s="88" t="s">
+        <v>1369</v>
+      </c>
+      <c r="D326" s="101" t="s">
+        <v>1399</v>
+      </c>
+      <c r="F326" s="46" t="s">
         <v>1371</v>
-      </c>
-      <c r="D326" s="101" t="s">
-        <v>1401</v>
-      </c>
-      <c r="F326" s="46" t="s">
-        <v>1373</v>
       </c>
       <c r="G326" s="46"/>
     </row>
@@ -16167,17 +16167,17 @@
         <v>109</v>
       </c>
       <c r="B327" s="92" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C327" s="92" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="D327" s="93" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="E327" s="92"/>
       <c r="F327" s="93" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="G327" s="92"/>
       <c r="H327" s="92"/>
@@ -16205,17 +16205,17 @@
         <v>109</v>
       </c>
       <c r="B328" s="92" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="C328" s="92" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="D328" s="93" t="s">
-        <v>1434</v>
+        <v>1431</v>
       </c>
       <c r="E328" s="92"/>
       <c r="F328" s="92" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="G328" s="92"/>
       <c r="H328" s="92"/>
@@ -16243,20 +16243,20 @@
         <v>109</v>
       </c>
       <c r="B329" s="92" t="s">
+        <v>832</v>
+      </c>
+      <c r="C329" s="92" t="s">
         <v>833</v>
       </c>
-      <c r="C329" s="92" t="s">
+      <c r="D329" s="94" t="s">
         <v>834</v>
-      </c>
-      <c r="D329" s="94" t="s">
-        <v>835</v>
       </c>
       <c r="E329" s="92"/>
       <c r="F329" s="95" t="s">
+        <v>835</v>
+      </c>
+      <c r="G329" s="92" t="s">
         <v>836</v>
-      </c>
-      <c r="G329" s="92" t="s">
-        <v>837</v>
       </c>
       <c r="H329" s="92"/>
       <c r="I329" s="92"/>
@@ -16283,20 +16283,20 @@
         <v>109</v>
       </c>
       <c r="B330" s="92" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C330" s="92" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="D330" s="92" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="E330" s="92"/>
       <c r="F330" s="96" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="G330" s="92" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H330" s="92"/>
       <c r="I330" s="92"/>
@@ -16323,20 +16323,20 @@
         <v>109</v>
       </c>
       <c r="B331" s="92" t="s">
+        <v>838</v>
+      </c>
+      <c r="C331" s="92" t="s">
+        <v>1380</v>
+      </c>
+      <c r="D331" s="93" t="s">
         <v>839</v>
-      </c>
-      <c r="C331" s="92" t="s">
-        <v>1382</v>
-      </c>
-      <c r="D331" s="93" t="s">
-        <v>840</v>
       </c>
       <c r="E331" s="92"/>
       <c r="F331" s="92" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="G331" s="92" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H331" s="92"/>
       <c r="I331" s="92"/>
@@ -16363,7 +16363,7 @@
         <v>113</v>
       </c>
       <c r="B332" s="46" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C332" s="46"/>
       <c r="D332" s="46"/>
@@ -16375,7 +16375,7 @@
         <v>41</v>
       </c>
       <c r="B333" s="92" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C333" s="92"/>
       <c r="D333" s="92"/>
@@ -16387,7 +16387,7 @@
       <c r="J333" s="92"/>
       <c r="K333" s="92"/>
       <c r="L333" s="92" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="M333" s="92"/>
       <c r="N333" s="92"/>
@@ -16409,7 +16409,7 @@
         <v>41</v>
       </c>
       <c r="B334" s="92" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="C334" s="92"/>
       <c r="D334" s="92"/>
@@ -16421,7 +16421,7 @@
       <c r="J334" s="92"/>
       <c r="K334" s="92"/>
       <c r="L334" s="92" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="M334" s="92"/>
       <c r="N334" s="92"/>
@@ -16443,7 +16443,7 @@
         <v>41</v>
       </c>
       <c r="B335" s="92" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C335" s="92"/>
       <c r="D335" s="92"/>
@@ -16455,7 +16455,7 @@
       <c r="J335" s="92"/>
       <c r="K335" s="92"/>
       <c r="L335" s="92" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="M335" s="92"/>
       <c r="N335" s="92"/>
@@ -16477,7 +16477,7 @@
         <v>41</v>
       </c>
       <c r="B336" s="92" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="C336" s="92"/>
       <c r="D336" s="92"/>
@@ -16489,7 +16489,7 @@
       <c r="J336" s="92"/>
       <c r="K336" s="92"/>
       <c r="L336" s="92" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="M336" s="92"/>
       <c r="N336" s="92"/>
@@ -16511,7 +16511,7 @@
         <v>41</v>
       </c>
       <c r="B337" s="92" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C337" s="92"/>
       <c r="D337" s="92"/>
@@ -16523,7 +16523,7 @@
       <c r="J337" s="92"/>
       <c r="K337" s="92"/>
       <c r="L337" s="92" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="M337" s="92"/>
       <c r="N337" s="92"/>
@@ -16573,7 +16573,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1" s="76" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B1" s="76" t="s">
         <v>1</v>
@@ -16590,520 +16590,520 @@
     </row>
     <row r="2" spans="1:5" ht="14.75">
       <c r="A2" s="77" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B2" s="77" t="s">
         <v>139</v>
       </c>
       <c r="C2" s="77" t="s">
+        <v>853</v>
+      </c>
+      <c r="D2" s="77" t="s">
         <v>854</v>
-      </c>
-      <c r="D2" s="77" t="s">
-        <v>855</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="14.75">
       <c r="A3" s="77" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B3" s="77" t="s">
+        <v>855</v>
+      </c>
+      <c r="C3" s="77" t="s">
         <v>856</v>
       </c>
-      <c r="C3" s="77" t="s">
+      <c r="D3" s="77" t="s">
         <v>857</v>
-      </c>
-      <c r="D3" s="77" t="s">
-        <v>858</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1">
       <c r="A4" s="45" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B4" s="16" t="s">
+        <v>858</v>
+      </c>
+      <c r="C4" s="16" t="s">
         <v>859</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="D4" s="78" t="s">
         <v>860</v>
-      </c>
-      <c r="D4" s="78" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1">
       <c r="A5" s="45" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B5" s="16" t="s">
+        <v>861</v>
+      </c>
+      <c r="C5" s="16" t="s">
         <v>862</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="D5" s="78" t="s">
         <v>863</v>
-      </c>
-      <c r="D5" s="78" t="s">
-        <v>864</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1">
       <c r="A6" s="45" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B6" s="16" t="s">
+        <v>864</v>
+      </c>
+      <c r="C6" s="16" t="s">
         <v>865</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="D6" s="40" t="s">
         <v>866</v>
-      </c>
-      <c r="D6" s="40" t="s">
-        <v>867</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1">
       <c r="A7" s="45" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B7" s="16" t="s">
+        <v>867</v>
+      </c>
+      <c r="C7" s="16" t="s">
         <v>868</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="D7" s="38" t="s">
         <v>869</v>
-      </c>
-      <c r="D7" s="38" t="s">
-        <v>870</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1">
       <c r="A8" s="45" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B8" s="16" t="s">
+        <v>870</v>
+      </c>
+      <c r="C8" s="16" t="s">
         <v>871</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="D8" s="78" t="s">
         <v>872</v>
-      </c>
-      <c r="D8" s="78" t="s">
-        <v>873</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1">
       <c r="A9" s="45" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B9" s="16" t="s">
+        <v>873</v>
+      </c>
+      <c r="C9" s="16" t="s">
         <v>874</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="D9" s="78" t="s">
         <v>875</v>
-      </c>
-      <c r="D9" s="78" t="s">
-        <v>876</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" customHeight="1">
       <c r="A10" s="45" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B10" s="16" t="s">
+        <v>876</v>
+      </c>
+      <c r="C10" s="16" t="s">
         <v>877</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="D10" s="78" t="s">
         <v>878</v>
-      </c>
-      <c r="D10" s="78" t="s">
-        <v>879</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.75" customHeight="1">
       <c r="A11" s="45" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B11" s="16" t="s">
+        <v>879</v>
+      </c>
+      <c r="C11" s="16" t="s">
         <v>880</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="D11" s="78" t="s">
         <v>881</v>
-      </c>
-      <c r="D11" s="78" t="s">
-        <v>882</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.75" customHeight="1">
       <c r="A12" s="45" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B12" s="16" t="s">
+        <v>882</v>
+      </c>
+      <c r="C12" s="16" t="s">
         <v>883</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="D12" s="78" t="s">
         <v>884</v>
-      </c>
-      <c r="D12" s="78" t="s">
-        <v>885</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.75" customHeight="1">
       <c r="A13" s="45" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B13" s="16" t="s">
+        <v>885</v>
+      </c>
+      <c r="C13" s="60" t="s">
         <v>886</v>
       </c>
-      <c r="C13" s="60" t="s">
+      <c r="D13" s="78" t="s">
         <v>887</v>
-      </c>
-      <c r="D13" s="78" t="s">
-        <v>888</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.75" customHeight="1">
       <c r="A14" s="45" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B14" s="16" t="s">
+        <v>888</v>
+      </c>
+      <c r="C14" s="16" t="s">
         <v>889</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="D14" s="78" t="s">
         <v>890</v>
-      </c>
-      <c r="D14" s="78" t="s">
-        <v>891</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.75" customHeight="1">
       <c r="A15" s="45" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B15" s="16" t="s">
+        <v>891</v>
+      </c>
+      <c r="C15" s="60" t="s">
         <v>892</v>
       </c>
-      <c r="C15" s="60" t="s">
+      <c r="D15" s="78" t="s">
         <v>893</v>
-      </c>
-      <c r="D15" s="78" t="s">
-        <v>894</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.75" customHeight="1">
       <c r="A16" s="45" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B16" s="16" t="s">
+        <v>894</v>
+      </c>
+      <c r="C16" s="16" t="s">
         <v>895</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="D16" s="78" t="s">
         <v>896</v>
-      </c>
-      <c r="D16" s="78" t="s">
-        <v>897</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75" customHeight="1">
       <c r="A17" s="45" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B17" s="5" t="s">
+        <v>897</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>898</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="D17" s="78" t="s">
         <v>899</v>
-      </c>
-      <c r="D17" s="78" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="13">
       <c r="A18" s="16" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B18" s="16" t="s">
+        <v>900</v>
+      </c>
+      <c r="C18" s="16" t="s">
         <v>901</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="D18" s="38" t="s">
         <v>902</v>
-      </c>
-      <c r="D18" s="38" t="s">
-        <v>903</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="13">
       <c r="A19" s="16" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B19" s="16" t="s">
+        <v>903</v>
+      </c>
+      <c r="C19" s="16" t="s">
         <v>904</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="D19" s="38" t="s">
         <v>905</v>
-      </c>
-      <c r="D19" s="38" t="s">
-        <v>906</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="13">
       <c r="A20" s="16" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B20" s="16" t="s">
+        <v>906</v>
+      </c>
+      <c r="C20" s="16" t="s">
         <v>907</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="D20" s="78" t="s">
         <v>908</v>
-      </c>
-      <c r="D20" s="78" t="s">
-        <v>909</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="13">
       <c r="A21" s="16" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B21" s="16" t="s">
+        <v>909</v>
+      </c>
+      <c r="C21" s="16" t="s">
         <v>910</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="D21" s="78" t="s">
         <v>911</v>
-      </c>
-      <c r="D21" s="78" t="s">
-        <v>912</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="13">
       <c r="A22" s="16" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B22" s="16" t="s">
+        <v>912</v>
+      </c>
+      <c r="C22" s="16" t="s">
         <v>913</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="D22" s="78" t="s">
         <v>914</v>
-      </c>
-      <c r="D22" s="78" t="s">
-        <v>915</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="13">
       <c r="A23" s="16" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B23" s="16" t="s">
+        <v>915</v>
+      </c>
+      <c r="C23" s="16" t="s">
         <v>916</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="D23" s="78" t="s">
         <v>917</v>
-      </c>
-      <c r="D23" s="78" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="13">
       <c r="A24" s="16" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B24" s="16" t="s">
+        <v>918</v>
+      </c>
+      <c r="C24" s="16" t="s">
         <v>919</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="D24" s="78" t="s">
         <v>920</v>
-      </c>
-      <c r="D24" s="78" t="s">
-        <v>921</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="13">
       <c r="A25" s="16" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B25" s="16" t="s">
+        <v>921</v>
+      </c>
+      <c r="C25" s="16" t="s">
         <v>922</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="D25" s="78" t="s">
         <v>923</v>
-      </c>
-      <c r="D25" s="78" t="s">
-        <v>924</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="13">
       <c r="A26" s="16" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B26" s="16" t="s">
+        <v>924</v>
+      </c>
+      <c r="C26" s="16" t="s">
         <v>925</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="D26" s="78" t="s">
         <v>926</v>
-      </c>
-      <c r="D26" s="78" t="s">
-        <v>927</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="13">
       <c r="A27" s="16" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B27" s="45" t="s">
+        <v>927</v>
+      </c>
+      <c r="C27" s="38" t="s">
         <v>928</v>
       </c>
-      <c r="C27" s="38" t="s">
+      <c r="D27" s="78" t="s">
         <v>929</v>
-      </c>
-      <c r="D27" s="78" t="s">
-        <v>930</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="13">
       <c r="A28" s="16" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B28" s="45" t="s">
+        <v>930</v>
+      </c>
+      <c r="C28" s="79" t="s">
         <v>931</v>
       </c>
-      <c r="C28" s="79" t="s">
+      <c r="D28" s="80" t="s">
         <v>932</v>
-      </c>
-      <c r="D28" s="80" t="s">
-        <v>933</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="13">
       <c r="A29" s="16" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B29" s="45" t="s">
+        <v>933</v>
+      </c>
+      <c r="C29" s="79" t="s">
         <v>934</v>
       </c>
-      <c r="C29" s="79" t="s">
+      <c r="D29" s="78" t="s">
         <v>935</v>
-      </c>
-      <c r="D29" s="78" t="s">
-        <v>936</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="13">
       <c r="A30" s="16" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B30" s="45" t="s">
+        <v>936</v>
+      </c>
+      <c r="C30" s="45" t="s">
         <v>937</v>
       </c>
-      <c r="C30" s="45" t="s">
+      <c r="D30" s="78" t="s">
         <v>938</v>
-      </c>
-      <c r="D30" s="78" t="s">
-        <v>939</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="13">
       <c r="A31" s="16" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B31" s="45" t="s">
+        <v>939</v>
+      </c>
+      <c r="C31" s="79" t="s">
         <v>940</v>
       </c>
-      <c r="C31" s="79" t="s">
+      <c r="D31" s="80" t="s">
         <v>941</v>
-      </c>
-      <c r="D31" s="80" t="s">
-        <v>942</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="13">
       <c r="A32" s="16" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B32" s="45" t="s">
+        <v>942</v>
+      </c>
+      <c r="C32" s="79" t="s">
         <v>943</v>
       </c>
-      <c r="C32" s="79" t="s">
+      <c r="D32" s="38" t="s">
         <v>944</v>
-      </c>
-      <c r="D32" s="38" t="s">
-        <v>945</v>
       </c>
     </row>
     <row r="33" spans="1:26" ht="13">
       <c r="A33" s="16" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B33" s="45" t="s">
+        <v>945</v>
+      </c>
+      <c r="C33" s="45" t="s">
         <v>946</v>
       </c>
-      <c r="C33" s="45" t="s">
+      <c r="D33" s="78" t="s">
         <v>947</v>
-      </c>
-      <c r="D33" s="78" t="s">
-        <v>948</v>
       </c>
     </row>
     <row r="34" spans="1:26" ht="13">
       <c r="A34" s="16" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B34" s="5" t="s">
+        <v>948</v>
+      </c>
+      <c r="C34" s="5" t="s">
         <v>949</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="D34" s="78" t="s">
         <v>950</v>
-      </c>
-      <c r="D34" s="78" t="s">
-        <v>951</v>
       </c>
     </row>
     <row r="35" spans="1:26" ht="13">
       <c r="A35" s="16" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B35" s="16" t="s">
+        <v>951</v>
+      </c>
+      <c r="C35" s="16" t="s">
         <v>952</v>
       </c>
-      <c r="C35" s="16" t="s">
+      <c r="D35" s="78" t="s">
         <v>953</v>
-      </c>
-      <c r="D35" s="78" t="s">
-        <v>954</v>
       </c>
     </row>
     <row r="36" spans="1:26" ht="13">
       <c r="A36" s="16" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B36" s="16" t="s">
+        <v>954</v>
+      </c>
+      <c r="C36" s="16" t="s">
         <v>955</v>
       </c>
-      <c r="C36" s="16" t="s">
+      <c r="D36" s="38" t="s">
         <v>956</v>
-      </c>
-      <c r="D36" s="38" t="s">
-        <v>957</v>
       </c>
     </row>
     <row r="37" spans="1:26" ht="13">
       <c r="A37" s="16" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B37" s="5" t="s">
+        <v>957</v>
+      </c>
+      <c r="C37" s="5" t="s">
         <v>958</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="D37" s="78" t="s">
         <v>959</v>
-      </c>
-      <c r="D37" s="78" t="s">
-        <v>960</v>
       </c>
     </row>
     <row r="38" spans="1:26" ht="13">
       <c r="A38" s="4" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B38" s="4" t="s">
+        <v>960</v>
+      </c>
+      <c r="C38" s="4" t="s">
         <v>961</v>
       </c>
-      <c r="C38" s="4" t="s">
-        <v>962</v>
-      </c>
       <c r="D38" s="4" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
@@ -17130,16 +17130,16 @@
     </row>
     <row r="39" spans="1:26" ht="13">
       <c r="A39" s="4" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B39" s="4" t="s">
+        <v>962</v>
+      </c>
+      <c r="C39" s="4" t="s">
         <v>963</v>
       </c>
-      <c r="C39" s="4" t="s">
-        <v>964</v>
-      </c>
       <c r="D39" s="4" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
@@ -17166,16 +17166,16 @@
     </row>
     <row r="40" spans="1:26" ht="13">
       <c r="A40" s="4" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B40" s="4" t="s">
+        <v>964</v>
+      </c>
+      <c r="C40" s="4" t="s">
         <v>965</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="D40" s="10" t="s">
         <v>966</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>967</v>
       </c>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
@@ -17202,19 +17202,19 @@
     </row>
     <row r="41" spans="1:26" ht="13">
       <c r="A41" s="4" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B41" s="4" t="s">
+        <v>967</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>968</v>
       </c>
-      <c r="C41" s="4" t="s">
-        <v>969</v>
-      </c>
       <c r="D41" s="4" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
@@ -17240,19 +17240,19 @@
     </row>
     <row r="42" spans="1:26" ht="13">
       <c r="A42" s="4" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B42" s="4" t="s">
+        <v>969</v>
+      </c>
+      <c r="C42" s="4" t="s">
         <v>970</v>
       </c>
-      <c r="C42" s="4" t="s">
-        <v>971</v>
-      </c>
       <c r="D42" s="4" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
@@ -17278,19 +17278,19 @@
     </row>
     <row r="43" spans="1:26" ht="13">
       <c r="A43" s="4" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B43" s="4" t="s">
+        <v>971</v>
+      </c>
+      <c r="C43" s="4" t="s">
         <v>972</v>
       </c>
-      <c r="C43" s="4" t="s">
-        <v>973</v>
-      </c>
       <c r="D43" s="4" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
@@ -17316,19 +17316,19 @@
     </row>
     <row r="44" spans="1:26" ht="13">
       <c r="A44" s="4" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B44" s="4" t="s">
+        <v>973</v>
+      </c>
+      <c r="C44" s="4" t="s">
         <v>974</v>
       </c>
-      <c r="C44" s="4" t="s">
-        <v>975</v>
-      </c>
       <c r="D44" s="4" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="F44" s="4"/>
       <c r="G44" s="4"/>
@@ -17354,19 +17354,19 @@
     </row>
     <row r="45" spans="1:26" ht="13">
       <c r="A45" s="4" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B45" s="4" t="s">
+        <v>975</v>
+      </c>
+      <c r="C45" s="4" t="s">
         <v>976</v>
       </c>
-      <c r="C45" s="4" t="s">
-        <v>977</v>
-      </c>
       <c r="D45" s="4" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
@@ -17392,19 +17392,19 @@
     </row>
     <row r="46" spans="1:26" ht="13">
       <c r="A46" s="4" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B46" s="4" t="s">
+        <v>977</v>
+      </c>
+      <c r="C46" s="4" t="s">
         <v>978</v>
       </c>
-      <c r="C46" s="4" t="s">
-        <v>979</v>
-      </c>
       <c r="D46" s="4" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
@@ -17430,19 +17430,19 @@
     </row>
     <row r="47" spans="1:26" ht="13">
       <c r="A47" s="4" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B47" s="4" t="s">
+        <v>979</v>
+      </c>
+      <c r="C47" s="4" t="s">
         <v>980</v>
       </c>
-      <c r="C47" s="4" t="s">
-        <v>981</v>
-      </c>
       <c r="D47" s="4" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
@@ -17468,19 +17468,19 @@
     </row>
     <row r="48" spans="1:26" ht="13">
       <c r="A48" s="4" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B48" s="4" t="s">
+        <v>981</v>
+      </c>
+      <c r="C48" s="4" t="s">
         <v>982</v>
       </c>
-      <c r="C48" s="4" t="s">
-        <v>983</v>
-      </c>
       <c r="D48" s="4" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
@@ -17506,19 +17506,19 @@
     </row>
     <row r="49" spans="1:26" ht="13">
       <c r="A49" s="4" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B49" s="4" t="s">
+        <v>983</v>
+      </c>
+      <c r="C49" s="4" t="s">
         <v>984</v>
       </c>
-      <c r="C49" s="4" t="s">
-        <v>985</v>
-      </c>
       <c r="D49" s="4" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
@@ -17544,19 +17544,19 @@
     </row>
     <row r="50" spans="1:26" ht="13">
       <c r="A50" s="4" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B50" s="4" t="s">
+        <v>985</v>
+      </c>
+      <c r="C50" s="4" t="s">
         <v>986</v>
       </c>
-      <c r="C50" s="4" t="s">
-        <v>987</v>
-      </c>
       <c r="D50" s="4" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="F50" s="4"/>
       <c r="G50" s="4"/>
@@ -17582,19 +17582,19 @@
     </row>
     <row r="51" spans="1:26" ht="13">
       <c r="A51" s="4" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B51" s="4" t="s">
+        <v>987</v>
+      </c>
+      <c r="C51" s="4" t="s">
         <v>988</v>
       </c>
-      <c r="C51" s="4" t="s">
-        <v>989</v>
-      </c>
       <c r="D51" s="4" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
@@ -17620,20 +17620,20 @@
     </row>
     <row r="52" spans="1:26" ht="13">
       <c r="A52" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B52" s="4" t="str">
         <f t="shared" ref="B52:B115" si="0">LOWER(SUBSTITUTE(C52," ",""))</f>
         <v>chakechakedistricthospital</v>
       </c>
       <c r="C52" s="21" t="s">
+        <v>989</v>
+      </c>
+      <c r="D52" s="14" t="s">
         <v>990</v>
       </c>
-      <c r="D52" s="14" t="s">
-        <v>991</v>
-      </c>
       <c r="E52" s="4" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
@@ -17659,20 +17659,20 @@
     </row>
     <row r="53" spans="1:26" ht="13">
       <c r="A53" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B53" s="4" t="str">
         <f t="shared" si="0"/>
         <v>pujiniphcu+</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
@@ -17698,20 +17698,20 @@
     </row>
     <row r="54" spans="1:26" ht="13">
       <c r="A54" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B54" s="4" t="str">
         <f t="shared" si="0"/>
         <v>tundauwaphcu+</v>
       </c>
       <c r="C54" s="21" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="D54" s="21" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="F54" s="4"/>
       <c r="G54" s="4"/>
@@ -17737,20 +17737,20 @@
     </row>
     <row r="55" spans="1:26" ht="13">
       <c r="A55" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B55" s="4" t="str">
         <f t="shared" si="0"/>
         <v>vitongojiphcc</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
@@ -17776,20 +17776,20 @@
     </row>
     <row r="56" spans="1:26" ht="13">
       <c r="A56" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B56" s="4" t="str">
         <f t="shared" si="0"/>
         <v>weshaphcu+</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
@@ -17815,20 +17815,20 @@
     </row>
     <row r="57" spans="1:26" ht="13">
       <c r="A57" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B57" s="4" t="str">
         <f t="shared" si="0"/>
         <v>kondephcu+</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
@@ -17854,20 +17854,20 @@
     </row>
     <row r="58" spans="1:26" ht="13">
       <c r="A58" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B58" s="4" t="str">
         <f t="shared" si="0"/>
         <v>makangalephcu+</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F58" s="4"/>
       <c r="G58" s="4"/>
@@ -17893,20 +17893,20 @@
     </row>
     <row r="59" spans="1:26" ht="13">
       <c r="A59" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B59" s="4" t="str">
         <f t="shared" si="0"/>
         <v>maziwangombephcu+</v>
       </c>
       <c r="C59" s="21" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="D59" s="21" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F59" s="4"/>
       <c r="G59" s="4"/>
@@ -17932,20 +17932,20 @@
     </row>
     <row r="60" spans="1:26" ht="13">
       <c r="A60" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B60" s="4" t="str">
         <f t="shared" si="0"/>
         <v>micheweniphcc</v>
       </c>
       <c r="C60" s="21" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="D60" s="21" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F60" s="4"/>
       <c r="G60" s="4"/>
@@ -17971,20 +17971,20 @@
     </row>
     <row r="61" spans="1:26" ht="13">
       <c r="A61" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B61" s="4" t="str">
         <f t="shared" si="0"/>
         <v>wingwiphcu+</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F61" s="4"/>
       <c r="G61" s="4"/>
@@ -18010,20 +18010,20 @@
     </row>
     <row r="62" spans="1:26" ht="13">
       <c r="A62" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B62" s="4" t="str">
         <f t="shared" si="0"/>
         <v>kiuyumbuyuniphcu+</v>
       </c>
       <c r="C62" s="21" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="D62" s="21" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F62" s="4"/>
       <c r="G62" s="4"/>
@@ -18049,20 +18049,20 @@
     </row>
     <row r="63" spans="1:26" ht="13">
       <c r="A63" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B63" s="4" t="str">
         <f t="shared" si="0"/>
         <v>bogoaphcu+</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="F63" s="4"/>
       <c r="G63" s="4"/>
@@ -18088,20 +18088,20 @@
     </row>
     <row r="64" spans="1:26" ht="13">
       <c r="A64" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B64" s="4" t="str">
         <f t="shared" si="0"/>
         <v>kengejaphcu+</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="F64" s="4"/>
       <c r="G64" s="4"/>
@@ -18127,20 +18127,20 @@
     </row>
     <row r="65" spans="1:26" ht="13">
       <c r="A65" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B65" s="4" t="str">
         <f t="shared" si="0"/>
         <v>abdallahmzeedistricthospital</v>
       </c>
       <c r="C65" s="21" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D65" s="14" t="s">
         <v>1004</v>
       </c>
-      <c r="D65" s="14" t="s">
-        <v>1005</v>
-      </c>
       <c r="E65" s="4" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="F65" s="4"/>
       <c r="G65" s="4"/>
@@ -18166,20 +18166,20 @@
     </row>
     <row r="66" spans="1:26" ht="13">
       <c r="A66" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B66" s="4" t="str">
         <f t="shared" si="0"/>
         <v>michenzaniphcu+</v>
       </c>
       <c r="C66" s="21" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="D66" s="21" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="F66" s="4"/>
       <c r="G66" s="4"/>
@@ -18205,20 +18205,20 @@
     </row>
     <row r="67" spans="1:26" ht="13">
       <c r="A67" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B67" s="4" t="str">
         <f t="shared" si="0"/>
         <v>fundophcu+</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="F67" s="4"/>
       <c r="G67" s="4"/>
@@ -18244,20 +18244,20 @@
     </row>
     <row r="68" spans="1:26" ht="13">
       <c r="A68" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B68" s="4" t="str">
         <f t="shared" si="0"/>
         <v>kojaniphcu+</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="F68" s="4"/>
       <c r="G68" s="4"/>
@@ -18283,20 +18283,20 @@
     </row>
     <row r="69" spans="1:26" ht="13">
       <c r="A69" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B69" s="4" t="str">
         <f t="shared" si="0"/>
         <v>makongeniphcu+</v>
       </c>
       <c r="C69" s="21" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="D69" s="21" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="F69" s="4"/>
       <c r="G69" s="4"/>
@@ -18322,20 +18322,20 @@
     </row>
     <row r="70" spans="1:26" ht="13">
       <c r="A70" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B70" s="4" t="str">
         <f t="shared" si="0"/>
         <v>wetedistricthospital</v>
       </c>
       <c r="C70" s="21" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D70" s="14" t="s">
         <v>1010</v>
       </c>
-      <c r="D70" s="14" t="s">
-        <v>1011</v>
-      </c>
       <c r="E70" s="4" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="F70" s="4"/>
       <c r="G70" s="4"/>
@@ -18361,20 +18361,20 @@
     </row>
     <row r="71" spans="1:26" ht="13">
       <c r="A71" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B71" s="4" t="str">
         <f t="shared" si="0"/>
         <v>mzambarauniphcu+</v>
       </c>
       <c r="C71" s="21" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="D71" s="21" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="F71" s="4"/>
       <c r="G71" s="4"/>
@@ -18400,20 +18400,20 @@
     </row>
     <row r="72" spans="1:26" ht="13">
       <c r="A72" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B72" s="4" t="str">
         <f t="shared" si="0"/>
         <v>junguniphcu+</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="F72" s="4"/>
       <c r="G72" s="4"/>
@@ -18439,20 +18439,20 @@
     </row>
     <row r="73" spans="1:26" ht="13">
       <c r="A73" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B73" s="4" t="str">
         <f t="shared" si="0"/>
         <v>ukunjwiphcu+</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="F73" s="4"/>
       <c r="G73" s="4"/>
@@ -18478,20 +18478,20 @@
     </row>
     <row r="74" spans="1:26" ht="13">
       <c r="A74" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B74" s="4" t="str">
         <f t="shared" si="0"/>
         <v>uondwephcu+</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="F74" s="4"/>
       <c r="G74" s="4"/>
@@ -18517,20 +18517,20 @@
     </row>
     <row r="75" spans="1:26" ht="13">
       <c r="A75" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B75" s="4" t="str">
         <f t="shared" si="0"/>
         <v>chwakaphcu+</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="F75" s="4"/>
       <c r="G75" s="4"/>
@@ -18556,20 +18556,20 @@
     </row>
     <row r="76" spans="1:26" ht="13">
       <c r="A76" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B76" s="4" t="str">
         <f t="shared" si="0"/>
         <v>mweraphcu+</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="F76" s="4"/>
       <c r="G76" s="4"/>
@@ -18595,20 +18595,20 @@
     </row>
     <row r="77" spans="1:26" ht="13">
       <c r="A77" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B77" s="4" t="str">
         <f t="shared" si="0"/>
         <v>ungujaukuuphcu+</v>
       </c>
       <c r="C77" s="21" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="D77" s="21" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="F77" s="4"/>
       <c r="G77" s="4"/>
@@ -18634,20 +18634,20 @@
     </row>
     <row r="78" spans="1:26" ht="13">
       <c r="A78" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B78" s="4" t="str">
         <f t="shared" si="0"/>
         <v>uziniphcu+</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="F78" s="4"/>
       <c r="G78" s="4"/>
@@ -18673,20 +18673,20 @@
     </row>
     <row r="79" spans="1:26" ht="13">
       <c r="A79" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B79" s="4" t="str">
         <f t="shared" si="0"/>
         <v>uroaphcu+</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="F79" s="4"/>
       <c r="G79" s="4"/>
@@ -18712,20 +18712,20 @@
     </row>
     <row r="80" spans="1:26" ht="13">
       <c r="A80" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B80" s="4" t="str">
         <f t="shared" si="0"/>
         <v>kivungedistricthospital</v>
       </c>
       <c r="C80" s="21" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D80" s="10" t="s">
         <v>1021</v>
       </c>
-      <c r="D80" s="10" t="s">
-        <v>1022</v>
-      </c>
       <c r="E80" s="4" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="F80" s="4"/>
       <c r="G80" s="4"/>
@@ -18751,20 +18751,20 @@
     </row>
     <row r="81" spans="1:26" ht="13">
       <c r="A81" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B81" s="4" t="str">
         <f t="shared" si="0"/>
         <v>matemwephcu+</v>
       </c>
       <c r="C81" s="21" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="D81" s="21" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="F81" s="4"/>
       <c r="G81" s="4"/>
@@ -18790,20 +18790,20 @@
     </row>
     <row r="82" spans="1:26" ht="13">
       <c r="A82" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B82" s="4" t="str">
         <f t="shared" si="0"/>
         <v>nungwiphcu+</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="F82" s="4"/>
       <c r="G82" s="4"/>
@@ -18829,20 +18829,20 @@
     </row>
     <row r="83" spans="1:26" ht="13">
       <c r="A83" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B83" s="4" t="str">
         <f t="shared" si="0"/>
         <v>pwanimchanganiphcu+</v>
       </c>
       <c r="C83" s="21" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="D83" s="21" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="F83" s="4"/>
       <c r="G83" s="4"/>
@@ -18868,20 +18868,20 @@
     </row>
     <row r="84" spans="1:26" ht="13">
       <c r="A84" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B84" s="4" t="str">
         <f t="shared" si="0"/>
         <v>tumbatugomaniphcu+</v>
       </c>
       <c r="C84" s="21" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="D84" s="21" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="F84" s="4"/>
       <c r="G84" s="4"/>
@@ -18907,20 +18907,20 @@
     </row>
     <row r="85" spans="1:26" ht="13">
       <c r="A85" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B85" s="4" t="str">
         <f t="shared" si="0"/>
         <v>kendwaphcu+</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="F85" s="4"/>
       <c r="G85" s="4"/>
@@ -18946,20 +18946,20 @@
     </row>
     <row r="86" spans="1:26" ht="13">
       <c r="A86" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B86" s="4" t="str">
         <f t="shared" si="0"/>
         <v>bumbwinimisufiniphcu+</v>
       </c>
       <c r="C86" s="21" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="D86" s="21" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="F86" s="4"/>
       <c r="G86" s="4"/>
@@ -18985,20 +18985,20 @@
     </row>
     <row r="87" spans="1:26" ht="13">
       <c r="A87" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B87" s="4" t="str">
         <f t="shared" si="0"/>
         <v>dongevijibweniphcu+</v>
       </c>
       <c r="C87" s="21" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="D87" s="21" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="F87" s="4"/>
       <c r="G87" s="4"/>
@@ -19024,20 +19024,20 @@
     </row>
     <row r="88" spans="1:26" ht="13">
       <c r="A88" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B88" s="4" t="str">
         <f t="shared" si="0"/>
         <v>kiongwephcu</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="F88" s="4"/>
       <c r="G88" s="4"/>
@@ -19063,20 +19063,20 @@
     </row>
     <row r="89" spans="1:26" ht="13">
       <c r="A89" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B89" s="4" t="str">
         <f t="shared" si="0"/>
         <v>kitopephcu</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="F89" s="4"/>
       <c r="G89" s="4"/>
@@ -19102,20 +19102,20 @@
     </row>
     <row r="90" spans="1:26" ht="13">
       <c r="A90" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B90" s="4" t="str">
         <f t="shared" si="0"/>
         <v>mahondaphcu+</v>
       </c>
       <c r="C90" s="21" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="D90" s="21" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="F90" s="4"/>
       <c r="G90" s="4"/>
@@ -19141,20 +19141,20 @@
     </row>
     <row r="91" spans="1:26" ht="13">
       <c r="A91" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B91" s="4" t="str">
         <f t="shared" si="0"/>
         <v>jambianiphcu+</v>
       </c>
       <c r="C91" s="21" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="D91" s="21" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="F91" s="4"/>
       <c r="G91" s="4"/>
@@ -19180,20 +19180,20 @@
     </row>
     <row r="92" spans="1:26" ht="13">
       <c r="A92" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B92" s="4" t="str">
         <f t="shared" si="0"/>
         <v>makunduchidistricthospital</v>
       </c>
       <c r="C92" s="21" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D92" s="10" t="s">
         <v>1034</v>
       </c>
-      <c r="D92" s="10" t="s">
-        <v>1035</v>
-      </c>
       <c r="E92" s="4" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="F92" s="4"/>
       <c r="G92" s="4"/>
@@ -19219,20 +19219,20 @@
     </row>
     <row r="93" spans="1:26" ht="13">
       <c r="A93" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B93" s="4" t="str">
         <f t="shared" si="0"/>
         <v>muyuniphcu+</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="F93" s="4"/>
       <c r="G93" s="4"/>
@@ -19258,20 +19258,20 @@
     </row>
     <row r="94" spans="1:26" ht="13">
       <c r="A94" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B94" s="4" t="str">
         <f t="shared" si="0"/>
         <v>bwejuuphcu+</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="F94" s="4"/>
       <c r="G94" s="4"/>
@@ -19297,20 +19297,20 @@
     </row>
     <row r="95" spans="1:26" ht="13">
       <c r="A95" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B95" s="4" t="str">
         <f t="shared" si="0"/>
         <v>chumbuniphcu+</v>
       </c>
       <c r="C95" s="21" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="D95" s="21" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F95" s="4"/>
       <c r="G95" s="4"/>
@@ -19336,20 +19336,20 @@
     </row>
     <row r="96" spans="1:26" ht="13">
       <c r="A96" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B96" s="4" t="str">
         <f t="shared" si="0"/>
         <v>mnazimmojahospital</v>
       </c>
       <c r="C96" s="21" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D96" s="10" t="s">
         <v>1039</v>
       </c>
-      <c r="D96" s="10" t="s">
-        <v>1040</v>
-      </c>
       <c r="E96" s="4" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F96" s="4"/>
       <c r="G96" s="4"/>
@@ -19375,20 +19375,20 @@
     </row>
     <row r="97" spans="1:26" ht="13">
       <c r="A97" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B97" s="4" t="str">
         <f t="shared" si="0"/>
         <v>mwembeladumchclinic</v>
       </c>
       <c r="C97" s="21" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D97" s="10" t="s">
         <v>1041</v>
       </c>
-      <c r="D97" s="10" t="s">
-        <v>1042</v>
-      </c>
       <c r="E97" s="4" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F97" s="4"/>
       <c r="G97" s="4"/>
@@ -19414,20 +19414,20 @@
     </row>
     <row r="98" spans="1:26" ht="13">
       <c r="A98" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B98" s="4" t="str">
         <f t="shared" si="0"/>
         <v>sebleniphcu+</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F98" s="4"/>
       <c r="G98" s="4"/>
@@ -19453,20 +19453,20 @@
     </row>
     <row r="99" spans="1:26" ht="13">
       <c r="A99" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B99" s="4" t="str">
         <f t="shared" si="0"/>
         <v>chukwaniphcu+</v>
       </c>
       <c r="C99" s="21" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="D99" s="21" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="F99" s="4"/>
       <c r="G99" s="4"/>
@@ -19492,20 +19492,20 @@
     </row>
     <row r="100" spans="1:26" ht="13">
       <c r="A100" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B100" s="4" t="str">
         <f t="shared" si="0"/>
         <v>fuoniphcu+</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="F100" s="4"/>
       <c r="G100" s="4"/>
@@ -19531,20 +19531,20 @@
     </row>
     <row r="101" spans="1:26" ht="13">
       <c r="A101" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B101" s="4" t="str">
         <f t="shared" si="0"/>
         <v>kombeniphcu+</v>
       </c>
       <c r="C101" s="21" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="D101" s="21" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="F101" s="4"/>
       <c r="G101" s="4"/>
@@ -19570,20 +19570,20 @@
     </row>
     <row r="102" spans="1:26" ht="13">
       <c r="A102" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B102" s="4" t="str">
         <f t="shared" si="0"/>
         <v>mtofaaniphcu+(kinuni)</v>
       </c>
       <c r="C102" s="21" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="D102" s="21" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="F102" s="4"/>
       <c r="G102" s="4"/>
@@ -19609,20 +19609,20 @@
     </row>
     <row r="103" spans="1:26" ht="13">
       <c r="A103" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B103" s="4" t="str">
         <f t="shared" si="0"/>
         <v>bumbwisudiphcu+</v>
       </c>
       <c r="C103" s="21" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="D103" s="21" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="F103" s="4"/>
       <c r="G103" s="4"/>
@@ -19648,20 +19648,20 @@
     </row>
     <row r="104" spans="1:26" ht="13">
       <c r="A104" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B104" s="4" t="str">
         <f t="shared" si="0"/>
         <v>selemphcu+</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="F104" s="4"/>
       <c r="G104" s="4"/>
@@ -19687,20 +19687,20 @@
     </row>
     <row r="105" spans="1:26" ht="13">
       <c r="A105" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B105" s="4" t="str">
         <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="F105" s="4"/>
       <c r="G105" s="4"/>
@@ -19726,20 +19726,20 @@
     </row>
     <row r="106" spans="1:26" ht="13">
       <c r="A106" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B106" s="4" t="str">
         <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F106" s="4"/>
       <c r="G106" s="4"/>
@@ -19765,20 +19765,20 @@
     </row>
     <row r="107" spans="1:26" ht="13">
       <c r="A107" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B107" s="4" t="str">
         <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="F107" s="4"/>
       <c r="G107" s="4"/>
@@ -19804,20 +19804,20 @@
     </row>
     <row r="108" spans="1:26" ht="13">
       <c r="A108" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B108" s="4" t="str">
         <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="F108" s="4"/>
       <c r="G108" s="4"/>
@@ -19843,20 +19843,20 @@
     </row>
     <row r="109" spans="1:26" ht="13">
       <c r="A109" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B109" s="4" t="str">
         <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="F109" s="4"/>
       <c r="G109" s="4"/>
@@ -19882,20 +19882,20 @@
     </row>
     <row r="110" spans="1:26" ht="13">
       <c r="A110" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B110" s="4" t="str">
         <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="F110" s="4"/>
       <c r="G110" s="4"/>
@@ -19921,20 +19921,20 @@
     </row>
     <row r="111" spans="1:26" ht="13">
       <c r="A111" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B111" s="4" t="str">
         <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="F111" s="4"/>
       <c r="G111" s="4"/>
@@ -19960,20 +19960,20 @@
     </row>
     <row r="112" spans="1:26" ht="13">
       <c r="A112" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B112" s="4" t="str">
         <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="F112" s="4"/>
       <c r="G112" s="4"/>
@@ -19999,20 +19999,20 @@
     </row>
     <row r="113" spans="1:26" ht="13">
       <c r="A113" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B113" s="4" t="str">
         <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="D113" s="10" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F113" s="4"/>
       <c r="G113" s="4"/>
@@ -20038,20 +20038,20 @@
     </row>
     <row r="114" spans="1:26" ht="13">
       <c r="A114" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B114" s="4" t="str">
         <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="D114" s="10" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="F114" s="4"/>
       <c r="G114" s="4"/>
@@ -20077,20 +20077,20 @@
     </row>
     <row r="115" spans="1:26" ht="13">
       <c r="A115" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B115" s="4" t="str">
         <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="D115" s="10" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="F115" s="4"/>
       <c r="G115" s="4"/>
@@ -20116,674 +20116,674 @@
     </row>
     <row r="116" spans="1:26" ht="13">
       <c r="A116" s="16" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B116" s="16" t="s">
         <v>139</v>
       </c>
       <c r="C116" s="16" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D116" s="38" t="s">
         <v>1051</v>
-      </c>
-      <c r="D116" s="38" t="s">
-        <v>1052</v>
       </c>
     </row>
     <row r="117" spans="1:26" ht="13">
       <c r="A117" s="16" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B117" s="16" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C117" s="60" t="s">
         <v>1053</v>
       </c>
-      <c r="C117" s="60" t="s">
+      <c r="D117" s="81" t="s">
         <v>1054</v>
-      </c>
-      <c r="D117" s="81" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="118" spans="1:26" ht="13">
       <c r="A118" s="16" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B118" s="16" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C118" s="5" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D118" s="38" t="s">
         <v>1056</v>
-      </c>
-      <c r="D118" s="38" t="s">
-        <v>1057</v>
       </c>
     </row>
     <row r="119" spans="1:26" ht="13">
       <c r="A119" s="16" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B119" s="16" t="s">
         <v>1058</v>
       </c>
-      <c r="B119" s="16" t="s">
+      <c r="C119" s="16" t="s">
         <v>1059</v>
       </c>
-      <c r="C119" s="16" t="s">
+      <c r="D119" s="78" t="s">
         <v>1060</v>
-      </c>
-      <c r="D119" s="78" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="120" spans="1:26" ht="13">
       <c r="A120" s="16" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="B120" s="16" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C120" s="16" t="s">
         <v>1062</v>
       </c>
-      <c r="C120" s="16" t="s">
+      <c r="D120" s="38" t="s">
         <v>1063</v>
-      </c>
-      <c r="D120" s="38" t="s">
-        <v>1064</v>
       </c>
     </row>
     <row r="121" spans="1:26" ht="13">
       <c r="A121" s="16" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="B121" s="16" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C121" s="60" t="s">
         <v>1065</v>
       </c>
-      <c r="C121" s="60" t="s">
+      <c r="D121" s="38" t="s">
         <v>1066</v>
-      </c>
-      <c r="D121" s="38" t="s">
-        <v>1067</v>
       </c>
     </row>
     <row r="122" spans="1:26" ht="13">
       <c r="A122" s="16" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="B122" s="16" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C122" s="60" t="s">
         <v>1068</v>
       </c>
-      <c r="C122" s="60" t="s">
+      <c r="D122" s="81" t="s">
         <v>1069</v>
-      </c>
-      <c r="D122" s="81" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="123" spans="1:26" ht="13">
       <c r="A123" s="16" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="B123" s="16" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C123" s="16" t="s">
         <v>1071</v>
       </c>
-      <c r="C123" s="16" t="s">
+      <c r="D123" s="78" t="s">
         <v>1072</v>
-      </c>
-      <c r="D123" s="78" t="s">
-        <v>1073</v>
       </c>
     </row>
     <row r="124" spans="1:26" ht="13">
       <c r="A124" s="16" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="B124" s="16" t="s">
+        <v>964</v>
+      </c>
+      <c r="C124" s="16" t="s">
         <v>965</v>
       </c>
-      <c r="C124" s="16" t="s">
-        <v>966</v>
-      </c>
       <c r="D124" s="78" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="125" spans="1:26" ht="13">
       <c r="A125" s="5" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B125" s="5" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C125" s="5" t="s">
         <v>1075</v>
       </c>
-      <c r="C125" s="5" t="s">
+      <c r="D125" s="78" t="s">
         <v>1076</v>
-      </c>
-      <c r="D125" s="78" t="s">
-        <v>1077</v>
       </c>
     </row>
     <row r="126" spans="1:26" ht="13">
       <c r="A126" s="5" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B126" s="5" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C126" s="5" t="s">
         <v>1078</v>
       </c>
-      <c r="C126" s="5" t="s">
+      <c r="D126" s="78" t="s">
         <v>1079</v>
-      </c>
-      <c r="D126" s="78" t="s">
-        <v>1080</v>
       </c>
     </row>
     <row r="127" spans="1:26" ht="13">
       <c r="A127" s="5" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B127" s="5" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C127" s="5" t="s">
         <v>1081</v>
       </c>
-      <c r="C127" s="5" t="s">
+      <c r="D127" s="78" t="s">
         <v>1082</v>
-      </c>
-      <c r="D127" s="78" t="s">
-        <v>1083</v>
       </c>
     </row>
     <row r="128" spans="1:26" ht="13">
       <c r="A128" s="5" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B128" s="5" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C128" s="5" t="s">
         <v>1084</v>
       </c>
-      <c r="C128" s="5" t="s">
+      <c r="D128" s="78" t="s">
         <v>1085</v>
-      </c>
-      <c r="D128" s="78" t="s">
-        <v>1086</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="13">
       <c r="A129" s="5" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B129" s="5" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C129" s="5" t="s">
         <v>1087</v>
       </c>
-      <c r="C129" s="5" t="s">
+      <c r="D129" s="78" t="s">
         <v>1088</v>
-      </c>
-      <c r="D129" s="78" t="s">
-        <v>1089</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="13">
       <c r="A130" s="5" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B130" s="5" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C130" s="5" t="s">
         <v>1090</v>
       </c>
-      <c r="C130" s="5" t="s">
-        <v>1091</v>
-      </c>
       <c r="D130" s="78" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="13">
       <c r="A131" s="5" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B131" s="5" t="s">
+        <v>964</v>
+      </c>
+      <c r="C131" s="5" t="s">
         <v>965</v>
       </c>
-      <c r="C131" s="5" t="s">
-        <v>966</v>
-      </c>
       <c r="D131" s="78" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="13">
       <c r="A132" s="16" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B132" s="16" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C132" s="16" t="s">
         <v>1092</v>
       </c>
-      <c r="C132" s="16" t="s">
+      <c r="D132" s="78" t="s">
         <v>1093</v>
-      </c>
-      <c r="D132" s="78" t="s">
-        <v>1094</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="13">
       <c r="A133" s="16" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B133" s="16" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C133" s="16" t="s">
         <v>1095</v>
       </c>
-      <c r="C133" s="16" t="s">
+      <c r="D133" s="78" t="s">
         <v>1096</v>
-      </c>
-      <c r="D133" s="78" t="s">
-        <v>1097</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="13">
       <c r="A134" s="16" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B134" s="16" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C134" s="16" t="s">
         <v>1098</v>
       </c>
-      <c r="C134" s="16" t="s">
+      <c r="D134" s="78" t="s">
         <v>1099</v>
-      </c>
-      <c r="D134" s="78" t="s">
-        <v>1100</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="13">
       <c r="A135" s="16" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B135" s="16" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C135" s="16" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D135" s="78" t="s">
         <v>1101</v>
-      </c>
-      <c r="D135" s="78" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="13">
       <c r="A136" s="16" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B136" s="16" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C136" s="16" t="s">
         <v>1103</v>
       </c>
-      <c r="C136" s="16" t="s">
+      <c r="D136" s="78" t="s">
         <v>1104</v>
-      </c>
-      <c r="D136" s="78" t="s">
-        <v>1105</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="13">
       <c r="A137" s="16" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B137" s="16" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C137" s="16" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="D137" s="78" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="13">
       <c r="A138" s="16" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B138" s="16" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C138" s="16" t="s">
         <v>1107</v>
       </c>
-      <c r="C138" s="16" t="s">
-        <v>1108</v>
-      </c>
       <c r="D138" s="78" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="13">
       <c r="A139" s="16" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B139" s="16" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C139" s="16" t="s">
         <v>1109</v>
       </c>
-      <c r="C139" s="16" t="s">
+      <c r="D139" s="78" t="s">
         <v>1110</v>
-      </c>
-      <c r="D139" s="78" t="s">
-        <v>1111</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="13">
       <c r="A140" s="16" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B140" s="16" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C140" s="16" t="s">
         <v>1112</v>
       </c>
-      <c r="C140" s="16" t="s">
+      <c r="D140" s="78" t="s">
         <v>1113</v>
-      </c>
-      <c r="D140" s="78" t="s">
-        <v>1114</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="13">
       <c r="A141" s="16" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B141" s="16" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C141" s="16" t="s">
         <v>1115</v>
       </c>
-      <c r="C141" s="16" t="s">
+      <c r="D141" s="78" t="s">
         <v>1116</v>
-      </c>
-      <c r="D141" s="78" t="s">
-        <v>1117</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="13">
       <c r="A142" s="16" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B142" s="16" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C142" s="16" t="s">
         <v>1118</v>
       </c>
-      <c r="C142" s="16" t="s">
+      <c r="D142" s="78" t="s">
         <v>1119</v>
-      </c>
-      <c r="D142" s="78" t="s">
-        <v>1120</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="13">
       <c r="A143" s="16" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B143" s="16" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="C143" s="16" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="D143" s="78" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="13">
       <c r="A144" s="16" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B144" s="16" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C144" s="16" t="s">
         <v>1122</v>
       </c>
-      <c r="C144" s="16" t="s">
+      <c r="D144" s="78" t="s">
         <v>1123</v>
-      </c>
-      <c r="D144" s="78" t="s">
-        <v>1124</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="13">
       <c r="A145" s="16" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B145" s="16" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C145" s="16" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D145" s="78" t="s">
         <v>1125</v>
-      </c>
-      <c r="D145" s="78" t="s">
-        <v>1126</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="13">
       <c r="A146" s="16" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B146" s="16" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C146" s="16" t="s">
         <v>1127</v>
       </c>
-      <c r="C146" s="16" t="s">
+      <c r="D146" s="78" t="s">
         <v>1128</v>
-      </c>
-      <c r="D146" s="78" t="s">
-        <v>1129</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="13">
       <c r="A147" s="16" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B147" s="16" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="C147" s="16" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="D147" s="78" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="13">
       <c r="A148" s="16" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B148" s="16" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C148" s="5" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D148" s="38" t="s">
         <v>1131</v>
-      </c>
-      <c r="C148" s="5" t="s">
-        <v>1131</v>
-      </c>
-      <c r="D148" s="38" t="s">
-        <v>1132</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="13">
       <c r="A149" s="16" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B149" s="16" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C149" s="16" t="s">
         <v>1133</v>
       </c>
-      <c r="C149" s="16" t="s">
+      <c r="D149" s="78" t="s">
         <v>1134</v>
-      </c>
-      <c r="D149" s="78" t="s">
-        <v>1135</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="13">
       <c r="A150" s="16" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B150" s="16" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C150" s="16" t="s">
         <v>1136</v>
       </c>
-      <c r="C150" s="16" t="s">
+      <c r="D150" s="78" t="s">
         <v>1137</v>
-      </c>
-      <c r="D150" s="78" t="s">
-        <v>1138</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="13">
       <c r="A151" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B151" s="2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C151" s="2" t="s">
         <v>1139</v>
       </c>
-      <c r="C151" s="2" t="s">
+      <c r="D151" s="40" t="s">
         <v>1140</v>
-      </c>
-      <c r="D151" s="40" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="13">
       <c r="A152" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B152" s="2" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C152" s="2" t="s">
         <v>1142</v>
       </c>
-      <c r="C152" s="2" t="s">
+      <c r="D152" s="40" t="s">
         <v>1143</v>
-      </c>
-      <c r="D152" s="40" t="s">
-        <v>1144</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="13">
       <c r="A153" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B153" s="2" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C153" s="2" t="s">
         <v>1145</v>
       </c>
-      <c r="C153" s="2" t="s">
+      <c r="D153" s="40" t="s">
         <v>1146</v>
-      </c>
-      <c r="D153" s="40" t="s">
-        <v>1147</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="13">
       <c r="A154" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B154" s="2" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C154" s="2" t="s">
         <v>1148</v>
       </c>
-      <c r="C154" s="2" t="s">
+      <c r="D154" s="40" t="s">
         <v>1149</v>
-      </c>
-      <c r="D154" s="40" t="s">
-        <v>1150</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="13">
       <c r="A155" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B155" s="2" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C155" s="2" t="s">
         <v>1151</v>
       </c>
-      <c r="C155" s="2" t="s">
+      <c r="D155" s="40" t="s">
         <v>1152</v>
-      </c>
-      <c r="D155" s="40" t="s">
-        <v>1153</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="13">
       <c r="A156" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B156" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C156" s="2" t="s">
         <v>1154</v>
       </c>
-      <c r="C156" s="2" t="s">
+      <c r="D156" s="40" t="s">
         <v>1155</v>
-      </c>
-      <c r="D156" s="40" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="13">
       <c r="A157" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B157" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C157" s="2" t="s">
         <v>1157</v>
       </c>
-      <c r="C157" s="2" t="s">
+      <c r="D157" s="40" t="s">
         <v>1158</v>
-      </c>
-      <c r="D157" s="40" t="s">
-        <v>1159</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="13">
       <c r="A158" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B158" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C158" s="2" t="s">
         <v>1160</v>
       </c>
-      <c r="C158" s="2" t="s">
+      <c r="D158" s="40" t="s">
         <v>1161</v>
-      </c>
-      <c r="D158" s="40" t="s">
-        <v>1162</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="13">
       <c r="A159" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B159" s="2" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C159" s="2" t="s">
         <v>1163</v>
       </c>
-      <c r="C159" s="2" t="s">
+      <c r="D159" s="40" t="s">
         <v>1164</v>
-      </c>
-      <c r="D159" s="40" t="s">
-        <v>1165</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="13">
       <c r="A160" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B160" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C160" s="2" t="s">
         <v>1166</v>
       </c>
-      <c r="C160" s="2" t="s">
+      <c r="D160" s="40" t="s">
         <v>1167</v>
-      </c>
-      <c r="D160" s="40" t="s">
-        <v>1168</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="13">
       <c r="A161" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B161" s="2" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C161" s="2" t="s">
         <v>1169</v>
       </c>
-      <c r="C161" s="2" t="s">
+      <c r="D161" s="40" t="s">
         <v>1170</v>
-      </c>
-      <c r="D161" s="40" t="s">
-        <v>1171</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="13">
       <c r="A162" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="D162" s="40" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="163" spans="1:5" ht="13">
       <c r="A163" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B163" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C163" s="13" t="s">
         <v>1173</v>
       </c>
-      <c r="C163" s="13" t="s">
-        <v>1174</v>
-      </c>
       <c r="D163" s="40" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="13">
@@ -20791,13 +20791,13 @@
         <v>171</v>
       </c>
       <c r="B164" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C164" s="65" t="s">
         <v>1175</v>
       </c>
-      <c r="C164" s="65" t="s">
+      <c r="D164" s="40" t="s">
         <v>1176</v>
-      </c>
-      <c r="D164" s="40" t="s">
-        <v>1177</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="13">
@@ -20805,13 +20805,13 @@
         <v>171</v>
       </c>
       <c r="B165" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C165" s="65" t="s">
         <v>1178</v>
       </c>
-      <c r="C165" s="65" t="s">
+      <c r="D165" s="72" t="s">
         <v>1179</v>
-      </c>
-      <c r="D165" s="72" t="s">
-        <v>1180</v>
       </c>
       <c r="E165" s="67"/>
     </row>
@@ -20820,13 +20820,13 @@
         <v>171</v>
       </c>
       <c r="B166" s="2" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C166" s="65" t="s">
         <v>1181</v>
       </c>
-      <c r="C166" s="65" t="s">
+      <c r="D166" s="66" t="s">
         <v>1182</v>
-      </c>
-      <c r="D166" s="66" t="s">
-        <v>1183</v>
       </c>
       <c r="E166" s="67"/>
     </row>
@@ -20835,13 +20835,13 @@
         <v>171</v>
       </c>
       <c r="B167" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C167" s="65" t="s">
         <v>1184</v>
       </c>
-      <c r="C167" s="65" t="s">
+      <c r="D167" s="66" t="s">
         <v>1185</v>
-      </c>
-      <c r="D167" s="66" t="s">
-        <v>1186</v>
       </c>
       <c r="E167" s="67"/>
     </row>
@@ -20850,13 +20850,13 @@
         <v>171</v>
       </c>
       <c r="B168" s="2" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C168" s="65" t="s">
         <v>1187</v>
       </c>
-      <c r="C168" s="65" t="s">
+      <c r="D168" s="66" t="s">
         <v>1188</v>
-      </c>
-      <c r="D168" s="66" t="s">
-        <v>1189</v>
       </c>
       <c r="E168" s="67"/>
     </row>
@@ -20865,13 +20865,13 @@
         <v>171</v>
       </c>
       <c r="B169" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C169" s="65" t="s">
         <v>1190</v>
       </c>
-      <c r="C169" s="65" t="s">
+      <c r="D169" s="66" t="s">
         <v>1191</v>
-      </c>
-      <c r="D169" s="66" t="s">
-        <v>1192</v>
       </c>
       <c r="E169" s="67"/>
     </row>
@@ -20880,13 +20880,13 @@
         <v>171</v>
       </c>
       <c r="B170" s="2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C170" s="65" t="s">
         <v>1193</v>
       </c>
-      <c r="C170" s="65" t="s">
+      <c r="D170" s="66" t="s">
         <v>1194</v>
-      </c>
-      <c r="D170" s="66" t="s">
-        <v>1195</v>
       </c>
       <c r="E170" s="67"/>
     </row>
@@ -20895,308 +20895,308 @@
         <v>171</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="C171" s="82" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="D171" s="66" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="E171" s="67"/>
     </row>
     <row r="172" spans="1:5" ht="13">
       <c r="A172" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B172" s="2" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C172" s="71" t="s">
         <v>1197</v>
       </c>
-      <c r="C172" s="71" t="s">
+      <c r="D172" s="40" t="s">
         <v>1198</v>
-      </c>
-      <c r="D172" s="40" t="s">
-        <v>1199</v>
       </c>
     </row>
     <row r="173" spans="1:5" ht="13">
       <c r="A173" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C173" s="71" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="D173" s="40" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="174" spans="1:5" ht="13">
       <c r="A174" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B174" s="2" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C174" s="71" t="s">
         <v>1201</v>
       </c>
-      <c r="C174" s="71" t="s">
+      <c r="D174" s="40" t="s">
         <v>1202</v>
-      </c>
-      <c r="D174" s="40" t="s">
-        <v>1203</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="13">
       <c r="A175" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="C175" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="D175" s="40" t="s">
         <v>1204</v>
-      </c>
-      <c r="D175" s="40" t="s">
-        <v>1205</v>
       </c>
     </row>
     <row r="176" spans="1:5" ht="13">
       <c r="A176" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B176" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C176" s="82" t="s">
         <v>1206</v>
       </c>
-      <c r="C176" s="82" t="s">
-        <v>1207</v>
-      </c>
       <c r="D176" s="40" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="13">
       <c r="A177" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B177" s="2" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C177" s="73" t="s">
         <v>1208</v>
       </c>
-      <c r="C177" s="73" t="s">
+      <c r="D177" s="2" t="s">
         <v>1209</v>
-      </c>
-      <c r="D177" s="2" t="s">
-        <v>1210</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="13">
       <c r="A178" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B178" s="2" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C178" s="71" t="s">
         <v>1211</v>
       </c>
-      <c r="C178" s="71" t="s">
+      <c r="D178" s="40" t="s">
         <v>1212</v>
-      </c>
-      <c r="D178" s="40" t="s">
-        <v>1213</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="13">
       <c r="A179" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B179" s="2" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C179" s="71" t="s">
         <v>1214</v>
       </c>
-      <c r="C179" s="71" t="s">
+      <c r="D179" s="40" t="s">
         <v>1215</v>
-      </c>
-      <c r="D179" s="40" t="s">
-        <v>1216</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="13">
       <c r="A180" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B180" s="2" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C180" s="71" t="s">
         <v>1217</v>
       </c>
-      <c r="C180" s="71" t="s">
+      <c r="D180" s="40" t="s">
         <v>1218</v>
-      </c>
-      <c r="D180" s="40" t="s">
-        <v>1219</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="13">
       <c r="A181" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="C181" s="82" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="D181" s="40" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="13">
       <c r="A182" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B182" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C182" s="65" t="s">
+        <v>1175</v>
+      </c>
+      <c r="D182" s="40" t="s">
         <v>1221</v>
-      </c>
-      <c r="C182" s="65" t="s">
-        <v>1176</v>
-      </c>
-      <c r="D182" s="40" t="s">
-        <v>1222</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="13">
       <c r="A183" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B183" s="2" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C183" s="65" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D183" s="40" t="s">
         <v>1223</v>
-      </c>
-      <c r="C183" s="65" t="s">
-        <v>1179</v>
-      </c>
-      <c r="D183" s="40" t="s">
-        <v>1224</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="13">
       <c r="A184" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="C184" s="65" t="s">
+        <v>1181</v>
+      </c>
+      <c r="D184" s="40" t="s">
         <v>1182</v>
-      </c>
-      <c r="D184" s="40" t="s">
-        <v>1183</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="13">
       <c r="A185" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="C185" s="65" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D185" s="40" t="s">
         <v>1185</v>
-      </c>
-      <c r="D185" s="40" t="s">
-        <v>1186</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="13">
       <c r="A186" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C186" s="65" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D186" s="40" t="s">
         <v>1188</v>
-      </c>
-      <c r="D186" s="40" t="s">
-        <v>1189</v>
       </c>
     </row>
     <row r="187" spans="1:4" ht="13">
       <c r="A187" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="C187" s="65" t="s">
+        <v>1190</v>
+      </c>
+      <c r="D187" s="40" t="s">
         <v>1191</v>
-      </c>
-      <c r="D187" s="40" t="s">
-        <v>1192</v>
       </c>
     </row>
     <row r="188" spans="1:4" ht="13">
       <c r="A188" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="C188" s="65" t="s">
+        <v>1193</v>
+      </c>
+      <c r="D188" s="40" t="s">
         <v>1194</v>
-      </c>
-      <c r="D188" s="40" t="s">
-        <v>1195</v>
       </c>
     </row>
     <row r="189" spans="1:4" ht="13">
       <c r="A189" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="C189" s="82" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="D189" s="40" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="13">
       <c r="A190" s="2" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="B190" s="2" t="s">
         <v>139</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D190" s="40" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="191" spans="1:4" ht="13">
       <c r="A191" s="2" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="B191" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="C191" s="2" t="s">
         <v>856</v>
       </c>
-      <c r="C191" s="2" t="s">
+      <c r="D191" s="40" t="s">
         <v>857</v>
-      </c>
-      <c r="D191" s="40" t="s">
-        <v>858</v>
       </c>
     </row>
     <row r="192" spans="1:4" ht="13">
       <c r="A192" s="2" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="C192" s="13" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="D192" s="40" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="193" spans="1:4" ht="14.25">
@@ -21204,13 +21204,13 @@
         <v>182</v>
       </c>
       <c r="B193" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C193" s="2" t="s">
         <v>1234</v>
       </c>
-      <c r="C193" s="2" t="s">
+      <c r="D193" s="83" t="s">
         <v>1235</v>
-      </c>
-      <c r="D193" s="83" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="194" spans="1:4" ht="14.25">
@@ -21218,13 +21218,13 @@
         <v>182</v>
       </c>
       <c r="B194" s="2" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C194" s="2" t="s">
         <v>1237</v>
       </c>
-      <c r="C194" s="2" t="s">
+      <c r="D194" s="83" t="s">
         <v>1238</v>
-      </c>
-      <c r="D194" s="83" t="s">
-        <v>1239</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="14.25">
@@ -21232,13 +21232,13 @@
         <v>182</v>
       </c>
       <c r="B195" s="2" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C195" s="2" t="s">
         <v>1240</v>
       </c>
-      <c r="C195" s="2" t="s">
+      <c r="D195" s="83" t="s">
         <v>1241</v>
-      </c>
-      <c r="D195" s="83" t="s">
-        <v>1242</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="14.25">
@@ -21246,13 +21246,13 @@
         <v>182</v>
       </c>
       <c r="B196" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C196" s="2" t="s">
         <v>1243</v>
       </c>
-      <c r="C196" s="2" t="s">
+      <c r="D196" s="83" t="s">
         <v>1244</v>
-      </c>
-      <c r="D196" s="83" t="s">
-        <v>1245</v>
       </c>
     </row>
     <row r="197" spans="1:4" ht="14.25">
@@ -21260,13 +21260,13 @@
         <v>182</v>
       </c>
       <c r="B197" s="2" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C197" s="2" t="s">
         <v>1246</v>
       </c>
-      <c r="C197" s="2" t="s">
+      <c r="D197" s="83" t="s">
         <v>1247</v>
-      </c>
-      <c r="D197" s="83" t="s">
-        <v>1248</v>
       </c>
     </row>
     <row r="198" spans="1:4" ht="13">
@@ -21274,13 +21274,13 @@
         <v>182</v>
       </c>
       <c r="B198" s="2" t="s">
+        <v>964</v>
+      </c>
+      <c r="C198" s="2" t="s">
         <v>965</v>
       </c>
-      <c r="C198" s="2" t="s">
-        <v>966</v>
-      </c>
       <c r="D198" s="40" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="199" spans="1:4" ht="13">
@@ -21288,181 +21288,181 @@
         <v>182</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="C199" s="13" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="D199" s="40" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="200" spans="1:4" ht="14.25">
       <c r="A200" s="2" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B200" s="2" t="s">
         <v>1249</v>
       </c>
-      <c r="B200" s="2" t="s">
+      <c r="C200" s="2" t="s">
         <v>1250</v>
       </c>
-      <c r="C200" s="2" t="s">
+      <c r="D200" s="83" t="s">
         <v>1251</v>
-      </c>
-      <c r="D200" s="83" t="s">
-        <v>1252</v>
       </c>
     </row>
     <row r="201" spans="1:4" ht="14.25">
       <c r="A201" s="2" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="B201" s="2" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C201" s="2" t="s">
         <v>1253</v>
       </c>
-      <c r="C201" s="2" t="s">
+      <c r="D201" s="83" t="s">
         <v>1254</v>
-      </c>
-      <c r="D201" s="83" t="s">
-        <v>1255</v>
       </c>
     </row>
     <row r="202" spans="1:4" ht="14.25">
       <c r="A202" s="2" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="B202" s="2" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C202" s="2" t="s">
         <v>1256</v>
       </c>
-      <c r="C202" s="2" t="s">
+      <c r="D202" s="83" t="s">
         <v>1257</v>
-      </c>
-      <c r="D202" s="83" t="s">
-        <v>1258</v>
       </c>
     </row>
     <row r="203" spans="1:4" ht="14.25">
       <c r="A203" s="2" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="B203" s="2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C203" s="2" t="s">
         <v>1259</v>
       </c>
-      <c r="C203" s="2" t="s">
+      <c r="D203" s="83" t="s">
         <v>1260</v>
-      </c>
-      <c r="D203" s="83" t="s">
-        <v>1261</v>
       </c>
     </row>
     <row r="204" spans="1:4" ht="13">
       <c r="A204" s="2" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="B204" s="2" t="s">
+        <v>964</v>
+      </c>
+      <c r="C204" s="2" t="s">
         <v>965</v>
       </c>
-      <c r="C204" s="2" t="s">
-        <v>966</v>
-      </c>
       <c r="D204" s="40" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="13">
       <c r="A205" s="2" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="C205" s="13" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="D205" s="40" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="206" spans="1:4" ht="14.25">
       <c r="A206" s="2" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B206" s="2" t="s">
         <v>1262</v>
       </c>
-      <c r="B206" s="2" t="s">
+      <c r="C206" s="2" t="s">
         <v>1263</v>
       </c>
-      <c r="C206" s="2" t="s">
-        <v>1264</v>
-      </c>
       <c r="D206" s="83" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="207" spans="1:4" ht="14.25">
       <c r="A207" s="2" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="B207" s="2" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C207" s="2" t="s">
         <v>1265</v>
       </c>
-      <c r="C207" s="2" t="s">
+      <c r="D207" s="83" t="s">
         <v>1266</v>
-      </c>
-      <c r="D207" s="83" t="s">
-        <v>1267</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="14.25">
       <c r="A208" s="2" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="B208" s="2" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C208" s="2" t="s">
         <v>1268</v>
       </c>
-      <c r="C208" s="2" t="s">
+      <c r="D208" s="83" t="s">
         <v>1269</v>
-      </c>
-      <c r="D208" s="83" t="s">
-        <v>1270</v>
       </c>
     </row>
     <row r="209" spans="1:4" ht="14.25">
       <c r="A209" s="2" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="B209" s="2" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C209" s="2" t="s">
         <v>1271</v>
       </c>
-      <c r="C209" s="2" t="s">
-        <v>1272</v>
-      </c>
       <c r="D209" s="83" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="210" spans="1:4" ht="13">
       <c r="A210" s="2" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="B210" s="2" t="s">
+        <v>964</v>
+      </c>
+      <c r="C210" s="2" t="s">
         <v>965</v>
       </c>
-      <c r="C210" s="2" t="s">
-        <v>966</v>
-      </c>
       <c r="D210" s="40" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="211" spans="1:4" ht="13">
       <c r="A211" s="2" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="C211" s="13" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="D211" s="40" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="212" spans="1:4" ht="13">
@@ -21470,13 +21470,13 @@
         <v>281</v>
       </c>
       <c r="B212" s="2" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C212" s="40" t="s">
         <v>1273</v>
       </c>
-      <c r="C212" s="40" t="s">
+      <c r="D212" s="2" t="s">
         <v>1274</v>
-      </c>
-      <c r="D212" s="2" t="s">
-        <v>1275</v>
       </c>
     </row>
     <row r="213" spans="1:4" ht="13">
@@ -21484,13 +21484,13 @@
         <v>281</v>
       </c>
       <c r="B213" s="2" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C213" s="2" t="s">
         <v>1276</v>
       </c>
-      <c r="C213" s="2" t="s">
+      <c r="D213" s="2" t="s">
         <v>1277</v>
-      </c>
-      <c r="D213" s="2" t="s">
-        <v>1278</v>
       </c>
     </row>
     <row r="214" spans="1:4" ht="13">
@@ -21498,13 +21498,13 @@
         <v>281</v>
       </c>
       <c r="B214" s="2" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C214" s="2" t="s">
         <v>1279</v>
       </c>
-      <c r="C214" s="2" t="s">
+      <c r="D214" s="2" t="s">
         <v>1280</v>
-      </c>
-      <c r="D214" s="2" t="s">
-        <v>1281</v>
       </c>
     </row>
     <row r="215" spans="1:4" ht="13">
@@ -21512,13 +21512,13 @@
         <v>281</v>
       </c>
       <c r="B215" s="2" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C215" s="2" t="s">
         <v>1282</v>
       </c>
-      <c r="C215" s="2" t="s">
+      <c r="D215" s="2" t="s">
         <v>1283</v>
-      </c>
-      <c r="D215" s="2" t="s">
-        <v>1284</v>
       </c>
     </row>
     <row r="216" spans="1:4" ht="13">
@@ -21526,13 +21526,13 @@
         <v>281</v>
       </c>
       <c r="B216" s="2" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C216" s="2" t="s">
         <v>1285</v>
       </c>
-      <c r="C216" s="2" t="s">
+      <c r="D216" s="2" t="s">
         <v>1286</v>
-      </c>
-      <c r="D216" s="2" t="s">
-        <v>1287</v>
       </c>
     </row>
     <row r="217" spans="1:4" ht="13">
@@ -21540,13 +21540,13 @@
         <v>281</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>1288</v>
+        <v>1433</v>
       </c>
       <c r="C217" s="40" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="218" spans="1:4" ht="13">
@@ -21554,13 +21554,13 @@
         <v>281</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="219" spans="1:4" ht="13">
@@ -21568,223 +21568,223 @@
         <v>281</v>
       </c>
       <c r="B219" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="C219" s="2" t="s">
         <v>898</v>
       </c>
-      <c r="C219" s="2" t="s">
+      <c r="D219" s="2" t="s">
         <v>899</v>
-      </c>
-      <c r="D219" s="2" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="220" spans="1:4" ht="13">
       <c r="A220" s="84" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C220" s="2" t="s">
         <v>1292</v>
       </c>
-      <c r="B220" s="2" t="s">
+      <c r="D220" s="2" t="s">
         <v>1293</v>
-      </c>
-      <c r="C220" s="2" t="s">
-        <v>1294</v>
-      </c>
-      <c r="D220" s="2" t="s">
-        <v>1295</v>
       </c>
     </row>
     <row r="221" spans="1:4" ht="13">
       <c r="A221" s="84" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="B221" s="2" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C221" s="40" t="s">
+        <v>1295</v>
+      </c>
+      <c r="D221" s="2" t="s">
         <v>1296</v>
-      </c>
-      <c r="C221" s="40" t="s">
-        <v>1297</v>
-      </c>
-      <c r="D221" s="2" t="s">
-        <v>1298</v>
       </c>
     </row>
     <row r="222" spans="1:4" ht="13">
       <c r="A222" s="84" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="B222" s="2" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>1298</v>
+      </c>
+      <c r="D222" s="2" t="s">
         <v>1299</v>
-      </c>
-      <c r="C222" s="2" t="s">
-        <v>1300</v>
-      </c>
-      <c r="D222" s="2" t="s">
-        <v>1301</v>
       </c>
     </row>
     <row r="223" spans="1:4" ht="13">
       <c r="A223" s="84" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="B223" s="2" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D223" s="2" t="s">
         <v>1302</v>
-      </c>
-      <c r="C223" s="2" t="s">
-        <v>1303</v>
-      </c>
-      <c r="D223" s="2" t="s">
-        <v>1304</v>
       </c>
     </row>
     <row r="224" spans="1:4" ht="13">
       <c r="A224" s="57" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="B224" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="C224" s="2" t="s">
         <v>898</v>
       </c>
-      <c r="C224" s="2" t="s">
+      <c r="D224" s="2" t="s">
         <v>899</v>
-      </c>
-      <c r="D224" s="2" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="225" spans="1:4" ht="13">
       <c r="A225" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B225" s="2" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>1304</v>
+      </c>
+      <c r="D225" s="2" t="s">
         <v>1305</v>
-      </c>
-      <c r="C225" s="2" t="s">
-        <v>1306</v>
-      </c>
-      <c r="D225" s="2" t="s">
-        <v>1307</v>
       </c>
     </row>
     <row r="226" spans="1:4" ht="13">
       <c r="A226" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B226" s="2" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="D226" s="2" t="s">
         <v>1308</v>
-      </c>
-      <c r="C226" s="2" t="s">
-        <v>1309</v>
-      </c>
-      <c r="D226" s="2" t="s">
-        <v>1310</v>
       </c>
     </row>
     <row r="227" spans="1:4" ht="13">
       <c r="A227" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B227" s="2" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>1310</v>
+      </c>
+      <c r="D227" s="2" t="s">
         <v>1311</v>
-      </c>
-      <c r="C227" s="2" t="s">
-        <v>1312</v>
-      </c>
-      <c r="D227" s="2" t="s">
-        <v>1313</v>
       </c>
     </row>
     <row r="228" spans="1:4" ht="13">
       <c r="A228" s="7" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B228" s="2" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D228" s="2" t="s">
         <v>1314</v>
-      </c>
-      <c r="C228" s="2" t="s">
-        <v>1315</v>
-      </c>
-      <c r="D228" s="2" t="s">
-        <v>1316</v>
       </c>
     </row>
     <row r="229" spans="1:4" ht="13">
       <c r="A229" s="7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B229" s="2" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>1316</v>
+      </c>
+      <c r="D229" s="2" t="s">
         <v>1317</v>
-      </c>
-      <c r="C229" s="2" t="s">
-        <v>1318</v>
-      </c>
-      <c r="D229" s="2" t="s">
-        <v>1319</v>
       </c>
     </row>
     <row r="230" spans="1:4" ht="13">
       <c r="A230" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B230" s="2" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>1319</v>
+      </c>
+      <c r="D230" s="2" t="s">
         <v>1320</v>
-      </c>
-      <c r="C230" s="2" t="s">
-        <v>1321</v>
-      </c>
-      <c r="D230" s="2" t="s">
-        <v>1322</v>
       </c>
     </row>
     <row r="231" spans="1:4" ht="13">
       <c r="A231" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B231" s="2" t="s">
         <v>139</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="232" spans="1:4" ht="13">
       <c r="A232" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B232" s="2" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D232" s="2" t="s">
         <v>1324</v>
-      </c>
-      <c r="C232" s="2" t="s">
-        <v>1325</v>
-      </c>
-      <c r="D232" s="2" t="s">
-        <v>1326</v>
       </c>
     </row>
     <row r="233" spans="1:4" ht="13">
       <c r="A233" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B233" s="2" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>1326</v>
+      </c>
+      <c r="D233" s="2" t="s">
         <v>1327</v>
-      </c>
-      <c r="C233" s="2" t="s">
-        <v>1328</v>
-      </c>
-      <c r="D233" s="2" t="s">
-        <v>1329</v>
       </c>
     </row>
     <row r="234" spans="1:4" ht="13">
       <c r="A234" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B234" s="2" t="s">
+        <v>1328</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>1329</v>
+      </c>
+      <c r="D234" s="2" t="s">
         <v>1330</v>
-      </c>
-      <c r="C234" s="2" t="s">
-        <v>1331</v>
-      </c>
-      <c r="D234" s="2" t="s">
-        <v>1332</v>
       </c>
     </row>
   </sheetData>
@@ -21806,39 +21806,39 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" customHeight="1">
       <c r="A1" s="76" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B1" s="76" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C1" s="76" t="s">
         <v>1333</v>
       </c>
-      <c r="B1" s="76" t="s">
+      <c r="D1" s="76" t="s">
         <v>1334</v>
       </c>
-      <c r="C1" s="76" t="s">
+      <c r="E1" s="76" t="s">
         <v>1335</v>
       </c>
-      <c r="D1" s="76" t="s">
+      <c r="F1" s="76" t="s">
         <v>1336</v>
-      </c>
-      <c r="E1" s="76" t="s">
-        <v>1337</v>
-      </c>
-      <c r="F1" s="76" t="s">
-        <v>1338</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.75">
       <c r="A2" s="85" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B2" s="85" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C2" s="86" t="s">
         <v>1339</v>
       </c>
-      <c r="B2" s="85" t="s">
+      <c r="D2" s="77" t="s">
         <v>1340</v>
       </c>
-      <c r="C2" s="86" t="s">
+      <c r="E2" s="77" t="s">
         <v>1341</v>
-      </c>
-      <c r="D2" s="77" t="s">
-        <v>1342</v>
-      </c>
-      <c r="E2" s="77" t="s">
-        <v>1343</v>
       </c>
       <c r="F2" s="77"/>
     </row>

--- a/forms/app/pregnancy.xlsx
+++ b/forms/app/pregnancy.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2481" uniqueCount="1435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2482" uniqueCount="1437">
   <si>
     <t xml:space="preserve">type</t>
   </si>
@@ -2737,6 +2737,32 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">${enabel} = "true" and (
+  selected(${previous_delivery_by_c_section},"yes") or selected(${previous_delivery_by_vacuum},"yes")
+  or selected(${previous_stillbirth},"yes")
+  or selected(${delivery_complications},'prolonged_labor')
+  or selected(${delivery_complications},'large_perineal_tear')
+  or selected(${delivery_complications},'retained_placenta')
+  or selected(${delivery_complications},'aph')
+  or selected(${delivery_complications},'postpartum_hemorrage')
+  or selected(${delivery_complications},'eclampsia')
+  or selected(${delivery_complications},'big_baby') or selected(${big_baby},"yes")
+  or ${previous_miscarriages} &gt; 0 and ${enabel}=”true”
+  or selected(${multiple_pregnancy},"yes")
+  or selected(${malpresentation},"yes")
+  or selected(${breech_position},"yes")
+  or selected(${medical_conditions},"high_blood_pressure")
+  or selected(${medical_conditions},"diabetes")
+  or selected(${medical_conditions},"sickle_cell")
+  or selected(${medical_conditions},"cardiac_disease")
+  or selected(${higher_facility_delivery},"yes")
+  or selected(${allow_partner_to_deliver_facility},"no") or selected(${partner_not_present},"yes") 
+  or selected(${ten_or_more_years},"yes")
+  or selected(${nutrition_restrictions},"yes")
+  or selected(${local_herbs},"yes")
+)</t>
+  </si>
+  <si>
     <t xml:space="preserve">c_section_risk</t>
   </si>
   <si>
@@ -2866,6 +2892,9 @@
   </si>
   <si>
     <t xml:space="preserve">Mimba kuharibika </t>
+  </si>
+  <si>
+    <t xml:space="preserve">${previous_miscarriages} &gt; 0 and ${enabel}=”true”</t>
   </si>
   <si>
     <t xml:space="preserve">multiple_pregnancy_risk</t>
@@ -15601,7 +15630,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="303" customFormat="false" ht="39" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="303" customFormat="false" ht="280.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="2" t="s">
         <v>109</v>
       </c>
@@ -15614,7 +15643,9 @@
       <c r="D303" s="12" t="s">
         <v>845</v>
       </c>
-      <c r="F303" s="2"/>
+      <c r="F303" s="12" t="s">
+        <v>846</v>
+      </c>
       <c r="G303" s="2"/>
     </row>
     <row r="304" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15622,16 +15653,16 @@
         <v>109</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C304" s="12" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="F304" s="2" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="G304" s="2"/>
     </row>
@@ -15640,16 +15671,16 @@
         <v>109</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C305" s="12" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="D305" s="4" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="F305" s="2" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="G305" s="2"/>
     </row>
@@ -15658,16 +15689,16 @@
         <v>109</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C306" s="12" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D306" s="4" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="F306" s="2" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="G306" s="2"/>
     </row>
@@ -15676,16 +15707,16 @@
         <v>109</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="F307" s="12" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="G307" s="2"/>
       <c r="L307" s="4"/>
@@ -15695,16 +15726,16 @@
         <v>109</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C308" s="12" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="F308" s="12" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="G308" s="2"/>
       <c r="L308" s="4"/>
@@ -15714,16 +15745,16 @@
         <v>109</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C309" s="12" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="F309" s="12" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="G309" s="2"/>
       <c r="L309" s="4"/>
@@ -15733,16 +15764,16 @@
         <v>109</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C310" s="12" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="F310" s="12" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="G310" s="2"/>
       <c r="L310" s="4"/>
@@ -15752,16 +15783,16 @@
         <v>109</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C311" s="12" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="F311" s="12" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="G311" s="2"/>
       <c r="L311" s="4"/>
@@ -15771,16 +15802,16 @@
         <v>109</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="D312" s="2" t="s">
         <v>457</v>
       </c>
       <c r="F312" s="12" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="G312" s="2"/>
       <c r="L312" s="4"/>
@@ -15790,35 +15821,35 @@
         <v>109</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C313" s="12" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="F313" s="12" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="G313" s="2"/>
       <c r="L313" s="4"/>
     </row>
-    <row r="314" s="36" customFormat="true" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="314" s="36" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="2" t="s">
         <v>109</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C314" s="12" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="D314" s="4" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="F314" s="2" t="s">
-        <v>257</v>
+        <v>889</v>
       </c>
       <c r="G314" s="2"/>
     </row>
@@ -15827,16 +15858,16 @@
         <v>109</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="C315" s="12" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="D315" s="4" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="F315" s="2" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="G315" s="2"/>
     </row>
@@ -15845,16 +15876,16 @@
         <v>109</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="C316" s="12" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="D316" s="4" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="F316" s="2" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="G316" s="2"/>
     </row>
@@ -15863,16 +15894,16 @@
         <v>109</v>
       </c>
       <c r="B317" s="12" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="C317" s="12" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="D317" s="4" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="F317" s="2" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="G317" s="2"/>
     </row>
@@ -15881,16 +15912,16 @@
         <v>109</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="F318" s="2" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="G318" s="2"/>
     </row>
@@ -15899,16 +15930,16 @@
         <v>109</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="F319" s="2" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="G319" s="2"/>
     </row>
@@ -15917,16 +15948,16 @@
         <v>109</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="C320" s="12" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="F320" s="2" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="G320" s="2"/>
     </row>
@@ -15935,16 +15966,16 @@
         <v>109</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="F321" s="2" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="G321" s="2"/>
     </row>
@@ -15953,16 +15984,16 @@
         <v>109</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="C322" s="12" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="D322" s="4" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="F322" s="2" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="G322" s="2"/>
     </row>
@@ -15971,16 +16002,16 @@
         <v>109</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="C323" s="12" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="D323" s="4" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="F323" s="2" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="G323" s="2"/>
     </row>
@@ -15989,16 +16020,16 @@
         <v>109</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="C324" s="12" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="D324" s="4" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="F324" s="2" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="G324" s="2"/>
     </row>
@@ -16007,16 +16038,16 @@
         <v>109</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C325" s="12" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="D325" s="4" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="F325" s="2" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="G325" s="2"/>
     </row>
@@ -16025,16 +16056,16 @@
         <v>109</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="C326" s="12" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="D326" s="4" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="F326" s="2" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="G326" s="2"/>
     </row>
@@ -16043,17 +16074,17 @@
         <v>109</v>
       </c>
       <c r="B327" s="37" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="C327" s="37" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="D327" s="38" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="E327" s="37"/>
       <c r="F327" s="38" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="G327" s="37"/>
       <c r="H327" s="37"/>
@@ -16081,17 +16112,17 @@
         <v>109</v>
       </c>
       <c r="B328" s="37" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="C328" s="37" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="D328" s="38" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="E328" s="37"/>
       <c r="F328" s="37" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="G328" s="37"/>
       <c r="H328" s="37"/>
@@ -16119,20 +16150,20 @@
         <v>109</v>
       </c>
       <c r="B329" s="37" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="C329" s="37" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="D329" s="39" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="E329" s="37"/>
       <c r="F329" s="40" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="G329" s="37" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="H329" s="37"/>
       <c r="I329" s="37"/>
@@ -16159,20 +16190,20 @@
         <v>109</v>
       </c>
       <c r="B330" s="37" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="C330" s="37" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="D330" s="37" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="E330" s="37"/>
       <c r="F330" s="41" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="G330" s="37" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="H330" s="37"/>
       <c r="I330" s="37"/>
@@ -16199,20 +16230,20 @@
         <v>109</v>
       </c>
       <c r="B331" s="37" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="C331" s="37" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="D331" s="38" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="E331" s="37"/>
       <c r="F331" s="37" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="G331" s="37" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="H331" s="37"/>
       <c r="I331" s="37"/>
@@ -16251,7 +16282,7 @@
         <v>41</v>
       </c>
       <c r="B333" s="37" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="C333" s="37"/>
       <c r="D333" s="37"/>
@@ -16263,7 +16294,7 @@
       <c r="J333" s="37"/>
       <c r="K333" s="37"/>
       <c r="L333" s="37" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="M333" s="37"/>
       <c r="N333" s="37"/>
@@ -16285,7 +16316,7 @@
         <v>41</v>
       </c>
       <c r="B334" s="37" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="C334" s="37"/>
       <c r="D334" s="37"/>
@@ -16297,7 +16328,7 @@
       <c r="J334" s="37"/>
       <c r="K334" s="37"/>
       <c r="L334" s="37" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="M334" s="37"/>
       <c r="N334" s="37"/>
@@ -16319,7 +16350,7 @@
         <v>41</v>
       </c>
       <c r="B335" s="37" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="C335" s="37"/>
       <c r="D335" s="37"/>
@@ -16331,7 +16362,7 @@
       <c r="J335" s="37"/>
       <c r="K335" s="37"/>
       <c r="L335" s="37" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="M335" s="37"/>
       <c r="N335" s="37"/>
@@ -16353,7 +16384,7 @@
         <v>41</v>
       </c>
       <c r="B336" s="37" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="C336" s="37"/>
       <c r="D336" s="37"/>
@@ -16365,7 +16396,7 @@
       <c r="J336" s="37"/>
       <c r="K336" s="37"/>
       <c r="L336" s="37" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="M336" s="37"/>
       <c r="N336" s="37"/>
@@ -16387,7 +16418,7 @@
         <v>41</v>
       </c>
       <c r="B337" s="37" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="C337" s="37"/>
       <c r="D337" s="37"/>
@@ -16399,7 +16430,7 @@
       <c r="J337" s="37"/>
       <c r="K337" s="37"/>
       <c r="L337" s="37" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="M337" s="37"/>
       <c r="N337" s="37"/>
@@ -16455,7 +16486,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="42" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="B1" s="42" t="s">
         <v>1</v>
@@ -16472,30 +16503,30 @@
     </row>
     <row r="2" customFormat="false" ht="14.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="43" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="B2" s="43" t="s">
         <v>139</v>
       </c>
       <c r="C2" s="43" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="D2" s="43" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="43" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="C3" s="43" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="D3" s="43" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16503,13 +16534,13 @@
         <v>474</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16517,13 +16548,13 @@
         <v>474</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16531,13 +16562,13 @@
         <v>474</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16545,13 +16576,13 @@
         <v>474</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16559,13 +16590,13 @@
         <v>474</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16573,13 +16604,13 @@
         <v>474</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16587,13 +16618,13 @@
         <v>474</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16601,13 +16632,13 @@
         <v>474</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16615,13 +16646,13 @@
         <v>474</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16629,13 +16660,13 @@
         <v>474</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16643,13 +16674,13 @@
         <v>474</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16657,13 +16688,13 @@
         <v>474</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16671,13 +16702,13 @@
         <v>474</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16685,13 +16716,13 @@
         <v>474</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16699,13 +16730,13 @@
         <v>538</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16713,13 +16744,13 @@
         <v>538</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16727,13 +16758,13 @@
         <v>569</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16741,13 +16772,13 @@
         <v>569</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16755,13 +16786,13 @@
         <v>569</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16769,13 +16800,13 @@
         <v>569</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16783,13 +16814,13 @@
         <v>569</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16797,13 +16828,13 @@
         <v>569</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16811,13 +16842,13 @@
         <v>569</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16825,13 +16856,13 @@
         <v>589</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16839,13 +16870,13 @@
         <v>589</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16853,13 +16884,13 @@
         <v>589</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16867,13 +16898,13 @@
         <v>589</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16881,13 +16912,13 @@
         <v>589</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16895,13 +16926,13 @@
         <v>589</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16909,13 +16940,13 @@
         <v>589</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16923,13 +16954,13 @@
         <v>589</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16937,13 +16968,13 @@
         <v>313</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16951,13 +16982,13 @@
         <v>313</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16965,13 +16996,13 @@
         <v>313</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16979,13 +17010,13 @@
         <v>721</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
@@ -17015,13 +17046,13 @@
         <v>721</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
@@ -17051,13 +17082,13 @@
         <v>721</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
@@ -17087,16 +17118,16 @@
         <v>726</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
@@ -17125,16 +17156,16 @@
         <v>726</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
@@ -17163,16 +17194,16 @@
         <v>726</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
@@ -17201,16 +17232,16 @@
         <v>726</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
@@ -17239,16 +17270,16 @@
         <v>726</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
@@ -17277,16 +17308,16 @@
         <v>726</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
@@ -17315,16 +17346,16 @@
         <v>726</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
@@ -17353,16 +17384,16 @@
         <v>726</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
@@ -17391,16 +17422,16 @@
         <v>726</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
@@ -17429,16 +17460,16 @@
         <v>726</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
@@ -17467,16 +17498,16 @@
         <v>726</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
@@ -17509,13 +17540,13 @@
         <v>chakechakedistricthospital</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
@@ -17548,13 +17579,13 @@
         <v>pujiniphcu+</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
@@ -17587,13 +17618,13 @@
         <v>tundauwaphcu+</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
@@ -17626,13 +17657,13 @@
         <v>vitongojiphcc</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
@@ -17665,13 +17696,13 @@
         <v>weshaphcu+</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
@@ -17704,13 +17735,13 @@
         <v>kondephcu+</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
@@ -17743,13 +17774,13 @@
         <v>makangalephcu+</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
@@ -17782,13 +17813,13 @@
         <v>maziwangombephcu+</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
@@ -17821,13 +17852,13 @@
         <v>micheweniphcc</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
@@ -17860,13 +17891,13 @@
         <v>wingwiphcu+</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
@@ -17899,13 +17930,13 @@
         <v>kiuyumbuyuniphcu+</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
@@ -17938,13 +17969,13 @@
         <v>bogoaphcu+</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
@@ -17977,13 +18008,13 @@
         <v>kengejaphcu+</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
@@ -18016,13 +18047,13 @@
         <v>abdallahmzeedistricthospital</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
@@ -18055,13 +18086,13 @@
         <v>michenzaniphcu+</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
@@ -18094,13 +18125,13 @@
         <v>fundophcu+</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
@@ -18133,13 +18164,13 @@
         <v>kojaniphcu+</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
@@ -18172,13 +18203,13 @@
         <v>makongeniphcu+</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
@@ -18211,13 +18242,13 @@
         <v>wetedistricthospital</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
@@ -18250,13 +18281,13 @@
         <v>mzambarauniphcu+</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
@@ -18289,13 +18320,13 @@
         <v>junguniphcu+</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
@@ -18328,13 +18359,13 @@
         <v>ukunjwiphcu+</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
@@ -18367,13 +18398,13 @@
         <v>uondwephcu+</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
@@ -18406,13 +18437,13 @@
         <v>chwakaphcu+</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
@@ -18445,13 +18476,13 @@
         <v>mweraphcu+</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
@@ -18484,13 +18515,13 @@
         <v>ungujaukuuphcu+</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
@@ -18523,13 +18554,13 @@
         <v>uziniphcu+</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
@@ -18562,13 +18593,13 @@
         <v>uroaphcu+</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
@@ -18601,13 +18632,13 @@
         <v>kivungedistricthospital</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
@@ -18640,13 +18671,13 @@
         <v>matemwephcu+</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
@@ -18679,13 +18710,13 @@
         <v>nungwiphcu+</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
@@ -18718,13 +18749,13 @@
         <v>pwanimchanganiphcu+</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
@@ -18757,13 +18788,13 @@
         <v>tumbatugomaniphcu+</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
@@ -18796,13 +18827,13 @@
         <v>kendwaphcu+</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
@@ -18835,13 +18866,13 @@
         <v>bumbwinimisufiniphcu+</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
@@ -18874,13 +18905,13 @@
         <v>dongevijibweniphcu+</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
@@ -18913,13 +18944,13 @@
         <v>kiongwephcu</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
@@ -18952,13 +18983,13 @@
         <v>kitopephcu</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
@@ -18991,13 +19022,13 @@
         <v>mahondaphcu+</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
@@ -19030,13 +19061,13 @@
         <v>jambianiphcu+</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
@@ -19069,13 +19100,13 @@
         <v>makunduchidistricthospital</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
@@ -19108,13 +19139,13 @@
         <v>muyuniphcu+</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
@@ -19147,13 +19178,13 @@
         <v>bwejuuphcu+</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
@@ -19186,13 +19217,13 @@
         <v>chumbuniphcu+</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
@@ -19225,13 +19256,13 @@
         <v>mnazimmojahospital</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
@@ -19264,13 +19295,13 @@
         <v>mwembeladumchclinic</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
@@ -19303,13 +19334,13 @@
         <v>sebleniphcu+</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
@@ -19342,13 +19373,13 @@
         <v>chukwaniphcu+</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
@@ -19381,13 +19412,13 @@
         <v>fuoniphcu+</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
@@ -19420,13 +19451,13 @@
         <v>kombeniphcu+</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
@@ -19459,13 +19490,13 @@
         <v>mtofaaniphcu+(kinuni)</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
@@ -19498,13 +19529,13 @@
         <v>bumbwisudiphcu+</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F103" s="2"/>
       <c r="G103" s="2"/>
@@ -19537,13 +19568,13 @@
         <v>selemphcu+</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
@@ -19576,13 +19607,13 @@
         <v>other</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
@@ -19615,13 +19646,13 @@
         <v>other</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
@@ -19654,13 +19685,13 @@
         <v>other</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
@@ -19693,13 +19724,13 @@
         <v>other</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
@@ -19732,13 +19763,13 @@
         <v>other</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
@@ -19771,13 +19802,13 @@
         <v>other</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="F110" s="2"/>
       <c r="G110" s="2"/>
@@ -19810,13 +19841,13 @@
         <v>other</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="F111" s="2"/>
       <c r="G111" s="2"/>
@@ -19849,13 +19880,13 @@
         <v>other</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="F112" s="2"/>
       <c r="G112" s="2"/>
@@ -19888,13 +19919,13 @@
         <v>other</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
@@ -19927,13 +19958,13 @@
         <v>other</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
@@ -19966,13 +19997,13 @@
         <v>other</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F115" s="2"/>
       <c r="G115" s="2"/>
@@ -20004,10 +20035,10 @@
         <v>139</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20015,13 +20046,13 @@
         <v>744</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="C117" s="14" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20029,97 +20060,97 @@
         <v>744</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="4" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="4" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="4" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="C121" s="14" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="4" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="C122" s="14" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="4" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="4" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20127,13 +20158,13 @@
         <v>753</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20141,13 +20172,13 @@
         <v>753</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20155,13 +20186,13 @@
         <v>753</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20169,13 +20200,13 @@
         <v>753</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20183,13 +20214,13 @@
         <v>753</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20197,13 +20228,13 @@
         <v>753</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20211,13 +20242,13 @@
         <v>753</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20225,13 +20256,13 @@
         <v>758</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20239,13 +20270,13 @@
         <v>758</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20253,13 +20284,13 @@
         <v>758</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20270,10 +20301,10 @@
         <v>526</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20281,13 +20312,13 @@
         <v>758</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20295,13 +20326,13 @@
         <v>758</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20309,13 +20340,13 @@
         <v>758</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20323,13 +20354,13 @@
         <v>758</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20337,13 +20368,13 @@
         <v>758</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20351,13 +20382,13 @@
         <v>758</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20365,13 +20396,13 @@
         <v>773</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20379,13 +20410,13 @@
         <v>773</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20393,13 +20424,13 @@
         <v>773</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20410,10 +20441,10 @@
         <v>342</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20421,13 +20452,13 @@
         <v>773</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20435,13 +20466,13 @@
         <v>773</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20449,13 +20480,13 @@
         <v>777</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20463,13 +20494,13 @@
         <v>777</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20477,13 +20508,13 @@
         <v>777</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20491,13 +20522,13 @@
         <v>791</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20505,13 +20536,13 @@
         <v>791</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20519,13 +20550,13 @@
         <v>791</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20533,13 +20564,13 @@
         <v>791</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20547,13 +20578,13 @@
         <v>797</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20561,13 +20592,13 @@
         <v>797</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20575,13 +20606,13 @@
         <v>797</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20589,13 +20620,13 @@
         <v>797</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20603,13 +20634,13 @@
         <v>797</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20617,13 +20648,13 @@
         <v>797</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20631,13 +20662,13 @@
         <v>797</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20645,13 +20676,13 @@
         <v>797</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20659,13 +20690,13 @@
         <v>797</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="C163" s="6" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20673,13 +20704,13 @@
         <v>173</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="C164" s="29" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20687,13 +20718,13 @@
         <v>173</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="C165" s="29" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="E165" s="30"/>
     </row>
@@ -20702,13 +20733,13 @@
         <v>173</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="C166" s="29" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="E166" s="30"/>
     </row>
@@ -20717,13 +20748,13 @@
         <v>173</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="C167" s="29" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="E167" s="30"/>
     </row>
@@ -20732,13 +20763,13 @@
         <v>173</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="C168" s="29" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="E168" s="30"/>
     </row>
@@ -20747,13 +20778,13 @@
         <v>173</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="C169" s="29" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="E169" s="30"/>
     </row>
@@ -20762,13 +20793,13 @@
         <v>173</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="C170" s="29" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="E170" s="30"/>
     </row>
@@ -20777,13 +20808,13 @@
         <v>173</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="C171" s="31" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="E171" s="30"/>
     </row>
@@ -20792,13 +20823,13 @@
         <v>804</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="C172" s="33" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20806,13 +20837,13 @@
         <v>804</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="C173" s="33" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20820,13 +20851,13 @@
         <v>804</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="C174" s="33" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20834,13 +20865,13 @@
         <v>804</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20848,13 +20879,13 @@
         <v>804</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="C176" s="31" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20862,13 +20893,13 @@
         <v>811</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="C177" s="34" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20876,13 +20907,13 @@
         <v>811</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="C178" s="33" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20890,13 +20921,13 @@
         <v>811</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="C179" s="33" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20904,13 +20935,13 @@
         <v>811</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="C180" s="33" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20918,13 +20949,13 @@
         <v>811</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="C181" s="31" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20932,13 +20963,13 @@
         <v>826</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="C182" s="29" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20946,13 +20977,13 @@
         <v>826</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="C183" s="29" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20960,13 +20991,13 @@
         <v>826</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="C184" s="29" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20974,13 +21005,13 @@
         <v>826</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="C185" s="29" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20988,13 +21019,13 @@
         <v>826</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="C186" s="29" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21002,13 +21033,13 @@
         <v>826</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="C187" s="29" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21016,13 +21047,13 @@
         <v>826</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="C188" s="29" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21030,55 +21061,55 @@
         <v>826</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="C189" s="31" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="2" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="B190" s="2" t="s">
         <v>139</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="2" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="2" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21086,13 +21117,13 @@
         <v>184</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="D193" s="44" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21100,13 +21131,13 @@
         <v>184</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="D194" s="44" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21114,13 +21145,13 @@
         <v>184</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="D195" s="44" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21128,13 +21159,13 @@
         <v>184</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="D196" s="44" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21142,13 +21173,13 @@
         <v>184</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="D197" s="44" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21156,13 +21187,13 @@
         <v>184</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21170,181 +21201,181 @@
         <v>184</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="C199" s="6" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="2" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="D200" s="44" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="2" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="D201" s="44" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="2" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="D202" s="44" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="2" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="D203" s="44" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="2" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="2" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="2" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="D206" s="44" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="2" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="D207" s="44" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="2" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="D208" s="44" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="2" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="D209" s="44" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="2" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="2" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="C211" s="6" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21352,13 +21383,13 @@
         <v>286</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>1389</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21366,13 +21397,13 @@
         <v>286</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="C213" s="12" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21380,13 +21411,13 @@
         <v>286</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="C214" s="12" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21394,13 +21425,13 @@
         <v>286</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="C215" s="12" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21408,13 +21439,13 @@
         <v>286</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="C216" s="12" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21422,10 +21453,10 @@
         <v>286</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>457</v>
@@ -21439,10 +21470,10 @@
         <v>391</v>
       </c>
       <c r="C218" s="12" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21450,83 +21481,83 @@
         <v>286</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="45" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="45" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="45" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="C222" s="12" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="45" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="4" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21534,13 +21565,13 @@
         <v>679</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21548,13 +21579,13 @@
         <v>679</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21562,13 +21593,13 @@
         <v>679</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21576,13 +21607,13 @@
         <v>679</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21590,13 +21621,13 @@
         <v>415</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21604,13 +21635,13 @@
         <v>415</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21621,10 +21652,10 @@
         <v>139</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21632,13 +21663,13 @@
         <v>332</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21646,13 +21677,13 @@
         <v>332</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21660,13 +21691,13 @@
         <v>332</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
     </row>
   </sheetData>
@@ -21694,39 +21725,39 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="42" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="B1" s="42" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="C1" s="42" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="D1" s="42" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="E1" s="42" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="F1" s="42" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="43" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="B2" s="43" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="C2" s="46" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="D2" s="43" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="E2" s="43" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="F2" s="43"/>
     </row>
